--- a/Project_Files.xlsx
+++ b/Project_Files.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="579">
   <si>
     <t>#</t>
   </si>
@@ -1055,8 +1055,9 @@
   id: string;
   user_name: string;
   email: string;
-  plan: "basic" | "pro" | "premium";
+  plan_type: "basic" | "pro" | "premium";
   status: "active" | "cancelled" | "expired";
+  amount: number;
   started_at: string;
   expires_at: string;
  }
@@ -1100,7 +1101,7 @@
   },
   {
   label: "Monthly Revenue",
-  value: `₹${memberships.filter((m) =&gt; m.status === "active").reduce((s, m) =&gt; s + Number((m as Record&lt;string, unknown&gt;).amount || 0), 0).toLocaleString()}`,
+  value: `₹${memberships.filter((m) =&gt; m.status === "active").reduce((s, m) =&gt; s + Number(m.amount || 0), 0).toLocaleString()}`,
   color: "text-blue-600",
   },
   {
@@ -1145,7 +1146,7 @@
   &lt;p className="text-xs text-gray-500"&gt;{m.email}&lt;/p&gt;
   &lt;/td&gt;
   &lt;td className="px-4 py-3"&gt;
-  &lt;Badge variant={planColor[m.plan]}&gt;{m.plan}&lt;/Badge&gt;
+  &lt;Badge variant={planColor[m.plan_type]}&gt;{m.plan_type}&lt;/Badge&gt;
   &lt;/td&gt;
   &lt;td className="px-4 py-3"&gt;
   &lt;Badge variant={statusColor[m.status]}&gt;{m.status}&lt;/Badge&gt;
@@ -1167,7 +1168,7 @@
  }</t>
   </si>
   <si>
-    <t>LyoqCiAqIEBtb2R1bGUgQWRtaW5NZW1iZXJzaGlwc1BhZ2UKICogQGRlc2NyaXB0aW9uIEFkbWluIG1lbWJlcnNoaXAgbWFuYWdlbWVudCBwYWdlIGZvciBtb25pdG9yaW5nIHN1YnNjcmlwdGlvbnMgYW5kIHJldmVudWUuCiAqLwoidXNlIGNsaWVudCI7CgppbXBvcnQgUmVhY3QsIHsgdXNlRWZmZWN0LCB1c2VTdGF0ZSB9IGZyb20gInJlYWN0IjsKaW1wb3J0IEJ1dHRvbiBmcm9tICJAL2NvbXBvbmVudHMvdWkvYnV0dG9uIjsKaW1wb3J0IHsgQmFkZ2UsIFNwaW5uZXIgfSBmcm9tICJAL2NvbXBvbmVudHMvdWkvaW5kZXgiOwppbXBvcnQgeyBhZG1pbkFwaSB9IGZyb20gIkAvbGliL2FwaSI7CgppbnRlcmZhY2UgTWVtYmVyc2hpcFJvdyB7CiAgaWQ6IHN0cmluZzsKICB1c2VyX25hbWU6IHN0cmluZzsKICBlbWFpbDogc3RyaW5nOwogIHBsYW46ICJiYXNpYyIgfCAicHJvIiB8ICJwcmVtaXVtIjsKICBzdGF0dXM6ICJhY3RpdmUiIHwgImNhbmNlbGxlZCIgfCAiZXhwaXJlZCI7CiAgc3RhcnRlZF9hdDogc3RyaW5nOwogIGV4cGlyZXNfYXQ6IHN0cmluZzsKfQoKY29uc3QgcGxhbkNvbG9yOiBSZWNvcmQ8c3RyaW5nLCAiZGVmYXVsdCIgfCAic3VjY2VzcyIgfCAiaW5mbyIgfCAiZXJyb3IiPiA9IHsKICBiYXNpYzogImRlZmF1bHQiLAogIHBybzogImluZm8iLAogIHByZW1pdW06ICJzdWNjZXNzIiwKfTsKCmNvbnN0IHN0YXR1c0NvbG9yOiBSZWNvcmQ8c3RyaW5nLCAiZGVmYXVsdCIgfCAic3VjY2VzcyIgfCAiaW5mbyIgfCAiZXJyb3IiPiA9IHsKICBhY3RpdmU6ICJzdWNjZXNzIiwKICBjYW5jZWxsZWQ6ICJlcnJvciIsCiAgZXhwaXJlZDogImRlZmF1bHQiLAp9OwoKZXhwb3J0IGRlZmF1bHQgZnVuY3Rpb24gQWRtaW5NZW1iZXJzaGlwc1BhZ2UoKSB7CiAgY29uc3QgW21lbWJlcnNoaXBzLCBzZXRNZW1iZXJzaGlwc10gPSB1c2VTdGF0ZTxNZW1iZXJzaGlwUm93W10+KFtdKTsKICBjb25zdCBbbG9hZGluZywgc2V0TG9hZGluZ10gPSB1c2VTdGF0ZSh0cnVlKTsKCiAgdXNlRWZmZWN0KCgpID0+IHsKICAgIGNvbnN0IGxvYWQgPSBhc3luYyAoKSA9PiB7CiAgICAgIHRyeSB7CiAgICAgICAgY29uc3QgcmVzID0gYXdhaXQgYWRtaW5BcGkubGlzdE1lbWJlcnNoaXBzKCk7CiAgICAgICAgY29uc3QgZGF0YSA9IHJlcy5kYXRhOwogICAgICAgIHNldE1lbWJlcnNoaXBzKEFycmF5LmlzQXJyYXkoZGF0YSkgPyBkYXRhIDogZGF0YS5pdGVtcyB8fCBbXSk7CiAgICAgIH0gY2F0Y2ggewogICAgICAgIHNldE1lbWJlcnNoaXBzKFtdKTsKICAgICAgfSBmaW5hbGx5IHsKICAgICAgICBzZXRMb2FkaW5nKGZhbHNlKTsKICAgICAgfQogICAgfTsKICAgIGxvYWQoKTsKICB9LCBbXSk7CgogIHJldHVybiAoCiAgICA8ZGl2PgogICAgICA8aDIgY2xhc3NOYW1lPSJ0ZXh0LXhsIGZvbnQtYm9sZCB0ZXh0LWdyYXktOTAwIG1iLTYiPk1lbWJlcnNoaXBzPC9oMj4KCiAgICAgIHsvKiBTdW1tYXJ5IENhcmRzICovfQogICAgICA8ZGl2IGNsYXNzTmFtZT0iZ3JpZCBncmlkLWNvbHMtMSBzbTpncmlkLWNvbHMtMyBnYXAtNCBtYi04Ij4KICAgICAgICB7WwogICAgICAgICAgewogICAgICAgICAgICBsYWJlbDogIkFjdGl2ZSBTdWJzY3JpcHRpb25zIiwKICAgICAgICAgICAgdmFsdWU6IFN0cmluZyhtZW1iZXJzaGlwcy5maWx0ZXIoKG0pID0+IG0uc3RhdHVzID09PSAiYWN0aXZlIikubGVuZ3RoKSwKICAgICAgICAgICAgY29sb3I6ICJ0ZXh0LWdyZWVuLTYwMCIsCiAgICAgICAgICB9LAogICAgICAgICAgewogICAgICAgICAgICBsYWJlbDogIk1vbnRobHkgUmV2ZW51ZSIsCiAgICAgICAgICAgIHZhbHVlOiBg4oK5JHttZW1iZXJzaGlwcy5maWx0ZXIoKG0pID0+IG0uc3RhdHVzID09PSAiYWN0aXZlIikucmVkdWNlKChzLCBtKSA9PiBzICsgTnVtYmVyKChtIGFzIFJlY29yZDxzdHJpbmcsIHVua25vd24+KS5hbW91bnQgfHwgMCksIDApLnRvTG9jYWxlU3RyaW5nKCl9YCwKICAgICAgICAgICAgY29sb3I6ICJ0ZXh0LWJsdWUtNjAwIiwKICAgICAgICAgIH0sCiAgICAgICAgICB7CiAgICAgICAgICAgIGxhYmVsOiAiRXhwaXJlZCAvIENhbmNlbGxlZCIsCiAgICAgICAgICAgIHZhbHVlOiBTdHJpbmcobWVtYmVyc2hpcHMuZmlsdGVyKChtKSA9PiBtLnN0YXR1cyAhPT0gImFjdGl2ZSIpLmxlbmd0aCksCiAgICAgICAgICAgIGNvbG9yOiAidGV4dC1hbWJlci02MDAiLAogICAgICAgICAgfSwKICAgICAgICBdLm1hcCgocykgPT4gKAogICAgICAgICAgPGRpdiBrZXk9e3MubGFiZWx9IGNsYXNzTmFtZT0iYmctd2hpdGUgcm91bmRlZC14bCBib3JkZXIgYm9yZGVyLWdyYXktMjAwIHAtNSI+CiAgICAgICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC1zbSB0ZXh0LWdyYXktNTAwIj57cy5sYWJlbH08L3A+CiAgICAgICAgICAgIDxwIGNsYXNzTmFtZT17YHRleHQtMnhsIGZvbnQtYm9sZCBtdC0xICR7cy5jb2xvcn1gfT57cy52YWx1ZX08L3A+CiAgICAgICAgICA8L2Rpdj4KICAgICAgICApKX0KICAgICAgPC9kaXY+CgogICAgICB7bG9hZGluZyA/ICgKICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iZmxleCBqdXN0aWZ5LWNlbnRlciBweS0yMCI+PFNwaW5uZXIgc2l6ZT0ibGciIC8+PC9kaXY+CiAgICAgICkgOiAoCiAgICAgICAgPGRpdiBjbGFzc05hbWU9ImJnLXdoaXRlIHJvdW5kZWQteGwgYm9yZGVyIGJvcmRlci1ncmF5LTIwMCBvdmVyZmxvdy1oaWRkZW4iPgogICAgICAgICAgPHRhYmxlIGNsYXNzTmFtZT0idy1mdWxsIj4KICAgICAgICAgICAgPHRoZWFkIGNsYXNzTmFtZT0iYmctZ3JheS01MCBib3JkZXItYiBib3JkZXItZ3JheS0yMDAiPgogICAgICAgICAgICAgIDx0cj4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+SG9zdDwvdGg+CiAgICAgICAgICAgICAgICA8dGggY2xhc3NOYW1lPSJ0ZXh0LWxlZnQgdGV4dC14cyBmb250LW1lZGl1bSB0ZXh0LWdyYXktNTAwIHVwcGVyY2FzZSBweC00IHB5LTMiPlBsYW48L3RoPgogICAgICAgICAgICAgICAgPHRoIGNsYXNzTmFtZT0idGV4dC1sZWZ0IHRleHQteHMgZm9udC1tZWRpdW0gdGV4dC1ncmF5LTUwMCB1cHBlcmNhc2UgcHgtNCBweS0zIj5TdGF0dXM8L3RoPgogICAgICAgICAgICAgICAgPHRoIGNsYXNzTmFtZT0idGV4dC1sZWZ0IHRleHQteHMgZm9udC1tZWRpdW0gdGV4dC1ncmF5LTUwMCB1cHBlcmNhc2UgcHgtNCBweS0zIj5TdGFydGVkPC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+RXhwaXJlczwvdGg+CiAgICAgICAgICAgICAgICA8dGggY2xhc3NOYW1lPSJ0ZXh0LWxlZnQgdGV4dC14cyBmb250LW1lZGl1bSB0ZXh0LWdyYXktNTAwIHVwcGVyY2FzZSBweC00IHB5LTMiPkFjdGlvbnM8L3RoPgogICAgICAgICAgICAgIDwvdHI+CiAgICAgICAgICAgIDwvdGhlYWQ+CiAgICAgICAgICAgIDx0Ym9keSBjbGFzc05hbWU9ImRpdmlkZS15IGRpdmlkZS1ncmF5LTEwMCI+CiAgICAgICAgICAgICAge21lbWJlcnNoaXBzLmxlbmd0aCA9PT0gMCA/ICgKICAgICAgICAgICAgICAgIDx0cj4KICAgICAgICAgICAgICAgICAgPHRkIGNvbFNwYW49ezZ9IGNsYXNzTmFtZT0idGV4dC1jZW50ZXIgcHktMTAgdGV4dC1zbSB0ZXh0LWdyYXktNTAwIj4KICAgICAgICAgICAgICAgICAgICBObyBtZW1iZXJzaGlwcyBmb3VuZAogICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgPC90cj4KICAgICAgICAgICAgICApIDogKAogICAgICAgICAgICAgICAgbWVtYmVyc2hpcHMubWFwKChtKSA9PiAoCiAgICAgICAgICAgICAgICAgIDx0ciBrZXk9e20uaWR9IGNsYXNzTmFtZT0iaG92ZXI6YmctZ3JheS01MCI+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIj4KICAgICAgICAgICAgICAgICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC1zbSBmb250LW1lZGl1bSB0ZXh0LWdyYXktOTAwIj57bS51c2VyX25hbWV9PC9wPgogICAgICAgICAgICAgICAgICAgICAgPHAgY2xhc3NOYW1lPSJ0ZXh0LXhzIHRleHQtZ3JheS01MDAiPnttLmVtYWlsfTwvcD4KICAgICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyI+CiAgICAgICAgICAgICAgICAgICAgICA8QmFkZ2UgdmFyaWFudD17cGxhbkNvbG9yW20ucGxhbl19PnttLnBsYW59PC9CYWRnZT4KICAgICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyI+CiAgICAgICAgICAgICAgICAgICAgICA8QmFkZ2UgdmFyaWFudD17c3RhdHVzQ29sb3JbbS5zdGF0dXNdfT57bS5zdGF0dXN9PC9CYWRnZT4KICAgICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyB0ZXh0LXNtIHRleHQtZ3JheS01MDAiPnttLnN0YXJ0ZWRfYXR9PC90ZD4KICAgICAgICAgICAgICAgICAgICA8dGQgY2xhc3NOYW1lPSJweC00IHB5LTMgdGV4dC1zbSB0ZXh0LWdyYXktNTAwIj57bS5leHBpcmVzX2F0fTwvdGQ+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIj4KICAgICAgICAgICAgICAgICAgICAgIDxCdXR0b24gdmFyaWFudD0iZ2hvc3QiIHNpemU9InNtIj5WaWV3PC9CdXR0b24+CiAgICAgICAgICAgICAgICAgICAgPC90ZD4KICAgICAgICAgICAgICAgICAgPC90cj4KICAgICAgICAgICAgICAgICkpCiAgICAgICAgICAgICAgKX0KICAgICAgICAgICAgPC90Ym9keT4KICAgICAgICAgIDwvdGFibGU+CiAgICAgICAgPC9kaXY+CiAgICAgICl9CiAgICA8L2Rpdj4KICApOwp9Cg==</t>
+    <t>LyoqCiAqIEBtb2R1bGUgQWRtaW5NZW1iZXJzaGlwc1BhZ2UKICogQGRlc2NyaXB0aW9uIEFkbWluIG1lbWJlcnNoaXAgbWFuYWdlbWVudCBwYWdlIGZvciBtb25pdG9yaW5nIHN1YnNjcmlwdGlvbnMgYW5kIHJldmVudWUuCiAqLwoidXNlIGNsaWVudCI7CgppbXBvcnQgUmVhY3QsIHsgdXNlRWZmZWN0LCB1c2VTdGF0ZSB9IGZyb20gInJlYWN0IjsKaW1wb3J0IEJ1dHRvbiBmcm9tICJAL2NvbXBvbmVudHMvdWkvYnV0dG9uIjsKaW1wb3J0IHsgQmFkZ2UsIFNwaW5uZXIgfSBmcm9tICJAL2NvbXBvbmVudHMvdWkvaW5kZXgiOwppbXBvcnQgeyBhZG1pbkFwaSB9IGZyb20gIkAvbGliL2FwaSI7CgppbnRlcmZhY2UgTWVtYmVyc2hpcFJvdyB7CiAgaWQ6IHN0cmluZzsKICB1c2VyX25hbWU6IHN0cmluZzsKICBlbWFpbDogc3RyaW5nOwogIHBsYW5fdHlwZTogImJhc2ljIiB8ICJwcm8iIHwgInByZW1pdW0iOwogIHN0YXR1czogImFjdGl2ZSIgfCAiY2FuY2VsbGVkIiB8ICJleHBpcmVkIjsKICBhbW91bnQ6IG51bWJlcjsKICBzdGFydGVkX2F0OiBzdHJpbmc7CiAgZXhwaXJlc19hdDogc3RyaW5nOwp9Cgpjb25zdCBwbGFuQ29sb3I6IFJlY29yZDxzdHJpbmcsICJkZWZhdWx0IiB8ICJzdWNjZXNzIiB8ICJpbmZvIiB8ICJlcnJvciI+ID0gewogIGJhc2ljOiAiZGVmYXVsdCIsCiAgcHJvOiAiaW5mbyIsCiAgcHJlbWl1bTogInN1Y2Nlc3MiLAp9OwoKY29uc3Qgc3RhdHVzQ29sb3I6IFJlY29yZDxzdHJpbmcsICJkZWZhdWx0IiB8ICJzdWNjZXNzIiB8ICJpbmZvIiB8ICJlcnJvciI+ID0gewogIGFjdGl2ZTogInN1Y2Nlc3MiLAogIGNhbmNlbGxlZDogImVycm9yIiwKICBleHBpcmVkOiAiZGVmYXVsdCIsCn07CgpleHBvcnQgZGVmYXVsdCBmdW5jdGlvbiBBZG1pbk1lbWJlcnNoaXBzUGFnZSgpIHsKICBjb25zdCBbbWVtYmVyc2hpcHMsIHNldE1lbWJlcnNoaXBzXSA9IHVzZVN0YXRlPE1lbWJlcnNoaXBSb3dbXT4oW10pOwogIGNvbnN0IFtsb2FkaW5nLCBzZXRMb2FkaW5nXSA9IHVzZVN0YXRlKHRydWUpOwoKICB1c2VFZmZlY3QoKCkgPT4gewogICAgY29uc3QgbG9hZCA9IGFzeW5jICgpID0+IHsKICAgICAgdHJ5IHsKICAgICAgICBjb25zdCByZXMgPSBhd2FpdCBhZG1pbkFwaS5saXN0TWVtYmVyc2hpcHMoKTsKICAgICAgICBjb25zdCBkYXRhID0gcmVzLmRhdGE7CiAgICAgICAgc2V0TWVtYmVyc2hpcHMoQXJyYXkuaXNBcnJheShkYXRhKSA/IGRhdGEgOiBkYXRhLml0ZW1zIHx8IFtdKTsKICAgICAgfSBjYXRjaCB7CiAgICAgICAgc2V0TWVtYmVyc2hpcHMoW10pOwogICAgICB9IGZpbmFsbHkgewogICAgICAgIHNldExvYWRpbmcoZmFsc2UpOwogICAgICB9CiAgICB9OwogICAgbG9hZCgpOwogIH0sIFtdKTsKCiAgcmV0dXJuICgKICAgIDxkaXY+CiAgICAgIDxoMiBjbGFzc05hbWU9InRleHQteGwgZm9udC1ib2xkIHRleHQtZ3JheS05MDAgbWItNiI+TWVtYmVyc2hpcHM8L2gyPgoKICAgICAgey8qIFN1bW1hcnkgQ2FyZHMgKi99CiAgICAgIDxkaXYgY2xhc3NOYW1lPSJncmlkIGdyaWQtY29scy0xIHNtOmdyaWQtY29scy0zIGdhcC00IG1iLTgiPgogICAgICAgIHtbCiAgICAgICAgICB7CiAgICAgICAgICAgIGxhYmVsOiAiQWN0aXZlIFN1YnNjcmlwdGlvbnMiLAogICAgICAgICAgICB2YWx1ZTogU3RyaW5nKG1lbWJlcnNoaXBzLmZpbHRlcigobSkgPT4gbS5zdGF0dXMgPT09ICJhY3RpdmUiKS5sZW5ndGgpLAogICAgICAgICAgICBjb2xvcjogInRleHQtZ3JlZW4tNjAwIiwKICAgICAgICAgIH0sCiAgICAgICAgICB7CiAgICAgICAgICAgIGxhYmVsOiAiTW9udGhseSBSZXZlbnVlIiwKICAgICAgICAgICAgdmFsdWU6IGDigrkke21lbWJlcnNoaXBzLmZpbHRlcigobSkgPT4gbS5zdGF0dXMgPT09ICJhY3RpdmUiKS5yZWR1Y2UoKHMsIG0pID0+IHMgKyBOdW1iZXIobS5hbW91bnQgfHwgMCksIDApLnRvTG9jYWxlU3RyaW5nKCl9YCwKICAgICAgICAgICAgY29sb3I6ICJ0ZXh0LWJsdWUtNjAwIiwKICAgICAgICAgIH0sCiAgICAgICAgICB7CiAgICAgICAgICAgIGxhYmVsOiAiRXhwaXJlZCAvIENhbmNlbGxlZCIsCiAgICAgICAgICAgIHZhbHVlOiBTdHJpbmcobWVtYmVyc2hpcHMuZmlsdGVyKChtKSA9PiBtLnN0YXR1cyAhPT0gImFjdGl2ZSIpLmxlbmd0aCksCiAgICAgICAgICAgIGNvbG9yOiAidGV4dC1hbWJlci02MDAiLAogICAgICAgICAgfSwKICAgICAgICBdLm1hcCgocykgPT4gKAogICAgICAgICAgPGRpdiBrZXk9e3MubGFiZWx9IGNsYXNzTmFtZT0iYmctd2hpdGUgcm91bmRlZC14bCBib3JkZXIgYm9yZGVyLWdyYXktMjAwIHAtNSI+CiAgICAgICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC1zbSB0ZXh0LWdyYXktNTAwIj57cy5sYWJlbH08L3A+CiAgICAgICAgICAgIDxwIGNsYXNzTmFtZT17YHRleHQtMnhsIGZvbnQtYm9sZCBtdC0xICR7cy5jb2xvcn1gfT57cy52YWx1ZX08L3A+CiAgICAgICAgICA8L2Rpdj4KICAgICAgICApKX0KICAgICAgPC9kaXY+CgogICAgICB7bG9hZGluZyA/ICgKICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iZmxleCBqdXN0aWZ5LWNlbnRlciBweS0yMCI+PFNwaW5uZXIgc2l6ZT0ibGciIC8+PC9kaXY+CiAgICAgICkgOiAoCiAgICAgICAgPGRpdiBjbGFzc05hbWU9ImJnLXdoaXRlIHJvdW5kZWQteGwgYm9yZGVyIGJvcmRlci1ncmF5LTIwMCBvdmVyZmxvdy1oaWRkZW4iPgogICAgICAgICAgPHRhYmxlIGNsYXNzTmFtZT0idy1mdWxsIj4KICAgICAgICAgICAgPHRoZWFkIGNsYXNzTmFtZT0iYmctZ3JheS01MCBib3JkZXItYiBib3JkZXItZ3JheS0yMDAiPgogICAgICAgICAgICAgIDx0cj4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+SG9zdDwvdGg+CiAgICAgICAgICAgICAgICA8dGggY2xhc3NOYW1lPSJ0ZXh0LWxlZnQgdGV4dC14cyBmb250LW1lZGl1bSB0ZXh0LWdyYXktNTAwIHVwcGVyY2FzZSBweC00IHB5LTMiPlBsYW48L3RoPgogICAgICAgICAgICAgICAgPHRoIGNsYXNzTmFtZT0idGV4dC1sZWZ0IHRleHQteHMgZm9udC1tZWRpdW0gdGV4dC1ncmF5LTUwMCB1cHBlcmNhc2UgcHgtNCBweS0zIj5TdGF0dXM8L3RoPgogICAgICAgICAgICAgICAgPHRoIGNsYXNzTmFtZT0idGV4dC1sZWZ0IHRleHQteHMgZm9udC1tZWRpdW0gdGV4dC1ncmF5LTUwMCB1cHBlcmNhc2UgcHgtNCBweS0zIj5TdGFydGVkPC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+RXhwaXJlczwvdGg+CiAgICAgICAgICAgICAgICA8dGggY2xhc3NOYW1lPSJ0ZXh0LWxlZnQgdGV4dC14cyBmb250LW1lZGl1bSB0ZXh0LWdyYXktNTAwIHVwcGVyY2FzZSBweC00IHB5LTMiPkFjdGlvbnM8L3RoPgogICAgICAgICAgICAgIDwvdHI+CiAgICAgICAgICAgIDwvdGhlYWQ+CiAgICAgICAgICAgIDx0Ym9keSBjbGFzc05hbWU9ImRpdmlkZS15IGRpdmlkZS1ncmF5LTEwMCI+CiAgICAgICAgICAgICAge21lbWJlcnNoaXBzLmxlbmd0aCA9PT0gMCA/ICgKICAgICAgICAgICAgICAgIDx0cj4KICAgICAgICAgICAgICAgICAgPHRkIGNvbFNwYW49ezZ9IGNsYXNzTmFtZT0idGV4dC1jZW50ZXIgcHktMTAgdGV4dC1zbSB0ZXh0LWdyYXktNTAwIj4KICAgICAgICAgICAgICAgICAgICBObyBtZW1iZXJzaGlwcyBmb3VuZAogICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgPC90cj4KICAgICAgICAgICAgICApIDogKAogICAgICAgICAgICAgICAgbWVtYmVyc2hpcHMubWFwKChtKSA9PiAoCiAgICAgICAgICAgICAgICAgIDx0ciBrZXk9e20uaWR9IGNsYXNzTmFtZT0iaG92ZXI6YmctZ3JheS01MCI+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIj4KICAgICAgICAgICAgICAgICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC1zbSBmb250LW1lZGl1bSB0ZXh0LWdyYXktOTAwIj57bS51c2VyX25hbWV9PC9wPgogICAgICAgICAgICAgICAgICAgICAgPHAgY2xhc3NOYW1lPSJ0ZXh0LXhzIHRleHQtZ3JheS01MDAiPnttLmVtYWlsfTwvcD4KICAgICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyI+CiAgICAgICAgICAgICAgICAgICAgICA8QmFkZ2UgdmFyaWFudD17cGxhbkNvbG9yW20ucGxhbl90eXBlXX0+e20ucGxhbl90eXBlfTwvQmFkZ2U+CiAgICAgICAgICAgICAgICAgICAgPC90ZD4KICAgICAgICAgICAgICAgICAgICA8dGQgY2xhc3NOYW1lPSJweC00IHB5LTMiPgogICAgICAgICAgICAgICAgICAgICAgPEJhZGdlIHZhcmlhbnQ9e3N0YXR1c0NvbG9yW20uc3RhdHVzXX0+e20uc3RhdHVzfTwvQmFkZ2U+CiAgICAgICAgICAgICAgICAgICAgPC90ZD4KICAgICAgICAgICAgICAgICAgICA8dGQgY2xhc3NOYW1lPSJweC00IHB5LTMgdGV4dC1zbSB0ZXh0LWdyYXktNTAwIj57bS5zdGFydGVkX2F0fTwvdGQ+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIHRleHQtc20gdGV4dC1ncmF5LTUwMCI+e20uZXhwaXJlc19hdH08L3RkPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyI+CiAgICAgICAgICAgICAgICAgICAgICA8QnV0dG9uIHZhcmlhbnQ9Imdob3N0IiBzaXplPSJzbSI+VmlldzwvQnV0dG9uPgogICAgICAgICAgICAgICAgICAgIDwvdGQ+CiAgICAgICAgICAgICAgICAgIDwvdHI+CiAgICAgICAgICAgICAgICApKQogICAgICAgICAgICAgICl9CiAgICAgICAgICAgIDwvdGJvZHk+CiAgICAgICAgICA8L3RhYmxlPgogICAgICAgIDwvZGl2PgogICAgICApfQogICAgPC9kaXY+CiAgKTsKfQo=</t>
   </si>
   <si>
     <t>frontend/src/app/admin/page.tsx</t>
@@ -1295,7 +1296,7 @@
  import Button from "@/components/ui/button";
  import { Badge, Spinner } from "@/components/ui/index";
  import { toast } from "@/components/ui/toast";
- import { adminApi, propertyApi, getApiError } from "@/lib/api";
+ import { adminApi, getApiError } from "@/lib/api";
  import type { Property } from "@/types";
  export default function AdminPropertiesPage() {
   const [properties, setProperties] = useState&lt;Property[]&gt;([]);
@@ -1327,7 +1328,7 @@
   }, [properties, search]);
   const handleToggleActive = async (id: string, currentlyActive: boolean) =&gt; {
   try {
-  await propertyApi.update(id, { is_active: !currentlyActive });
+  await adminApi.togglePropertyStatus(id);
   setProperties((prev) =&gt;
   prev.map((p) =&gt; (p.id === id ? { ...p, is_active: !currentlyActive } : p))
   );
@@ -1377,7 +1378,7 @@
   &lt;div className="h-10 w-14 rounded bg-gray-200 flex-shrink-0" /&gt;
   &lt;div&gt;
   &lt;p className="text-sm font-medium text-gray-900"&gt;{p.title}&lt;/p&gt;
-  &lt;p className="text-xs text-gray-500"&gt;{p.city}{p.country ? `, ${p.country}` : ""}&lt;/p&gt;
+  &lt;p className="text-xs text-gray-500"&gt;{p.city}&lt;/p&gt;
   &lt;/div&gt;
   &lt;/div&gt;
   &lt;/td&gt;
@@ -1410,7 +1411,7 @@
  }</t>
   </si>
   <si>
-    <t>LyoqCiAqIEBtb2R1bGUgQWRtaW5Qcm9wZXJ0aWVzUGFnZQogKiBAZGVzY3JpcHRpb24gQWRtaW4gcHJvcGVydHkgbW9kZXJhdGlvbiBwYWdlIGZvciByZXZpZXdpbmcsIGFwcHJvdmluZywgYW5kIHJlbW92aW5nIGxpc3RpbmdzLgogKi8KInVzZSBjbGllbnQiOwoKaW1wb3J0IFJlYWN0LCB7IHVzZUVmZmVjdCwgdXNlU3RhdGUsIHVzZU1lbW8gfSBmcm9tICJyZWFjdCI7CmltcG9ydCBMaW5rIGZyb20gIm5leHQvbGluayI7CmltcG9ydCBCdXR0b24gZnJvbSAiQC9jb21wb25lbnRzL3VpL2J1dHRvbiI7CmltcG9ydCB7IEJhZGdlLCBTcGlubmVyIH0gZnJvbSAiQC9jb21wb25lbnRzL3VpL2luZGV4IjsKaW1wb3J0IHsgdG9hc3QgfSBmcm9tICJAL2NvbXBvbmVudHMvdWkvdG9hc3QiOwppbXBvcnQgeyBhZG1pbkFwaSwgcHJvcGVydHlBcGksIGdldEFwaUVycm9yIH0gZnJvbSAiQC9saWIvYXBpIjsKaW1wb3J0IHR5cGUgeyBQcm9wZXJ0eSB9IGZyb20gIkAvdHlwZXMiOwoKZXhwb3J0IGRlZmF1bHQgZnVuY3Rpb24gQWRtaW5Qcm9wZXJ0aWVzUGFnZSgpIHsKICBjb25zdCBbcHJvcGVydGllcywgc2V0UHJvcGVydGllc10gPSB1c2VTdGF0ZTxQcm9wZXJ0eVtdPihbXSk7CiAgY29uc3QgW2xvYWRpbmcsIHNldExvYWRpbmddID0gdXNlU3RhdGUodHJ1ZSk7CiAgY29uc3QgW3NlYXJjaCwgc2V0U2VhcmNoXSA9IHVzZVN0YXRlKCIiKTsKCiAgdXNlRWZmZWN0KCgpID0+IHsKICAgIGNvbnN0IGxvYWQgPSBhc3luYyAoKSA9PiB7CiAgICAgIHRyeSB7CiAgICAgICAgY29uc3QgcmVzID0gYXdhaXQgYWRtaW5BcGkubGlzdFByb3BlcnRpZXMoKTsKICAgICAgICBjb25zdCBkYXRhID0gcmVzLmRhdGE7CiAgICAgICAgc2V0UHJvcGVydGllcyhBcnJheS5pc0FycmF5KGRhdGEpID8gZGF0YSA6IGRhdGEuaXRlbXMgfHwgW10pOwogICAgICB9IGNhdGNoIHsKICAgICAgICBzZXRQcm9wZXJ0aWVzKFtdKTsKICAgICAgfSBmaW5hbGx5IHsKICAgICAgICBzZXRMb2FkaW5nKGZhbHNlKTsKICAgICAgfQogICAgfTsKICAgIGxvYWQoKTsKICB9LCBbXSk7CgogIGNvbnN0IGZpbHRlcmVkID0gdXNlTWVtbygoKSA9PiB7CiAgICBpZiAoIXNlYXJjaC50cmltKCkpIHJldHVybiBwcm9wZXJ0aWVzOwogICAgY29uc3QgcSA9IHNlYXJjaC50b0xvd2VyQ2FzZSgpOwogICAgcmV0dXJuIHByb3BlcnRpZXMuZmlsdGVyKAogICAgICAocCkgPT4KICAgICAgICBwLnRpdGxlPy50b0xvd2VyQ2FzZSgpLmluY2x1ZGVzKHEpIHx8CiAgICAgICAgcC5jaXR5Py50b0xvd2VyQ2FzZSgpLmluY2x1ZGVzKHEpIHx8CiAgICAgICAgcC5ob3N0X25hbWU/LnRvTG93ZXJDYXNlKCkuaW5jbHVkZXMocSkKICAgICk7CiAgfSwgW3Byb3BlcnRpZXMsIHNlYXJjaF0pOwoKICBjb25zdCBoYW5kbGVUb2dnbGVBY3RpdmUgPSBhc3luYyAoaWQ6IHN0cmluZywgY3VycmVudGx5QWN0aXZlOiBib29sZWFuKSA9PiB7CiAgICB0cnkgewogICAgICBhd2FpdCBwcm9wZXJ0eUFwaS51cGRhdGUoaWQsIHsgaXNfYWN0aXZlOiAhY3VycmVudGx5QWN0aXZlIH0pOwogICAgICBzZXRQcm9wZXJ0aWVzKChwcmV2KSA9PgogICAgICAgIHByZXYubWFwKChwKSA9PiAocC5pZCA9PT0gaWQgPyB7IC4uLnAsIGlzX2FjdGl2ZTogIWN1cnJlbnRseUFjdGl2ZSB9IDogcCkpCiAgICAgICk7CiAgICAgIHRvYXN0LnN1Y2Nlc3MoY3VycmVudGx5QWN0aXZlID8gIlByb3BlcnR5IGRlYWN0aXZhdGVkIiA6ICJQcm9wZXJ0eSBhY3RpdmF0ZWQiKTsKICAgIH0gY2F0Y2ggKGVycjogdW5rbm93bikgewogICAgICB0b2FzdC5lcnJvcihnZXRBcGlFcnJvcihlcnIpKTsKICAgIH0KICB9OwoKICByZXR1cm4gKAogICAgPGRpdj4KICAgICAgPGRpdiBjbGFzc05hbWU9ImZsZXggaXRlbXMtY2VudGVyIGp1c3RpZnktYmV0d2VlbiBtYi02Ij4KICAgICAgICA8aDIgY2xhc3NOYW1lPSJ0ZXh0LXhsIGZvbnQtYm9sZCB0ZXh0LWdyYXktOTAwIj5Qcm9wZXJ0aWVzPC9oMj4KICAgICAgICA8aW5wdXQKICAgICAgICAgIHR5cGU9InRleHQiCiAgICAgICAgICBwbGFjZWhvbGRlcj0iU2VhcmNoIHByb3BlcnRpZXMuLi4iCiAgICAgICAgICB2YWx1ZT17c2VhcmNofQogICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiBzZXRTZWFyY2goZS50YXJnZXQudmFsdWUpfQogICAgICAgICAgY2xhc3NOYW1lPSJib3JkZXIgYm9yZGVyLWdyYXktMzAwIHJvdW5kZWQtbGcgcHgtMyBweS0yIHRleHQtc20gZm9jdXM6b3V0bGluZS1ub25lIGZvY3VzOnJpbmctMiBmb2N1czpyaW5nLXJvc2UtMjAwIgogICAgICAgIC8+CiAgICAgIDwvZGl2PgoKICAgICAge2xvYWRpbmcgPyAoCiAgICAgICAgPGRpdiBjbGFzc05hbWU9ImZsZXgganVzdGlmeS1jZW50ZXIgcHktMjAiPjxTcGlubmVyIHNpemU9ImxnIiAvPjwvZGl2PgogICAgICApIDogKAogICAgICAgIDxkaXYgY2xhc3NOYW1lPSJiZy13aGl0ZSByb3VuZGVkLXhsIGJvcmRlciBib3JkZXItZ3JheS0yMDAgb3ZlcmZsb3ctaGlkZGVuIj4KICAgICAgICAgIDx0YWJsZSBjbGFzc05hbWU9InctZnVsbCI+CiAgICAgICAgICAgIDx0aGVhZCBjbGFzc05hbWU9ImJnLWdyYXktNTAgYm9yZGVyLWIgYm9yZGVyLWdyYXktMjAwIj4KICAgICAgICAgICAgICA8dHI+CiAgICAgICAgICAgICAgICA8dGggY2xhc3NOYW1lPSJ0ZXh0LWxlZnQgdGV4dC14cyBmb250LW1lZGl1bSB0ZXh0LWdyYXktNTAwIHVwcGVyY2FzZSBweC00IHB5LTMiPlByb3BlcnR5PC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+SG9zdDwvdGg+CiAgICAgICAgICAgICAgICA8dGggY2xhc3NOYW1lPSJ0ZXh0LWxlZnQgdGV4dC14cyBmb250LW1lZGl1bSB0ZXh0LWdyYXktNTAwIHVwcGVyY2FzZSBweC00IHB5LTMiPlN0YXR1czwvdGg+CiAgICAgICAgICAgICAgICA8dGggY2xhc3NOYW1lPSJ0ZXh0LWxlZnQgdGV4dC14cyBmb250LW1lZGl1bSB0ZXh0LWdyYXktNTAwIHVwcGVyY2FzZSBweC00IHB5LTMiPlByaWNlL05pZ2h0PC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+QWN0aW9uczwvdGg+CiAgICAgICAgICAgICAgPC90cj4KICAgICAgICAgICAgPC90aGVhZD4KICAgICAgICAgICAgPHRib2R5IGNsYXNzTmFtZT0iZGl2aWRlLXkgZGl2aWRlLWdyYXktMTAwIj4KICAgICAgICAgICAgICB7ZmlsdGVyZWQubGVuZ3RoID09PSAwID8gKAogICAgICAgICAgICAgICAgPHRyPgogICAgICAgICAgICAgICAgICA8dGQgY29sU3Bhbj17NX0gY2xhc3NOYW1lPSJ0ZXh0LWNlbnRlciBweS0xMCB0ZXh0LXNtIHRleHQtZ3JheS01MDAiPgogICAgICAgICAgICAgICAgICAgIE5vIHByb3BlcnRpZXMgZm91bmQKICAgICAgICAgICAgICAgICAgPC90ZD4KICAgICAgICAgICAgICAgIDwvdHI+CiAgICAgICAgICAgICAgKSA6ICgKICAgICAgICAgICAgICAgIGZpbHRlcmVkLm1hcCgocCkgPT4gKAogICAgICAgICAgICAgICAgICA8dHIga2V5PXtwLmlkfSBjbGFzc05hbWU9ImhvdmVyOmJnLWdyYXktNTAiPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyI+CiAgICAgICAgICAgICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iZmxleCBpdGVtcy1jZW50ZXIgZ2FwLTMiPgogICAgICAgICAgICAgICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iaC0xMCB3LTE0IHJvdW5kZWQgYmctZ3JheS0yMDAgZmxleC1zaHJpbmstMCIgLz4KICAgICAgICAgICAgICAgICAgICAgICAgPGRpdj4KICAgICAgICAgICAgICAgICAgICAgICAgICA8cCBjbGFzc05hbWU9InRleHQtc20gZm9udC1tZWRpdW0gdGV4dC1ncmF5LTkwMCI+e3AudGl0bGV9PC9wPgogICAgICAgICAgICAgICAgICAgICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC14cyB0ZXh0LWdyYXktNTAwIj57cC5jaXR5fXtwLmNvdW50cnkgPyBgLCAke3AuY291bnRyeX1gIDogIiJ9PC9wPgogICAgICAgICAgICAgICAgICAgICAgICA8L2Rpdj4KICAgICAgICAgICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgICAgICAgIDwvdGQ+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIHRleHQtc20gdGV4dC1ncmF5LTYwMCI+e3AuaG9zdF9uYW1lIHx8ICLigJQifTwvdGQ+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIj4KICAgICAgICAgICAgICAgICAgICAgIDxCYWRnZSB2YXJpYW50PXtwLmlzX2FjdGl2ZSA/ICJzdWNjZXNzIiA6ICJkZWZhdWx0In0+e3AuaXNfYWN0aXZlID8gImFjdGl2ZSIgOiAiaW5hY3RpdmUifTwvQmFkZ2U+CiAgICAgICAgICAgICAgICAgICAgPC90ZD4KICAgICAgICAgICAgICAgICAgICA8dGQgY2xhc3NOYW1lPSJweC00IHB5LTMgdGV4dC1zbSB0ZXh0LWdyYXktOTAwIj7igrl7cC5wcmljZV9wZXJfbmlnaHR9PC90ZD4KICAgICAgICAgICAgICAgICAgICA8dGQgY2xhc3NOYW1lPSJweC00IHB5LTMgZmxleCBnYXAtMiI+CiAgICAgICAgICAgICAgICAgICAgICA8TGluayBocmVmPXtgL3Byb3BlcnRpZXMvJHtwLmlkfWB9PgogICAgICAgICAgICAgICAgICAgICAgICA8QnV0dG9uIHZhcmlhbnQ9Imdob3N0IiBzaXplPSJzbSI+VmlldzwvQnV0dG9uPgogICAgICAgICAgICAgICAgICAgICAgPC9MaW5rPgogICAgICAgICAgICAgICAgICAgICAgPEJ1dHRvbgogICAgICAgICAgICAgICAgICAgICAgICB2YXJpYW50PXtwLmlzX2FjdGl2ZSA/ICJkYW5nZXIiIDogIm91dGxpbmUifQogICAgICAgICAgICAgICAgICAgICAgICBzaXplPSJzbSIKICAgICAgICAgICAgICAgICAgICAgICAgb25DbGljaz17KCkgPT4gaGFuZGxlVG9nZ2xlQWN0aXZlKHAuaWQsICEhcC5pc19hY3RpdmUpfQogICAgICAgICAgICAgICAgICAgICAgPgogICAgICAgICAgICAgICAgICAgICAgICB7cC5pc19hY3RpdmUgPyAiRGVhY3RpdmF0ZSIgOiAiQWN0aXZhdGUifQogICAgICAgICAgICAgICAgICAgICAgPC9CdXR0b24+CiAgICAgICAgICAgICAgICAgICAgPC90ZD4KICAgICAgICAgICAgICAgICAgPC90cj4KICAgICAgICAgICAgICAgICkpCiAgICAgICAgICAgICAgKX0KICAgICAgICAgICAgPC90Ym9keT4KICAgICAgICAgIDwvdGFibGU+CiAgICAgICAgPC9kaXY+CiAgICAgICl9CiAgICA8L2Rpdj4KICApOwp9Cg==</t>
+    <t>LyoqCiAqIEBtb2R1bGUgQWRtaW5Qcm9wZXJ0aWVzUGFnZQogKiBAZGVzY3JpcHRpb24gQWRtaW4gcHJvcGVydHkgbW9kZXJhdGlvbiBwYWdlIGZvciByZXZpZXdpbmcsIGFwcHJvdmluZywgYW5kIHJlbW92aW5nIGxpc3RpbmdzLgogKi8KInVzZSBjbGllbnQiOwoKaW1wb3J0IFJlYWN0LCB7IHVzZUVmZmVjdCwgdXNlU3RhdGUsIHVzZU1lbW8gfSBmcm9tICJyZWFjdCI7CmltcG9ydCBMaW5rIGZyb20gIm5leHQvbGluayI7CmltcG9ydCBCdXR0b24gZnJvbSAiQC9jb21wb25lbnRzL3VpL2J1dHRvbiI7CmltcG9ydCB7IEJhZGdlLCBTcGlubmVyIH0gZnJvbSAiQC9jb21wb25lbnRzL3VpL2luZGV4IjsKaW1wb3J0IHsgdG9hc3QgfSBmcm9tICJAL2NvbXBvbmVudHMvdWkvdG9hc3QiOwppbXBvcnQgeyBhZG1pbkFwaSwgZ2V0QXBpRXJyb3IgfSBmcm9tICJAL2xpYi9hcGkiOwppbXBvcnQgdHlwZSB7IFByb3BlcnR5IH0gZnJvbSAiQC90eXBlcyI7CgpleHBvcnQgZGVmYXVsdCBmdW5jdGlvbiBBZG1pblByb3BlcnRpZXNQYWdlKCkgewogIGNvbnN0IFtwcm9wZXJ0aWVzLCBzZXRQcm9wZXJ0aWVzXSA9IHVzZVN0YXRlPFByb3BlcnR5W10+KFtdKTsKICBjb25zdCBbbG9hZGluZywgc2V0TG9hZGluZ10gPSB1c2VTdGF0ZSh0cnVlKTsKICBjb25zdCBbc2VhcmNoLCBzZXRTZWFyY2hdID0gdXNlU3RhdGUoIiIpOwoKICB1c2VFZmZlY3QoKCkgPT4gewogICAgY29uc3QgbG9hZCA9IGFzeW5jICgpID0+IHsKICAgICAgdHJ5IHsKICAgICAgICBjb25zdCByZXMgPSBhd2FpdCBhZG1pbkFwaS5saXN0UHJvcGVydGllcygpOwogICAgICAgIGNvbnN0IGRhdGEgPSByZXMuZGF0YTsKICAgICAgICBzZXRQcm9wZXJ0aWVzKEFycmF5LmlzQXJyYXkoZGF0YSkgPyBkYXRhIDogZGF0YS5pdGVtcyB8fCBbXSk7CiAgICAgIH0gY2F0Y2ggewogICAgICAgIHNldFByb3BlcnRpZXMoW10pOwogICAgICB9IGZpbmFsbHkgewogICAgICAgIHNldExvYWRpbmcoZmFsc2UpOwogICAgICB9CiAgICB9OwogICAgbG9hZCgpOwogIH0sIFtdKTsKCiAgY29uc3QgZmlsdGVyZWQgPSB1c2VNZW1vKCgpID0+IHsKICAgIGlmICghc2VhcmNoLnRyaW0oKSkgcmV0dXJuIHByb3BlcnRpZXM7CiAgICBjb25zdCBxID0gc2VhcmNoLnRvTG93ZXJDYXNlKCk7CiAgICByZXR1cm4gcHJvcGVydGllcy5maWx0ZXIoCiAgICAgIChwKSA9PgogICAgICAgIHAudGl0bGU/LnRvTG93ZXJDYXNlKCkuaW5jbHVkZXMocSkgfHwKICAgICAgICBwLmNpdHk/LnRvTG93ZXJDYXNlKCkuaW5jbHVkZXMocSkgfHwKICAgICAgICBwLmhvc3RfbmFtZT8udG9Mb3dlckNhc2UoKS5pbmNsdWRlcyhxKQogICAgKTsKICB9LCBbcHJvcGVydGllcywgc2VhcmNoXSk7CgogIGNvbnN0IGhhbmRsZVRvZ2dsZUFjdGl2ZSA9IGFzeW5jIChpZDogc3RyaW5nLCBjdXJyZW50bHlBY3RpdmU6IGJvb2xlYW4pID0+IHsKICAgIHRyeSB7CiAgICAgIGF3YWl0IGFkbWluQXBpLnRvZ2dsZVByb3BlcnR5U3RhdHVzKGlkKTsKICAgICAgc2V0UHJvcGVydGllcygocHJldikgPT4KICAgICAgICBwcmV2Lm1hcCgocCkgPT4gKHAuaWQgPT09IGlkID8geyAuLi5wLCBpc19hY3RpdmU6ICFjdXJyZW50bHlBY3RpdmUgfSA6IHApKQogICAgICApOwogICAgICB0b2FzdC5zdWNjZXNzKGN1cnJlbnRseUFjdGl2ZSA/ICJQcm9wZXJ0eSBkZWFjdGl2YXRlZCIgOiAiUHJvcGVydHkgYWN0aXZhdGVkIik7CiAgICB9IGNhdGNoIChlcnI6IHVua25vd24pIHsKICAgICAgdG9hc3QuZXJyb3IoZ2V0QXBpRXJyb3IoZXJyKSk7CiAgICB9CiAgfTsKCiAgcmV0dXJuICgKICAgIDxkaXY+CiAgICAgIDxkaXYgY2xhc3NOYW1lPSJmbGV4IGl0ZW1zLWNlbnRlciBqdXN0aWZ5LWJldHdlZW4gbWItNiI+CiAgICAgICAgPGgyIGNsYXNzTmFtZT0idGV4dC14bCBmb250LWJvbGQgdGV4dC1ncmF5LTkwMCI+UHJvcGVydGllczwvaDI+CiAgICAgICAgPGlucHV0CiAgICAgICAgICB0eXBlPSJ0ZXh0IgogICAgICAgICAgcGxhY2Vob2xkZXI9IlNlYXJjaCBwcm9wZXJ0aWVzLi4uIgogICAgICAgICAgdmFsdWU9e3NlYXJjaH0KICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gc2V0U2VhcmNoKGUudGFyZ2V0LnZhbHVlKX0KICAgICAgICAgIGNsYXNzTmFtZT0iYm9yZGVyIGJvcmRlci1ncmF5LTMwMCByb3VuZGVkLWxnIHB4LTMgcHktMiB0ZXh0LXNtIGZvY3VzOm91dGxpbmUtbm9uZSBmb2N1czpyaW5nLTIgZm9jdXM6cmluZy1yb3NlLTIwMCIKICAgICAgICAvPgogICAgICA8L2Rpdj4KCiAgICAgIHtsb2FkaW5nID8gKAogICAgICAgIDxkaXYgY2xhc3NOYW1lPSJmbGV4IGp1c3RpZnktY2VudGVyIHB5LTIwIj48U3Bpbm5lciBzaXplPSJsZyIgLz48L2Rpdj4KICAgICAgKSA6ICgKICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iYmctd2hpdGUgcm91bmRlZC14bCBib3JkZXIgYm9yZGVyLWdyYXktMjAwIG92ZXJmbG93LWhpZGRlbiI+CiAgICAgICAgICA8dGFibGUgY2xhc3NOYW1lPSJ3LWZ1bGwiPgogICAgICAgICAgICA8dGhlYWQgY2xhc3NOYW1lPSJiZy1ncmF5LTUwIGJvcmRlci1iIGJvcmRlci1ncmF5LTIwMCI+CiAgICAgICAgICAgICAgPHRyPgogICAgICAgICAgICAgICAgPHRoIGNsYXNzTmFtZT0idGV4dC1sZWZ0IHRleHQteHMgZm9udC1tZWRpdW0gdGV4dC1ncmF5LTUwMCB1cHBlcmNhc2UgcHgtNCBweS0zIj5Qcm9wZXJ0eTwvdGg+CiAgICAgICAgICAgICAgICA8dGggY2xhc3NOYW1lPSJ0ZXh0LWxlZnQgdGV4dC14cyBmb250LW1lZGl1bSB0ZXh0LWdyYXktNTAwIHVwcGVyY2FzZSBweC00IHB5LTMiPkhvc3Q8L3RoPgogICAgICAgICAgICAgICAgPHRoIGNsYXNzTmFtZT0idGV4dC1sZWZ0IHRleHQteHMgZm9udC1tZWRpdW0gdGV4dC1ncmF5LTUwMCB1cHBlcmNhc2UgcHgtNCBweS0zIj5TdGF0dXM8L3RoPgogICAgICAgICAgICAgICAgPHRoIGNsYXNzTmFtZT0idGV4dC1sZWZ0IHRleHQteHMgZm9udC1tZWRpdW0gdGV4dC1ncmF5LTUwMCB1cHBlcmNhc2UgcHgtNCBweS0zIj5QcmljZS9OaWdodDwvdGg+CiAgICAgICAgICAgICAgICA8dGggY2xhc3NOYW1lPSJ0ZXh0LWxlZnQgdGV4dC14cyBmb250LW1lZGl1bSB0ZXh0LWdyYXktNTAwIHVwcGVyY2FzZSBweC00IHB5LTMiPkFjdGlvbnM8L3RoPgogICAgICAgICAgICAgIDwvdHI+CiAgICAgICAgICAgIDwvdGhlYWQ+CiAgICAgICAgICAgIDx0Ym9keSBjbGFzc05hbWU9ImRpdmlkZS15IGRpdmlkZS1ncmF5LTEwMCI+CiAgICAgICAgICAgICAge2ZpbHRlcmVkLmxlbmd0aCA9PT0gMCA/ICgKICAgICAgICAgICAgICAgIDx0cj4KICAgICAgICAgICAgICAgICAgPHRkIGNvbFNwYW49ezV9IGNsYXNzTmFtZT0idGV4dC1jZW50ZXIgcHktMTAgdGV4dC1zbSB0ZXh0LWdyYXktNTAwIj4KICAgICAgICAgICAgICAgICAgICBObyBwcm9wZXJ0aWVzIGZvdW5kCiAgICAgICAgICAgICAgICAgIDwvdGQ+CiAgICAgICAgICAgICAgICA8L3RyPgogICAgICAgICAgICAgICkgOiAoCiAgICAgICAgICAgICAgICBmaWx0ZXJlZC5tYXAoKHApID0+ICgKICAgICAgICAgICAgICAgICAgPHRyIGtleT17cC5pZH0gY2xhc3NOYW1lPSJob3ZlcjpiZy1ncmF5LTUwIj4KICAgICAgICAgICAgICAgICAgICA8dGQgY2xhc3NOYW1lPSJweC00IHB5LTMiPgogICAgICAgICAgICAgICAgICAgICAgPGRpdiBjbGFzc05hbWU9ImZsZXggaXRlbXMtY2VudGVyIGdhcC0zIj4KICAgICAgICAgICAgICAgICAgICAgICAgPGRpdiBjbGFzc05hbWU9ImgtMTAgdy0xNCByb3VuZGVkIGJnLWdyYXktMjAwIGZsZXgtc2hyaW5rLTAiIC8+CiAgICAgICAgICAgICAgICAgICAgICAgIDxkaXY+CiAgICAgICAgICAgICAgICAgICAgICAgICAgPHAgY2xhc3NOYW1lPSJ0ZXh0LXNtIGZvbnQtbWVkaXVtIHRleHQtZ3JheS05MDAiPntwLnRpdGxlfTwvcD4KICAgICAgICAgICAgICAgICAgICAgICAgICA8cCBjbGFzc05hbWU9InRleHQteHMgdGV4dC1ncmF5LTUwMCI+e3AuY2l0eX08L3A+CiAgICAgICAgICAgICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgICAgICAgICAgPC9kaXY+CiAgICAgICAgICAgICAgICAgICAgPC90ZD4KICAgICAgICAgICAgICAgICAgICA8dGQgY2xhc3NOYW1lPSJweC00IHB5LTMgdGV4dC1zbSB0ZXh0LWdyYXktNjAwIj57cC5ob3N0X25hbWUgfHwgIuKAlCJ9PC90ZD4KICAgICAgICAgICAgICAgICAgICA8dGQgY2xhc3NOYW1lPSJweC00IHB5LTMiPgogICAgICAgICAgICAgICAgICAgICAgPEJhZGdlIHZhcmlhbnQ9e3AuaXNfYWN0aXZlID8gInN1Y2Nlc3MiIDogImRlZmF1bHQifT57cC5pc19hY3RpdmUgPyAiYWN0aXZlIiA6ICJpbmFjdGl2ZSJ9PC9CYWRnZT4KICAgICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyB0ZXh0LXNtIHRleHQtZ3JheS05MDAiPuKCuXtwLnByaWNlX3Blcl9uaWdodH08L3RkPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyBmbGV4IGdhcC0yIj4KICAgICAgICAgICAgICAgICAgICAgIDxMaW5rIGhyZWY9e2AvcHJvcGVydGllcy8ke3AuaWR9YH0+CiAgICAgICAgICAgICAgICAgICAgICAgIDxCdXR0b24gdmFyaWFudD0iZ2hvc3QiIHNpemU9InNtIj5WaWV3PC9CdXR0b24+CiAgICAgICAgICAgICAgICAgICAgICA8L0xpbms+CiAgICAgICAgICAgICAgICAgICAgICA8QnV0dG9uCiAgICAgICAgICAgICAgICAgICAgICAgIHZhcmlhbnQ9e3AuaXNfYWN0aXZlID8gImRhbmdlciIgOiAib3V0bGluZSJ9CiAgICAgICAgICAgICAgICAgICAgICAgIHNpemU9InNtIgogICAgICAgICAgICAgICAgICAgICAgICBvbkNsaWNrPXsoKSA9PiBoYW5kbGVUb2dnbGVBY3RpdmUocC5pZCwgISFwLmlzX2FjdGl2ZSl9CiAgICAgICAgICAgICAgICAgICAgICA+CiAgICAgICAgICAgICAgICAgICAgICAgIHtwLmlzX2FjdGl2ZSA/ICJEZWFjdGl2YXRlIiA6ICJBY3RpdmF0ZSJ9CiAgICAgICAgICAgICAgICAgICAgICA8L0J1dHRvbj4KICAgICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgICA8L3RyPgogICAgICAgICAgICAgICAgKSkKICAgICAgICAgICAgICApfQogICAgICAgICAgICA8L3Rib2R5PgogICAgICAgICAgPC90YWJsZT4KICAgICAgICA8L2Rpdj4KICAgICAgKX0KICAgIDwvZGl2PgogICk7Cn0K</t>
   </si>
   <si>
     <t>frontend/src/app/admin/users/page.tsx</t>
@@ -1512,7 +1513,7 @@
   &lt;tr key={u.id} className="hover:bg-gray-50"&gt;
   &lt;td className="px-4 py-3"&gt;
   &lt;div className="flex items-center gap-3"&gt;
-  &lt;Avatar src={u.avatar_url} fallback={u.full_name || "U"} size="sm" /&gt;
+  &lt;Avatar fallback={u.full_name || "U"} size="sm" /&gt;
   &lt;span className="text-sm font-medium text-gray-900"&gt;
   {u.full_name}
   &lt;/span&gt;
@@ -1551,7 +1552,7 @@
  }</t>
   </si>
   <si>
-    <t>LyoqCiAqIEBtb2R1bGUgQWRtaW5Vc2Vyc1BhZ2UKICogQGRlc2NyaXB0aW9uIEFkbWluIHVzZXIgbWFuYWdlbWVudCBwYWdlIHdpdGggc2VhcmNoLCByb2xlIGJhZGdlcywgYW5kIGJhbi91bmJhbiBhY3Rpb25zLgogKi8KInVzZSBjbGllbnQiOwoKaW1wb3J0IFJlYWN0LCB7IHVzZUVmZmVjdCwgdXNlU3RhdGUsIHVzZU1lbW8gfSBmcm9tICJyZWFjdCI7CmltcG9ydCBCdXR0b24gZnJvbSAiQC9jb21wb25lbnRzL3VpL2J1dHRvbiI7CmltcG9ydCB7IEF2YXRhciwgQmFkZ2UsIFNwaW5uZXIgfSBmcm9tICJAL2NvbXBvbmVudHMvdWkvaW5kZXgiOwppbXBvcnQgeyB0b2FzdCB9IGZyb20gIkAvY29tcG9uZW50cy91aS90b2FzdCI7CmltcG9ydCB0eXBlIHsgVXNlciB9IGZyb20gIkAvdHlwZXMiOwppbXBvcnQgeyBhZG1pbkFwaSwgZ2V0QXBpRXJyb3IgfSBmcm9tICJAL2xpYi9hcGkiOwoKZXhwb3J0IGRlZmF1bHQgZnVuY3Rpb24gQWRtaW5Vc2Vyc1BhZ2UoKSB7CiAgY29uc3QgW3VzZXJzLCBzZXRVc2Vyc10gPSB1c2VTdGF0ZTxVc2VyW10+KFtdKTsKICBjb25zdCBbbG9hZGluZywgc2V0TG9hZGluZ10gPSB1c2VTdGF0ZSh0cnVlKTsKICBjb25zdCBbcGFnZSwgc2V0UGFnZV0gPSB1c2VTdGF0ZSgxKTsKICBjb25zdCBbc2VhcmNoLCBzZXRTZWFyY2hdID0gdXNlU3RhdGUoIiIpOwoKICB1c2VFZmZlY3QoKCkgPT4gewogICAgY29uc3QgbG9hZCA9IGFzeW5jICgpID0+IHsKICAgICAgc2V0TG9hZGluZyh0cnVlKTsKICAgICAgdHJ5IHsKICAgICAgICBjb25zdCByZXMgPSBhd2FpdCBhZG1pbkFwaS5saXN0VXNlcnMocGFnZSk7CiAgICAgICAgY29uc3QgZGF0YSA9IHJlcy5kYXRhOwogICAgICAgIHNldFVzZXJzKEFycmF5LmlzQXJyYXkoZGF0YSkgPyBkYXRhIDogZGF0YS5pdGVtcyB8fCBbXSk7CiAgICAgIH0gZmluYWxseSB7CiAgICAgICAgc2V0TG9hZGluZyhmYWxzZSk7CiAgICAgIH0KICAgIH07CiAgICBsb2FkKCk7CiAgfSwgW3BhZ2VdKTsKCiAgLy8gQ2xpZW50LXNpZGUgc2VhcmNoIGZpbHRlcgogIGNvbnN0IGZpbHRlcmVkVXNlcnMgPSB1c2VNZW1vKCgpID0+IHsKICAgIGlmICghc2VhcmNoLnRyaW0oKSkgcmV0dXJuIHVzZXJzOwogICAgY29uc3QgcSA9IHNlYXJjaC50b0xvd2VyQ2FzZSgpOwogICAgcmV0dXJuIHVzZXJzLmZpbHRlcigKICAgICAgKHUpID0+CiAgICAgICAgdS5mdWxsX25hbWU/LnRvTG93ZXJDYXNlKCkuaW5jbHVkZXMocSkgfHwKICAgICAgICB1LmVtYWlsPy50b0xvd2VyQ2FzZSgpLmluY2x1ZGVzKHEpIHx8CiAgICAgICAgdS5yb2xlPy50b0xvd2VyQ2FzZSgpLmluY2x1ZGVzKHEpCiAgICApOwogIH0sIFt1c2Vycywgc2VhcmNoXSk7CgogIGNvbnN0IGhhbmRsZVRvZ2dsZVN0YXR1cyA9IGFzeW5jICh1c2VySWQ6IHN0cmluZykgPT4gewogICAgdHJ5IHsKICAgICAgY29uc3QgcmVzID0gYXdhaXQgYWRtaW5BcGkudG9nZ2xlVXNlclN0YXR1cyh1c2VySWQpOwogICAgICBjb25zdCBpc0FjdGl2ZSA9IHJlcy5kYXRhLmlzX2FjdGl2ZTsKICAgICAgc2V0VXNlcnMoKHByZXYpID0+CiAgICAgICAgcHJldi5tYXAoKHUpID0+ICh1LmlkID09PSB1c2VySWQgPyB7IC4uLnUsIGlzX2FjdGl2ZTogaXNBY3RpdmUgfSA6IHUpKQogICAgICApOwogICAgICB0b2FzdC5zdWNjZXNzKGlzQWN0aXZlID8gIlVzZXIgYWN0aXZhdGVkIiA6ICJVc2VyIGRlYWN0aXZhdGVkIik7CiAgICB9IGNhdGNoIChlcnI6IHVua25vd24pIHsKICAgICAgdG9hc3QuZXJyb3IoZ2V0QXBpRXJyb3IoZXJyKSk7CiAgICB9CiAgfTsKCiAgY29uc3Qgcm9sZUNvbG9yOiBSZWNvcmQ8c3RyaW5nLCAiZGVmYXVsdCIgfCAic3VjY2VzcyIgfCAiaW5mbyIgfCAiZXJyb3IiPiA9IHsKICAgIHVzZXI6ICJkZWZhdWx0IiwKICAgIGhvc3Q6ICJzdWNjZXNzIiwKICAgIGFkbWluOiAiZXJyb3IiLAogIH07CgogIHJldHVybiAoCiAgICA8ZGl2PgogICAgICA8ZGl2IGNsYXNzTmFtZT0iZmxleCBpdGVtcy1jZW50ZXIganVzdGlmeS1iZXR3ZWVuIG1iLTYiPgogICAgICAgIDxoMiBjbGFzc05hbWU9InRleHQteGwgZm9udC1ib2xkIHRleHQtZ3JheS05MDAiPlVzZXJzPC9oMj4KICAgICAgICA8aW5wdXQKICAgICAgICAgIHR5cGU9InRleHQiCiAgICAgICAgICBwbGFjZWhvbGRlcj0iU2VhcmNoIHVzZXJzLi4uIgogICAgICAgICAgdmFsdWU9e3NlYXJjaH0KICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gc2V0U2VhcmNoKGUudGFyZ2V0LnZhbHVlKX0KICAgICAgICAgIGNsYXNzTmFtZT0iYm9yZGVyIGJvcmRlci1ncmF5LTMwMCByb3VuZGVkLWxnIHB4LTMgcHktMiB0ZXh0LXNtIGZvY3VzOm91dGxpbmUtbm9uZSBmb2N1czpyaW5nLTIgZm9jdXM6cmluZy1yb3NlLTIwMCIKICAgICAgICAvPgogICAgICA8L2Rpdj4KCiAgICAgIHtsb2FkaW5nID8gKAogICAgICAgIDxkaXYgY2xhc3NOYW1lPSJmbGV4IGp1c3RpZnktY2VudGVyIHB5LTIwIj48U3Bpbm5lciBzaXplPSJsZyIgLz48L2Rpdj4KICAgICAgKSA6ICgKICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iYmctd2hpdGUgcm91bmRlZC14bCBib3JkZXIgYm9yZGVyLWdyYXktMjAwIG92ZXJmbG93LWhpZGRlbiI+CiAgICAgICAgICA8dGFibGUgY2xhc3NOYW1lPSJ3LWZ1bGwiPgogICAgICAgICAgICA8dGhlYWQgY2xhc3NOYW1lPSJiZy1ncmF5LTUwIGJvcmRlci1iIGJvcmRlci1ncmF5LTIwMCI+CiAgICAgICAgICAgICAgPHRyPgogICAgICAgICAgICAgICAgPHRoIGNsYXNzTmFtZT0idGV4dC1sZWZ0IHRleHQteHMgZm9udC1tZWRpdW0gdGV4dC1ncmF5LTUwMCB1cHBlcmNhc2UgcHgtNCBweS0zIj5Vc2VyPC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+RW1haWw8L3RoPgogICAgICAgICAgICAgICAgPHRoIGNsYXNzTmFtZT0idGV4dC1sZWZ0IHRleHQteHMgZm9udC1tZWRpdW0gdGV4dC1ncmF5LTUwMCB1cHBlcmNhc2UgcHgtNCBweS0zIj5Sb2xlPC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+U3RhdHVzPC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+Sm9pbmVkPC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+QWN0aW9uczwvdGg+CiAgICAgICAgICAgICAgPC90cj4KICAgICAgICAgICAgPC90aGVhZD4KICAgICAgICAgICAgPHRib2R5IGNsYXNzTmFtZT0iZGl2aWRlLXkgZGl2aWRlLWdyYXktMTAwIj4KICAgICAgICAgICAgICB7ZmlsdGVyZWRVc2Vycy5sZW5ndGggPT09IDAgPyAoCiAgICAgICAgICAgICAgICA8dHI+CiAgICAgICAgICAgICAgICAgIDx0ZCBjb2xTcGFuPXs2fSBjbGFzc05hbWU9InRleHQtY2VudGVyIHB5LTEwIHRleHQtc20gdGV4dC1ncmF5LTUwMCI+CiAgICAgICAgICAgICAgICAgICAgTm8gdXNlcnMgZm91bmQKICAgICAgICAgICAgICAgICAgPC90ZD4KICAgICAgICAgICAgICAgIDwvdHI+CiAgICAgICAgICAgICAgKSA6ICgKICAgICAgICAgICAgICAgIGZpbHRlcmVkVXNlcnMubWFwKCh1KSA9PiAoCiAgICAgICAgICAgICAgICAgIDx0ciBrZXk9e3UuaWR9IGNsYXNzTmFtZT0iaG92ZXI6YmctZ3JheS01MCI+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIj4KICAgICAgICAgICAgICAgICAgICAgIDxkaXYgY2xhc3NOYW1lPSJmbGV4IGl0ZW1zLWNlbnRlciBnYXAtMyI+CiAgICAgICAgICAgICAgICAgICAgICAgIDxBdmF0YXIgc3JjPXt1LmF2YXRhcl91cmx9IGZhbGxiYWNrPXt1LmZ1bGxfbmFtZSB8fCAiVSJ9IHNpemU9InNtIiAvPgogICAgICAgICAgICAgICAgICAgICAgICA8c3BhbiBjbGFzc05hbWU9InRleHQtc20gZm9udC1tZWRpdW0gdGV4dC1ncmF5LTkwMCI+CiAgICAgICAgICAgICAgICAgICAgICAgICAge3UuZnVsbF9uYW1lfQogICAgICAgICAgICAgICAgICAgICAgICA8L3NwYW4+CiAgICAgICAgICAgICAgICAgICAgICA8L2Rpdj4KICAgICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyB0ZXh0LXNtIHRleHQtZ3JheS02MDAiPnt1LmVtYWlsfTwvdGQ+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIj4KICAgICAgICAgICAgICAgICAgICAgIDxCYWRnZSB2YXJpYW50PXtyb2xlQ29sb3JbdS5yb2xlXSB8fCAiZGVmYXVsdCJ9Pnt1LnJvbGV9PC9CYWRnZT4KICAgICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyI+CiAgICAgICAgICAgICAgICAgICAgICA8QmFkZ2UgdmFyaWFudD17dS5pc19hY3RpdmUgPyAic3VjY2VzcyIgOiAiZXJyb3IifT4KICAgICAgICAgICAgICAgICAgICAgICAge3UuaXNfYWN0aXZlID8gIkFjdGl2ZSIgOiAiRGlzYWJsZWQifQogICAgICAgICAgICAgICAgICAgICAgPC9CYWRnZT4KICAgICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyB0ZXh0LXNtIHRleHQtZ3JheS01MDAiPgogICAgICAgICAgICAgICAgICAgICAge25ldyBEYXRlKHUuY3JlYXRlZF9hdCkudG9Mb2NhbGVEYXRlU3RyaW5nKCl9CiAgICAgICAgICAgICAgICAgICAgPC90ZD4KICAgICAgICAgICAgICAgICAgICA8dGQgY2xhc3NOYW1lPSJweC00IHB5LTMiPgogICAgICAgICAgICAgICAgICAgICAgPEJ1dHRvbgogICAgICAgICAgICAgICAgICAgICAgICB2YXJpYW50PSJnaG9zdCIKICAgICAgICAgICAgICAgICAgICAgICAgc2l6ZT0ic20iCiAgICAgICAgICAgICAgICAgICAgICAgIG9uQ2xpY2s9eygpID0+IGhhbmRsZVRvZ2dsZVN0YXR1cyh1LmlkKX0KICAgICAgICAgICAgICAgICAgICAgID4KICAgICAgICAgICAgICAgICAgICAgICAge3UuaXNfYWN0aXZlID8gIkRpc2FibGUiIDogIkVuYWJsZSJ9CiAgICAgICAgICAgICAgICAgICAgICA8L0J1dHRvbj4KICAgICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgICA8L3RyPgogICAgICAgICAgICAgICAgKSkKICAgICAgICAgICAgICApfQogICAgICAgICAgICA8L3Rib2R5PgogICAgICAgICAgPC90YWJsZT4KICAgICAgICA8L2Rpdj4KICAgICAgKX0KICAgIDwvZGl2PgogICk7Cn0K</t>
+    <t>LyoqCiAqIEBtb2R1bGUgQWRtaW5Vc2Vyc1BhZ2UKICogQGRlc2NyaXB0aW9uIEFkbWluIHVzZXIgbWFuYWdlbWVudCBwYWdlIHdpdGggc2VhcmNoLCByb2xlIGJhZGdlcywgYW5kIGJhbi91bmJhbiBhY3Rpb25zLgogKi8KInVzZSBjbGllbnQiOwoKaW1wb3J0IFJlYWN0LCB7IHVzZUVmZmVjdCwgdXNlU3RhdGUsIHVzZU1lbW8gfSBmcm9tICJyZWFjdCI7CmltcG9ydCBCdXR0b24gZnJvbSAiQC9jb21wb25lbnRzL3VpL2J1dHRvbiI7CmltcG9ydCB7IEF2YXRhciwgQmFkZ2UsIFNwaW5uZXIgfSBmcm9tICJAL2NvbXBvbmVudHMvdWkvaW5kZXgiOwppbXBvcnQgeyB0b2FzdCB9IGZyb20gIkAvY29tcG9uZW50cy91aS90b2FzdCI7CmltcG9ydCB0eXBlIHsgVXNlciB9IGZyb20gIkAvdHlwZXMiOwppbXBvcnQgeyBhZG1pbkFwaSwgZ2V0QXBpRXJyb3IgfSBmcm9tICJAL2xpYi9hcGkiOwoKZXhwb3J0IGRlZmF1bHQgZnVuY3Rpb24gQWRtaW5Vc2Vyc1BhZ2UoKSB7CiAgY29uc3QgW3VzZXJzLCBzZXRVc2Vyc10gPSB1c2VTdGF0ZTxVc2VyW10+KFtdKTsKICBjb25zdCBbbG9hZGluZywgc2V0TG9hZGluZ10gPSB1c2VTdGF0ZSh0cnVlKTsKICBjb25zdCBbcGFnZSwgc2V0UGFnZV0gPSB1c2VTdGF0ZSgxKTsKICBjb25zdCBbc2VhcmNoLCBzZXRTZWFyY2hdID0gdXNlU3RhdGUoIiIpOwoKICB1c2VFZmZlY3QoKCkgPT4gewogICAgY29uc3QgbG9hZCA9IGFzeW5jICgpID0+IHsKICAgICAgc2V0TG9hZGluZyh0cnVlKTsKICAgICAgdHJ5IHsKICAgICAgICBjb25zdCByZXMgPSBhd2FpdCBhZG1pbkFwaS5saXN0VXNlcnMocGFnZSk7CiAgICAgICAgY29uc3QgZGF0YSA9IHJlcy5kYXRhOwogICAgICAgIHNldFVzZXJzKEFycmF5LmlzQXJyYXkoZGF0YSkgPyBkYXRhIDogZGF0YS5pdGVtcyB8fCBbXSk7CiAgICAgIH0gZmluYWxseSB7CiAgICAgICAgc2V0TG9hZGluZyhmYWxzZSk7CiAgICAgIH0KICAgIH07CiAgICBsb2FkKCk7CiAgfSwgW3BhZ2VdKTsKCiAgLy8gQ2xpZW50LXNpZGUgc2VhcmNoIGZpbHRlcgogIGNvbnN0IGZpbHRlcmVkVXNlcnMgPSB1c2VNZW1vKCgpID0+IHsKICAgIGlmICghc2VhcmNoLnRyaW0oKSkgcmV0dXJuIHVzZXJzOwogICAgY29uc3QgcSA9IHNlYXJjaC50b0xvd2VyQ2FzZSgpOwogICAgcmV0dXJuIHVzZXJzLmZpbHRlcigKICAgICAgKHUpID0+CiAgICAgICAgdS5mdWxsX25hbWU/LnRvTG93ZXJDYXNlKCkuaW5jbHVkZXMocSkgfHwKICAgICAgICB1LmVtYWlsPy50b0xvd2VyQ2FzZSgpLmluY2x1ZGVzKHEpIHx8CiAgICAgICAgdS5yb2xlPy50b0xvd2VyQ2FzZSgpLmluY2x1ZGVzKHEpCiAgICApOwogIH0sIFt1c2Vycywgc2VhcmNoXSk7CgogIGNvbnN0IGhhbmRsZVRvZ2dsZVN0YXR1cyA9IGFzeW5jICh1c2VySWQ6IHN0cmluZykgPT4gewogICAgdHJ5IHsKICAgICAgY29uc3QgcmVzID0gYXdhaXQgYWRtaW5BcGkudG9nZ2xlVXNlclN0YXR1cyh1c2VySWQpOwogICAgICBjb25zdCBpc0FjdGl2ZSA9IHJlcy5kYXRhLmlzX2FjdGl2ZTsKICAgICAgc2V0VXNlcnMoKHByZXYpID0+CiAgICAgICAgcHJldi5tYXAoKHUpID0+ICh1LmlkID09PSB1c2VySWQgPyB7IC4uLnUsIGlzX2FjdGl2ZTogaXNBY3RpdmUgfSA6IHUpKQogICAgICApOwogICAgICB0b2FzdC5zdWNjZXNzKGlzQWN0aXZlID8gIlVzZXIgYWN0aXZhdGVkIiA6ICJVc2VyIGRlYWN0aXZhdGVkIik7CiAgICB9IGNhdGNoIChlcnI6IHVua25vd24pIHsKICAgICAgdG9hc3QuZXJyb3IoZ2V0QXBpRXJyb3IoZXJyKSk7CiAgICB9CiAgfTsKCiAgY29uc3Qgcm9sZUNvbG9yOiBSZWNvcmQ8c3RyaW5nLCAiZGVmYXVsdCIgfCAic3VjY2VzcyIgfCAiaW5mbyIgfCAiZXJyb3IiPiA9IHsKICAgIHVzZXI6ICJkZWZhdWx0IiwKICAgIGhvc3Q6ICJzdWNjZXNzIiwKICAgIGFkbWluOiAiZXJyb3IiLAogIH07CgogIHJldHVybiAoCiAgICA8ZGl2PgogICAgICA8ZGl2IGNsYXNzTmFtZT0iZmxleCBpdGVtcy1jZW50ZXIganVzdGlmeS1iZXR3ZWVuIG1iLTYiPgogICAgICAgIDxoMiBjbGFzc05hbWU9InRleHQteGwgZm9udC1ib2xkIHRleHQtZ3JheS05MDAiPlVzZXJzPC9oMj4KICAgICAgICA8aW5wdXQKICAgICAgICAgIHR5cGU9InRleHQiCiAgICAgICAgICBwbGFjZWhvbGRlcj0iU2VhcmNoIHVzZXJzLi4uIgogICAgICAgICAgdmFsdWU9e3NlYXJjaH0KICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gc2V0U2VhcmNoKGUudGFyZ2V0LnZhbHVlKX0KICAgICAgICAgIGNsYXNzTmFtZT0iYm9yZGVyIGJvcmRlci1ncmF5LTMwMCByb3VuZGVkLWxnIHB4LTMgcHktMiB0ZXh0LXNtIGZvY3VzOm91dGxpbmUtbm9uZSBmb2N1czpyaW5nLTIgZm9jdXM6cmluZy1yb3NlLTIwMCIKICAgICAgICAvPgogICAgICA8L2Rpdj4KCiAgICAgIHtsb2FkaW5nID8gKAogICAgICAgIDxkaXYgY2xhc3NOYW1lPSJmbGV4IGp1c3RpZnktY2VudGVyIHB5LTIwIj48U3Bpbm5lciBzaXplPSJsZyIgLz48L2Rpdj4KICAgICAgKSA6ICgKICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iYmctd2hpdGUgcm91bmRlZC14bCBib3JkZXIgYm9yZGVyLWdyYXktMjAwIG92ZXJmbG93LWhpZGRlbiI+CiAgICAgICAgICA8dGFibGUgY2xhc3NOYW1lPSJ3LWZ1bGwiPgogICAgICAgICAgICA8dGhlYWQgY2xhc3NOYW1lPSJiZy1ncmF5LTUwIGJvcmRlci1iIGJvcmRlci1ncmF5LTIwMCI+CiAgICAgICAgICAgICAgPHRyPgogICAgICAgICAgICAgICAgPHRoIGNsYXNzTmFtZT0idGV4dC1sZWZ0IHRleHQteHMgZm9udC1tZWRpdW0gdGV4dC1ncmF5LTUwMCB1cHBlcmNhc2UgcHgtNCBweS0zIj5Vc2VyPC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+RW1haWw8L3RoPgogICAgICAgICAgICAgICAgPHRoIGNsYXNzTmFtZT0idGV4dC1sZWZ0IHRleHQteHMgZm9udC1tZWRpdW0gdGV4dC1ncmF5LTUwMCB1cHBlcmNhc2UgcHgtNCBweS0zIj5Sb2xlPC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+U3RhdHVzPC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+Sm9pbmVkPC90aD4KICAgICAgICAgICAgICAgIDx0aCBjbGFzc05hbWU9InRleHQtbGVmdCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHRleHQtZ3JheS01MDAgdXBwZXJjYXNlIHB4LTQgcHktMyI+QWN0aW9uczwvdGg+CiAgICAgICAgICAgICAgPC90cj4KICAgICAgICAgICAgPC90aGVhZD4KICAgICAgICAgICAgPHRib2R5IGNsYXNzTmFtZT0iZGl2aWRlLXkgZGl2aWRlLWdyYXktMTAwIj4KICAgICAgICAgICAgICB7ZmlsdGVyZWRVc2Vycy5sZW5ndGggPT09IDAgPyAoCiAgICAgICAgICAgICAgICA8dHI+CiAgICAgICAgICAgICAgICAgIDx0ZCBjb2xTcGFuPXs2fSBjbGFzc05hbWU9InRleHQtY2VudGVyIHB5LTEwIHRleHQtc20gdGV4dC1ncmF5LTUwMCI+CiAgICAgICAgICAgICAgICAgICAgTm8gdXNlcnMgZm91bmQKICAgICAgICAgICAgICAgICAgPC90ZD4KICAgICAgICAgICAgICAgIDwvdHI+CiAgICAgICAgICAgICAgKSA6ICgKICAgICAgICAgICAgICAgIGZpbHRlcmVkVXNlcnMubWFwKCh1KSA9PiAoCiAgICAgICAgICAgICAgICAgIDx0ciBrZXk9e3UuaWR9IGNsYXNzTmFtZT0iaG92ZXI6YmctZ3JheS01MCI+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIj4KICAgICAgICAgICAgICAgICAgICAgIDxkaXYgY2xhc3NOYW1lPSJmbGV4IGl0ZW1zLWNlbnRlciBnYXAtMyI+CiAgICAgICAgICAgICAgICAgICAgICAgIDxBdmF0YXIgZmFsbGJhY2s9e3UuZnVsbF9uYW1lIHx8ICJVIn0gc2l6ZT0ic20iIC8+CiAgICAgICAgICAgICAgICAgICAgICAgIDxzcGFuIGNsYXNzTmFtZT0idGV4dC1zbSBmb250LW1lZGl1bSB0ZXh0LWdyYXktOTAwIj4KICAgICAgICAgICAgICAgICAgICAgICAgICB7dS5mdWxsX25hbWV9CiAgICAgICAgICAgICAgICAgICAgICAgIDwvc3Bhbj4KICAgICAgICAgICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgICAgICAgIDwvdGQ+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIHRleHQtc20gdGV4dC1ncmF5LTYwMCI+e3UuZW1haWx9PC90ZD4KICAgICAgICAgICAgICAgICAgICA8dGQgY2xhc3NOYW1lPSJweC00IHB5LTMiPgogICAgICAgICAgICAgICAgICAgICAgPEJhZGdlIHZhcmlhbnQ9e3JvbGVDb2xvclt1LnJvbGVdIHx8ICJkZWZhdWx0In0+e3Uucm9sZX08L0JhZGdlPgogICAgICAgICAgICAgICAgICAgIDwvdGQ+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIj4KICAgICAgICAgICAgICAgICAgICAgIDxCYWRnZSB2YXJpYW50PXt1LmlzX2FjdGl2ZSA/ICJzdWNjZXNzIiA6ICJlcnJvciJ9PgogICAgICAgICAgICAgICAgICAgICAgICB7dS5pc19hY3RpdmUgPyAiQWN0aXZlIiA6ICJEaXNhYmxlZCJ9CiAgICAgICAgICAgICAgICAgICAgICA8L0JhZGdlPgogICAgICAgICAgICAgICAgICAgIDwvdGQ+CiAgICAgICAgICAgICAgICAgICAgPHRkIGNsYXNzTmFtZT0icHgtNCBweS0zIHRleHQtc20gdGV4dC1ncmF5LTUwMCI+CiAgICAgICAgICAgICAgICAgICAgICB7bmV3IERhdGUodS5jcmVhdGVkX2F0KS50b0xvY2FsZURhdGVTdHJpbmcoKX0KICAgICAgICAgICAgICAgICAgICA8L3RkPgogICAgICAgICAgICAgICAgICAgIDx0ZCBjbGFzc05hbWU9InB4LTQgcHktMyI+CiAgICAgICAgICAgICAgICAgICAgICA8QnV0dG9uCiAgICAgICAgICAgICAgICAgICAgICAgIHZhcmlhbnQ9Imdob3N0IgogICAgICAgICAgICAgICAgICAgICAgICBzaXplPSJzbSIKICAgICAgICAgICAgICAgICAgICAgICAgb25DbGljaz17KCkgPT4gaGFuZGxlVG9nZ2xlU3RhdHVzKHUuaWQpfQogICAgICAgICAgICAgICAgICAgICAgPgogICAgICAgICAgICAgICAgICAgICAgICB7dS5pc19hY3RpdmUgPyAiRGlzYWJsZSIgOiAiRW5hYmxlIn0KICAgICAgICAgICAgICAgICAgICAgIDwvQnV0dG9uPgogICAgICAgICAgICAgICAgICAgIDwvdGQ+CiAgICAgICAgICAgICAgICAgIDwvdHI+CiAgICAgICAgICAgICAgICApKQogICAgICAgICAgICAgICl9CiAgICAgICAgICAgIDwvdGJvZHk+CiAgICAgICAgICA8L3RhYmxlPgogICAgICAgIDwvZGl2PgogICAgICApfQogICAgPC9kaXY+CiAgKTsKfQo=</t>
   </si>
   <si>
     <t>frontend/src/app/api/auth/[...all]/route.ts</t>
@@ -2881,7 +2882,7 @@
   {
   tier: "basic",
   name: "Basic",
-  price: 29,
+  price: 2499,
   listing_limit: 5,
   features: [
   "Up to 5 property listings",
@@ -2894,7 +2895,7 @@
   {
   tier: "pro",
   name: "Professional",
-  price: 79,
+  price: 6499,
   listing_limit: 25,
   popular: true,
   features: [
@@ -2910,7 +2911,7 @@
   {
   tier: "premium",
   name: "Premium",
-  price: 199,
+  price: 16499,
   listing_limit: "Unlimited",
   features: [
   "Unlimited property listings",
@@ -3059,7 +3060,7 @@
  }</t>
   </si>
   <si>
-    <t>LyoqCiAqIEBtb2R1bGUgTWVtYmVyc2hpcFBhZ2UKICogQGRlc2NyaXB0aW9uIEhvc3QgbWVtYmVyc2hpcCB0aWVyIG1hbmFnZW1lbnQgcGFnZSBzaG93aW5nIGN1cnJlbnQgcGxhbiwgdGllciBjb21wYXJpc29uLCBhbmQgdXBncmFkZSBmbG93LgogKi8KInVzZSBjbGllbnQiOwoKaW1wb3J0IFJlYWN0LCB7IHVzZUVmZmVjdCwgdXNlU3RhdGUgfSBmcm9tICJyZWFjdCI7CmltcG9ydCBCdXR0b24gZnJvbSAiQC9jb21wb25lbnRzL3VpL2J1dHRvbiI7CmltcG9ydCB7IEJhZGdlLCBDYXJkLCBTcGlubmVyIH0gZnJvbSAiQC9jb21wb25lbnRzL3VpL2luZGV4IjsKaW1wb3J0IHsgdG9hc3QgfSBmcm9tICJAL2NvbXBvbmVudHMvdWkvdG9hc3QiOwppbXBvcnQgeyBtZW1iZXJzaGlwQXBpIH0gZnJvbSAiQC9saWIvYXBpIjsKCmludGVyZmFjZSBNZW1iZXJzaGlwUGxhbiB7CiAgdGllcjogc3RyaW5nOwogIG5hbWU6IHN0cmluZzsKICBwcmljZTogbnVtYmVyOwogIGZlYXR1cmVzOiBzdHJpbmdbXTsKICBsaXN0aW5nX2xpbWl0OiBudW1iZXIgfCAiVW5saW1pdGVkIjsKICBwb3B1bGFyPzogYm9vbGVhbjsKfQoKY29uc3QgcGxhbnM6IE1lbWJlcnNoaXBQbGFuW10gPSBbCiAgewogICAgdGllcjogImJhc2ljIiwKICAgIG5hbWU6ICJCYXNpYyIsCiAgICBwcmljZTogMjksCiAgICBsaXN0aW5nX2xpbWl0OiA1LAogICAgZmVhdHVyZXM6IFsKICAgICAgIlVwIHRvIDUgcHJvcGVydHkgbGlzdGluZ3MiLAogICAgICAiU3RhbmRhcmQgc2VhcmNoIHBsYWNlbWVudCIsCiAgICAgICJFbWFpbCBzdXBwb3J0IiwKICAgICAgIkJhc2ljIGFuYWx5dGljcyIsCiAgICAgICIwJSBjb21taXNzaW9uIOKAlCBhbHdheXMiLAogICAgXSwKICB9LAogIHsKICAgIHRpZXI6ICJwcm8iLAogICAgbmFtZTogIlByb2Zlc3Npb25hbCIsCiAgICBwcmljZTogNzksCiAgICBsaXN0aW5nX2xpbWl0OiAyNSwKICAgIHBvcHVsYXI6IHRydWUsCiAgICBmZWF0dXJlczogWwogICAgICAiVXAgdG8gMjUgcHJvcGVydHkgbGlzdGluZ3MiLAogICAgICAiUHJpb3JpdHkgc2VhcmNoIHBsYWNlbWVudCIsCiAgICAgICJQcmlvcml0eSBzdXBwb3J0IiwKICAgICAgIkFkdmFuY2VkIGFuYWx5dGljcyAmIHJlcG9ydHMiLAogICAgICAiSG91cmx5IGJvb2tpbmdzIGVuYWJsZWQiLAogICAgICAiQ3VzdG9tIGJvb2tpbmcgcnVsZXMiLAogICAgICAiMCUgY29tbWlzc2lvbiDigJQgYWx3YXlzIiwKICAgIF0sCiAgfSwKICB7CiAgICB0aWVyOiAicHJlbWl1bSIsCiAgICBuYW1lOiAiUHJlbWl1bSIsCiAgICBwcmljZTogMTk5LAogICAgbGlzdGluZ19saW1pdDogIlVubGltaXRlZCIsCiAgICBmZWF0dXJlczogWwogICAgICAiVW5saW1pdGVkIHByb3BlcnR5IGxpc3RpbmdzIiwKICAgICAgIlRvcCBzZWFyY2ggcGxhY2VtZW50IiwKICAgICAgIkRlZGljYXRlZCBhY2NvdW50IG1hbmFnZXIiLAogICAgICAiRnVsbCBhbmFseXRpY3Mgc3VpdGUiLAogICAgICAiQVBJIGFjY2VzcyIsCiAgICAgICJNdWx0aS1jYWxlbmRhciBzeW5jIiwKICAgICAgIldoaXRlLWxhYmVsIGJvb2tpbmcgcGFnZSIsCiAgICAgICIwJSBjb21taXNzaW9uIOKAlCBhbHdheXMiLAogICAgXSwKICB9LApdOwoKZXhwb3J0IGRlZmF1bHQgZnVuY3Rpb24gTWVtYmVyc2hpcFBhZ2UoKSB7CiAgY29uc3QgW2N1cnJlbnRQbGFuLCBzZXRDdXJyZW50UGxhbl0gPSB1c2VTdGF0ZTxzdHJpbmcgfCBudWxsPihudWxsKTsKICBjb25zdCBbbG9hZGluZywgc2V0TG9hZGluZ10gPSB1c2VTdGF0ZSh0cnVlKTsKICBjb25zdCBbYWN0aW9uTG9hZGluZywgc2V0QWN0aW9uTG9hZGluZ10gPSB1c2VTdGF0ZTxzdHJpbmcgfCBudWxsPihudWxsKTsKCiAgdXNlRWZmZWN0KCgpID0+IHsKICAgIGNvbnN0IGxvYWQgPSBhc3luYyAoKSA9PiB7CiAgICAgIHRyeSB7CiAgICAgICAgY29uc3QgcmVzID0gYXdhaXQgbWVtYmVyc2hpcEFwaS5nZXRDdXJyZW50KCk7CiAgICAgICAgc2V0Q3VycmVudFBsYW4ocmVzPy5kYXRhPy5wbGFuX3R5cGUgfHwgbnVsbCk7CiAgICAgIH0gY2F0Y2ggewogICAgICAgIHNldEN1cnJlbnRQbGFuKG51bGwpOwogICAgICB9IGZpbmFsbHkgewogICAgICAgIHNldExvYWRpbmcoZmFsc2UpOwogICAgICB9CiAgICB9OwogICAgbG9hZCgpOwogIH0sIFtdKTsKCiAgY29uc3QgaGFuZGxlU3Vic2NyaWJlID0gYXN5bmMgKHRpZXI6IHN0cmluZykgPT4gewogICAgc2V0QWN0aW9uTG9hZGluZyh0aWVyKTsKICAgIHRyeSB7CiAgICAgIGF3YWl0IG1lbWJlcnNoaXBBcGkuc3Vic2NyaWJlKHRpZXIsICJwbGFjZWhvbGRlcl90b2tlbiIpOwogICAgICBzZXRDdXJyZW50UGxhbih0aWVyKTsKICAgICAgdG9hc3Quc3VjY2VzcygKICAgICAgICBjdXJyZW50UGxhbgogICAgICAgICAgPyBgU3dpdGNoZWQgdG8gJHt0aWVyfSBwbGFuIWAKICAgICAgICAgIDogYFN1YnNjcmliZWQgdG8gJHt0aWVyfSBwbGFuIWAKICAgICAgKTsKICAgIH0gY2F0Y2ggKGVycjogdW5rbm93bikgewogICAgICBjb25zdCBheGlvc0VyciA9IGVyciBhcyB7IHJlc3BvbnNlPzogeyBkYXRhPzogeyBkZXRhaWw/OiBzdHJpbmcgfSB9IH07CiAgICAgIGNvbnN0IGRldGFpbCA9IGF4aW9zRXJyPy5yZXNwb25zZT8uZGF0YT8uZGV0YWlsOwogICAgICB0b2FzdC5lcnJvcihkZXRhaWwgfHwgKGVyciBpbnN0YW5jZW9mIEVycm9yID8gZXJyLm1lc3NhZ2UgOiAiU3Vic2NyaXB0aW9uIGZhaWxlZCIpKTsKICAgIH0gZmluYWxseSB7CiAgICAgIHNldEFjdGlvbkxvYWRpbmcobnVsbCk7CiAgICB9CiAgfTsKCiAgY29uc3QgaGFuZGxlQ2FuY2VsID0gYXN5bmMgKCkgPT4gewogICAgaWYgKCFjb25maXJtKCJBcmUgeW91IHN1cmUgeW91IHdhbnQgdG8gY2FuY2VsIHlvdXIgbWVtYmVyc2hpcD8iKSkgcmV0dXJuOwogICAgdHJ5IHsKICAgICAgYXdhaXQgbWVtYmVyc2hpcEFwaS5jYW5jZWwoKTsKICAgICAgc2V0Q3VycmVudFBsYW4obnVsbCk7CiAgICAgIHRvYXN0LnN1Y2Nlc3MoIk1lbWJlcnNoaXAgY2FuY2VsbGVkIik7CiAgICB9IGNhdGNoIChlcnI6IHVua25vd24pIHsKICAgICAgdG9hc3QuZXJyb3IoZXJyIGluc3RhbmNlb2YgRXJyb3IgPyBlcnIubWVzc2FnZSA6ICJDYW5jZWwgZmFpbGVkIik7CiAgICB9CiAgfTsKCiAgaWYgKGxvYWRpbmcpIHsKICAgIHJldHVybiA8ZGl2IGNsYXNzTmFtZT0iZmxleCBqdXN0aWZ5LWNlbnRlciBweS0yMCI+PFNwaW5uZXIgc2l6ZT0ibGciIC8+PC9kaXY+OwogIH0KCiAgcmV0dXJuICgKICAgIDxkaXY+CiAgICAgIDxkaXYgY2xhc3NOYW1lPSJtYi04Ij4KICAgICAgICA8aDIgY2xhc3NOYW1lPSJ0ZXh0LXhsIGZvbnQtYm9sZCB0ZXh0LWdyYXktOTAwIj5NZW1iZXJzaGlwIFBsYW48L2gyPgogICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC1zbSB0ZXh0LWdyYXktNTAwIG10LTEiPgogICAgICAgICAgQ2hvb3NlIHRoZSBwbGFuIHRoYXQgZml0cyB5b3VyIGhvc3RpbmcgbmVlZHMuIFplcm8gY29tbWlzc2lvbnMgb24gZXZlcnkgcGxhbi4KICAgICAgICA8L3A+CiAgICAgIDwvZGl2PgoKICAgICAge2N1cnJlbnRQbGFuICYmICgKICAgICAgICA8ZGl2IGNsYXNzTmFtZT0icm91bmRlZC14bCBiZy1ncmVlbi01MCBib3JkZXIgYm9yZGVyLWdyZWVuLTIwMCBwLTQgbWItNiBmbGV4IGl0ZW1zLWNlbnRlciBqdXN0aWZ5LWJldHdlZW4iPgogICAgICAgICAgPGRpdj4KICAgICAgICAgICAgPHAgY2xhc3NOYW1lPSJ0ZXh0LXNtIGZvbnQtbWVkaXVtIHRleHQtZ3JlZW4tODAwIj4KICAgICAgICAgICAgICBDdXJyZW50IHBsYW46IDxzcGFuIGNsYXNzTmFtZT0iZm9udC1ib2xkIGNhcGl0YWxpemUiPntjdXJyZW50UGxhbn08L3NwYW4+CiAgICAgICAgICAgIDwvcD4KICAgICAgICAgICAgPHAgY2xhc3NOYW1lPSJ0ZXh0LXhzIHRleHQtZ3JlZW4tNjAwIG10LTAuNSI+WW91ciBtZW1iZXJzaGlwIGlzIGFjdGl2ZTwvcD4KICAgICAgICAgIDwvZGl2PgogICAgICAgICAgPEJ1dHRvbiB2YXJpYW50PSJvdXRsaW5lIiBzaXplPSJzbSIgb25DbGljaz17aGFuZGxlQ2FuY2VsfT4KICAgICAgICAgICAgQ2FuY2VsIFBsYW4KICAgICAgICAgIDwvQnV0dG9uPgogICAgICAgIDwvZGl2PgogICAgICApfQoKICAgICAgPGRpdiBjbGFzc05hbWU9ImdyaWQgZ3JpZC1jb2xzLTEgbWQ6Z3JpZC1jb2xzLTMgZ2FwLTYiPgogICAgICAgIHtwbGFucy5tYXAoKHBsYW4pID0+IHsKICAgICAgICAgIGNvbnN0IGlzQ3VycmVudCA9IGN1cnJlbnRQbGFuID09PSBwbGFuLnRpZXI7CiAgICAgICAgICByZXR1cm4gKAogICAgICAgICAgICA8ZGl2CiAgICAgICAgICAgICAga2V5PXtwbGFuLnRpZXJ9CiAgICAgICAgICAgICAgY2xhc3NOYW1lPXtgcmVsYXRpdmUgcm91bmRlZC14bCBib3JkZXItMiBwLTYgJHsKICAgICAgICAgICAgICAgIHBsYW4ucG9wdWxhcgogICAgICAgICAgICAgICAgICA/ICJib3JkZXItcm9zZS01MDAgc2hhZG93LWxnIgogICAgICAgICAgICAgICAgICA6IGlzQ3VycmVudAogICAgICAgICAgICAgICAgICA/ICJib3JkZXItZ3JlZW4tNTAwIgogICAgICAgICAgICAgICAgICA6ICJib3JkZXItZ3JheS0yMDAiCiAgICAgICAgICAgICAgfWB9CiAgICAgICAgICAgID4KICAgICAgICAgICAgICB7cGxhbi5wb3B1bGFyICYmICgKICAgICAgICAgICAgICAgIDxkaXYgY2xhc3NOYW1lPSJhYnNvbHV0ZSAtdG9wLTMgbGVmdC0xLzIgLXRyYW5zbGF0ZS14LTEvMiI+CiAgICAgICAgICAgICAgICAgIDxCYWRnZSB2YXJpYW50PSJlcnJvciI+TW9zdCBQb3B1bGFyPC9CYWRnZT4KICAgICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgICl9CgogICAgICAgICAgICAgIDxoMyBjbGFzc05hbWU9InRleHQtbGcgZm9udC1ib2xkIHRleHQtZ3JheS05MDAiPntwbGFuLm5hbWV9PC9oMz4KICAgICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0ibXQtMiBmbGV4IGl0ZW1zLWJhc2VsaW5lIGdhcC0xIj4KICAgICAgICAgICAgICAgIDxzcGFuIGNsYXNzTmFtZT0idGV4dC0zeGwgZm9udC1ib2xkIHRleHQtZ3JheS05MDAiPuKCuXtwbGFuLnByaWNlfTwvc3Bhbj4KICAgICAgICAgICAgICAgIDxzcGFuIGNsYXNzTmFtZT0idGV4dC1ncmF5LTUwMCI+L21vbnRoPC9zcGFuPgogICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC1zbSB0ZXh0LWdyYXktNTAwIG10LTEiPgogICAgICAgICAgICAgICAge3BsYW4ubGlzdGluZ19saW1pdCA9PT0gIlVubGltaXRlZCIKICAgICAgICAgICAgICAgICAgPyAiVW5saW1pdGVkIGxpc3RpbmdzIgogICAgICAgICAgICAgICAgICA6IGBVcCB0byAke3BsYW4ubGlzdGluZ19saW1pdH0gbGlzdGluZ3NgfQogICAgICAgICAgICAgIDwvcD4KCiAgICAgICAgICAgICAgPHVsIGNsYXNzTmFtZT0ibXQtNiBzcGFjZS15LTIiPgogICAgICAgICAgICAgICAge3BsYW4uZmVhdHVyZXMubWFwKChmKSA9PiAoCiAgICAgICAgICAgICAgICAgIDxsaSBrZXk9e2Z9IGNsYXNzTmFtZT0iZmxleCBpdGVtcy1zdGFydCBnYXAtMiB0ZXh0LXNtIHRleHQtZ3JheS02MDAiPgogICAgICAgICAgICAgICAgICAgIDxzcGFuIGNsYXNzTmFtZT0idGV4dC1ncmVlbi01MDAgc2hyaW5rLTAgbXQtMC41Ij7inJM8L3NwYW4+CiAgICAgICAgICAgICAgICAgICAge2Z9CiAgICAgICAgICAgICAgICAgIDwvbGk+CiAgICAgICAgICAgICAgICApKX0KICAgICAgICAgICAgICA8L3VsPgoKICAgICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0ibXQtNiI+CiAgICAgICAgICAgICAgICB7aXNDdXJyZW50ID8gKAogICAgICAgICAgICAgICAgICA8QnV0dG9uIGZ1bGxXaWR0aCB2YXJpYW50PSJvdXRsaW5lIiBkaXNhYmxlZD4KICAgICAgICAgICAgICAgICAgICBDdXJyZW50IFBsYW4KICAgICAgICAgICAgICAgICAgPC9CdXR0b24+CiAgICAgICAgICAgICAgICApIDogKAogICAgICAgICAgICAgICAgICA8QnV0dG9uCiAgICAgICAgICAgICAgICAgICAgZnVsbFdpZHRoCiAgICAgICAgICAgICAgICAgICAgdmFyaWFudD17cGxhbi5wb3B1bGFyID8gInByaW1hcnkiIDogIm91dGxpbmUifQogICAgICAgICAgICAgICAgICAgIGxvYWRpbmc9e2FjdGlvbkxvYWRpbmcgPT09IHBsYW4udGllcn0KICAgICAgICAgICAgICAgICAgICBvbkNsaWNrPXsoKSA9PiBoYW5kbGVTdWJzY3JpYmUocGxhbi50aWVyKX0KICAgICAgICAgICAgICAgICAgPgogICAgICAgICAgICAgICAgICAgIHtjdXJyZW50UGxhbiA/ICJTd2l0Y2ggUGxhbiIgOiAiU3Vic2NyaWJlIn0KICAgICAgICAgICAgICAgICAgPC9CdXR0b24+CiAgICAgICAgICAgICAgICApfQogICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICA8L2Rpdj4KICAgICAgICAgICk7CiAgICAgICAgfSl9CiAgICAgIDwvZGl2PgoKICAgICAgPGRpdiBjbGFzc05hbWU9Im10LTggdGV4dC1jZW50ZXIgdGV4dC1zbSB0ZXh0LWdyYXktNTAwIj4KICAgICAgICBBbGwgcGxhbnMgaW5jbHVkZSA8c3Ryb25nPjAlIGNvbW1pc3Npb248L3N0cm9uZz4gb24gYWxsIGJvb2tpbmdzLgogICAgICAgIFlvdSBrZWVwIDEwMCUgb2YgeW91ciByZXZlbnVlLgogICAgICA8L2Rpdj4KICAgIDwvZGl2PgogICk7Cn0K</t>
+    <t>LyoqCiAqIEBtb2R1bGUgTWVtYmVyc2hpcFBhZ2UKICogQGRlc2NyaXB0aW9uIEhvc3QgbWVtYmVyc2hpcCB0aWVyIG1hbmFnZW1lbnQgcGFnZSBzaG93aW5nIGN1cnJlbnQgcGxhbiwgdGllciBjb21wYXJpc29uLCBhbmQgdXBncmFkZSBmbG93LgogKi8KInVzZSBjbGllbnQiOwoKaW1wb3J0IFJlYWN0LCB7IHVzZUVmZmVjdCwgdXNlU3RhdGUgfSBmcm9tICJyZWFjdCI7CmltcG9ydCBCdXR0b24gZnJvbSAiQC9jb21wb25lbnRzL3VpL2J1dHRvbiI7CmltcG9ydCB7IEJhZGdlLCBDYXJkLCBTcGlubmVyIH0gZnJvbSAiQC9jb21wb25lbnRzL3VpL2luZGV4IjsKaW1wb3J0IHsgdG9hc3QgfSBmcm9tICJAL2NvbXBvbmVudHMvdWkvdG9hc3QiOwppbXBvcnQgeyBtZW1iZXJzaGlwQXBpIH0gZnJvbSAiQC9saWIvYXBpIjsKCmludGVyZmFjZSBNZW1iZXJzaGlwUGxhbiB7CiAgdGllcjogc3RyaW5nOwogIG5hbWU6IHN0cmluZzsKICBwcmljZTogbnVtYmVyOwogIGZlYXR1cmVzOiBzdHJpbmdbXTsKICBsaXN0aW5nX2xpbWl0OiBudW1iZXIgfCAiVW5saW1pdGVkIjsKICBwb3B1bGFyPzogYm9vbGVhbjsKfQoKY29uc3QgcGxhbnM6IE1lbWJlcnNoaXBQbGFuW10gPSBbCiAgewogICAgdGllcjogImJhc2ljIiwKICAgIG5hbWU6ICJCYXNpYyIsCiAgICBwcmljZTogMjQ5OSwKICAgIGxpc3RpbmdfbGltaXQ6IDUsCiAgICBmZWF0dXJlczogWwogICAgICAiVXAgdG8gNSBwcm9wZXJ0eSBsaXN0aW5ncyIsCiAgICAgICJTdGFuZGFyZCBzZWFyY2ggcGxhY2VtZW50IiwKICAgICAgIkVtYWlsIHN1cHBvcnQiLAogICAgICAiQmFzaWMgYW5hbHl0aWNzIiwKICAgICAgIjAlIGNvbW1pc3Npb24g4oCUIGFsd2F5cyIsCiAgICBdLAogIH0sCiAgewogICAgdGllcjogInBybyIsCiAgICBuYW1lOiAiUHJvZmVzc2lvbmFsIiwKICAgIHByaWNlOiA2NDk5LAogICAgbGlzdGluZ19saW1pdDogMjUsCiAgICBwb3B1bGFyOiB0cnVlLAogICAgZmVhdHVyZXM6IFsKICAgICAgIlVwIHRvIDI1IHByb3BlcnR5IGxpc3RpbmdzIiwKICAgICAgIlByaW9yaXR5IHNlYXJjaCBwbGFjZW1lbnQiLAogICAgICAiUHJpb3JpdHkgc3VwcG9ydCIsCiAgICAgICJBZHZhbmNlZCBhbmFseXRpY3MgJiByZXBvcnRzIiwKICAgICAgIkhvdXJseSBib29raW5ncyBlbmFibGVkIiwKICAgICAgIkN1c3RvbSBib29raW5nIHJ1bGVzIiwKICAgICAgIjAlIGNvbW1pc3Npb24g4oCUIGFsd2F5cyIsCiAgICBdLAogIH0sCiAgewogICAgdGllcjogInByZW1pdW0iLAogICAgbmFtZTogIlByZW1pdW0iLAogICAgcHJpY2U6IDE2NDk5LAogICAgbGlzdGluZ19saW1pdDogIlVubGltaXRlZCIsCiAgICBmZWF0dXJlczogWwogICAgICAiVW5saW1pdGVkIHByb3BlcnR5IGxpc3RpbmdzIiwKICAgICAgIlRvcCBzZWFyY2ggcGxhY2VtZW50IiwKICAgICAgIkRlZGljYXRlZCBhY2NvdW50IG1hbmFnZXIiLAogICAgICAiRnVsbCBhbmFseXRpY3Mgc3VpdGUiLAogICAgICAiQVBJIGFjY2VzcyIsCiAgICAgICJNdWx0aS1jYWxlbmRhciBzeW5jIiwKICAgICAgIldoaXRlLWxhYmVsIGJvb2tpbmcgcGFnZSIsCiAgICAgICIwJSBjb21taXNzaW9uIOKAlCBhbHdheXMiLAogICAgXSwKICB9LApdOwoKZXhwb3J0IGRlZmF1bHQgZnVuY3Rpb24gTWVtYmVyc2hpcFBhZ2UoKSB7CiAgY29uc3QgW2N1cnJlbnRQbGFuLCBzZXRDdXJyZW50UGxhbl0gPSB1c2VTdGF0ZTxzdHJpbmcgfCBudWxsPihudWxsKTsKICBjb25zdCBbbG9hZGluZywgc2V0TG9hZGluZ10gPSB1c2VTdGF0ZSh0cnVlKTsKICBjb25zdCBbYWN0aW9uTG9hZGluZywgc2V0QWN0aW9uTG9hZGluZ10gPSB1c2VTdGF0ZTxzdHJpbmcgfCBudWxsPihudWxsKTsKCiAgdXNlRWZmZWN0KCgpID0+IHsKICAgIGNvbnN0IGxvYWQgPSBhc3luYyAoKSA9PiB7CiAgICAgIHRyeSB7CiAgICAgICAgY29uc3QgcmVzID0gYXdhaXQgbWVtYmVyc2hpcEFwaS5nZXRDdXJyZW50KCk7CiAgICAgICAgc2V0Q3VycmVudFBsYW4ocmVzPy5kYXRhPy5wbGFuX3R5cGUgfHwgbnVsbCk7CiAgICAgIH0gY2F0Y2ggewogICAgICAgIHNldEN1cnJlbnRQbGFuKG51bGwpOwogICAgICB9IGZpbmFsbHkgewogICAgICAgIHNldExvYWRpbmcoZmFsc2UpOwogICAgICB9CiAgICB9OwogICAgbG9hZCgpOwogIH0sIFtdKTsKCiAgY29uc3QgaGFuZGxlU3Vic2NyaWJlID0gYXN5bmMgKHRpZXI6IHN0cmluZykgPT4gewogICAgc2V0QWN0aW9uTG9hZGluZyh0aWVyKTsKICAgIHRyeSB7CiAgICAgIGF3YWl0IG1lbWJlcnNoaXBBcGkuc3Vic2NyaWJlKHRpZXIsICJwbGFjZWhvbGRlcl90b2tlbiIpOwogICAgICBzZXRDdXJyZW50UGxhbih0aWVyKTsKICAgICAgdG9hc3Quc3VjY2VzcygKICAgICAgICBjdXJyZW50UGxhbgogICAgICAgICAgPyBgU3dpdGNoZWQgdG8gJHt0aWVyfSBwbGFuIWAKICAgICAgICAgIDogYFN1YnNjcmliZWQgdG8gJHt0aWVyfSBwbGFuIWAKICAgICAgKTsKICAgIH0gY2F0Y2ggKGVycjogdW5rbm93bikgewogICAgICBjb25zdCBheGlvc0VyciA9IGVyciBhcyB7IHJlc3BvbnNlPzogeyBkYXRhPzogeyBkZXRhaWw/OiBzdHJpbmcgfSB9IH07CiAgICAgIGNvbnN0IGRldGFpbCA9IGF4aW9zRXJyPy5yZXNwb25zZT8uZGF0YT8uZGV0YWlsOwogICAgICB0b2FzdC5lcnJvcihkZXRhaWwgfHwgKGVyciBpbnN0YW5jZW9mIEVycm9yID8gZXJyLm1lc3NhZ2UgOiAiU3Vic2NyaXB0aW9uIGZhaWxlZCIpKTsKICAgIH0gZmluYWxseSB7CiAgICAgIHNldEFjdGlvbkxvYWRpbmcobnVsbCk7CiAgICB9CiAgfTsKCiAgY29uc3QgaGFuZGxlQ2FuY2VsID0gYXN5bmMgKCkgPT4gewogICAgaWYgKCFjb25maXJtKCJBcmUgeW91IHN1cmUgeW91IHdhbnQgdG8gY2FuY2VsIHlvdXIgbWVtYmVyc2hpcD8iKSkgcmV0dXJuOwogICAgdHJ5IHsKICAgICAgYXdhaXQgbWVtYmVyc2hpcEFwaS5jYW5jZWwoKTsKICAgICAgc2V0Q3VycmVudFBsYW4obnVsbCk7CiAgICAgIHRvYXN0LnN1Y2Nlc3MoIk1lbWJlcnNoaXAgY2FuY2VsbGVkIik7CiAgICB9IGNhdGNoIChlcnI6IHVua25vd24pIHsKICAgICAgdG9hc3QuZXJyb3IoZXJyIGluc3RhbmNlb2YgRXJyb3IgPyBlcnIubWVzc2FnZSA6ICJDYW5jZWwgZmFpbGVkIik7CiAgICB9CiAgfTsKCiAgaWYgKGxvYWRpbmcpIHsKICAgIHJldHVybiA8ZGl2IGNsYXNzTmFtZT0iZmxleCBqdXN0aWZ5LWNlbnRlciBweS0yMCI+PFNwaW5uZXIgc2l6ZT0ibGciIC8+PC9kaXY+OwogIH0KCiAgcmV0dXJuICgKICAgIDxkaXY+CiAgICAgIDxkaXYgY2xhc3NOYW1lPSJtYi04Ij4KICAgICAgICA8aDIgY2xhc3NOYW1lPSJ0ZXh0LXhsIGZvbnQtYm9sZCB0ZXh0LWdyYXktOTAwIj5NZW1iZXJzaGlwIFBsYW48L2gyPgogICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC1zbSB0ZXh0LWdyYXktNTAwIG10LTEiPgogICAgICAgICAgQ2hvb3NlIHRoZSBwbGFuIHRoYXQgZml0cyB5b3VyIGhvc3RpbmcgbmVlZHMuIFplcm8gY29tbWlzc2lvbnMgb24gZXZlcnkgcGxhbi4KICAgICAgICA8L3A+CiAgICAgIDwvZGl2PgoKICAgICAge2N1cnJlbnRQbGFuICYmICgKICAgICAgICA8ZGl2IGNsYXNzTmFtZT0icm91bmRlZC14bCBiZy1ncmVlbi01MCBib3JkZXIgYm9yZGVyLWdyZWVuLTIwMCBwLTQgbWItNiBmbGV4IGl0ZW1zLWNlbnRlciBqdXN0aWZ5LWJldHdlZW4iPgogICAgICAgICAgPGRpdj4KICAgICAgICAgICAgPHAgY2xhc3NOYW1lPSJ0ZXh0LXNtIGZvbnQtbWVkaXVtIHRleHQtZ3JlZW4tODAwIj4KICAgICAgICAgICAgICBDdXJyZW50IHBsYW46IDxzcGFuIGNsYXNzTmFtZT0iZm9udC1ib2xkIGNhcGl0YWxpemUiPntjdXJyZW50UGxhbn08L3NwYW4+CiAgICAgICAgICAgIDwvcD4KICAgICAgICAgICAgPHAgY2xhc3NOYW1lPSJ0ZXh0LXhzIHRleHQtZ3JlZW4tNjAwIG10LTAuNSI+WW91ciBtZW1iZXJzaGlwIGlzIGFjdGl2ZTwvcD4KICAgICAgICAgIDwvZGl2PgogICAgICAgICAgPEJ1dHRvbiB2YXJpYW50PSJvdXRsaW5lIiBzaXplPSJzbSIgb25DbGljaz17aGFuZGxlQ2FuY2VsfT4KICAgICAgICAgICAgQ2FuY2VsIFBsYW4KICAgICAgICAgIDwvQnV0dG9uPgogICAgICAgIDwvZGl2PgogICAgICApfQoKICAgICAgPGRpdiBjbGFzc05hbWU9ImdyaWQgZ3JpZC1jb2xzLTEgbWQ6Z3JpZC1jb2xzLTMgZ2FwLTYiPgogICAgICAgIHtwbGFucy5tYXAoKHBsYW4pID0+IHsKICAgICAgICAgIGNvbnN0IGlzQ3VycmVudCA9IGN1cnJlbnRQbGFuID09PSBwbGFuLnRpZXI7CiAgICAgICAgICByZXR1cm4gKAogICAgICAgICAgICA8ZGl2CiAgICAgICAgICAgICAga2V5PXtwbGFuLnRpZXJ9CiAgICAgICAgICAgICAgY2xhc3NOYW1lPXtgcmVsYXRpdmUgcm91bmRlZC14bCBib3JkZXItMiBwLTYgJHsKICAgICAgICAgICAgICAgIHBsYW4ucG9wdWxhcgogICAgICAgICAgICAgICAgICA/ICJib3JkZXItcm9zZS01MDAgc2hhZG93LWxnIgogICAgICAgICAgICAgICAgICA6IGlzQ3VycmVudAogICAgICAgICAgICAgICAgICA/ICJib3JkZXItZ3JlZW4tNTAwIgogICAgICAgICAgICAgICAgICA6ICJib3JkZXItZ3JheS0yMDAiCiAgICAgICAgICAgICAgfWB9CiAgICAgICAgICAgID4KICAgICAgICAgICAgICB7cGxhbi5wb3B1bGFyICYmICgKICAgICAgICAgICAgICAgIDxkaXYgY2xhc3NOYW1lPSJhYnNvbHV0ZSAtdG9wLTMgbGVmdC0xLzIgLXRyYW5zbGF0ZS14LTEvMiI+CiAgICAgICAgICAgICAgICAgIDxCYWRnZSB2YXJpYW50PSJlcnJvciI+TW9zdCBQb3B1bGFyPC9CYWRnZT4KICAgICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgICl9CgogICAgICAgICAgICAgIDxoMyBjbGFzc05hbWU9InRleHQtbGcgZm9udC1ib2xkIHRleHQtZ3JheS05MDAiPntwbGFuLm5hbWV9PC9oMz4KICAgICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0ibXQtMiBmbGV4IGl0ZW1zLWJhc2VsaW5lIGdhcC0xIj4KICAgICAgICAgICAgICAgIDxzcGFuIGNsYXNzTmFtZT0idGV4dC0zeGwgZm9udC1ib2xkIHRleHQtZ3JheS05MDAiPuKCuXtwbGFuLnByaWNlfTwvc3Bhbj4KICAgICAgICAgICAgICAgIDxzcGFuIGNsYXNzTmFtZT0idGV4dC1ncmF5LTUwMCI+L21vbnRoPC9zcGFuPgogICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC1zbSB0ZXh0LWdyYXktNTAwIG10LTEiPgogICAgICAgICAgICAgICAge3BsYW4ubGlzdGluZ19saW1pdCA9PT0gIlVubGltaXRlZCIKICAgICAgICAgICAgICAgICAgPyAiVW5saW1pdGVkIGxpc3RpbmdzIgogICAgICAgICAgICAgICAgICA6IGBVcCB0byAke3BsYW4ubGlzdGluZ19saW1pdH0gbGlzdGluZ3NgfQogICAgICAgICAgICAgIDwvcD4KCiAgICAgICAgICAgICAgPHVsIGNsYXNzTmFtZT0ibXQtNiBzcGFjZS15LTIiPgogICAgICAgICAgICAgICAge3BsYW4uZmVhdHVyZXMubWFwKChmKSA9PiAoCiAgICAgICAgICAgICAgICAgIDxsaSBrZXk9e2Z9IGNsYXNzTmFtZT0iZmxleCBpdGVtcy1zdGFydCBnYXAtMiB0ZXh0LXNtIHRleHQtZ3JheS02MDAiPgogICAgICAgICAgICAgICAgICAgIDxzcGFuIGNsYXNzTmFtZT0idGV4dC1ncmVlbi01MDAgc2hyaW5rLTAgbXQtMC41Ij7inJM8L3NwYW4+CiAgICAgICAgICAgICAgICAgICAge2Z9CiAgICAgICAgICAgICAgICAgIDwvbGk+CiAgICAgICAgICAgICAgICApKX0KICAgICAgICAgICAgICA8L3VsPgoKICAgICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0ibXQtNiI+CiAgICAgICAgICAgICAgICB7aXNDdXJyZW50ID8gKAogICAgICAgICAgICAgICAgICA8QnV0dG9uIGZ1bGxXaWR0aCB2YXJpYW50PSJvdXRsaW5lIiBkaXNhYmxlZD4KICAgICAgICAgICAgICAgICAgICBDdXJyZW50IFBsYW4KICAgICAgICAgICAgICAgICAgPC9CdXR0b24+CiAgICAgICAgICAgICAgICApIDogKAogICAgICAgICAgICAgICAgICA8QnV0dG9uCiAgICAgICAgICAgICAgICAgICAgZnVsbFdpZHRoCiAgICAgICAgICAgICAgICAgICAgdmFyaWFudD17cGxhbi5wb3B1bGFyID8gInByaW1hcnkiIDogIm91dGxpbmUifQogICAgICAgICAgICAgICAgICAgIGxvYWRpbmc9e2FjdGlvbkxvYWRpbmcgPT09IHBsYW4udGllcn0KICAgICAgICAgICAgICAgICAgICBvbkNsaWNrPXsoKSA9PiBoYW5kbGVTdWJzY3JpYmUocGxhbi50aWVyKX0KICAgICAgICAgICAgICAgICAgPgogICAgICAgICAgICAgICAgICAgIHtjdXJyZW50UGxhbiA/ICJTd2l0Y2ggUGxhbiIgOiAiU3Vic2NyaWJlIn0KICAgICAgICAgICAgICAgICAgPC9CdXR0b24+CiAgICAgICAgICAgICAgICApfQogICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICA8L2Rpdj4KICAgICAgICAgICk7CiAgICAgICAgfSl9CiAgICAgIDwvZGl2PgoKICAgICAgPGRpdiBjbGFzc05hbWU9Im10LTggdGV4dC1jZW50ZXIgdGV4dC1zbSB0ZXh0LWdyYXktNTAwIj4KICAgICAgICBBbGwgcGxhbnMgaW5jbHVkZSA8c3Ryb25nPjAlIGNvbW1pc3Npb248L3N0cm9uZz4gb24gYWxsIGJvb2tpbmdzLgogICAgICAgIFlvdSBrZWVwIDEwMCUgb2YgeW91ciByZXZlbnVlLgogICAgICA8L2Rpdj4KICAgIDwvZGl2PgogICk7Cn0K</t>
   </si>
   <si>
     <t>frontend/src/app/dashboard/page.tsx</t>
@@ -3451,17 +3452,11 @@
   property_type: "apartment",
   address: "",
   city: "",
-  state: "",
-  country: "",
-  zip_code: "",
   latitude: "",
   longitude: "",
   nightly_price: "",
-  bedrooms: "1",
-  bathrooms: "1",
   max_guests: "2",
   amenities: [] as string[],
-  house_rules: "",
   // Hourly config
   enable_hourly: false,
   hourly_rate: "",
@@ -3644,21 +3639,6 @@
   value={form.property_type}
   onChange={(e) =&gt; update("property_type", e.target.value)}
   /&gt;
-  &lt;div className="grid grid-cols-3 gap-3"&gt;
-  &lt;Input
-  label="Bedrooms"
-  type="number"
-  min={0}
-  value={form.bedrooms}
-  onChange={(e) =&gt; update("bedrooms", e.target.value)}
-  /&gt;
-  &lt;Input
-  label="Bathrooms"
-  type="number"
-  min={1}
-  value={form.bathrooms}
-  onChange={(e) =&gt; update("bathrooms", e.target.value)}
-  /&gt;
   &lt;Input
   label="Max guests"
   type="number"
@@ -3668,7 +3648,6 @@
   onChange={(e) =&gt; update("max_guests", e.target.value)}
   error={errors.max_guests}
   /&gt;
-  &lt;/div&gt;
   {/* Amenities */}
   &lt;div&gt;
   &lt;label className="block text-sm font-medium text-gray-700 mb-2"&gt;
@@ -3703,32 +3682,12 @@
   onChange={(e) =&gt; update("address", e.target.value)}
   error={errors.address}
   /&gt;
-  &lt;div className="grid grid-cols-2 gap-3"&gt;
   &lt;Input
   label="City"
   value={form.city}
   onChange={(e) =&gt; update("city", e.target.value)}
   error={errors.city}
   /&gt;
-  &lt;Input
-  label="State / Province"
-  value={form.state}
-  onChange={(e) =&gt; update("state", e.target.value)}
-  /&gt;
-  &lt;/div&gt;
-  &lt;div className="grid grid-cols-2 gap-3"&gt;
-  &lt;Input
-  label="Country"
-  value={form.country}
-  onChange={(e) =&gt; update("country", e.target.value)}
-  error={errors.country}
-  /&gt;
-  &lt;Input
-  label="Zip code"
-  value={form.zip_code}
-  onChange={(e) =&gt; update("zip_code", e.target.value)}
-  /&gt;
-  &lt;/div&gt;
   &lt;div className="grid grid-cols-2 gap-3"&gt;
   &lt;Input
   label="Latitude (optional)"
@@ -3753,7 +3712,7 @@
   {step === 3 &amp;&amp; (
   &lt;div className="space-y-4"&gt;
   &lt;Input
-  label="Nightly price ($)"
+  label="Nightly price (₹)"
   type="number"
   min={1}
   placeholder="100"
@@ -3778,7 +3737,7 @@
   {form.enable_hourly &amp;&amp; (
   &lt;div className="grid grid-cols-3 gap-3 mt-3"&gt;
   &lt;Input
-  label="Hourly rate ($)"
+  label="Hourly rate (₹)"
   type="number"
   min={1}
   value={form.hourly_rate}
@@ -3801,13 +3760,6 @@
   &lt;/div&gt;
   )}
   &lt;/div&gt;
-  &lt;Textarea
-  label="House rules (optional)"
-  placeholder="No smoking, quiet hours after 10pm..."
-  rows={4}
-  value={form.house_rules}
-  onChange={(e) =&gt; update("house_rules", e.target.value)}
-  /&gt;
   &lt;/div&gt;
   )}
   {/* Step 4: Photos */}
@@ -3913,7 +3865,7 @@
  }</t>
   </si>
   <si>
-    <t>LyoqCiAqIEBtb2R1bGUgTmV3UHJvcGVydHlQYWdlCiAqIEBkZXNjcmlwdGlvbiBNdWx0aS1zdGVwIGZvcm0gZm9yIGhvc3RzIHRvIGNyZWF0ZSBhIG5ldyBwcm9wZXJ0eSBsaXN0aW5nLgogKi8KInVzZSBjbGllbnQiOwoKaW1wb3J0IFJlYWN0LCB7IHVzZVN0YXRlIH0gZnJvbSAicmVhY3QiOwppbXBvcnQgeyB1c2VSb3V0ZXIgfSBmcm9tICJuZXh0L25hdmlnYXRpb24iOwppbXBvcnQgQnV0dG9uIGZyb20gIkAvY29tcG9uZW50cy91aS9idXR0b24iOwppbXBvcnQgSW5wdXQgZnJvbSAiQC9jb21wb25lbnRzL3VpL2lucHV0IjsKaW1wb3J0IHsgU2VsZWN0LCBUZXh0YXJlYSB9IGZyb20gIkAvY29tcG9uZW50cy91aS9pbmRleCI7CmltcG9ydCB7IHRvYXN0IH0gZnJvbSAiQC9jb21wb25lbnRzL3VpL3RvYXN0IjsKaW1wb3J0IHsgcHJvcGVydHlBcGkgfSBmcm9tICJAL2xpYi9hcGkiOwoKY29uc3QgcHJvcGVydHlUeXBlcyA9IFsKICB7IHZhbHVlOiAiYXBhcnRtZW50IiwgbGFiZWw6ICJBcGFydG1lbnQiIH0sCiAgeyB2YWx1ZTogImhvdXNlIiwgbGFiZWw6ICJIb3VzZSIgfSwKICB7IHZhbHVlOiAidmlsbGEiLCBsYWJlbDogIlZpbGxhIiB9LAogIHsgdmFsdWU6ICJjYWJpbiIsIGxhYmVsOiAiQ2FiaW4iIH0sCiAgeyB2YWx1ZTogInN0dWRpbyIsIGxhYmVsOiAiU3R1ZGlvIiB9LAogIHsgdmFsdWU6ICJsb2Z0IiwgbGFiZWw6ICJMb2Z0IiB9LAogIHsgdmFsdWU6ICJjb3R0YWdlIiwgbGFiZWw6ICJDb3R0YWdlIiB9LAogIHsgdmFsdWU6ICJjb25kbyIsIGxhYmVsOiAiQ29uZG8iIH0sCl07Cgpjb25zdCBhbWVuaXR5T3B0aW9ucyA9IFsKICAiV2lGaSIsICJLaXRjaGVuIiwgIkZyZWUgUGFya2luZyIsICJQb29sIiwgIkhvdCBUdWIiLCAiQWlyIENvbmRpdGlvbmluZyIsCiAgIldhc2hlciIsICJEcnllciIsICJHeW0iLCAiUGV0IEZyaWVuZGx5IiwgIkRlZGljYXRlZCBXb3Jrc3BhY2UiLAogICJUViIsICJGaXJlcGxhY2UiLCAiQkJRIEdyaWxsIiwgIkVWIENoYXJnZXIiLCAiRWxldmF0b3IiLAogICJEb29ybWFuIiwgIlNlY3VyaXR5IENhbWVyYSIsICJTbW9rZSBBbGFybSIsICJGaXJzdCBBaWQgS2l0IiwKXTsKCmV4cG9ydCBkZWZhdWx0IGZ1bmN0aW9uIE5ld1Byb3BlcnR5UGFnZSgpIHsKICBjb25zdCByb3V0ZXIgPSB1c2VSb3V0ZXIoKTsKICBjb25zdCBbbG9hZGluZywgc2V0TG9hZGluZ10gPSB1c2VTdGF0ZShmYWxzZSk7CiAgY29uc3QgW3N0ZXAsIHNldFN0ZXBdID0gdXNlU3RhdGUoMSk7CiAgY29uc3QgW2Zvcm0sIHNldEZvcm1dID0gdXNlU3RhdGUoewogICAgdGl0bGU6ICIiLAogICAgZGVzY3JpcHRpb246ICIiLAogICAgcHJvcGVydHlfdHlwZTogImFwYXJ0bWVudCIsCiAgICBhZGRyZXNzOiAiIiwKICAgIGNpdHk6ICIiLAogICAgc3RhdGU6ICIiLAogICAgY291bnRyeTogIiIsCiAgICB6aXBfY29kZTogIiIsCiAgICBsYXRpdHVkZTogIiIsCiAgICBsb25naXR1ZGU6ICIiLAogICAgbmlnaHRseV9wcmljZTogIiIsCiAgICBiZWRyb29tczogIjEiLAogICAgYmF0aHJvb21zOiAiMSIsCiAgICBtYXhfZ3Vlc3RzOiAiMiIsCiAgICBhbWVuaXRpZXM6IFtdIGFzIHN0cmluZ1tdLAogICAgaG91c2VfcnVsZXM6ICIiLAogICAgLy8gSG91cmx5IGNvbmZpZwogICAgZW5hYmxlX2hvdXJseTogZmFsc2UsCiAgICBob3VybHlfcmF0ZTogIiIsCiAgICBtaW5faG91cnM6ICIyIiwKICAgIG1heF9ob3VyczogIjEyIiwKICB9KTsKICBjb25zdCBbZXJyb3JzLCBzZXRFcnJvcnNdID0gdXNlU3RhdGU8UmVjb3JkPHN0cmluZywgc3RyaW5nPj4oe30pOwogIGNvbnN0IFtpbWFnZXMsIHNldEltYWdlc10gPSB1c2VTdGF0ZTx7IGZpbGU6IEZpbGU7IHByZXZpZXc6IHN0cmluZzsgaXNQcmltYXJ5OiBib29sZWFuIH1bXT4oW10pOwoKICBjb25zdCB1cGRhdGUgPSAoZmllbGQ6IHN0cmluZywgdmFsdWU6IHVua25vd24pID0+CiAgICBzZXRGb3JtKChwcmV2KSA9PiAoeyAuLi5wcmV2LCBbZmllbGRdOiB2YWx1ZSB9KSk7CgogIGNvbnN0IHRvZ2dsZUFtZW5pdHkgPSAoYW1lbml0eTogc3RyaW5nKSA9PiB7CiAgICBjb25zdCBuZXh0ID0gZm9ybS5hbWVuaXRpZXMuaW5jbHVkZXMoYW1lbml0eSkKICAgICAgPyBmb3JtLmFtZW5pdGllcy5maWx0ZXIoKGEpID0+IGEgIT09IGFtZW5pdHkpCiAgICAgIDogWy4uLmZvcm0uYW1lbml0aWVzLCBhbWVuaXR5XTsKICAgIHVwZGF0ZSgiYW1lbml0aWVzIiwgbmV4dCk7CiAgfTsKCiAgY29uc3QgYWRkSW1hZ2VzID0gKGZpbGVzOiBGaWxlTGlzdCB8IG51bGwpID0+IHsKICAgIGlmICghZmlsZXMpIHJldHVybjsKICAgIGNvbnN0IG5ld0ltYWdlcyA9IEFycmF5LmZyb20oZmlsZXMpCiAgICAgIC5maWx0ZXIoKGYpID0+IGYudHlwZS5zdGFydHNXaXRoKCJpbWFnZS8iKSkKICAgICAgLm1hcCgoZmlsZSkgPT4gKHsKICAgICAgICBmaWxlLAogICAgICAgIHByZXZpZXc6IFVSTC5jcmVhdGVPYmplY3RVUkwoZmlsZSksCiAgICAgICAgaXNQcmltYXJ5OiBmYWxzZSwKICAgICAgfSkpOwogICAgc2V0SW1hZ2VzKChwcmV2KSA9PiB7CiAgICAgIGNvbnN0IGNvbWJpbmVkID0gWy4uLnByZXYsIC4uLm5ld0ltYWdlc107CiAgICAgIC8vIEF1dG8tc2V0IGZpcnN0IGltYWdlIGFzIHByaW1hcnkgaWYgbm9uZSBzZWxlY3RlZAogICAgICBpZiAoY29tYmluZWQubGVuZ3RoID4gMCAmJiAhY29tYmluZWQuc29tZSgoaW1nKSA9PiBpbWcuaXNQcmltYXJ5KSkgewogICAgICAgIGNvbWJpbmVkWzBdLmlzUHJpbWFyeSA9IHRydWU7CiAgICAgIH0KICAgICAgcmV0dXJuIGNvbWJpbmVkOwogICAgfSk7CiAgfTsKCiAgY29uc3QgcmVtb3ZlSW1hZ2UgPSAoaW5kZXg6IG51bWJlcikgPT4gewogICAgc2V0SW1hZ2VzKChwcmV2KSA9PiB7CiAgICAgIGNvbnN0IG5leHQgPSBwcmV2LmZpbHRlcigoXywgaSkgPT4gaSAhPT0gaW5kZXgpOwogICAgICAvLyBSZXZva2Ugb2JqZWN0IFVSTCB0byBmcmVlIG1lbW9yeQogICAgICBVUkwucmV2b2tlT2JqZWN0VVJMKHByZXZbaW5kZXhdLnByZXZpZXcpOwogICAgICAvLyBJZiByZW1vdmVkIGltYWdlIHdhcyBwcmltYXJ5LCBhc3NpZ24gdG8gZmlyc3QgcmVtYWluaW5nCiAgICAgIGlmIChwcmV2W2luZGV4XS5pc1ByaW1hcnkgJiYgbmV4dC5sZW5ndGggPiAwKSB7CiAgICAgICAgbmV4dFswXS5pc1ByaW1hcnkgPSB0cnVlOwogICAgICB9CiAgICAgIHJldHVybiBuZXh0OwogICAgfSk7CiAgfTsKCiAgY29uc3Qgc2V0UHJpbWFyeUltYWdlID0gKGluZGV4OiBudW1iZXIpID0+IHsKICAgIHNldEltYWdlcygocHJldikgPT4KICAgICAgcHJldi5tYXAoKGltZywgaSkgPT4gKHsgLi4uaW1nLCBpc1ByaW1hcnk6IGkgPT09IGluZGV4IH0pKQogICAgKTsKICB9OwoKICBjb25zdCB2YWxpZGF0ZVN0ZXAgPSAoczogbnVtYmVyKTogYm9vbGVhbiA9PiB7CiAgICBjb25zdCBlcnJzOiBSZWNvcmQ8c3RyaW5nLCBzdHJpbmc+ID0ge307CiAgICBpZiAocyA9PT0gMSkgewogICAgICBpZiAoIWZvcm0udGl0bGUudHJpbSgpKSBlcnJzLnRpdGxlID0gIlRpdGxlIGlzIHJlcXVpcmVkIjsKICAgICAgZWxzZSBpZiAoZm9ybS50aXRsZS50cmltKCkubGVuZ3RoIDwgMykgZXJycy50aXRsZSA9ICJUaXRsZSBtdXN0IGJlIGF0IGxlYXN0IDMgY2hhcmFjdGVycyI7CiAgICAgIGlmICghZm9ybS5kZXNjcmlwdGlvbi50cmltKCkpIGVycnMuZGVzY3JpcHRpb24gPSAiRGVzY3JpcHRpb24gaXMgcmVxdWlyZWQiOwogICAgICBlbHNlIGlmIChmb3JtLmRlc2NyaXB0aW9uLnRyaW0oKS5sZW5ndGggPCAxMCkgZXJycy5kZXNjcmlwdGlvbiA9ICJEZXNjcmlwdGlvbiBtdXN0IGJlIGF0IGxlYXN0IDEwIGNoYXJhY3RlcnMiOwogICAgICBpZiAocGFyc2VJbnQoZm9ybS5tYXhfZ3Vlc3RzKSA+IDUwKSBlcnJzLm1heF9ndWVzdHMgPSAiTWF4aW11bSA1MCBndWVzdHMgYWxsb3dlZCI7CiAgICB9CiAgICBpZiAocyA9PT0gMikgewogICAgICBpZiAoIWZvcm0uYWRkcmVzcy50cmltKCkpIGVycnMuYWRkcmVzcyA9ICJBZGRyZXNzIGlzIHJlcXVpcmVkIjsKICAgICAgZWxzZSBpZiAoZm9ybS5hZGRyZXNzLnRyaW0oKS5sZW5ndGggPCA1KSBlcnJzLmFkZHJlc3MgPSAiQWRkcmVzcyBtdXN0IGJlIGF0IGxlYXN0IDUgY2hhcmFjdGVycyI7CiAgICAgIGlmICghZm9ybS5jaXR5LnRyaW0oKSkgZXJycy5jaXR5ID0gIkNpdHkgaXMgcmVxdWlyZWQiOwogICAgfQogICAgaWYgKHMgPT09IDMpIHsKICAgICAgaWYgKCFmb3JtLm5pZ2h0bHlfcHJpY2UgfHwgcGFyc2VGbG9hdChmb3JtLm5pZ2h0bHlfcHJpY2UpIDw9IDApCiAgICAgICAgZXJycy5uaWdodGx5X3ByaWNlID0gIlZhbGlkIHByaWNlIHJlcXVpcmVkIjsKICAgIH0KICAgIHNldEVycm9ycyhlcnJzKTsKICAgIHJldHVybiBPYmplY3Qua2V5cyhlcnJzKS5sZW5ndGggPT09IDA7CiAgfTsKCiAgY29uc3QgaGFuZGxlU3VibWl0ID0gYXN5bmMgKCkgPT4gewogICAgaWYgKCF2YWxpZGF0ZVN0ZXAoMykpIHJldHVybjsKICAgIHNldExvYWRpbmcodHJ1ZSk7CiAgICB0cnkgewogICAgICBjb25zdCBwYXlsb2FkID0gewogICAgICAgIHRpdGxlOiBmb3JtLnRpdGxlLAogICAgICAgIGRlc2NyaXB0aW9uOiBmb3JtLmRlc2NyaXB0aW9uLAogICAgICAgIGFkZHJlc3M6IGZvcm0uYWRkcmVzcywKICAgICAgICBjaXR5OiBmb3JtLmNpdHksCiAgICAgICAgbGF0aXR1ZGU6IGZvcm0ubGF0aXR1ZGUgPyBwYXJzZUZsb2F0KGZvcm0ubGF0aXR1ZGUpIDogdW5kZWZpbmVkLAogICAgICAgIGxvbmdpdHVkZTogZm9ybS5sb25naXR1ZGUgPyBwYXJzZUZsb2F0KGZvcm0ubG9uZ2l0dWRlKSA6IHVuZGVmaW5lZCwKICAgICAgICBwcmljZV9wZXJfbmlnaHQ6IHBhcnNlRmxvYXQoZm9ybS5uaWdodGx5X3ByaWNlKSwKICAgICAgICBtYXhfZ3Vlc3RzOiBwYXJzZUludChmb3JtLm1heF9ndWVzdHMpLAogICAgICAgIGFtZW5pdGllczogZm9ybS5hbWVuaXRpZXMsCiAgICAgIH07CiAgICAgIGNvbnN0IGNyZWF0ZWQgPSBhd2FpdCBwcm9wZXJ0eUFwaS5jcmVhdGUocGF5bG9hZCk7CiAgICAgIGNvbnN0IHByb3BlcnR5SWQgPSBjcmVhdGVkLmRhdGEuaWQ7CgogICAgICAvLyBVcGxvYWQgaW1hZ2VzCiAgICAgIGlmIChpbWFnZXMubGVuZ3RoID4gMCkgewogICAgICAgIGZvciAoY29uc3QgaW1nIG9mIGltYWdlcykgewogICAgICAgICAgdHJ5IHsKICAgICAgICAgICAgYXdhaXQgcHJvcGVydHlBcGkudXBsb2FkSW1hZ2UocHJvcGVydHlJZCwgaW1nLmZpbGUsIGltZy5pc1ByaW1hcnkpOwogICAgICAgICAgfSBjYXRjaCB7CiAgICAgICAgICAgIHRvYXN0LmVycm9yKGBGYWlsZWQgdG8gdXBsb2FkICR7aW1nLmZpbGUubmFtZX1gKTsKICAgICAgICAgIH0KICAgICAgICB9CiAgICAgIH0KCiAgICAgIC8vIENvbmZpZ3VyZSBob3VybHkgYm9va2luZyB2aWEgc2VwYXJhdGUgZW5kcG9pbnQgaWYgZW5hYmxlZAogICAgICBpZiAoZm9ybS5lbmFibGVfaG91cmx5ICYmIGZvcm0uaG91cmx5X3JhdGUpIHsKICAgICAgICBhd2FpdCBwcm9wZXJ0eUFwaS5jb25maWd1cmVIb3VybHkocHJvcGVydHlJZCwgewogICAgICAgICAgaG91cmx5X3ByaWNlOiBwYXJzZUZsb2F0KGZvcm0uaG91cmx5X3JhdGUpLAogICAgICAgICAgbWluX2hvdXJzOiBwYXJzZUludChmb3JtLm1pbl9ob3VycyksCiAgICAgICAgICBtYXhfaG91cnM6IHBhcnNlSW50KGZvcm0ubWF4X2hvdXJzKSwKICAgICAgICB9KTsKICAgICAgfQoKICAgICAgdG9hc3Quc3VjY2VzcygiTGlzdGluZyBjcmVhdGVkISIpOwogICAgICByb3V0ZXIucHVzaChgL3Byb3BlcnRpZXMvJHtwcm9wZXJ0eUlkfWApOwogICAgfSBjYXRjaCAoZXJyOiB1bmtub3duKSB7CiAgICAgIC8vIEV4dHJhY3QgbWVzc2FnZSBmcm9tIEF4aW9zIGVycm9yIG9yIGdlbmVyaWMgRXJyb3IKICAgICAgY29uc3QgYXhpb3NFcnIgPSBlcnIgYXMgeyByZXNwb25zZT86IHsgc3RhdHVzPzogbnVtYmVyOyBkYXRhPzogeyBkZXRhaWw/OiBzdHJpbmcgfSB9IH07CiAgICAgIGNvbnN0IHN0YXR1cyA9IGF4aW9zRXJyPy5yZXNwb25zZT8uc3RhdHVzOwogICAgICBjb25zdCBkZXRhaWwgPSBheGlvc0Vycj8ucmVzcG9uc2U/LmRhdGE/LmRldGFpbDsKCiAgICAgIGlmIChzdGF0dXMgPT09IDQwMiB8fCBkZXRhaWw/LnRvTG93ZXJDYXNlKCkuaW5jbHVkZXMoIm1lbWJlcnNoaXAiKSkgewogICAgICAgIHRvYXN0LmVycm9yKCJBbiBhY3RpdmUgbWVtYmVyc2hpcCBpcyByZXF1aXJlZCB0byBjcmVhdGUgbGlzdGluZ3MuIFBsZWFzZSBzdWJzY3JpYmUgdG8gYSBwbGFuIGZpcnN0LiIpOwogICAgICB9IGVsc2UgewogICAgICAgIHRvYXN0LmVycm9yKGRldGFpbCB8fCAoZXJyIGluc3RhbmNlb2YgRXJyb3IgPyBlcnIubWVzc2FnZSA6ICJGYWlsZWQgdG8gY3JlYXRlIGxpc3RpbmciKSk7CiAgICAgIH0KICAgIH0gZmluYWxseSB7CiAgICAgIHNldExvYWRpbmcoZmFsc2UpOwogICAgfQogIH07CgogIHJldHVybiAoCiAgICA8ZGl2PgogICAgICA8aDIgY2xhc3NOYW1lPSJ0ZXh0LXhsIGZvbnQtYm9sZCB0ZXh0LWdyYXktOTAwIG1iLTIiPkNyZWF0ZSBOZXcgTGlzdGluZzwvaDI+CiAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC1zbSB0ZXh0LWdyYXktNTAwIG1iLTYiPgogICAgICAgIEZpbGwgaW4gdGhlIGRldGFpbHMgdG8gbGlzdCB5b3VyIHByb3BlcnR5IG9uIFN0YXlOZXN0LgogICAgICA8L3A+CgogICAgICB7LyogUHJvZ3Jlc3MgKi99CiAgICAgIDxkaXYgY2xhc3NOYW1lPSJmbGV4IGl0ZW1zLWNlbnRlciBnYXAtMiBtYi04Ij4KICAgICAgICB7WyJEZXRhaWxzIiwgIkxvY2F0aW9uIiwgIlByaWNpbmcgJiBSdWxlcyIsICJQaG90b3MiXS5tYXAoKGxhYmVsLCBpKSA9PiAoCiAgICAgICAgICA8UmVhY3QuRnJhZ21lbnQga2V5PXtsYWJlbH0+CiAgICAgICAgICAgIDxkaXYgY2xhc3NOYW1lPSJmbGV4IGl0ZW1zLWNlbnRlciBnYXAtMiI+CiAgICAgICAgICAgICAgPGRpdgogICAgICAgICAgICAgICAgY2xhc3NOYW1lPXtgaC04IHctOCByb3VuZGVkLWZ1bGwgZmxleCBpdGVtcy1jZW50ZXIganVzdGlmeS1jZW50ZXIgdGV4dC1zbSBmb250LW1lZGl1bSAkewogICAgICAgICAgICAgICAgICBzdGVwID4gaSArIDEKICAgICAgICAgICAgICAgICAgICA/ICJiZy1ncmVlbi0xMDAgdGV4dC1ncmVlbi03MDAiCiAgICAgICAgICAgICAgICAgICAgOiBzdGVwID09PSBpICsgMQogICAgICAgICAgICAgICAgICAgID8gImJnLXJvc2UtNjAwIHRleHQtd2hpdGUiCiAgICAgICAgICAgICAgICAgICAgOiAiYmctZ3JheS0xMDAgdGV4dC1ncmF5LTQwMCIKICAgICAgICAgICAgICAgIH1gfQogICAgICAgICAgICAgID4KICAgICAgICAgICAgICAgIHtzdGVwID4gaSArIDEgPyAi4pyTIiA6IGkgKyAxfQogICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgIDxzcGFuCiAgICAgICAgICAgICAgICBjbGFzc05hbWU9e2B0ZXh0LXNtIGZvbnQtbWVkaXVtIGhpZGRlbiBzbTpibG9jayAkewogICAgICAgICAgICAgICAgICBzdGVwID09PSBpICsgMSA/ICJ0ZXh0LWdyYXktOTAwIiA6ICJ0ZXh0LWdyYXktNDAwIgogICAgICAgICAgICAgICAgfWB9CiAgICAgICAgICAgICAgPgogICAgICAgICAgICAgICAge2xhYmVsfQogICAgICAgICAgICAgIDwvc3Bhbj4KICAgICAgICAgICAgPC9kaXY+CiAgICAgICAgICAgIHtpIDwgMyAmJiA8ZGl2IGNsYXNzTmFtZT0iZmxleC0xIGgtcHggYmctZ3JheS0yMDAiIC8+fQogICAgICAgICAgPC9SZWFjdC5GcmFnbWVudD4KICAgICAgICApKX0KICAgICAgPC9kaXY+CgogICAgICA8ZGl2IGNsYXNzTmFtZT0icm91bmRlZC14bCBib3JkZXIgYm9yZGVyLWdyYXktMjAwIGJnLXdoaXRlIHAtNiI+CiAgICAgICAgey8qIFN0ZXAgMTogRGV0YWlscyAqL30KICAgICAgICB7c3RlcCA9PT0gMSAmJiAoCiAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0ic3BhY2UteS00Ij4KICAgICAgICAgICAgPElucHV0CiAgICAgICAgICAgICAgbGFiZWw9IlByb3BlcnR5IHRpdGxlIgogICAgICAgICAgICAgIHBsYWNlaG9sZGVyPSJlLmcuLCBTdW5ueSBEb3dudG93biBMb2Z0IHdpdGggQ2l0eSBWaWV3cyIKICAgICAgICAgICAgICB2YWx1ZT17Zm9ybS50aXRsZX0KICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgidGl0bGUiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgZXJyb3I9e2Vycm9ycy50aXRsZX0KICAgICAgICAgICAgLz4KICAgICAgICAgICAgPFRleHRhcmVhCiAgICAgICAgICAgICAgbGFiZWw9IkRlc2NyaXB0aW9uIgogICAgICAgICAgICAgIHBsYWNlaG9sZGVyPSJEZXNjcmliZSB5b3VyIHByb3BlcnR5IOKAlCB3aGF0IG1ha2VzIGl0IHVuaXF1ZT8iCiAgICAgICAgICAgICAgcm93cz17NX0KICAgICAgICAgICAgICB2YWx1ZT17Zm9ybS5kZXNjcmlwdGlvbn0KICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgiZGVzY3JpcHRpb24iLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgZXJyb3I9e2Vycm9ycy5kZXNjcmlwdGlvbn0KICAgICAgICAgICAgLz4KICAgICAgICAgICAgPFNlbGVjdAogICAgICAgICAgICAgIGxhYmVsPSJQcm9wZXJ0eSB0eXBlIgogICAgICAgICAgICAgIG9wdGlvbnM9e3Byb3BlcnR5VHlwZXN9CiAgICAgICAgICAgICAgdmFsdWU9e2Zvcm0ucHJvcGVydHlfdHlwZX0KICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgicHJvcGVydHlfdHlwZSIsIGUudGFyZ2V0LnZhbHVlKX0KICAgICAgICAgICAgLz4KICAgICAgICAgICAgPGRpdiBjbGFzc05hbWU9ImdyaWQgZ3JpZC1jb2xzLTMgZ2FwLTMiPgogICAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgICAgbGFiZWw9IkJlZHJvb21zIgogICAgICAgICAgICAgICAgdHlwZT0ibnVtYmVyIgogICAgICAgICAgICAgICAgbWluPXswfQogICAgICAgICAgICAgICAgdmFsdWU9e2Zvcm0uYmVkcm9vbXN9CiAgICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgiYmVkcm9vbXMiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgICA8SW5wdXQKICAgICAgICAgICAgICAgIGxhYmVsPSJCYXRocm9vbXMiCiAgICAgICAgICAgICAgICB0eXBlPSJudW1iZXIiCiAgICAgICAgICAgICAgICBtaW49ezF9CiAgICAgICAgICAgICAgICB2YWx1ZT17Zm9ybS5iYXRocm9vbXN9CiAgICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgiYmF0aHJvb21zIiwgZS50YXJnZXQudmFsdWUpfQogICAgICAgICAgICAgIC8+CiAgICAgICAgICAgICAgPElucHV0CiAgICAgICAgICAgICAgICBsYWJlbD0iTWF4IGd1ZXN0cyIKICAgICAgICAgICAgICAgIHR5cGU9Im51bWJlciIKICAgICAgICAgICAgICAgIG1pbj17MX0KICAgICAgICAgICAgICAgIG1heD17NTB9CiAgICAgICAgICAgICAgICB2YWx1ZT17Zm9ybS5tYXhfZ3Vlc3RzfQogICAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoIm1heF9ndWVzdHMiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgICBlcnJvcj17ZXJyb3JzLm1heF9ndWVzdHN9CiAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgPC9kaXY+CgogICAgICAgICAgICB7LyogQW1lbml0aWVzICovfQogICAgICAgICAgICA8ZGl2PgogICAgICAgICAgICAgIDxsYWJlbCBjbGFzc05hbWU9ImJsb2NrIHRleHQtc20gZm9udC1tZWRpdW0gdGV4dC1ncmF5LTcwMCBtYi0yIj4KICAgICAgICAgICAgICAgIEFtZW5pdGllcwogICAgICAgICAgICAgIDwvbGFiZWw+CiAgICAgICAgICAgICAgPGRpdiBjbGFzc05hbWU9ImZsZXggZmxleC13cmFwIGdhcC0yIj4KICAgICAgICAgICAgICAgIHthbWVuaXR5T3B0aW9ucy5tYXAoKGFtZW5pdHkpID0+ICgKICAgICAgICAgICAgICAgICAgPGJ1dHRvbgogICAgICAgICAgICAgICAgICAgIGtleT17YW1lbml0eX0KICAgICAgICAgICAgICAgICAgICB0eXBlPSJidXR0b24iCiAgICAgICAgICAgICAgICAgICAgb25DbGljaz17KCkgPT4gdG9nZ2xlQW1lbml0eShhbWVuaXR5KX0KICAgICAgICAgICAgICAgICAgICBjbGFzc05hbWU9e2BweC0zIHB5LTEuNSByb3VuZGVkLWZ1bGwgdGV4dC1zbSBib3JkZXIgdHJhbnNpdGlvbiAkewogICAgICAgICAgICAgICAgICAgICAgZm9ybS5hbWVuaXRpZXMuaW5jbHVkZXMoYW1lbml0eSkKICAgICAgICAgICAgICAgICAgICAgICAgPyAiYmctcm9zZS01MCBib3JkZXItcm9zZS0zMDAgdGV4dC1yb3NlLTcwMCIKICAgICAgICAgICAgICAgICAgICAgICAgOiAiYm9yZGVyLWdyYXktMjAwIHRleHQtZ3JheS02MDAgaG92ZXI6Ym9yZGVyLWdyYXktMzAwIgogICAgICAgICAgICAgICAgICAgIH1gfQogICAgICAgICAgICAgICAgICA+CiAgICAgICAgICAgICAgICAgICAge2FtZW5pdHl9CiAgICAgICAgICAgICAgICAgIDwvYnV0dG9uPgogICAgICAgICAgICAgICAgKSl9CiAgICAgICAgICAgICAgPC9kaXY+CiAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgPC9kaXY+CiAgICAgICAgKX0KCiAgICAgICAgey8qIFN0ZXAgMjogTG9jYXRpb24gKi99CiAgICAgICAge3N0ZXAgPT09IDIgJiYgKAogICAgICAgICAgPGRpdiBjbGFzc05hbWU9InNwYWNlLXktNCI+CiAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgIGxhYmVsPSJTdHJlZXQgYWRkcmVzcyIKICAgICAgICAgICAgICBwbGFjZWhvbGRlcj0iMTIzIE1haW4gU3RyZWV0IgogICAgICAgICAgICAgIHZhbHVlPXtmb3JtLmFkZHJlc3N9CiAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoImFkZHJlc3MiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgZXJyb3I9e2Vycm9ycy5hZGRyZXNzfQogICAgICAgICAgICAvPgogICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iZ3JpZCBncmlkLWNvbHMtMiBnYXAtMyI+CiAgICAgICAgICAgICAgPElucHV0CiAgICAgICAgICAgICAgICBsYWJlbD0iQ2l0eSIKICAgICAgICAgICAgICAgIHZhbHVlPXtmb3JtLmNpdHl9CiAgICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgiY2l0eSIsIGUudGFyZ2V0LnZhbHVlKX0KICAgICAgICAgICAgICAgIGVycm9yPXtlcnJvcnMuY2l0eX0KICAgICAgICAgICAgICAvPgogICAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgICAgbGFiZWw9IlN0YXRlIC8gUHJvdmluY2UiCiAgICAgICAgICAgICAgICB2YWx1ZT17Zm9ybS5zdGF0ZX0KICAgICAgICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gdXBkYXRlKCJzdGF0ZSIsIGUudGFyZ2V0LnZhbHVlKX0KICAgICAgICAgICAgICAvPgogICAgICAgICAgICA8L2Rpdj4KICAgICAgICAgICAgPGRpdiBjbGFzc05hbWU9ImdyaWQgZ3JpZC1jb2xzLTIgZ2FwLTMiPgogICAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgICAgbGFiZWw9IkNvdW50cnkiCiAgICAgICAgICAgICAgICB2YWx1ZT17Zm9ybS5jb3VudHJ5fQogICAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoImNvdW50cnkiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgICBlcnJvcj17ZXJyb3JzLmNvdW50cnl9CiAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgICA8SW5wdXQKICAgICAgICAgICAgICAgIGxhYmVsPSJaaXAgY29kZSIKICAgICAgICAgICAgICAgIHZhbHVlPXtmb3JtLnppcF9jb2RlfQogICAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoInppcF9jb2RlIiwgZS50YXJnZXQudmFsdWUpfQogICAgICAgICAgICAgIC8+CiAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iZ3JpZCBncmlkLWNvbHMtMiBnYXAtMyI+CiAgICAgICAgICAgICAgPElucHV0CiAgICAgICAgICAgICAgICBsYWJlbD0iTGF0aXR1ZGUgKG9wdGlvbmFsKSIKICAgICAgICAgICAgICAgIHR5cGU9Im51bWJlciIKICAgICAgICAgICAgICAgIHN0ZXA9ImFueSIKICAgICAgICAgICAgICAgIHBsYWNlaG9sZGVyPSI0MC43MTI4IgogICAgICAgICAgICAgICAgdmFsdWU9e2Zvcm0ubGF0aXR1ZGV9CiAgICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgibGF0aXR1ZGUiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgICA8SW5wdXQKICAgICAgICAgICAgICAgIGxhYmVsPSJMb25naXR1ZGUgKG9wdGlvbmFsKSIKICAgICAgICAgICAgICAgIHR5cGU9Im51bWJlciIKICAgICAgICAgICAgICAgIHN0ZXA9ImFueSIKICAgICAgICAgICAgICAgIHBsYWNlaG9sZGVyPSItNzQuMDA2MCIKICAgICAgICAgICAgICAgIHZhbHVlPXtmb3JtLmxvbmdpdHVkZX0KICAgICAgICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gdXBkYXRlKCJsb25naXR1ZGUiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgPC9kaXY+CiAgICAgICAgICA8L2Rpdj4KICAgICAgICApfQoKICAgICAgICB7LyogU3RlcCAzOiBQcmljaW5nICYgUnVsZXMgKi99CiAgICAgICAge3N0ZXAgPT09IDMgJiYgKAogICAgICAgICAgPGRpdiBjbGFzc05hbWU9InNwYWNlLXktNCI+CiAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgIGxhYmVsPSJOaWdodGx5IHByaWNlICgkKSIKICAgICAgICAgICAgICB0eXBlPSJudW1iZXIiCiAgICAgICAgICAgICAgbWluPXsxfQogICAgICAgICAgICAgIHBsYWNlaG9sZGVyPSIxMDAiCiAgICAgICAgICAgICAgdmFsdWU9e2Zvcm0ubmlnaHRseV9wcmljZX0KICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgibmlnaHRseV9wcmljZSIsIGUudGFyZ2V0LnZhbHVlKX0KICAgICAgICAgICAgICBlcnJvcj17ZXJyb3JzLm5pZ2h0bHlfcHJpY2V9CiAgICAgICAgICAgIC8+CgogICAgICAgICAgICB7LyogSG91cmx5IGJvb2tpbmcgdG9nZ2xlICovfQogICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0icm91bmRlZC1sZyBib3JkZXIgYm9yZGVyLWdyYXktMjAwIHAtNCI+CiAgICAgICAgICAgICAgPGxhYmVsIGNsYXNzTmFtZT0iZmxleCBpdGVtcy1jZW50ZXIgZ2FwLTMiPgogICAgICAgICAgICAgICAgPGlucHV0CiAgICAgICAgICAgICAgICAgIHR5cGU9ImNoZWNrYm94IgogICAgICAgICAgICAgICAgICBjaGVja2VkPXtmb3JtLmVuYWJsZV9ob3VybHl9CiAgICAgICAgICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gdXBkYXRlKCJlbmFibGVfaG91cmx5IiwgZS50YXJnZXQuY2hlY2tlZCl9CiAgICAgICAgICAgICAgICAgIGNsYXNzTmFtZT0icm91bmRlZCBib3JkZXItZ3JheS0zMDAgdGV4dC1yb3NlLTYwMCBmb2N1czpyaW5nLXJvc2UtNTAwIgogICAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgICAgIDxkaXY+CiAgICAgICAgICAgICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC1zbSBmb250LW1lZGl1bSB0ZXh0LWdyYXktOTAwIj5FbmFibGUgaG91cmx5IGJvb2tpbmdzPC9wPgogICAgICAgICAgICAgICAgICA8cCBjbGFzc05hbWU9InRleHQteHMgdGV4dC1ncmF5LTUwMCI+QWxsb3cgZ3Vlc3RzIHRvIGJvb2sgYnkgdGhlIGhvdXI8L3A+CiAgICAgICAgICAgICAgICA8L2Rpdj4KICAgICAgICAgICAgICA8L2xhYmVsPgogICAgICAgICAgICAgIHtmb3JtLmVuYWJsZV9ob3VybHkgJiYgKAogICAgICAgICAgICAgICAgPGRpdiBjbGFzc05hbWU9ImdyaWQgZ3JpZC1jb2xzLTMgZ2FwLTMgbXQtMyI+CiAgICAgICAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgICAgICAgIGxhYmVsPSJIb3VybHkgcmF0ZSAoJCkiCiAgICAgICAgICAgICAgICAgICAgdHlwZT0ibnVtYmVyIgogICAgICAgICAgICAgICAgICAgIG1pbj17MX0KICAgICAgICAgICAgICAgICAgICB2YWx1ZT17Zm9ybS5ob3VybHlfcmF0ZX0KICAgICAgICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgiaG91cmx5X3JhdGUiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgICAgIC8+CiAgICAgICAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgICAgICAgIGxhYmVsPSJNaW4gaG91cnMiCiAgICAgICAgICAgICAgICAgICAgdHlwZT0ibnVtYmVyIgogICAgICAgICAgICAgICAgICAgIG1pbj17MX0KICAgICAgICAgICAgICAgICAgICB2YWx1ZT17Zm9ybS5taW5faG91cnN9CiAgICAgICAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoIm1pbl9ob3VycyIsIGUudGFyZ2V0LnZhbHVlKX0KICAgICAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgICAgICAgPElucHV0CiAgICAgICAgICAgICAgICAgICAgbGFiZWw9Ik1heCBob3VycyIKICAgICAgICAgICAgICAgICAgICB0eXBlPSJudW1iZXIiCiAgICAgICAgICAgICAgICAgICAgbWluPXsxfQogICAgICAgICAgICAgICAgICAgIHZhbHVlPXtmb3JtLm1heF9ob3Vyc30KICAgICAgICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgibWF4X2hvdXJzIiwgZS50YXJnZXQudmFsdWUpfQogICAgICAgICAgICAgICAgICAvPgogICAgICAgICAgICAgICAgPC9kaXY+CiAgICAgICAgICAgICAgKX0KICAgICAgICAgICAgPC9kaXY+CgogICAgICAgICAgICA8VGV4dGFyZWEKICAgICAgICAgICAgICBsYWJlbD0iSG91c2UgcnVsZXMgKG9wdGlvbmFsKSIKICAgICAgICAgICAgICBwbGFjZWhvbGRlcj0iTm8gc21va2luZywgcXVpZXQgaG91cnMgYWZ0ZXIgMTBwbS4uLiIKICAgICAgICAgICAgICByb3dzPXs0fQogICAgICAgICAgICAgIHZhbHVlPXtmb3JtLmhvdXNlX3J1bGVzfQogICAgICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gdXBkYXRlKCJob3VzZV9ydWxlcyIsIGUudGFyZ2V0LnZhbHVlKX0KICAgICAgICAgICAgLz4KICAgICAgICAgIDwvZGl2PgogICAgICAgICl9CgogICAgICAgIHsvKiBTdGVwIDQ6IFBob3RvcyAqL30KICAgICAgICB7c3RlcCA9PT0gNCAmJiAoCiAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0ic3BhY2UteS00Ij4KICAgICAgICAgICAgPGRpdj4KICAgICAgICAgICAgICA8bGFiZWwgY2xhc3NOYW1lPSJibG9jayB0ZXh0LXNtIGZvbnQtbWVkaXVtIHRleHQtZ3JheS03MDAgbWItMiI+CiAgICAgICAgICAgICAgICBQcm9wZXJ0eSBQaG90b3MKICAgICAgICAgICAgICA8L2xhYmVsPgogICAgICAgICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC14cyB0ZXh0LWdyYXktNTAwIG1iLTMiPgogICAgICAgICAgICAgICAgVXBsb2FkIGhpZ2gtcXVhbGl0eSBpbWFnZXMuIFRoZSBmaXJzdCBpbWFnZSAob3IgdGhlIG9uZSB5b3UgbWFyaykgd2lsbCBiZSB0aGUgY292ZXIgcGhvdG8uCiAgICAgICAgICAgICAgPC9wPgogICAgICAgICAgICAgIDxsYWJlbCBjbGFzc05hbWU9ImZsZXggZmxleC1jb2wgaXRlbXMtY2VudGVyIGp1c3RpZnktY2VudGVyIHctZnVsbCBoLTQwIGJvcmRlci0yIGJvcmRlci1kYXNoZWQgYm9yZGVyLWdyYXktMzAwIHJvdW5kZWQteGwgY3Vyc29yLXBvaW50ZXIgaG92ZXI6Ym9yZGVyLXJvc2UtNDAwIGhvdmVyOmJnLXJvc2UtNTAgdHJhbnNpdGlvbiI+CiAgICAgICAgICAgICAgICA8c3ZnCiAgICAgICAgICAgICAgICAgIGNsYXNzTmFtZT0iaC0xMCB3LTEwIHRleHQtZ3JheS00MDAgbWItMiIKICAgICAgICAgICAgICAgICAgZmlsbD0ibm9uZSIKICAgICAgICAgICAgICAgICAgdmlld0JveD0iMCAwIDI0IDI0IgogICAgICAgICAgICAgICAgICBzdHJva2U9ImN1cnJlbnRDb2xvciIKICAgICAgICAgICAgICAgID4KICAgICAgICAgICAgICAgICAgPHBhdGgKICAgICAgICAgICAgICAgICAgICBzdHJva2VMaW5lY2FwPSJyb3VuZCIKICAgICAgICAgICAgICAgICAgICBzdHJva2VMaW5lam9pbj0icm91bmQiCiAgICAgICAgICAgICAgICAgICAgc3Ryb2tlV2lkdGg9ezEuNX0KICAgICAgICAgICAgICAgICAgICBkPSJNMTIgMTZ2LThtMCAwbC0zIDNtMy0zbDMgM000IDE2djFhMyAzIDAgMDAzIDNoMTBhMyAzIDAgMDAzLTN2LTEiCiAgICAgICAgICAgICAgICAgIC8+CiAgICAgICAgICAgICAgICA8L3N2Zz4KICAgICAgICAgICAgICAgIDxzcGFuIGNsYXNzTmFtZT0idGV4dC1zbSB0ZXh0LWdyYXktNTAwIj5DbGljayB0byB1cGxvYWQgaW1hZ2VzPC9zcGFuPgogICAgICAgICAgICAgICAgPHNwYW4gY2xhc3NOYW1lPSJ0ZXh0LXhzIHRleHQtZ3JheS00MDAgbXQtMSI+SlBHLCBQTkcsIFdlYlAg4oCUIG1heCAxMCBNQiBlYWNoPC9zcGFuPgogICAgICAgICAgICAgICAgPGlucHV0CiAgICAgICAgICAgICAgICAgIHR5cGU9ImZpbGUiCiAgICAgICAgICAgICAgICAgIGFjY2VwdD0iaW1hZ2UvKiIKICAgICAgICAgICAgICAgICAgbXVsdGlwbGUKICAgICAgICAgICAgICAgICAgY2xhc3NOYW1lPSJoaWRkZW4iCiAgICAgICAgICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gYWRkSW1hZ2VzKGUudGFyZ2V0LmZpbGVzKX0KICAgICAgICAgICAgICAgIC8+CiAgICAgICAgICAgICAgPC9sYWJlbD4KICAgICAgICAgICAgPC9kaXY+CgogICAgICAgICAgICB7aW1hZ2VzLmxlbmd0aCA+IDAgJiYgKAogICAgICAgICAgICAgIDxkaXYgY2xhc3NOYW1lPSJncmlkIGdyaWQtY29scy0yIHNtOmdyaWQtY29scy0zIGdhcC00Ij4KICAgICAgICAgICAgICAgIHtpbWFnZXMubWFwKChpbWcsIGkpID0+ICgKICAgICAgICAgICAgICAgICAgPGRpdgogICAgICAgICAgICAgICAgICAgIGtleT17aW1nLnByZXZpZXd9CiAgICAgICAgICAgICAgICAgICAgY2xhc3NOYW1lPXtgcmVsYXRpdmUgZ3JvdXAgcm91bmRlZC1sZyBvdmVyZmxvdy1oaWRkZW4gYm9yZGVyLTIgJHsKICAgICAgICAgICAgICAgICAgICAgIGltZy5pc1ByaW1hcnkgPyAiYm9yZGVyLXJvc2UtNTAwIiA6ICJib3JkZXItZ3JheS0yMDAiCiAgICAgICAgICAgICAgICAgICAgfWB9CiAgICAgICAgICAgICAgICAgID4KICAgICAgICAgICAgICAgICAgICA8aW1nCiAgICAgICAgICAgICAgICAgICAgICBzcmM9e2ltZy5wcmV2aWV3fQogICAgICAgICAgICAgICAgICAgICAgYWx0PXtgVXBsb2FkICR7aSArIDF9YH0KICAgICAgICAgICAgICAgICAgICAgIGNsYXNzTmFtZT0idy1mdWxsIGgtMzIgb2JqZWN0LWNvdmVyIgogICAgICAgICAgICAgICAgICAgIC8+CiAgICAgICAgICAgICAgICAgICAge2ltZy5pc1ByaW1hcnkgJiYgKAogICAgICAgICAgICAgICAgICAgICAgPHNwYW4gY2xhc3NOYW1lPSJhYnNvbHV0ZSB0b3AtMS41IGxlZnQtMS41IGJnLXJvc2UtNjAwIHRleHQtd2hpdGUgdGV4dC14cyBmb250LW1lZGl1bSBweC0yIHB5LTAuNSByb3VuZGVkLWZ1bGwiPgogICAgICAgICAgICAgICAgICAgICAgICBDb3ZlcgogICAgICAgICAgICAgICAgICAgICAgPC9zcGFuPgogICAgICAgICAgICAgICAgICAgICl9CiAgICAgICAgICAgICAgICAgICAgPGRpdiBjbGFzc05hbWU9ImFic29sdXRlIGluc2V0LTAgYmctYmxhY2svMCBncm91cC1ob3ZlcjpiZy1ibGFjay80MCB0cmFuc2l0aW9uIGZsZXggaXRlbXMtY2VudGVyIGp1c3RpZnktY2VudGVyIGdhcC0yIG9wYWNpdHktMCBncm91cC1ob3ZlcjpvcGFjaXR5LTEwMCI+CiAgICAgICAgICAgICAgICAgICAgICB7IWltZy5pc1ByaW1hcnkgJiYgKAogICAgICAgICAgICAgICAgICAgICAgICA8YnV0dG9uCiAgICAgICAgICAgICAgICAgICAgICAgICAgdHlwZT0iYnV0dG9uIgogICAgICAgICAgICAgICAgICAgICAgICAgIG9uQ2xpY2s9eygpID0+IHNldFByaW1hcnlJbWFnZShpKX0KICAgICAgICAgICAgICAgICAgICAgICAgICBjbGFzc05hbWU9ImJnLXdoaXRlIHRleHQtZ3JheS03MDAgdGV4dC14cyBmb250LW1lZGl1bSBweC0yIHB5LTEgcm91bmRlZC1tZCBob3ZlcjpiZy1ncmF5LTEwMCIKICAgICAgICAgICAgICAgICAgICAgICAgPgogICAgICAgICAgICAgICAgICAgICAgICAgIFNldCBDb3ZlcgogICAgICAgICAgICAgICAgICAgICAgICA8L2J1dHRvbj4KICAgICAgICAgICAgICAgICAgICAgICl9CiAgICAgICAgICAgICAgICAgICAgICA8YnV0dG9uCiAgICAgICAgICAgICAgICAgICAgICAgIHR5cGU9ImJ1dHRvbiIKICAgICAgICAgICAgICAgICAgICAgICAgb25DbGljaz17KCkgPT4gcmVtb3ZlSW1hZ2UoaSl9CiAgICAgICAgICAgICAgICAgICAgICAgIGNsYXNzTmFtZT0iYmctd2hpdGUgdGV4dC1yZWQtNjAwIHRleHQteHMgZm9udC1tZWRpdW0gcHgtMiBweS0xIHJvdW5kZWQtbWQgaG92ZXI6YmctcmVkLTUwIgogICAgICAgICAgICAgICAgICAgICAgPgogICAgICAgICAgICAgICAgICAgICAgICBSZW1vdmUKICAgICAgICAgICAgICAgICAgICAgIDwvYnV0dG9uPgogICAgICAgICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgICAgICA8L2Rpdj4KICAgICAgICAgICAgICAgICkpfQogICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICApfQogICAgICAgICAgPC9kaXY+CiAgICAgICAgKX0KCiAgICAgICAgey8qIE5hdmlnYXRpb24gKi99CiAgICAgICAgPGRpdiBjbGFzc05hbWU9ImZsZXgganVzdGlmeS1iZXR3ZWVuIG10LTggcHQtNCBib3JkZXItdCI+CiAgICAgICAgICB7c3RlcCA+IDEgPyAoCiAgICAgICAgICAgIDxCdXR0b24gdmFyaWFudD0ib3V0bGluZSIgb25DbGljaz17KCkgPT4gc2V0U3RlcChzdGVwIC0gMSl9PgogICAgICAgICAgICAgIEJhY2sKICAgICAgICAgICAgPC9CdXR0b24+CiAgICAgICAgICApIDogKAogICAgICAgICAgICA8ZGl2IC8+CiAgICAgICAgICApfQogICAgICAgICAge3N0ZXAgPCA0ID8gKAogICAgICAgICAgICA8QnV0dG9uIG9uQ2xpY2s9eygpID0+IHZhbGlkYXRlU3RlcChzdGVwKSAmJiBzZXRTdGVwKHN0ZXAgKyAxKX0+CiAgICAgICAgICAgICAgQ29udGludWUKICAgICAgICAgICAgPC9CdXR0b24+CiAgICAgICAgICApIDogKAogICAgICAgICAgICA8QnV0dG9uIGxvYWRpbmc9e2xvYWRpbmd9IG9uQ2xpY2s9e2hhbmRsZVN1Ym1pdH0+CiAgICAgICAgICAgICAgUHVibGlzaCBMaXN0aW5nCiAgICAgICAgICAgIDwvQnV0dG9uPgogICAgICAgICAgKX0KICAgICAgICA8L2Rpdj4KICAgICAgPC9kaXY+CiAgICA8L2Rpdj4KICApOwp9Cg==</t>
+    <t>LyoqCiAqIEBtb2R1bGUgTmV3UHJvcGVydHlQYWdlCiAqIEBkZXNjcmlwdGlvbiBNdWx0aS1zdGVwIGZvcm0gZm9yIGhvc3RzIHRvIGNyZWF0ZSBhIG5ldyBwcm9wZXJ0eSBsaXN0aW5nLgogKi8KInVzZSBjbGllbnQiOwoKaW1wb3J0IFJlYWN0LCB7IHVzZVN0YXRlIH0gZnJvbSAicmVhY3QiOwppbXBvcnQgeyB1c2VSb3V0ZXIgfSBmcm9tICJuZXh0L25hdmlnYXRpb24iOwppbXBvcnQgQnV0dG9uIGZyb20gIkAvY29tcG9uZW50cy91aS9idXR0b24iOwppbXBvcnQgSW5wdXQgZnJvbSAiQC9jb21wb25lbnRzL3VpL2lucHV0IjsKaW1wb3J0IHsgU2VsZWN0LCBUZXh0YXJlYSB9IGZyb20gIkAvY29tcG9uZW50cy91aS9pbmRleCI7CmltcG9ydCB7IHRvYXN0IH0gZnJvbSAiQC9jb21wb25lbnRzL3VpL3RvYXN0IjsKaW1wb3J0IHsgcHJvcGVydHlBcGkgfSBmcm9tICJAL2xpYi9hcGkiOwoKY29uc3QgcHJvcGVydHlUeXBlcyA9IFsKICB7IHZhbHVlOiAiYXBhcnRtZW50IiwgbGFiZWw6ICJBcGFydG1lbnQiIH0sCiAgeyB2YWx1ZTogImhvdXNlIiwgbGFiZWw6ICJIb3VzZSIgfSwKICB7IHZhbHVlOiAidmlsbGEiLCBsYWJlbDogIlZpbGxhIiB9LAogIHsgdmFsdWU6ICJjYWJpbiIsIGxhYmVsOiAiQ2FiaW4iIH0sCiAgeyB2YWx1ZTogInN0dWRpbyIsIGxhYmVsOiAiU3R1ZGlvIiB9LAogIHsgdmFsdWU6ICJsb2Z0IiwgbGFiZWw6ICJMb2Z0IiB9LAogIHsgdmFsdWU6ICJjb3R0YWdlIiwgbGFiZWw6ICJDb3R0YWdlIiB9LAogIHsgdmFsdWU6ICJjb25kbyIsIGxhYmVsOiAiQ29uZG8iIH0sCl07Cgpjb25zdCBhbWVuaXR5T3B0aW9ucyA9IFsKICAiV2lGaSIsICJLaXRjaGVuIiwgIkZyZWUgUGFya2luZyIsICJQb29sIiwgIkhvdCBUdWIiLCAiQWlyIENvbmRpdGlvbmluZyIsCiAgIldhc2hlciIsICJEcnllciIsICJHeW0iLCAiUGV0IEZyaWVuZGx5IiwgIkRlZGljYXRlZCBXb3Jrc3BhY2UiLAogICJUViIsICJGaXJlcGxhY2UiLCAiQkJRIEdyaWxsIiwgIkVWIENoYXJnZXIiLCAiRWxldmF0b3IiLAogICJEb29ybWFuIiwgIlNlY3VyaXR5IENhbWVyYSIsICJTbW9rZSBBbGFybSIsICJGaXJzdCBBaWQgS2l0IiwKXTsKCmV4cG9ydCBkZWZhdWx0IGZ1bmN0aW9uIE5ld1Byb3BlcnR5UGFnZSgpIHsKICBjb25zdCByb3V0ZXIgPSB1c2VSb3V0ZXIoKTsKICBjb25zdCBbbG9hZGluZywgc2V0TG9hZGluZ10gPSB1c2VTdGF0ZShmYWxzZSk7CiAgY29uc3QgW3N0ZXAsIHNldFN0ZXBdID0gdXNlU3RhdGUoMSk7CiAgY29uc3QgW2Zvcm0sIHNldEZvcm1dID0gdXNlU3RhdGUoewogICAgdGl0bGU6ICIiLAogICAgZGVzY3JpcHRpb246ICIiLAogICAgcHJvcGVydHlfdHlwZTogImFwYXJ0bWVudCIsCiAgICBhZGRyZXNzOiAiIiwKICAgIGNpdHk6ICIiLAogICAgbGF0aXR1ZGU6ICIiLAogICAgbG9uZ2l0dWRlOiAiIiwKICAgIG5pZ2h0bHlfcHJpY2U6ICIiLAogICAgbWF4X2d1ZXN0czogIjIiLAogICAgYW1lbml0aWVzOiBbXSBhcyBzdHJpbmdbXSwKICAgIC8vIEhvdXJseSBjb25maWcKICAgIGVuYWJsZV9ob3VybHk6IGZhbHNlLAogICAgaG91cmx5X3JhdGU6ICIiLAogICAgbWluX2hvdXJzOiAiMiIsCiAgICBtYXhfaG91cnM6ICIxMiIsCiAgfSk7CiAgY29uc3QgW2Vycm9ycywgc2V0RXJyb3JzXSA9IHVzZVN0YXRlPFJlY29yZDxzdHJpbmcsIHN0cmluZz4+KHt9KTsKICBjb25zdCBbaW1hZ2VzLCBzZXRJbWFnZXNdID0gdXNlU3RhdGU8eyBmaWxlOiBGaWxlOyBwcmV2aWV3OiBzdHJpbmc7IGlzUHJpbWFyeTogYm9vbGVhbiB9W10+KFtdKTsKCiAgY29uc3QgdXBkYXRlID0gKGZpZWxkOiBzdHJpbmcsIHZhbHVlOiB1bmtub3duKSA9PgogICAgc2V0Rm9ybSgocHJldikgPT4gKHsgLi4ucHJldiwgW2ZpZWxkXTogdmFsdWUgfSkpOwoKICBjb25zdCB0b2dnbGVBbWVuaXR5ID0gKGFtZW5pdHk6IHN0cmluZykgPT4gewogICAgY29uc3QgbmV4dCA9IGZvcm0uYW1lbml0aWVzLmluY2x1ZGVzKGFtZW5pdHkpCiAgICAgID8gZm9ybS5hbWVuaXRpZXMuZmlsdGVyKChhKSA9PiBhICE9PSBhbWVuaXR5KQogICAgICA6IFsuLi5mb3JtLmFtZW5pdGllcywgYW1lbml0eV07CiAgICB1cGRhdGUoImFtZW5pdGllcyIsIG5leHQpOwogIH07CgogIGNvbnN0IGFkZEltYWdlcyA9IChmaWxlczogRmlsZUxpc3QgfCBudWxsKSA9PiB7CiAgICBpZiAoIWZpbGVzKSByZXR1cm47CiAgICBjb25zdCBuZXdJbWFnZXMgPSBBcnJheS5mcm9tKGZpbGVzKQogICAgICAuZmlsdGVyKChmKSA9PiBmLnR5cGUuc3RhcnRzV2l0aCgiaW1hZ2UvIikpCiAgICAgIC5tYXAoKGZpbGUpID0+ICh7CiAgICAgICAgZmlsZSwKICAgICAgICBwcmV2aWV3OiBVUkwuY3JlYXRlT2JqZWN0VVJMKGZpbGUpLAogICAgICAgIGlzUHJpbWFyeTogZmFsc2UsCiAgICAgIH0pKTsKICAgIHNldEltYWdlcygocHJldikgPT4gewogICAgICBjb25zdCBjb21iaW5lZCA9IFsuLi5wcmV2LCAuLi5uZXdJbWFnZXNdOwogICAgICAvLyBBdXRvLXNldCBmaXJzdCBpbWFnZSBhcyBwcmltYXJ5IGlmIG5vbmUgc2VsZWN0ZWQKICAgICAgaWYgKGNvbWJpbmVkLmxlbmd0aCA+IDAgJiYgIWNvbWJpbmVkLnNvbWUoKGltZykgPT4gaW1nLmlzUHJpbWFyeSkpIHsKICAgICAgICBjb21iaW5lZFswXS5pc1ByaW1hcnkgPSB0cnVlOwogICAgICB9CiAgICAgIHJldHVybiBjb21iaW5lZDsKICAgIH0pOwogIH07CgogIGNvbnN0IHJlbW92ZUltYWdlID0gKGluZGV4OiBudW1iZXIpID0+IHsKICAgIHNldEltYWdlcygocHJldikgPT4gewogICAgICBjb25zdCBuZXh0ID0gcHJldi5maWx0ZXIoKF8sIGkpID0+IGkgIT09IGluZGV4KTsKICAgICAgLy8gUmV2b2tlIG9iamVjdCBVUkwgdG8gZnJlZSBtZW1vcnkKICAgICAgVVJMLnJldm9rZU9iamVjdFVSTChwcmV2W2luZGV4XS5wcmV2aWV3KTsKICAgICAgLy8gSWYgcmVtb3ZlZCBpbWFnZSB3YXMgcHJpbWFyeSwgYXNzaWduIHRvIGZpcnN0IHJlbWFpbmluZwogICAgICBpZiAocHJldltpbmRleF0uaXNQcmltYXJ5ICYmIG5leHQubGVuZ3RoID4gMCkgewogICAgICAgIG5leHRbMF0uaXNQcmltYXJ5ID0gdHJ1ZTsKICAgICAgfQogICAgICByZXR1cm4gbmV4dDsKICAgIH0pOwogIH07CgogIGNvbnN0IHNldFByaW1hcnlJbWFnZSA9IChpbmRleDogbnVtYmVyKSA9PiB7CiAgICBzZXRJbWFnZXMoKHByZXYpID0+CiAgICAgIHByZXYubWFwKChpbWcsIGkpID0+ICh7IC4uLmltZywgaXNQcmltYXJ5OiBpID09PSBpbmRleCB9KSkKICAgICk7CiAgfTsKCiAgY29uc3QgdmFsaWRhdGVTdGVwID0gKHM6IG51bWJlcik6IGJvb2xlYW4gPT4gewogICAgY29uc3QgZXJyczogUmVjb3JkPHN0cmluZywgc3RyaW5nPiA9IHt9OwogICAgaWYgKHMgPT09IDEpIHsKICAgICAgaWYgKCFmb3JtLnRpdGxlLnRyaW0oKSkgZXJycy50aXRsZSA9ICJUaXRsZSBpcyByZXF1aXJlZCI7CiAgICAgIGVsc2UgaWYgKGZvcm0udGl0bGUudHJpbSgpLmxlbmd0aCA8IDMpIGVycnMudGl0bGUgPSAiVGl0bGUgbXVzdCBiZSBhdCBsZWFzdCAzIGNoYXJhY3RlcnMiOwogICAgICBpZiAoIWZvcm0uZGVzY3JpcHRpb24udHJpbSgpKSBlcnJzLmRlc2NyaXB0aW9uID0gIkRlc2NyaXB0aW9uIGlzIHJlcXVpcmVkIjsKICAgICAgZWxzZSBpZiAoZm9ybS5kZXNjcmlwdGlvbi50cmltKCkubGVuZ3RoIDwgMTApIGVycnMuZGVzY3JpcHRpb24gPSAiRGVzY3JpcHRpb24gbXVzdCBiZSBhdCBsZWFzdCAxMCBjaGFyYWN0ZXJzIjsKICAgICAgaWYgKHBhcnNlSW50KGZvcm0ubWF4X2d1ZXN0cykgPiA1MCkgZXJycy5tYXhfZ3Vlc3RzID0gIk1heGltdW0gNTAgZ3Vlc3RzIGFsbG93ZWQiOwogICAgfQogICAgaWYgKHMgPT09IDIpIHsKICAgICAgaWYgKCFmb3JtLmFkZHJlc3MudHJpbSgpKSBlcnJzLmFkZHJlc3MgPSAiQWRkcmVzcyBpcyByZXF1aXJlZCI7CiAgICAgIGVsc2UgaWYgKGZvcm0uYWRkcmVzcy50cmltKCkubGVuZ3RoIDwgNSkgZXJycy5hZGRyZXNzID0gIkFkZHJlc3MgbXVzdCBiZSBhdCBsZWFzdCA1IGNoYXJhY3RlcnMiOwogICAgICBpZiAoIWZvcm0uY2l0eS50cmltKCkpIGVycnMuY2l0eSA9ICJDaXR5IGlzIHJlcXVpcmVkIjsKICAgIH0KICAgIGlmIChzID09PSAzKSB7CiAgICAgIGlmICghZm9ybS5uaWdodGx5X3ByaWNlIHx8IHBhcnNlRmxvYXQoZm9ybS5uaWdodGx5X3ByaWNlKSA8PSAwKQogICAgICAgIGVycnMubmlnaHRseV9wcmljZSA9ICJWYWxpZCBwcmljZSByZXF1aXJlZCI7CiAgICB9CiAgICBzZXRFcnJvcnMoZXJycyk7CiAgICByZXR1cm4gT2JqZWN0LmtleXMoZXJycykubGVuZ3RoID09PSAwOwogIH07CgogIGNvbnN0IGhhbmRsZVN1Ym1pdCA9IGFzeW5jICgpID0+IHsKICAgIGlmICghdmFsaWRhdGVTdGVwKDMpKSByZXR1cm47CiAgICBzZXRMb2FkaW5nKHRydWUpOwogICAgdHJ5IHsKICAgICAgY29uc3QgcGF5bG9hZCA9IHsKICAgICAgICB0aXRsZTogZm9ybS50aXRsZSwKICAgICAgICBkZXNjcmlwdGlvbjogZm9ybS5kZXNjcmlwdGlvbiwKICAgICAgICBhZGRyZXNzOiBmb3JtLmFkZHJlc3MsCiAgICAgICAgY2l0eTogZm9ybS5jaXR5LAogICAgICAgIGxhdGl0dWRlOiBmb3JtLmxhdGl0dWRlID8gcGFyc2VGbG9hdChmb3JtLmxhdGl0dWRlKSA6IHVuZGVmaW5lZCwKICAgICAgICBsb25naXR1ZGU6IGZvcm0ubG9uZ2l0dWRlID8gcGFyc2VGbG9hdChmb3JtLmxvbmdpdHVkZSkgOiB1bmRlZmluZWQsCiAgICAgICAgcHJpY2VfcGVyX25pZ2h0OiBwYXJzZUZsb2F0KGZvcm0ubmlnaHRseV9wcmljZSksCiAgICAgICAgbWF4X2d1ZXN0czogcGFyc2VJbnQoZm9ybS5tYXhfZ3Vlc3RzKSwKICAgICAgICBhbWVuaXRpZXM6IGZvcm0uYW1lbml0aWVzLAogICAgICB9OwogICAgICBjb25zdCBjcmVhdGVkID0gYXdhaXQgcHJvcGVydHlBcGkuY3JlYXRlKHBheWxvYWQpOwogICAgICBjb25zdCBwcm9wZXJ0eUlkID0gY3JlYXRlZC5kYXRhLmlkOwoKICAgICAgLy8gVXBsb2FkIGltYWdlcwogICAgICBpZiAoaW1hZ2VzLmxlbmd0aCA+IDApIHsKICAgICAgICBmb3IgKGNvbnN0IGltZyBvZiBpbWFnZXMpIHsKICAgICAgICAgIHRyeSB7CiAgICAgICAgICAgIGF3YWl0IHByb3BlcnR5QXBpLnVwbG9hZEltYWdlKHByb3BlcnR5SWQsIGltZy5maWxlLCBpbWcuaXNQcmltYXJ5KTsKICAgICAgICAgIH0gY2F0Y2ggewogICAgICAgICAgICB0b2FzdC5lcnJvcihgRmFpbGVkIHRvIHVwbG9hZCAke2ltZy5maWxlLm5hbWV9YCk7CiAgICAgICAgICB9CiAgICAgICAgfQogICAgICB9CgogICAgICAvLyBDb25maWd1cmUgaG91cmx5IGJvb2tpbmcgdmlhIHNlcGFyYXRlIGVuZHBvaW50IGlmIGVuYWJsZWQKICAgICAgaWYgKGZvcm0uZW5hYmxlX2hvdXJseSAmJiBmb3JtLmhvdXJseV9yYXRlKSB7CiAgICAgICAgYXdhaXQgcHJvcGVydHlBcGkuY29uZmlndXJlSG91cmx5KHByb3BlcnR5SWQsIHsKICAgICAgICAgIGhvdXJseV9wcmljZTogcGFyc2VGbG9hdChmb3JtLmhvdXJseV9yYXRlKSwKICAgICAgICAgIG1pbl9ob3VyczogcGFyc2VJbnQoZm9ybS5taW5faG91cnMpLAogICAgICAgICAgbWF4X2hvdXJzOiBwYXJzZUludChmb3JtLm1heF9ob3VycyksCiAgICAgICAgfSk7CiAgICAgIH0KCiAgICAgIHRvYXN0LnN1Y2Nlc3MoIkxpc3RpbmcgY3JlYXRlZCEiKTsKICAgICAgcm91dGVyLnB1c2goYC9wcm9wZXJ0aWVzLyR7cHJvcGVydHlJZH1gKTsKICAgIH0gY2F0Y2ggKGVycjogdW5rbm93bikgewogICAgICAvLyBFeHRyYWN0IG1lc3NhZ2UgZnJvbSBBeGlvcyBlcnJvciBvciBnZW5lcmljIEVycm9yCiAgICAgIGNvbnN0IGF4aW9zRXJyID0gZXJyIGFzIHsgcmVzcG9uc2U/OiB7IHN0YXR1cz86IG51bWJlcjsgZGF0YT86IHsgZGV0YWlsPzogc3RyaW5nIH0gfSB9OwogICAgICBjb25zdCBzdGF0dXMgPSBheGlvc0Vycj8ucmVzcG9uc2U/LnN0YXR1czsKICAgICAgY29uc3QgZGV0YWlsID0gYXhpb3NFcnI/LnJlc3BvbnNlPy5kYXRhPy5kZXRhaWw7CgogICAgICBpZiAoc3RhdHVzID09PSA0MDIgfHwgZGV0YWlsPy50b0xvd2VyQ2FzZSgpLmluY2x1ZGVzKCJtZW1iZXJzaGlwIikpIHsKICAgICAgICB0b2FzdC5lcnJvcigiQW4gYWN0aXZlIG1lbWJlcnNoaXAgaXMgcmVxdWlyZWQgdG8gY3JlYXRlIGxpc3RpbmdzLiBQbGVhc2Ugc3Vic2NyaWJlIHRvIGEgcGxhbiBmaXJzdC4iKTsKICAgICAgfSBlbHNlIHsKICAgICAgICB0b2FzdC5lcnJvcihkZXRhaWwgfHwgKGVyciBpbnN0YW5jZW9mIEVycm9yID8gZXJyLm1lc3NhZ2UgOiAiRmFpbGVkIHRvIGNyZWF0ZSBsaXN0aW5nIikpOwogICAgICB9CiAgICB9IGZpbmFsbHkgewogICAgICBzZXRMb2FkaW5nKGZhbHNlKTsKICAgIH0KICB9OwoKICByZXR1cm4gKAogICAgPGRpdj4KICAgICAgPGgyIGNsYXNzTmFtZT0idGV4dC14bCBmb250LWJvbGQgdGV4dC1ncmF5LTkwMCBtYi0yIj5DcmVhdGUgTmV3IExpc3Rpbmc8L2gyPgogICAgICA8cCBjbGFzc05hbWU9InRleHQtc20gdGV4dC1ncmF5LTUwMCBtYi02Ij4KICAgICAgICBGaWxsIGluIHRoZSBkZXRhaWxzIHRvIGxpc3QgeW91ciBwcm9wZXJ0eSBvbiBTdGF5TmVzdC4KICAgICAgPC9wPgoKICAgICAgey8qIFByb2dyZXNzICovfQogICAgICA8ZGl2IGNsYXNzTmFtZT0iZmxleCBpdGVtcy1jZW50ZXIgZ2FwLTIgbWItOCI+CiAgICAgICAge1siRGV0YWlscyIsICJMb2NhdGlvbiIsICJQcmljaW5nICYgUnVsZXMiLCAiUGhvdG9zIl0ubWFwKChsYWJlbCwgaSkgPT4gKAogICAgICAgICAgPFJlYWN0LkZyYWdtZW50IGtleT17bGFiZWx9PgogICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iZmxleCBpdGVtcy1jZW50ZXIgZ2FwLTIiPgogICAgICAgICAgICAgIDxkaXYKICAgICAgICAgICAgICAgIGNsYXNzTmFtZT17YGgtOCB3LTggcm91bmRlZC1mdWxsIGZsZXggaXRlbXMtY2VudGVyIGp1c3RpZnktY2VudGVyIHRleHQtc20gZm9udC1tZWRpdW0gJHsKICAgICAgICAgICAgICAgICAgc3RlcCA+IGkgKyAxCiAgICAgICAgICAgICAgICAgICAgPyAiYmctZ3JlZW4tMTAwIHRleHQtZ3JlZW4tNzAwIgogICAgICAgICAgICAgICAgICAgIDogc3RlcCA9PT0gaSArIDEKICAgICAgICAgICAgICAgICAgICA/ICJiZy1yb3NlLTYwMCB0ZXh0LXdoaXRlIgogICAgICAgICAgICAgICAgICAgIDogImJnLWdyYXktMTAwIHRleHQtZ3JheS00MDAiCiAgICAgICAgICAgICAgICB9YH0KICAgICAgICAgICAgICA+CiAgICAgICAgICAgICAgICB7c3RlcCA+IGkgKyAxID8gIuKckyIgOiBpICsgMX0KICAgICAgICAgICAgICA8L2Rpdj4KICAgICAgICAgICAgICA8c3BhbgogICAgICAgICAgICAgICAgY2xhc3NOYW1lPXtgdGV4dC1zbSBmb250LW1lZGl1bSBoaWRkZW4gc206YmxvY2sgJHsKICAgICAgICAgICAgICAgICAgc3RlcCA9PT0gaSArIDEgPyAidGV4dC1ncmF5LTkwMCIgOiAidGV4dC1ncmF5LTQwMCIKICAgICAgICAgICAgICAgIH1gfQogICAgICAgICAgICAgID4KICAgICAgICAgICAgICAgIHtsYWJlbH0KICAgICAgICAgICAgICA8L3NwYW4+CiAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICB7aSA8IDMgJiYgPGRpdiBjbGFzc05hbWU9ImZsZXgtMSBoLXB4IGJnLWdyYXktMjAwIiAvPn0KICAgICAgICAgIDwvUmVhY3QuRnJhZ21lbnQ+CiAgICAgICAgKSl9CiAgICAgIDwvZGl2PgoKICAgICAgPGRpdiBjbGFzc05hbWU9InJvdW5kZWQteGwgYm9yZGVyIGJvcmRlci1ncmF5LTIwMCBiZy13aGl0ZSBwLTYiPgogICAgICAgIHsvKiBTdGVwIDE6IERldGFpbHMgKi99CiAgICAgICAge3N0ZXAgPT09IDEgJiYgKAogICAgICAgICAgPGRpdiBjbGFzc05hbWU9InNwYWNlLXktNCI+CiAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgIGxhYmVsPSJQcm9wZXJ0eSB0aXRsZSIKICAgICAgICAgICAgICBwbGFjZWhvbGRlcj0iZS5nLiwgU3VubnkgRG93bnRvd24gTG9mdCB3aXRoIENpdHkgVmlld3MiCiAgICAgICAgICAgICAgdmFsdWU9e2Zvcm0udGl0bGV9CiAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoInRpdGxlIiwgZS50YXJnZXQudmFsdWUpfQogICAgICAgICAgICAgIGVycm9yPXtlcnJvcnMudGl0bGV9CiAgICAgICAgICAgIC8+CiAgICAgICAgICAgIDxUZXh0YXJlYQogICAgICAgICAgICAgIGxhYmVsPSJEZXNjcmlwdGlvbiIKICAgICAgICAgICAgICBwbGFjZWhvbGRlcj0iRGVzY3JpYmUgeW91ciBwcm9wZXJ0eSDigJQgd2hhdCBtYWtlcyBpdCB1bmlxdWU/IgogICAgICAgICAgICAgIHJvd3M9ezV9CiAgICAgICAgICAgICAgdmFsdWU9e2Zvcm0uZGVzY3JpcHRpb259CiAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoImRlc2NyaXB0aW9uIiwgZS50YXJnZXQudmFsdWUpfQogICAgICAgICAgICAgIGVycm9yPXtlcnJvcnMuZGVzY3JpcHRpb259CiAgICAgICAgICAgIC8+CiAgICAgICAgICAgIDxTZWxlY3QKICAgICAgICAgICAgICBsYWJlbD0iUHJvcGVydHkgdHlwZSIKICAgICAgICAgICAgICBvcHRpb25zPXtwcm9wZXJ0eVR5cGVzfQogICAgICAgICAgICAgIHZhbHVlPXtmb3JtLnByb3BlcnR5X3R5cGV9CiAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoInByb3BlcnR5X3R5cGUiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgIC8+CiAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgIGxhYmVsPSJNYXggZ3Vlc3RzIgogICAgICAgICAgICAgIHR5cGU9Im51bWJlciIKICAgICAgICAgICAgICBtaW49ezF9CiAgICAgICAgICAgICAgbWF4PXs1MH0KICAgICAgICAgICAgICB2YWx1ZT17Zm9ybS5tYXhfZ3Vlc3RzfQogICAgICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gdXBkYXRlKCJtYXhfZ3Vlc3RzIiwgZS50YXJnZXQudmFsdWUpfQogICAgICAgICAgICAgIGVycm9yPXtlcnJvcnMubWF4X2d1ZXN0c30KICAgICAgICAgICAgLz4KCiAgICAgICAgICAgIHsvKiBBbWVuaXRpZXMgKi99CiAgICAgICAgICAgIDxkaXY+CiAgICAgICAgICAgICAgPGxhYmVsIGNsYXNzTmFtZT0iYmxvY2sgdGV4dC1zbSBmb250LW1lZGl1bSB0ZXh0LWdyYXktNzAwIG1iLTIiPgogICAgICAgICAgICAgICAgQW1lbml0aWVzCiAgICAgICAgICAgICAgPC9sYWJlbD4KICAgICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iZmxleCBmbGV4LXdyYXAgZ2FwLTIiPgogICAgICAgICAgICAgICAge2FtZW5pdHlPcHRpb25zLm1hcCgoYW1lbml0eSkgPT4gKAogICAgICAgICAgICAgICAgICA8YnV0dG9uCiAgICAgICAgICAgICAgICAgICAga2V5PXthbWVuaXR5fQogICAgICAgICAgICAgICAgICAgIHR5cGU9ImJ1dHRvbiIKICAgICAgICAgICAgICAgICAgICBvbkNsaWNrPXsoKSA9PiB0b2dnbGVBbWVuaXR5KGFtZW5pdHkpfQogICAgICAgICAgICAgICAgICAgIGNsYXNzTmFtZT17YHB4LTMgcHktMS41IHJvdW5kZWQtZnVsbCB0ZXh0LXNtIGJvcmRlciB0cmFuc2l0aW9uICR7CiAgICAgICAgICAgICAgICAgICAgICBmb3JtLmFtZW5pdGllcy5pbmNsdWRlcyhhbWVuaXR5KQogICAgICAgICAgICAgICAgICAgICAgICA/ICJiZy1yb3NlLTUwIGJvcmRlci1yb3NlLTMwMCB0ZXh0LXJvc2UtNzAwIgogICAgICAgICAgICAgICAgICAgICAgICA6ICJib3JkZXItZ3JheS0yMDAgdGV4dC1ncmF5LTYwMCBob3Zlcjpib3JkZXItZ3JheS0zMDAiCiAgICAgICAgICAgICAgICAgICAgfWB9CiAgICAgICAgICAgICAgICAgID4KICAgICAgICAgICAgICAgICAgICB7YW1lbml0eX0KICAgICAgICAgICAgICAgICAgPC9idXR0b24+CiAgICAgICAgICAgICAgICApKX0KICAgICAgICAgICAgICA8L2Rpdj4KICAgICAgICAgICAgPC9kaXY+CiAgICAgICAgICA8L2Rpdj4KICAgICAgICApfQoKICAgICAgICB7LyogU3RlcCAyOiBMb2NhdGlvbiAqL30KICAgICAgICB7c3RlcCA9PT0gMiAmJiAoCiAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0ic3BhY2UteS00Ij4KICAgICAgICAgICAgPElucHV0CiAgICAgICAgICAgICAgbGFiZWw9IlN0cmVldCBhZGRyZXNzIgogICAgICAgICAgICAgIHBsYWNlaG9sZGVyPSIxMjMgTWFpbiBTdHJlZXQiCiAgICAgICAgICAgICAgdmFsdWU9e2Zvcm0uYWRkcmVzc30KICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgiYWRkcmVzcyIsIGUudGFyZ2V0LnZhbHVlKX0KICAgICAgICAgICAgICBlcnJvcj17ZXJyb3JzLmFkZHJlc3N9CiAgICAgICAgICAgIC8+CiAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgIGxhYmVsPSJDaXR5IgogICAgICAgICAgICAgIHZhbHVlPXtmb3JtLmNpdHl9CiAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoImNpdHkiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgZXJyb3I9e2Vycm9ycy5jaXR5fQogICAgICAgICAgICAvPgogICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iZ3JpZCBncmlkLWNvbHMtMiBnYXAtMyI+CiAgICAgICAgICAgICAgPElucHV0CiAgICAgICAgICAgICAgICBsYWJlbD0iTGF0aXR1ZGUgKG9wdGlvbmFsKSIKICAgICAgICAgICAgICAgIHR5cGU9Im51bWJlciIKICAgICAgICAgICAgICAgIHN0ZXA9ImFueSIKICAgICAgICAgICAgICAgIHBsYWNlaG9sZGVyPSI0MC43MTI4IgogICAgICAgICAgICAgICAgdmFsdWU9e2Zvcm0ubGF0aXR1ZGV9CiAgICAgICAgICAgICAgICBvbkNoYW5nZT17KGUpID0+IHVwZGF0ZSgibGF0aXR1ZGUiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgICA8SW5wdXQKICAgICAgICAgICAgICAgIGxhYmVsPSJMb25naXR1ZGUgKG9wdGlvbmFsKSIKICAgICAgICAgICAgICAgIHR5cGU9Im51bWJlciIKICAgICAgICAgICAgICAgIHN0ZXA9ImFueSIKICAgICAgICAgICAgICAgIHBsYWNlaG9sZGVyPSItNzQuMDA2MCIKICAgICAgICAgICAgICAgIHZhbHVlPXtmb3JtLmxvbmdpdHVkZX0KICAgICAgICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gdXBkYXRlKCJsb25naXR1ZGUiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgPC9kaXY+CiAgICAgICAgICA8L2Rpdj4KICAgICAgICApfQoKICAgICAgICB7LyogU3RlcCAzOiBQcmljaW5nICYgUnVsZXMgKi99CiAgICAgICAge3N0ZXAgPT09IDMgJiYgKAogICAgICAgICAgPGRpdiBjbGFzc05hbWU9InNwYWNlLXktNCI+CiAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgIGxhYmVsPSJOaWdodGx5IHByaWNlICjigrkpIgogICAgICAgICAgICAgIHR5cGU9Im51bWJlciIKICAgICAgICAgICAgICBtaW49ezF9CiAgICAgICAgICAgICAgcGxhY2Vob2xkZXI9IjEwMCIKICAgICAgICAgICAgICB2YWx1ZT17Zm9ybS5uaWdodGx5X3ByaWNlfQogICAgICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gdXBkYXRlKCJuaWdodGx5X3ByaWNlIiwgZS50YXJnZXQudmFsdWUpfQogICAgICAgICAgICAgIGVycm9yPXtlcnJvcnMubmlnaHRseV9wcmljZX0KICAgICAgICAgICAgLz4KCiAgICAgICAgICAgIHsvKiBIb3VybHkgYm9va2luZyB0b2dnbGUgKi99CiAgICAgICAgICAgIDxkaXYgY2xhc3NOYW1lPSJyb3VuZGVkLWxnIGJvcmRlciBib3JkZXItZ3JheS0yMDAgcC00Ij4KICAgICAgICAgICAgICA8bGFiZWwgY2xhc3NOYW1lPSJmbGV4IGl0ZW1zLWNlbnRlciBnYXAtMyI+CiAgICAgICAgICAgICAgICA8aW5wdXQKICAgICAgICAgICAgICAgICAgdHlwZT0iY2hlY2tib3giCiAgICAgICAgICAgICAgICAgIGNoZWNrZWQ9e2Zvcm0uZW5hYmxlX2hvdXJseX0KICAgICAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoImVuYWJsZV9ob3VybHkiLCBlLnRhcmdldC5jaGVja2VkKX0KICAgICAgICAgICAgICAgICAgY2xhc3NOYW1lPSJyb3VuZGVkIGJvcmRlci1ncmF5LTMwMCB0ZXh0LXJvc2UtNjAwIGZvY3VzOnJpbmctcm9zZS01MDAiCiAgICAgICAgICAgICAgICAvPgogICAgICAgICAgICAgICAgPGRpdj4KICAgICAgICAgICAgICAgICAgPHAgY2xhc3NOYW1lPSJ0ZXh0LXNtIGZvbnQtbWVkaXVtIHRleHQtZ3JheS05MDAiPkVuYWJsZSBob3VybHkgYm9va2luZ3M8L3A+CiAgICAgICAgICAgICAgICAgIDxwIGNsYXNzTmFtZT0idGV4dC14cyB0ZXh0LWdyYXktNTAwIj5BbGxvdyBndWVzdHMgdG8gYm9vayBieSB0aGUgaG91cjwvcD4KICAgICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgIDwvbGFiZWw+CiAgICAgICAgICAgICAge2Zvcm0uZW5hYmxlX2hvdXJseSAmJiAoCiAgICAgICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iZ3JpZCBncmlkLWNvbHMtMyBnYXAtMyBtdC0zIj4KICAgICAgICAgICAgICAgICAgPElucHV0CiAgICAgICAgICAgICAgICAgICAgbGFiZWw9IkhvdXJseSByYXRlICjigrkpIgogICAgICAgICAgICAgICAgICAgIHR5cGU9Im51bWJlciIKICAgICAgICAgICAgICAgICAgICBtaW49ezF9CiAgICAgICAgICAgICAgICAgICAgdmFsdWU9e2Zvcm0uaG91cmx5X3JhdGV9CiAgICAgICAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoImhvdXJseV9yYXRlIiwgZS50YXJnZXQudmFsdWUpfQogICAgICAgICAgICAgICAgICAvPgogICAgICAgICAgICAgICAgICA8SW5wdXQKICAgICAgICAgICAgICAgICAgICBsYWJlbD0iTWluIGhvdXJzIgogICAgICAgICAgICAgICAgICAgIHR5cGU9Im51bWJlciIKICAgICAgICAgICAgICAgICAgICBtaW49ezF9CiAgICAgICAgICAgICAgICAgICAgdmFsdWU9e2Zvcm0ubWluX2hvdXJzfQogICAgICAgICAgICAgICAgICAgIG9uQ2hhbmdlPXsoZSkgPT4gdXBkYXRlKCJtaW5faG91cnMiLCBlLnRhcmdldC52YWx1ZSl9CiAgICAgICAgICAgICAgICAgIC8+CiAgICAgICAgICAgICAgICAgIDxJbnB1dAogICAgICAgICAgICAgICAgICAgIGxhYmVsPSJNYXggaG91cnMiCiAgICAgICAgICAgICAgICAgICAgdHlwZT0ibnVtYmVyIgogICAgICAgICAgICAgICAgICAgIG1pbj17MX0KICAgICAgICAgICAgICAgICAgICB2YWx1ZT17Zm9ybS5tYXhfaG91cnN9CiAgICAgICAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiB1cGRhdGUoIm1heF9ob3VycyIsIGUudGFyZ2V0LnZhbHVlKX0KICAgICAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgICl9CiAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgPC9kaXY+CiAgICAgICAgKX0KCiAgICAgICAgey8qIFN0ZXAgNDogUGhvdG9zICovfQogICAgICAgIHtzdGVwID09PSA0ICYmICgKICAgICAgICAgIDxkaXYgY2xhc3NOYW1lPSJzcGFjZS15LTQiPgogICAgICAgICAgICA8ZGl2PgogICAgICAgICAgICAgIDxsYWJlbCBjbGFzc05hbWU9ImJsb2NrIHRleHQtc20gZm9udC1tZWRpdW0gdGV4dC1ncmF5LTcwMCBtYi0yIj4KICAgICAgICAgICAgICAgIFByb3BlcnR5IFBob3RvcwogICAgICAgICAgICAgIDwvbGFiZWw+CiAgICAgICAgICAgICAgPHAgY2xhc3NOYW1lPSJ0ZXh0LXhzIHRleHQtZ3JheS01MDAgbWItMyI+CiAgICAgICAgICAgICAgICBVcGxvYWQgaGlnaC1xdWFsaXR5IGltYWdlcy4gVGhlIGZpcnN0IGltYWdlIChvciB0aGUgb25lIHlvdSBtYXJrKSB3aWxsIGJlIHRoZSBjb3ZlciBwaG90by4KICAgICAgICAgICAgICA8L3A+CiAgICAgICAgICAgICAgPGxhYmVsIGNsYXNzTmFtZT0iZmxleCBmbGV4LWNvbCBpdGVtcy1jZW50ZXIganVzdGlmeS1jZW50ZXIgdy1mdWxsIGgtNDAgYm9yZGVyLTIgYm9yZGVyLWRhc2hlZCBib3JkZXItZ3JheS0zMDAgcm91bmRlZC14bCBjdXJzb3ItcG9pbnRlciBob3Zlcjpib3JkZXItcm9zZS00MDAgaG92ZXI6Ymctcm9zZS01MCB0cmFuc2l0aW9uIj4KICAgICAgICAgICAgICAgIDxzdmcKICAgICAgICAgICAgICAgICAgY2xhc3NOYW1lPSJoLTEwIHctMTAgdGV4dC1ncmF5LTQwMCBtYi0yIgogICAgICAgICAgICAgICAgICBmaWxsPSJub25lIgogICAgICAgICAgICAgICAgICB2aWV3Qm94PSIwIDAgMjQgMjQiCiAgICAgICAgICAgICAgICAgIHN0cm9rZT0iY3VycmVudENvbG9yIgogICAgICAgICAgICAgICAgPgogICAgICAgICAgICAgICAgICA8cGF0aAogICAgICAgICAgICAgICAgICAgIHN0cm9rZUxpbmVjYXA9InJvdW5kIgogICAgICAgICAgICAgICAgICAgIHN0cm9rZUxpbmVqb2luPSJyb3VuZCIKICAgICAgICAgICAgICAgICAgICBzdHJva2VXaWR0aD17MS41fQogICAgICAgICAgICAgICAgICAgIGQ9Ik0xMiAxNnYtOG0wIDBsLTMgM20zLTNsMyAzTTQgMTZ2MWEzIDMgMCAwMDMgM2gxMGEzIDMgMCAwMDMtM3YtMSIKICAgICAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgICAgIDwvc3ZnPgogICAgICAgICAgICAgICAgPHNwYW4gY2xhc3NOYW1lPSJ0ZXh0LXNtIHRleHQtZ3JheS01MDAiPkNsaWNrIHRvIHVwbG9hZCBpbWFnZXM8L3NwYW4+CiAgICAgICAgICAgICAgICA8c3BhbiBjbGFzc05hbWU9InRleHQteHMgdGV4dC1ncmF5LTQwMCBtdC0xIj5KUEcsIFBORywgV2ViUCDigJQgbWF4IDEwIE1CIGVhY2g8L3NwYW4+CiAgICAgICAgICAgICAgICA8aW5wdXQKICAgICAgICAgICAgICAgICAgdHlwZT0iZmlsZSIKICAgICAgICAgICAgICAgICAgYWNjZXB0PSJpbWFnZS8qIgogICAgICAgICAgICAgICAgICBtdWx0aXBsZQogICAgICAgICAgICAgICAgICBjbGFzc05hbWU9ImhpZGRlbiIKICAgICAgICAgICAgICAgICAgb25DaGFuZ2U9eyhlKSA9PiBhZGRJbWFnZXMoZS50YXJnZXQuZmlsZXMpfQogICAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgICA8L2xhYmVsPgogICAgICAgICAgICA8L2Rpdj4KCiAgICAgICAgICAgIHtpbWFnZXMubGVuZ3RoID4gMCAmJiAoCiAgICAgICAgICAgICAgPGRpdiBjbGFzc05hbWU9ImdyaWQgZ3JpZC1jb2xzLTIgc206Z3JpZC1jb2xzLTMgZ2FwLTQiPgogICAgICAgICAgICAgICAge2ltYWdlcy5tYXAoKGltZywgaSkgPT4gKAogICAgICAgICAgICAgICAgICA8ZGl2CiAgICAgICAgICAgICAgICAgICAga2V5PXtpbWcucHJldmlld30KICAgICAgICAgICAgICAgICAgICBjbGFzc05hbWU9e2ByZWxhdGl2ZSBncm91cCByb3VuZGVkLWxnIG92ZXJmbG93LWhpZGRlbiBib3JkZXItMiAkewogICAgICAgICAgICAgICAgICAgICAgaW1nLmlzUHJpbWFyeSA/ICJib3JkZXItcm9zZS01MDAiIDogImJvcmRlci1ncmF5LTIwMCIKICAgICAgICAgICAgICAgICAgICB9YH0KICAgICAgICAgICAgICAgICAgPgogICAgICAgICAgICAgICAgICAgIDxpbWcKICAgICAgICAgICAgICAgICAgICAgIHNyYz17aW1nLnByZXZpZXd9CiAgICAgICAgICAgICAgICAgICAgICBhbHQ9e2BVcGxvYWQgJHtpICsgMX1gfQogICAgICAgICAgICAgICAgICAgICAgY2xhc3NOYW1lPSJ3LWZ1bGwgaC0zMiBvYmplY3QtY292ZXIiCiAgICAgICAgICAgICAgICAgICAgLz4KICAgICAgICAgICAgICAgICAgICB7aW1nLmlzUHJpbWFyeSAmJiAoCiAgICAgICAgICAgICAgICAgICAgICA8c3BhbiBjbGFzc05hbWU9ImFic29sdXRlIHRvcC0xLjUgbGVmdC0xLjUgYmctcm9zZS02MDAgdGV4dC13aGl0ZSB0ZXh0LXhzIGZvbnQtbWVkaXVtIHB4LTIgcHktMC41IHJvdW5kZWQtZnVsbCI+CiAgICAgICAgICAgICAgICAgICAgICAgIENvdmVyCiAgICAgICAgICAgICAgICAgICAgICA8L3NwYW4+CiAgICAgICAgICAgICAgICAgICAgKX0KICAgICAgICAgICAgICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iYWJzb2x1dGUgaW5zZXQtMCBiZy1ibGFjay8wIGdyb3VwLWhvdmVyOmJnLWJsYWNrLzQwIHRyYW5zaXRpb24gZmxleCBpdGVtcy1jZW50ZXIganVzdGlmeS1jZW50ZXIgZ2FwLTIgb3BhY2l0eS0wIGdyb3VwLWhvdmVyOm9wYWNpdHktMTAwIj4KICAgICAgICAgICAgICAgICAgICAgIHshaW1nLmlzUHJpbWFyeSAmJiAoCiAgICAgICAgICAgICAgICAgICAgICAgIDxidXR0b24KICAgICAgICAgICAgICAgICAgICAgICAgICB0eXBlPSJidXR0b24iCiAgICAgICAgICAgICAgICAgICAgICAgICAgb25DbGljaz17KCkgPT4gc2V0UHJpbWFyeUltYWdlKGkpfQogICAgICAgICAgICAgICAgICAgICAgICAgIGNsYXNzTmFtZT0iYmctd2hpdGUgdGV4dC1ncmF5LTcwMCB0ZXh0LXhzIGZvbnQtbWVkaXVtIHB4LTIgcHktMSByb3VuZGVkLW1kIGhvdmVyOmJnLWdyYXktMTAwIgogICAgICAgICAgICAgICAgICAgICAgICA+CiAgICAgICAgICAgICAgICAgICAgICAgICAgU2V0IENvdmVyCiAgICAgICAgICAgICAgICAgICAgICAgIDwvYnV0dG9uPgogICAgICAgICAgICAgICAgICAgICAgKX0KICAgICAgICAgICAgICAgICAgICAgIDxidXR0b24KICAgICAgICAgICAgICAgICAgICAgICAgdHlwZT0iYnV0dG9uIgogICAgICAgICAgICAgICAgICAgICAgICBvbkNsaWNrPXsoKSA9PiByZW1vdmVJbWFnZShpKX0KICAgICAgICAgICAgICAgICAgICAgICAgY2xhc3NOYW1lPSJiZy13aGl0ZSB0ZXh0LXJlZC02MDAgdGV4dC14cyBmb250LW1lZGl1bSBweC0yIHB5LTEgcm91bmRlZC1tZCBob3ZlcjpiZy1yZWQtNTAiCiAgICAgICAgICAgICAgICAgICAgICA+CiAgICAgICAgICAgICAgICAgICAgICAgIFJlbW92ZQogICAgICAgICAgICAgICAgICAgICAgPC9idXR0b24+CiAgICAgICAgICAgICAgICAgICAgPC9kaXY+CiAgICAgICAgICAgICAgICAgIDwvZGl2PgogICAgICAgICAgICAgICAgKSl9CiAgICAgICAgICAgICAgPC9kaXY+CiAgICAgICAgICAgICl9CiAgICAgICAgICA8L2Rpdj4KICAgICAgICApfQoKICAgICAgICB7LyogTmF2aWdhdGlvbiAqL30KICAgICAgICA8ZGl2IGNsYXNzTmFtZT0iZmxleCBqdXN0aWZ5LWJldHdlZW4gbXQtOCBwdC00IGJvcmRlci10Ij4KICAgICAgICAgIHtzdGVwID4gMSA/ICgKICAgICAgICAgICAgPEJ1dHRvbiB2YXJpYW50PSJvdXRsaW5lIiBvbkNsaWNrPXsoKSA9PiBzZXRTdGVwKHN0ZXAgLSAxKX0+CiAgICAgICAgICAgICAgQmFjawogICAgICAgICAgICA8L0J1dHRvbj4KICAgICAgICAgICkgOiAoCiAgICAgICAgICAgIDxkaXYgLz4KICAgICAgICAgICl9CiAgICAgICAgICB7c3RlcCA8IDQgPyAoCiAgICAgICAgICAgIDxCdXR0b24gb25DbGljaz17KCkgPT4gdmFsaWRhdGVTdGVwKHN0ZXApICYmIHNldFN0ZXAoc3RlcCArIDEpfT4KICAgICAgICAgICAgICBDb250aW51ZQogICAgICAgICAgICA8L0J1dHRvbj4KICAgICAgICAgICkgOiAoCiAgICAgICAgICAgIDxCdXR0b24gbG9hZGluZz17bG9hZGluZ30gb25DbGljaz17aGFuZGxlU3VibWl0fT4KICAgICAgICAgICAgICBQdWJsaXNoIExpc3RpbmcKICAgICAgICAgICAgPC9CdXR0b24+CiAgICAgICAgICApfQogICAgICAgIDwvZGl2PgogICAgICA8L2Rpdj4KICAgIDwvZGl2PgogICk7Cn0K</t>
   </si>
   <si>
     <t>frontend/src/app/dashboard/properties/page.tsx</t>
@@ -7693,10 +7645,12 @@
   api.get("/admin/memberships", { params: { page } }),
   toggleUserStatus: (userId: string) =&gt;
   api.put(`/admin/users/${userId}/status`),
+  togglePropertyStatus: (propertyId: string) =&gt;
+  api.put(`/admin/properties/${propertyId}/status`),
  };</t>
   </si>
   <si>
-    <t>LyoqCiAqIEFQSSBjbGllbnQgZm9yIFN0YXlOZXN0IGJhY2tlbmQuCiAqCiAqIEhhbmRsZXMgSldUIHRva2VuIG1hbmFnZW1lbnQgYW5kIHJlcXVlc3QvcmVzcG9uc2UgaW50ZXJjZXB0b3JzLgogKi8KCmltcG9ydCBheGlvcywgeyB0eXBlIEF4aW9zSW5zdGFuY2UsIHR5cGUgSW50ZXJuYWxBeGlvc1JlcXVlc3RDb25maWcgfSBmcm9tICJheGlvcyI7CmltcG9ydCB7IHVzZUF1dGhTdG9yZSB9IGZyb20gIkAvc3RvcmVzL2F1dGgtc3RvcmUiOwoKY29uc3QgQVBJX0JBU0VfVVJMID0KICBwcm9jZXNzLmVudi5ORVhUX1BVQkxJQ19BUElfVVJMIHx8ICJodHRwOi8vbG9jYWxob3N0OjgwMDAvYXBpL3YxIjsKCmNvbnN0IGFwaTogQXhpb3NJbnN0YW5jZSA9IGF4aW9zLmNyZWF0ZSh7CiAgYmFzZVVSTDogQVBJX0JBU0VfVVJMLAogIGhlYWRlcnM6IHsgIkNvbnRlbnQtVHlwZSI6ICJhcHBsaWNhdGlvbi9qc29uIiB9LAp9KTsKCi8vIFJlcXVlc3QgaW50ZXJjZXB0b3Ig4oCUIGF0dGFjaCBCZXR0ZXJBdXRoIHNlc3Npb24gdG9rZW4gYXMgQmVhcmVyCmFwaS5pbnRlcmNlcHRvcnMucmVxdWVzdC51c2UoKGNvbmZpZzogSW50ZXJuYWxBeGlvc1JlcXVlc3RDb25maWcpID0+IHsKICBpZiAodHlwZW9mIHdpbmRvdyAhPT0gInVuZGVmaW5lZCIpIHsKICAgIGNvbnN0IHsgc2Vzc2lvblRva2VuIH0gPSB1c2VBdXRoU3RvcmUuZ2V0U3RhdGUoKTsKICAgIGlmIChzZXNzaW9uVG9rZW4pIHsKICAgICAgY29uZmlnLmhlYWRlcnMuQXV0aG9yaXphdGlvbiA9IGBCZWFyZXIgJHtzZXNzaW9uVG9rZW59YDsKICAgIH0KICB9CiAgcmV0dXJuIGNvbmZpZzsKfSk7CgovLyBSZXNwb25zZSBpbnRlcmNlcHRvciDigJQgcmVkaXJlY3QgdG8gbG9naW4gb24gNDAxIChhdm9pZCBpbmZpbml0ZSBsb29wKQphcGkuaW50ZXJjZXB0b3JzLnJlc3BvbnNlLnVzZSgKICAocmVzcG9uc2UpID0+IHJlc3BvbnNlLAogIChlcnJvcjogdW5rbm93bikgPT4gewogICAgY29uc3QgYXhpb3NFcnJvciA9IGVycm9yIGFzIHsgcmVzcG9uc2U/OiB7IHN0YXR1czogbnVtYmVyIH0gfTsKICAgIGlmICgKICAgICAgYXhpb3NFcnJvci5yZXNwb25zZT8uc3RhdHVzID09PSA0MDEgJiYKICAgICAgdHlwZW9mIHdpbmRvdyAhPT0gInVuZGVmaW5lZCIgJiYKICAgICAgIXdpbmRvdy5sb2NhdGlvbi5wYXRobmFtZS5zdGFydHNXaXRoKCIvYXV0aC8iKQogICAgKSB7CiAgICAgIHdpbmRvdy5sb2NhdGlvbi5ocmVmID0gIi9hdXRoL2xvZ2luIjsKICAgIH0KICAgIHJldHVybiBQcm9taXNlLnJlamVjdChlcnJvcik7CiAgfQopOwoKZXhwb3J0IGRlZmF1bHQgYXBpOwoKLyoqCiAqIEV4dHJhY3QgYSBodW1hbi1yZWFkYWJsZSBlcnJvciBtZXNzYWdlIGZyb20gYW4gQXhpb3MgZXJyb3Igb3IgZ2VuZXJpYyBlcnJvci4KICovCmV4cG9ydCBmdW5jdGlvbiBnZXRBcGlFcnJvcihlcnI6IHVua25vd24pOiBzdHJpbmcgewogIGlmIChlcnIgJiYgdHlwZW9mIGVyciA9PT0gIm9iamVjdCIgJiYgInJlc3BvbnNlIiBpbiBlcnIpIHsKICAgIGNvbnN0IGF4aW9zRXJyID0gZXJyIGFzIHsgcmVzcG9uc2U/OiB7IGRhdGE/OiB7IGRldGFpbD86IHN0cmluZyB9IH0gfTsKICAgIGNvbnN0IGRldGFpbCA9IGF4aW9zRXJyLnJlc3BvbnNlPy5kYXRhPy5kZXRhaWw7CiAgICBpZiAodHlwZW9mIGRldGFpbCA9PT0gInN0cmluZyIpIHJldHVybiBkZXRhaWw7CiAgfQogIGlmIChlcnIgaW5zdGFuY2VvZiBFcnJvcikgcmV0dXJuIGVyci5tZXNzYWdlOwogIHJldHVybiAiQW4gdW5leHBlY3RlZCBlcnJvciBvY2N1cnJlZCI7Cn0KCi8vIC0tLS0tLS0tLS0gUHJvZmlsZSAobm9uLWF1dGggdXNlciBwcm9maWxlIGRhdGEpIC0tLS0tLS0tLS0KLyoqIFByb2ZpbGUgQVBJIG1ldGhvZHMg4oCUIGF1dGggaXRzZWxmIGlzIGhhbmRsZWQgYnkgQmV0dGVyQXV0aC4gKi8KZXhwb3J0IGNvbnN0IHByb2ZpbGVBcGkgPSB7CiAgZ2V0OiAoKSA9PiBhcGkuZ2V0KCIvYXV0aC9tZSIpLAogIHVwZGF0ZTogKGRhdGE6IHsgZnVsbF9uYW1lPzogc3RyaW5nOyBwaG9uZT86IHN0cmluZyB9KSA9PgogICAgYXBpLnB1dCgiL2F1dGgvbWUiLCBkYXRhKSwKfTsKCi8vIC0tLS0tLS0tLS0gUHJvcGVydGllcyAtLS0tLS0tLS0tCi8qKiBQcm9wZXJ0eSBDUlVELCBpbWFnZSB1cGxvYWQsIGFuZCBob3VybHktY29uZmlnIEFQSSBtZXRob2RzLiAqLwpleHBvcnQgY29uc3QgcHJvcGVydHlBcGkgPSB7CiAgc2VhcmNoOiAocGFyYW1zPzogUmVjb3JkPHN0cmluZywgdW5rbm93bj4pID0+CiAgICBhcGkuZ2V0KCIvcHJvcGVydGllcyIsIHsgcGFyYW1zIH0pLAoKICBnZXRCeUlkOiAoaWQ6IHN0cmluZykgPT4gYXBpLmdldChgL3Byb3BlcnRpZXMvJHtpZH1gKSwKCiAgY3JlYXRlOiAoZGF0YTogUmVjb3JkPHN0cmluZywgdW5rbm93bj4pID0+IGFwaS5wb3N0KCIvcHJvcGVydGllcyIsIGRhdGEpLAoKICB1cGRhdGU6IChpZDogc3RyaW5nLCBkYXRhOiBSZWNvcmQ8c3RyaW5nLCB1bmtub3duPikgPT4KICAgIGFwaS5wdXQoYC9wcm9wZXJ0aWVzLyR7aWR9YCwgZGF0YSksCgogIGRlbGV0ZTogKGlkOiBzdHJpbmcpID0+IGFwaS5kZWxldGUoYC9wcm9wZXJ0aWVzLyR7aWR9YCksCgogIHVwbG9hZEltYWdlOiAoaWQ6IHN0cmluZywgZmlsZTogRmlsZSwgaXNQcmltYXJ5ID0gZmFsc2UpID0+IHsKICAgIGNvbnN0IGZvcm1EYXRhID0gbmV3IEZvcm1EYXRhKCk7CiAgICBmb3JtRGF0YS5hcHBlbmQoImZpbGUiLCBmaWxlKTsKICAgIHJldHVybiBhcGkucG9zdChgL3Byb3BlcnRpZXMvJHtpZH0vaW1hZ2VzP2lzX3ByaW1hcnk9JHtpc1ByaW1hcnl9YCwgZm9ybURhdGEsIHsKICAgICAgaGVhZGVyczogeyAiQ29udGVudC1UeXBlIjogIm11bHRpcGFydC9mb3JtLWRhdGEiIH0sCiAgICB9KTsKICB9LAoKICBjb25maWd1cmVIb3VybHk6IChpZDogc3RyaW5nLCBkYXRhOiBSZWNvcmQ8c3RyaW5nLCB1bmtub3duPikgPT4KICAgIGFwaS5wdXQoYC9wcm9wZXJ0aWVzLyR7aWR9L2hvdXJseWAsIGRhdGEpLAp9OwoKLy8gLS0tLS0tLS0tLSBCb29raW5ncyAtLS0tLS0tLS0tCi8qKiBCb29raW5nIGxpZmVjeWNsZSBBUEkgbWV0aG9kcyAoY3JlYXRlLCBsaXN0LCBzdGF0dXMsIGNhbmNlbCkuICovCmV4cG9ydCBjb25zdCBib29raW5nQXBpID0gewogIGNyZWF0ZTogKGRhdGE6IFJlY29yZDxzdHJpbmcsIHVua25vd24+KSA9PiBhcGkucG9zdCgiL2Jvb2tpbmdzIiwgZGF0YSksCiAgbGlzdDogKHBhZ2UgPSAxKSA9PiBhcGkuZ2V0KCIvYm9va2luZ3MiLCB7IHBhcmFtczogeyBwYWdlIH0gfSksCiAgZ2V0QnlJZDogKGlkOiBzdHJpbmcpID0+IGFwaS5nZXQoYC9ib29raW5ncy8ke2lkfWApLAogIHVwZGF0ZVN0YXR1czogKGlkOiBzdHJpbmcsIHN0YXR1czogc3RyaW5nKSA9PgogICAgYXBpLnB1dChgL2Jvb2tpbmdzLyR7aWR9L3N0YXR1c2AsIHsgc3RhdHVzIH0pLAogIGNhbmNlbDogKGlkOiBzdHJpbmcpID0+IGFwaS5wb3N0KGAvYm9va2luZ3MvJHtpZH0vY2FuY2VsYCksCn07CgovLyAtLS0tLS0tLS0tIE1lc3NhZ2luZyAtLS0tLS0tLS0tCi8qKiBNZXNzYWdpbmcgQVBJIG1ldGhvZHMgZm9yIGNvbnZlcnNhdGlvbnMgYW5kIG1lc3NhZ2VzLiAqLwpleHBvcnQgY29uc3QgbWVzc2FnZUFwaSA9IHsKICBzdGFydENvbnZlcnNhdGlvbjogKGRhdGE6IHsgcHJvcGVydHlfaWQ6IHN0cmluZzsgbWVzc2FnZTogc3RyaW5nIH0pID0+CiAgICBhcGkucG9zdCgiL2NvbnZlcnNhdGlvbnMiLCBkYXRhKSwKICBsaXN0Q29udmVyc2F0aW9uczogKHBhZ2UgPSAxKSA9PgogICAgYXBpLmdldCgiL2NvbnZlcnNhdGlvbnMiLCB7IHBhcmFtczogeyBwYWdlIH0gfSksCiAgZ2V0Q29udmVyc2F0aW9uOiAoY29udmVyc2F0aW9uSWQ6IHN0cmluZykgPT4KICAgIGFwaS5nZXQoYC9jb252ZXJzYXRpb25zLyR7Y29udmVyc2F0aW9uSWR9YCksCiAgZ2V0TWVzc2FnZXM6IChjb252ZXJzYXRpb25JZDogc3RyaW5nLCBwYWdlID0gMSkgPT4KICAgIGFwaS5nZXQoYC9jb252ZXJzYXRpb25zLyR7Y29udmVyc2F0aW9uSWR9L21lc3NhZ2VzYCwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAogIHNlbmRNZXNzYWdlOiAoY29udmVyc2F0aW9uSWQ6IHN0cmluZywgY29udGVudDogc3RyaW5nKSA9PgogICAgYXBpLnBvc3QoYC9jb252ZXJzYXRpb25zLyR7Y29udmVyc2F0aW9uSWR9L21lc3NhZ2VzYCwgeyBjb250ZW50IH0pLAogIG1hcmtSZWFkOiAobWVzc2FnZUlkOiBzdHJpbmcpID0+IGFwaS5wdXQoYC9tZXNzYWdlcy8ke21lc3NhZ2VJZH0vcmVhZGApLAp9OwoKLy8gLS0tLS0tLS0tLSBSZXZpZXdzIC0tLS0tLS0tLS0KLyoqIFJldmlldyBzdWJtaXNzaW9uIGFuZCByZXRyaWV2YWwgQVBJIG1ldGhvZHMuICovCmV4cG9ydCBjb25zdCByZXZpZXdBcGkgPSB7CiAgY3JlYXRlOiAoZGF0YTogeyBib29raW5nX2lkOiBzdHJpbmc7IHJhdGluZzogbnVtYmVyOyBjb21tZW50Pzogc3RyaW5nIH0pID0+CiAgICBhcGkucG9zdCgiL3Jldmlld3MiLCBkYXRhKSwKICBsaXN0QnlQcm9wZXJ0eTogKHByb3BlcnR5SWQ6IHN0cmluZywgcGFnZSA9IDEpID0+CiAgICBhcGkuZ2V0KGAvcmV2aWV3cy9wcm9wZXJ0eS8ke3Byb3BlcnR5SWR9YCwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAogIGhvc3RSZXZpZXdzOiAocGFnZSA9IDEpID0+CiAgICBhcGkuZ2V0KCIvcmV2aWV3cy9ob3N0IiwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAp9OwoKLy8gLS0tLS0tLS0tLSBNZW1iZXJzaGlwcyAtLS0tLS0tLS0tCi8qKiBNZW1iZXJzaGlwIHBsYW4gYnJvd3NpbmcsIHN1YnNjcmlwdGlvbiwgYW5kIGNhbmNlbGxhdGlvbiBBUEkgbWV0aG9kcy4gKi8KZXhwb3J0IGNvbnN0IG1lbWJlcnNoaXBBcGkgPSB7CiAgZ2V0UGxhbnM6ICgpID0+IGFwaS5nZXQoIi9tZW1iZXJzaGlwcy9wbGFucyIpLAogIHN1YnNjcmliZTogKHBsYW5UeXBlOiBzdHJpbmcsIHBheW1lbnRUb2tlbjogc3RyaW5nKSA9PgogICAgYXBpLnBvc3QoIi9tZW1iZXJzaGlwcy9zdWJzY3JpYmUiLCB7CiAgICAgIHBsYW5fdHlwZTogcGxhblR5cGUsCiAgICAgIHBheW1lbnRfdG9rZW46IHBheW1lbnRUb2tlbiwKICAgIH0pLAogIGdldEN1cnJlbnQ6ICgpID0+IGFwaS5nZXQoIi9tZW1iZXJzaGlwcy9jdXJyZW50IiksCiAgY2FuY2VsOiAoKSA9PiBhcGkucHV0KCIvbWVtYmVyc2hpcHMvY2FuY2VsIiksCn07CgovLyAtLS0tLS0tLS0tIEFkbWluIC0tLS0tLS0tLS0KLyoqIEFkbWluIGRhc2hib2FyZCBhbmQgbWFuYWdlbWVudCBBUEkgbWV0aG9kcy4gKi8KZXhwb3J0IGNvbnN0IGFkbWluQXBpID0gewogIGRhc2hib2FyZDogKCkgPT4gYXBpLmdldCgiL2FkbWluL2Rhc2hib2FyZCIpLAogIGxpc3RVc2VyczogKHBhZ2UgPSAxKSA9PiBhcGkuZ2V0KCIvYWRtaW4vdXNlcnMiLCB7IHBhcmFtczogeyBwYWdlIH0gfSksCiAgbGlzdFByb3BlcnRpZXM6IChwYWdlID0gMSkgPT4KICAgIGFwaS5nZXQoIi9hZG1pbi9wcm9wZXJ0aWVzIiwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAogIGxpc3RCb29raW5nczogKHBhZ2UgPSAxKSA9PgogICAgYXBpLmdldCgiL2FkbWluL2Jvb2tpbmdzIiwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAogIGxpc3RNZW1iZXJzaGlwczogKHBhZ2UgPSAxKSA9PgogICAgYXBpLmdldCgiL2FkbWluL21lbWJlcnNoaXBzIiwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAogIHRvZ2dsZVVzZXJTdGF0dXM6ICh1c2VySWQ6IHN0cmluZykgPT4KICAgIGFwaS5wdXQoYC9hZG1pbi91c2Vycy8ke3VzZXJJZH0vc3RhdHVzYCksCn07Cg==</t>
+    <t>LyoqCiAqIEFQSSBjbGllbnQgZm9yIFN0YXlOZXN0IGJhY2tlbmQuCiAqCiAqIEhhbmRsZXMgSldUIHRva2VuIG1hbmFnZW1lbnQgYW5kIHJlcXVlc3QvcmVzcG9uc2UgaW50ZXJjZXB0b3JzLgogKi8KCmltcG9ydCBheGlvcywgeyB0eXBlIEF4aW9zSW5zdGFuY2UsIHR5cGUgSW50ZXJuYWxBeGlvc1JlcXVlc3RDb25maWcgfSBmcm9tICJheGlvcyI7CmltcG9ydCB7IHVzZUF1dGhTdG9yZSB9IGZyb20gIkAvc3RvcmVzL2F1dGgtc3RvcmUiOwoKY29uc3QgQVBJX0JBU0VfVVJMID0KICBwcm9jZXNzLmVudi5ORVhUX1BVQkxJQ19BUElfVVJMIHx8ICJodHRwOi8vbG9jYWxob3N0OjgwMDAvYXBpL3YxIjsKCmNvbnN0IGFwaTogQXhpb3NJbnN0YW5jZSA9IGF4aW9zLmNyZWF0ZSh7CiAgYmFzZVVSTDogQVBJX0JBU0VfVVJMLAogIGhlYWRlcnM6IHsgIkNvbnRlbnQtVHlwZSI6ICJhcHBsaWNhdGlvbi9qc29uIiB9LAp9KTsKCi8vIFJlcXVlc3QgaW50ZXJjZXB0b3Ig4oCUIGF0dGFjaCBCZXR0ZXJBdXRoIHNlc3Npb24gdG9rZW4gYXMgQmVhcmVyCmFwaS5pbnRlcmNlcHRvcnMucmVxdWVzdC51c2UoKGNvbmZpZzogSW50ZXJuYWxBeGlvc1JlcXVlc3RDb25maWcpID0+IHsKICBpZiAodHlwZW9mIHdpbmRvdyAhPT0gInVuZGVmaW5lZCIpIHsKICAgIGNvbnN0IHsgc2Vzc2lvblRva2VuIH0gPSB1c2VBdXRoU3RvcmUuZ2V0U3RhdGUoKTsKICAgIGlmIChzZXNzaW9uVG9rZW4pIHsKICAgICAgY29uZmlnLmhlYWRlcnMuQXV0aG9yaXphdGlvbiA9IGBCZWFyZXIgJHtzZXNzaW9uVG9rZW59YDsKICAgIH0KICB9CiAgcmV0dXJuIGNvbmZpZzsKfSk7CgovLyBSZXNwb25zZSBpbnRlcmNlcHRvciDigJQgcmVkaXJlY3QgdG8gbG9naW4gb24gNDAxIChhdm9pZCBpbmZpbml0ZSBsb29wKQphcGkuaW50ZXJjZXB0b3JzLnJlc3BvbnNlLnVzZSgKICAocmVzcG9uc2UpID0+IHJlc3BvbnNlLAogIChlcnJvcjogdW5rbm93bikgPT4gewogICAgY29uc3QgYXhpb3NFcnJvciA9IGVycm9yIGFzIHsgcmVzcG9uc2U/OiB7IHN0YXR1czogbnVtYmVyIH0gfTsKICAgIGlmICgKICAgICAgYXhpb3NFcnJvci5yZXNwb25zZT8uc3RhdHVzID09PSA0MDEgJiYKICAgICAgdHlwZW9mIHdpbmRvdyAhPT0gInVuZGVmaW5lZCIgJiYKICAgICAgIXdpbmRvdy5sb2NhdGlvbi5wYXRobmFtZS5zdGFydHNXaXRoKCIvYXV0aC8iKQogICAgKSB7CiAgICAgIHdpbmRvdy5sb2NhdGlvbi5ocmVmID0gIi9hdXRoL2xvZ2luIjsKICAgIH0KICAgIHJldHVybiBQcm9taXNlLnJlamVjdChlcnJvcik7CiAgfQopOwoKZXhwb3J0IGRlZmF1bHQgYXBpOwoKLyoqCiAqIEV4dHJhY3QgYSBodW1hbi1yZWFkYWJsZSBlcnJvciBtZXNzYWdlIGZyb20gYW4gQXhpb3MgZXJyb3Igb3IgZ2VuZXJpYyBlcnJvci4KICovCmV4cG9ydCBmdW5jdGlvbiBnZXRBcGlFcnJvcihlcnI6IHVua25vd24pOiBzdHJpbmcgewogIGlmIChlcnIgJiYgdHlwZW9mIGVyciA9PT0gIm9iamVjdCIgJiYgInJlc3BvbnNlIiBpbiBlcnIpIHsKICAgIGNvbnN0IGF4aW9zRXJyID0gZXJyIGFzIHsgcmVzcG9uc2U/OiB7IGRhdGE/OiB7IGRldGFpbD86IHN0cmluZyB9IH0gfTsKICAgIGNvbnN0IGRldGFpbCA9IGF4aW9zRXJyLnJlc3BvbnNlPy5kYXRhPy5kZXRhaWw7CiAgICBpZiAodHlwZW9mIGRldGFpbCA9PT0gInN0cmluZyIpIHJldHVybiBkZXRhaWw7CiAgfQogIGlmIChlcnIgaW5zdGFuY2VvZiBFcnJvcikgcmV0dXJuIGVyci5tZXNzYWdlOwogIHJldHVybiAiQW4gdW5leHBlY3RlZCBlcnJvciBvY2N1cnJlZCI7Cn0KCi8vIC0tLS0tLS0tLS0gUHJvZmlsZSAobm9uLWF1dGggdXNlciBwcm9maWxlIGRhdGEpIC0tLS0tLS0tLS0KLyoqIFByb2ZpbGUgQVBJIG1ldGhvZHMg4oCUIGF1dGggaXRzZWxmIGlzIGhhbmRsZWQgYnkgQmV0dGVyQXV0aC4gKi8KZXhwb3J0IGNvbnN0IHByb2ZpbGVBcGkgPSB7CiAgZ2V0OiAoKSA9PiBhcGkuZ2V0KCIvYXV0aC9tZSIpLAogIHVwZGF0ZTogKGRhdGE6IHsgZnVsbF9uYW1lPzogc3RyaW5nOyBwaG9uZT86IHN0cmluZyB9KSA9PgogICAgYXBpLnB1dCgiL2F1dGgvbWUiLCBkYXRhKSwKfTsKCi8vIC0tLS0tLS0tLS0gUHJvcGVydGllcyAtLS0tLS0tLS0tCi8qKiBQcm9wZXJ0eSBDUlVELCBpbWFnZSB1cGxvYWQsIGFuZCBob3VybHktY29uZmlnIEFQSSBtZXRob2RzLiAqLwpleHBvcnQgY29uc3QgcHJvcGVydHlBcGkgPSB7CiAgc2VhcmNoOiAocGFyYW1zPzogUmVjb3JkPHN0cmluZywgdW5rbm93bj4pID0+CiAgICBhcGkuZ2V0KCIvcHJvcGVydGllcyIsIHsgcGFyYW1zIH0pLAoKICBnZXRCeUlkOiAoaWQ6IHN0cmluZykgPT4gYXBpLmdldChgL3Byb3BlcnRpZXMvJHtpZH1gKSwKCiAgY3JlYXRlOiAoZGF0YTogUmVjb3JkPHN0cmluZywgdW5rbm93bj4pID0+IGFwaS5wb3N0KCIvcHJvcGVydGllcyIsIGRhdGEpLAoKICB1cGRhdGU6IChpZDogc3RyaW5nLCBkYXRhOiBSZWNvcmQ8c3RyaW5nLCB1bmtub3duPikgPT4KICAgIGFwaS5wdXQoYC9wcm9wZXJ0aWVzLyR7aWR9YCwgZGF0YSksCgogIGRlbGV0ZTogKGlkOiBzdHJpbmcpID0+IGFwaS5kZWxldGUoYC9wcm9wZXJ0aWVzLyR7aWR9YCksCgogIHVwbG9hZEltYWdlOiAoaWQ6IHN0cmluZywgZmlsZTogRmlsZSwgaXNQcmltYXJ5ID0gZmFsc2UpID0+IHsKICAgIGNvbnN0IGZvcm1EYXRhID0gbmV3IEZvcm1EYXRhKCk7CiAgICBmb3JtRGF0YS5hcHBlbmQoImZpbGUiLCBmaWxlKTsKICAgIHJldHVybiBhcGkucG9zdChgL3Byb3BlcnRpZXMvJHtpZH0vaW1hZ2VzP2lzX3ByaW1hcnk9JHtpc1ByaW1hcnl9YCwgZm9ybURhdGEsIHsKICAgICAgaGVhZGVyczogeyAiQ29udGVudC1UeXBlIjogIm11bHRpcGFydC9mb3JtLWRhdGEiIH0sCiAgICB9KTsKICB9LAoKICBjb25maWd1cmVIb3VybHk6IChpZDogc3RyaW5nLCBkYXRhOiBSZWNvcmQ8c3RyaW5nLCB1bmtub3duPikgPT4KICAgIGFwaS5wdXQoYC9wcm9wZXJ0aWVzLyR7aWR9L2hvdXJseWAsIGRhdGEpLAp9OwoKLy8gLS0tLS0tLS0tLSBCb29raW5ncyAtLS0tLS0tLS0tCi8qKiBCb29raW5nIGxpZmVjeWNsZSBBUEkgbWV0aG9kcyAoY3JlYXRlLCBsaXN0LCBzdGF0dXMsIGNhbmNlbCkuICovCmV4cG9ydCBjb25zdCBib29raW5nQXBpID0gewogIGNyZWF0ZTogKGRhdGE6IFJlY29yZDxzdHJpbmcsIHVua25vd24+KSA9PiBhcGkucG9zdCgiL2Jvb2tpbmdzIiwgZGF0YSksCiAgbGlzdDogKHBhZ2UgPSAxKSA9PiBhcGkuZ2V0KCIvYm9va2luZ3MiLCB7IHBhcmFtczogeyBwYWdlIH0gfSksCiAgZ2V0QnlJZDogKGlkOiBzdHJpbmcpID0+IGFwaS5nZXQoYC9ib29raW5ncy8ke2lkfWApLAogIHVwZGF0ZVN0YXR1czogKGlkOiBzdHJpbmcsIHN0YXR1czogc3RyaW5nKSA9PgogICAgYXBpLnB1dChgL2Jvb2tpbmdzLyR7aWR9L3N0YXR1c2AsIHsgc3RhdHVzIH0pLAogIGNhbmNlbDogKGlkOiBzdHJpbmcpID0+IGFwaS5wb3N0KGAvYm9va2luZ3MvJHtpZH0vY2FuY2VsYCksCn07CgovLyAtLS0tLS0tLS0tIE1lc3NhZ2luZyAtLS0tLS0tLS0tCi8qKiBNZXNzYWdpbmcgQVBJIG1ldGhvZHMgZm9yIGNvbnZlcnNhdGlvbnMgYW5kIG1lc3NhZ2VzLiAqLwpleHBvcnQgY29uc3QgbWVzc2FnZUFwaSA9IHsKICBzdGFydENvbnZlcnNhdGlvbjogKGRhdGE6IHsgcHJvcGVydHlfaWQ6IHN0cmluZzsgbWVzc2FnZTogc3RyaW5nIH0pID0+CiAgICBhcGkucG9zdCgiL2NvbnZlcnNhdGlvbnMiLCBkYXRhKSwKICBsaXN0Q29udmVyc2F0aW9uczogKHBhZ2UgPSAxKSA9PgogICAgYXBpLmdldCgiL2NvbnZlcnNhdGlvbnMiLCB7IHBhcmFtczogeyBwYWdlIH0gfSksCiAgZ2V0Q29udmVyc2F0aW9uOiAoY29udmVyc2F0aW9uSWQ6IHN0cmluZykgPT4KICAgIGFwaS5nZXQoYC9jb252ZXJzYXRpb25zLyR7Y29udmVyc2F0aW9uSWR9YCksCiAgZ2V0TWVzc2FnZXM6IChjb252ZXJzYXRpb25JZDogc3RyaW5nLCBwYWdlID0gMSkgPT4KICAgIGFwaS5nZXQoYC9jb252ZXJzYXRpb25zLyR7Y29udmVyc2F0aW9uSWR9L21lc3NhZ2VzYCwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAogIHNlbmRNZXNzYWdlOiAoY29udmVyc2F0aW9uSWQ6IHN0cmluZywgY29udGVudDogc3RyaW5nKSA9PgogICAgYXBpLnBvc3QoYC9jb252ZXJzYXRpb25zLyR7Y29udmVyc2F0aW9uSWR9L21lc3NhZ2VzYCwgeyBjb250ZW50IH0pLAogIG1hcmtSZWFkOiAobWVzc2FnZUlkOiBzdHJpbmcpID0+IGFwaS5wdXQoYC9tZXNzYWdlcy8ke21lc3NhZ2VJZH0vcmVhZGApLAp9OwoKLy8gLS0tLS0tLS0tLSBSZXZpZXdzIC0tLS0tLS0tLS0KLyoqIFJldmlldyBzdWJtaXNzaW9uIGFuZCByZXRyaWV2YWwgQVBJIG1ldGhvZHMuICovCmV4cG9ydCBjb25zdCByZXZpZXdBcGkgPSB7CiAgY3JlYXRlOiAoZGF0YTogeyBib29raW5nX2lkOiBzdHJpbmc7IHJhdGluZzogbnVtYmVyOyBjb21tZW50Pzogc3RyaW5nIH0pID0+CiAgICBhcGkucG9zdCgiL3Jldmlld3MiLCBkYXRhKSwKICBsaXN0QnlQcm9wZXJ0eTogKHByb3BlcnR5SWQ6IHN0cmluZywgcGFnZSA9IDEpID0+CiAgICBhcGkuZ2V0KGAvcmV2aWV3cy9wcm9wZXJ0eS8ke3Byb3BlcnR5SWR9YCwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAogIGhvc3RSZXZpZXdzOiAocGFnZSA9IDEpID0+CiAgICBhcGkuZ2V0KCIvcmV2aWV3cy9ob3N0IiwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAp9OwoKLy8gLS0tLS0tLS0tLSBNZW1iZXJzaGlwcyAtLS0tLS0tLS0tCi8qKiBNZW1iZXJzaGlwIHBsYW4gYnJvd3NpbmcsIHN1YnNjcmlwdGlvbiwgYW5kIGNhbmNlbGxhdGlvbiBBUEkgbWV0aG9kcy4gKi8KZXhwb3J0IGNvbnN0IG1lbWJlcnNoaXBBcGkgPSB7CiAgZ2V0UGxhbnM6ICgpID0+IGFwaS5nZXQoIi9tZW1iZXJzaGlwcy9wbGFucyIpLAogIHN1YnNjcmliZTogKHBsYW5UeXBlOiBzdHJpbmcsIHBheW1lbnRUb2tlbjogc3RyaW5nKSA9PgogICAgYXBpLnBvc3QoIi9tZW1iZXJzaGlwcy9zdWJzY3JpYmUiLCB7CiAgICAgIHBsYW5fdHlwZTogcGxhblR5cGUsCiAgICAgIHBheW1lbnRfdG9rZW46IHBheW1lbnRUb2tlbiwKICAgIH0pLAogIGdldEN1cnJlbnQ6ICgpID0+IGFwaS5nZXQoIi9tZW1iZXJzaGlwcy9jdXJyZW50IiksCiAgY2FuY2VsOiAoKSA9PiBhcGkucHV0KCIvbWVtYmVyc2hpcHMvY2FuY2VsIiksCn07CgovLyAtLS0tLS0tLS0tIEFkbWluIC0tLS0tLS0tLS0KLyoqIEFkbWluIGRhc2hib2FyZCBhbmQgbWFuYWdlbWVudCBBUEkgbWV0aG9kcy4gKi8KZXhwb3J0IGNvbnN0IGFkbWluQXBpID0gewogIGRhc2hib2FyZDogKCkgPT4gYXBpLmdldCgiL2FkbWluL2Rhc2hib2FyZCIpLAogIGxpc3RVc2VyczogKHBhZ2UgPSAxKSA9PiBhcGkuZ2V0KCIvYWRtaW4vdXNlcnMiLCB7IHBhcmFtczogeyBwYWdlIH0gfSksCiAgbGlzdFByb3BlcnRpZXM6IChwYWdlID0gMSkgPT4KICAgIGFwaS5nZXQoIi9hZG1pbi9wcm9wZXJ0aWVzIiwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAogIGxpc3RCb29raW5nczogKHBhZ2UgPSAxKSA9PgogICAgYXBpLmdldCgiL2FkbWluL2Jvb2tpbmdzIiwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAogIGxpc3RNZW1iZXJzaGlwczogKHBhZ2UgPSAxKSA9PgogICAgYXBpLmdldCgiL2FkbWluL21lbWJlcnNoaXBzIiwgeyBwYXJhbXM6IHsgcGFnZSB9IH0pLAogIHRvZ2dsZVVzZXJTdGF0dXM6ICh1c2VySWQ6IHN0cmluZykgPT4KICAgIGFwaS5wdXQoYC9hZG1pbi91c2Vycy8ke3VzZXJJZH0vc3RhdHVzYCksCiAgdG9nZ2xlUHJvcGVydHlTdGF0dXM6IChwcm9wZXJ0eUlkOiBzdHJpbmcpID0+CiAgICBhcGkucHV0KGAvYWRtaW4vcHJvcGVydGllcy8ke3Byb3BlcnR5SWR9L3N0YXR1c2ApLAp9Owo=</t>
   </si>
   <si>
     <t>frontend/src/lib/auth-client.ts</t>
@@ -8053,7 +8007,6 @@
   email: string;
   full_name: string;
   phone?: string;
-  avatar_url?: string;
   role: "user" | "host" | "admin";
   is_active: boolean;
   created_at: string;
@@ -8093,7 +8046,6 @@
   title: string;
   description: string;
   city: string;
-  country?: string;
   address: string;
   latitude?: number;
   longitude?: number;
@@ -8120,7 +8072,7 @@
   total_price: number;
   booking_type: "nightly" | "hourly";
   hours?: number;
-  status: "pending" | "confirmed" | "cancelled" | "completed" | "rejected" | "checked_in";
+  status: "pending" | "confirmed" | "cancelled" | "completed" | "rejected";
   created_at: string;
   updated_at: string;
   /** Populated by admin endpoints */
@@ -8190,7 +8142,7 @@
  }</t>
   </si>
   <si>
-    <t>LyoqCiAqIEBtb2R1bGUgdHlwZXMKICogQGRlc2NyaXB0aW9uIFR5cGVTY3JpcHQgaW50ZXJmYWNlcyBtYXRjaGluZyB0aGUgYmFja2VuZCBQeWRhbnRpYyBzY2hlbWFzLgogKiBUaGVzZSB0eXBlcyBhcmUgc2hhcmVkIGFjcm9zcyB0aGUgZW50aXJlIGZyb250ZW5kLgogKi8KCi8qKiBSZXByZXNlbnRzIGFuIGF1dGhlbnRpY2F0ZWQgdXNlci4gKi8KZXhwb3J0IGludGVyZmFjZSBVc2VyIHsKICBpZDogc3RyaW5nOwogIGVtYWlsOiBzdHJpbmc7CiAgZnVsbF9uYW1lOiBzdHJpbmc7CiAgcGhvbmU/OiBzdHJpbmc7CiAgYXZhdGFyX3VybD86IHN0cmluZzsKICByb2xlOiAidXNlciIgfCAiaG9zdCIgfCAiYWRtaW4iOwogIGlzX2FjdGl2ZTogYm9vbGVhbjsKICBjcmVhdGVkX2F0OiBzdHJpbmc7Cn0KCi8qKiBIb3N0J3MgcHVibGljIHByb2ZpbGUgd2l0aCBidXNpbmVzcyBpbmZvLCB2ZXJpZmljYXRpb24gc3RhdHVzLCBhbmQgcmF0aW5nLiAqLwpleHBvcnQgaW50ZXJmYWNlIEhvc3RQcm9maWxlIHsKICBpZDogc3RyaW5nOwogIHVzZXJfaWQ6IHN0cmluZzsKICBidXNpbmVzc19uYW1lPzogc3RyaW5nOwogIGJpbz86IHN0cmluZzsKICBwaG9uZV92aXNpYmxlOiBib29sZWFuOwogIGlzX3ZlcmlmaWVkOiBib29sZWFuOwogIGF2Z19yYXRpbmc6IG51bWJlcjsKICB0b3RhbF9yZXZpZXdzOiBudW1iZXI7CiAgY3JlYXRlZF9hdDogc3RyaW5nOwp9CgovKiogQSBzaW5nbGUgaW1hZ2UgYXR0YWNoZWQgdG8gYSBwcm9wZXJ0eSBsaXN0aW5nLiAqLwpleHBvcnQgaW50ZXJmYWNlIFByb3BlcnR5SW1hZ2UgewogIGlkOiBzdHJpbmc7CiAgaW1hZ2VfdXJsOiBzdHJpbmc7CiAgaXNfcHJpbWFyeTogYm9vbGVhbjsKICBzb3J0X29yZGVyOiBudW1iZXI7Cn0KCi8qKiBIb3VybHkgYm9va2luZyBjb25maWd1cmF0aW9uIGZvciBhIHByb3BlcnR5LiAqLwpleHBvcnQgaW50ZXJmYWNlIEhvdXJseUJvb2tpbmdDb25maWcgewogIGlkOiBzdHJpbmc7CiAgaG91cmx5X3ByaWNlOiBudW1iZXI7CiAgbWluX2hvdXJzOiBudW1iZXI7CiAgbWF4X2hvdXJzOiBudW1iZXI7CiAgYXZhaWxhYmxlX2Zyb206IHN0cmluZzsKICBhdmFpbGFibGVfdG86IHN0cmluZzsKfQoKLyoqIEEgcmVudGFibGUgcHJvcGVydHkgbGlzdGluZyB3aXRoIGxvY2F0aW9uLCBwcmljaW5nLCBhbmQgaW1hZ2VzLiAqLwpleHBvcnQgaW50ZXJmYWNlIFByb3BlcnR5IHsKICBpZDogc3RyaW5nOwogIGhvc3RfaWQ6IHN0cmluZzsKICB0aXRsZTogc3RyaW5nOwogIGRlc2NyaXB0aW9uOiBzdHJpbmc7CiAgY2l0eTogc3RyaW5nOwogIGNvdW50cnk/OiBzdHJpbmc7CiAgYWRkcmVzczogc3RyaW5nOwogIGxhdGl0dWRlPzogbnVtYmVyOwogIGxvbmdpdHVkZT86IG51bWJlcjsKICBwcmljZV9wZXJfbmlnaHQ6IG51bWJlcjsKICBtYXhfZ3Vlc3RzOiBudW1iZXI7CiAgYW1lbml0aWVzPzogc3RyaW5nW107CiAgaXNfYWN0aXZlOiBib29sZWFuOwogIGhvdXJseV9lbmFibGVkOiBib29sZWFuOwogIGltYWdlczogUHJvcGVydHlJbWFnZVtdOwogIGhvdXJseV9jb25maWc/OiBIb3VybHlCb29raW5nQ29uZmlnOwogIGNyZWF0ZWRfYXQ6IHN0cmluZzsKICB1cGRhdGVkX2F0OiBzdHJpbmc7CiAgLyoqIFBvcHVsYXRlZCBieSBhZG1pbiBlbmRwb2ludHMgKi8KICBob3N0X25hbWU/OiBzdHJpbmc7Cn0KCi8qKiBBIGNvbmZpcm1lZCBvciBwZW5kaW5nIGJvb2tpbmcgYmV0d2VlbiBhIGd1ZXN0IGFuZCBhIHByb3BlcnR5LiAqLwpleHBvcnQgaW50ZXJmYWNlIEJvb2tpbmcgewogIGlkOiBzdHJpbmc7CiAgcHJvcGVydHlfaWQ6IHN0cmluZzsKICBndWVzdF9pZDogc3RyaW5nOwogIGhvc3RfaWQ6IHN0cmluZzsKICBjaGVja19pbjogc3RyaW5nOwogIGNoZWNrX291dDogc3RyaW5nOwogIHRvdGFsX3ByaWNlOiBudW1iZXI7CiAgYm9va2luZ190eXBlOiAibmlnaHRseSIgfCAiaG91cmx5IjsKICBob3Vycz86IG51bWJlcjsKICBzdGF0dXM6ICJwZW5kaW5nIiB8ICJjb25maXJtZWQiIHwgImNhbmNlbGxlZCIgfCAiY29tcGxldGVkIiB8ICJyZWplY3RlZCIgfCAiY2hlY2tlZF9pbiI7CiAgY3JlYXRlZF9hdDogc3RyaW5nOwogIHVwZGF0ZWRfYXQ6IHN0cmluZzsKICAvKiogUG9wdWxhdGVkIGJ5IGFkbWluIGVuZHBvaW50cyAqLwogIHByb3BlcnR5X3RpdGxlPzogc3RyaW5nOwogIGd1ZXN0X25hbWU/OiBzdHJpbmc7Cn0KCi8qKiBBIG1lc3NhZ2luZyBjb252ZXJzYXRpb24gYmV0d2VlbiBhIGd1ZXN0IGFuZCBhIGhvc3QgYWJvdXQgYSBwcm9wZXJ0eS4gKi8KZXhwb3J0IGludGVyZmFjZSBDb252ZXJzYXRpb24gewogIGlkOiBzdHJpbmc7CiAgcHJvcGVydHlfaWQ6IHN0cmluZzsKICBndWVzdF9pZDogc3RyaW5nOwogIGhvc3RfaWQ6IHN0cmluZzsKICBwcm9wZXJ0eV90aXRsZT86IHN0cmluZzsKICBvdGhlcl9wYXJ0eV9uYW1lPzogc3RyaW5nOwogIGNyZWF0ZWRfYXQ6IHN0cmluZzsKICB1cGRhdGVkX2F0OiBzdHJpbmc7CiAgbGFzdF9tZXNzYWdlPzogTWVzc2FnZTsKICB1bnJlYWRfY291bnQ6IG51bWJlcjsKfQoKLyoqIEEgc2luZ2xlIG1lc3NhZ2UgaW4gYSBjb252ZXJzYXRpb24uICovCmV4cG9ydCBpbnRlcmZhY2UgTWVzc2FnZSB7CiAgaWQ6IHN0cmluZzsKICBjb252ZXJzYXRpb25faWQ6IHN0cmluZzsKICBzZW5kZXJfaWQ6IHN0cmluZzsKICBjb250ZW50OiBzdHJpbmc7CiAgbWVzc2FnZV90eXBlOiAidGV4dCI7CiAgaXNfcmVhZDogYm9vbGVhbjsKICBjcmVhdGVkX2F0OiBzdHJpbmc7Cn0KCi8qKiBBIGd1ZXN0IHJldmlldyBmb3IgYSBjb21wbGV0ZWQgYm9va2luZy4gKi8KZXhwb3J0IGludGVyZmFjZSBSZXZpZXcgewogIGlkOiBzdHJpbmc7CiAgYm9va2luZ19pZDogc3RyaW5nOwogIHByb3BlcnR5X2lkOiBzdHJpbmc7CiAgcmV2aWV3ZXJfaWQ6IHN0cmluZzsKICByYXRpbmc6IG51bWJlcjsKICBjb21tZW50Pzogc3RyaW5nOwogIGNyZWF0ZWRfYXQ6IHN0cmluZzsKfQoKLyoqIERlc2NyaWJlcyBhIG1lbWJlcnNoaXAgcGxhbiB0aWVyIChCYXNpYywgUHJvLCBQcmVtaXVtKS4gKi8KZXhwb3J0IGludGVyZmFjZSBNZW1iZXJzaGlwUGxhbiB7CiAgcGxhbl90eXBlOiBzdHJpbmc7CiAgbGFiZWw6IHN0cmluZzsKICBwcmljZTogbnVtYmVyOwogIG1heF9saXN0aW5nczogbnVtYmVyOwp9CgovKiogQW4gYWN0aXZlIG9yIGhpc3RvcmljYWwgaG9zdCBtZW1iZXJzaGlwIHN1YnNjcmlwdGlvbi4gKi8KZXhwb3J0IGludGVyZmFjZSBNZW1iZXJzaGlwIHsKICBpZDogc3RyaW5nOwogIGhvc3RfaWQ6IHN0cmluZzsKICBwbGFuX3R5cGU6IHN0cmluZzsKICBzdGFydF9kYXRlOiBzdHJpbmc7CiAgZW5kX2RhdGU6IHN0cmluZzsKICBzdGF0dXM6ICJhY3RpdmUiIHwgImNhbmNlbGxlZCIgfCAiZXhwaXJlZCIgfCAicGFzdF9kdWUiOwogIGF1dG9fcmVuZXc6IGJvb2xlYW47CiAgYW1vdW50OiBudW1iZXI7CiAgbWF4X2xpc3RpbmdzOiBudW1iZXI7CiAgY3JlYXRlZF9hdDogc3RyaW5nOwogIHVwZGF0ZWRfYXQ6IHN0cmluZzsKfQoKLyoqIEdlbmVyaWMgcGFnaW5hdGVkIEFQSSByZXNwb25zZSB3cmFwcGVyLiAqLwpleHBvcnQgaW50ZXJmYWNlIFBhZ2luYXRlZFJlc3BvbnNlPFQ+IHsKICBpdGVtczogVFtdOwogIHRvdGFsOiBudW1iZXI7CiAgcGFnZTogbnVtYmVyOwogIHBhZ2Vfc2l6ZTogbnVtYmVyOwp9Cg==</t>
+    <t>LyoqCiAqIEBtb2R1bGUgdHlwZXMKICogQGRlc2NyaXB0aW9uIFR5cGVTY3JpcHQgaW50ZXJmYWNlcyBtYXRjaGluZyB0aGUgYmFja2VuZCBQeWRhbnRpYyBzY2hlbWFzLgogKiBUaGVzZSB0eXBlcyBhcmUgc2hhcmVkIGFjcm9zcyB0aGUgZW50aXJlIGZyb250ZW5kLgogKi8KCi8qKiBSZXByZXNlbnRzIGFuIGF1dGhlbnRpY2F0ZWQgdXNlci4gKi8KZXhwb3J0IGludGVyZmFjZSBVc2VyIHsKICBpZDogc3RyaW5nOwogIGVtYWlsOiBzdHJpbmc7CiAgZnVsbF9uYW1lOiBzdHJpbmc7CiAgcGhvbmU/OiBzdHJpbmc7CiAgcm9sZTogInVzZXIiIHwgImhvc3QiIHwgImFkbWluIjsKICBpc19hY3RpdmU6IGJvb2xlYW47CiAgY3JlYXRlZF9hdDogc3RyaW5nOwp9CgovKiogSG9zdCdzIHB1YmxpYyBwcm9maWxlIHdpdGggYnVzaW5lc3MgaW5mbywgdmVyaWZpY2F0aW9uIHN0YXR1cywgYW5kIHJhdGluZy4gKi8KZXhwb3J0IGludGVyZmFjZSBIb3N0UHJvZmlsZSB7CiAgaWQ6IHN0cmluZzsKICB1c2VyX2lkOiBzdHJpbmc7CiAgYnVzaW5lc3NfbmFtZT86IHN0cmluZzsKICBiaW8/OiBzdHJpbmc7CiAgcGhvbmVfdmlzaWJsZTogYm9vbGVhbjsKICBpc192ZXJpZmllZDogYm9vbGVhbjsKICBhdmdfcmF0aW5nOiBudW1iZXI7CiAgdG90YWxfcmV2aWV3czogbnVtYmVyOwogIGNyZWF0ZWRfYXQ6IHN0cmluZzsKfQoKLyoqIEEgc2luZ2xlIGltYWdlIGF0dGFjaGVkIHRvIGEgcHJvcGVydHkgbGlzdGluZy4gKi8KZXhwb3J0IGludGVyZmFjZSBQcm9wZXJ0eUltYWdlIHsKICBpZDogc3RyaW5nOwogIGltYWdlX3VybDogc3RyaW5nOwogIGlzX3ByaW1hcnk6IGJvb2xlYW47CiAgc29ydF9vcmRlcjogbnVtYmVyOwp9CgovKiogSG91cmx5IGJvb2tpbmcgY29uZmlndXJhdGlvbiBmb3IgYSBwcm9wZXJ0eS4gKi8KZXhwb3J0IGludGVyZmFjZSBIb3VybHlCb29raW5nQ29uZmlnIHsKICBpZDogc3RyaW5nOwogIGhvdXJseV9wcmljZTogbnVtYmVyOwogIG1pbl9ob3VyczogbnVtYmVyOwogIG1heF9ob3VyczogbnVtYmVyOwogIGF2YWlsYWJsZV9mcm9tOiBzdHJpbmc7CiAgYXZhaWxhYmxlX3RvOiBzdHJpbmc7Cn0KCi8qKiBBIHJlbnRhYmxlIHByb3BlcnR5IGxpc3Rpbmcgd2l0aCBsb2NhdGlvbiwgcHJpY2luZywgYW5kIGltYWdlcy4gKi8KZXhwb3J0IGludGVyZmFjZSBQcm9wZXJ0eSB7CiAgaWQ6IHN0cmluZzsKICBob3N0X2lkOiBzdHJpbmc7CiAgdGl0bGU6IHN0cmluZzsKICBkZXNjcmlwdGlvbjogc3RyaW5nOwogIGNpdHk6IHN0cmluZzsKICBhZGRyZXNzOiBzdHJpbmc7CiAgbGF0aXR1ZGU/OiBudW1iZXI7CiAgbG9uZ2l0dWRlPzogbnVtYmVyOwogIHByaWNlX3Blcl9uaWdodDogbnVtYmVyOwogIG1heF9ndWVzdHM6IG51bWJlcjsKICBhbWVuaXRpZXM/OiBzdHJpbmdbXTsKICBpc19hY3RpdmU6IGJvb2xlYW47CiAgaG91cmx5X2VuYWJsZWQ6IGJvb2xlYW47CiAgaW1hZ2VzOiBQcm9wZXJ0eUltYWdlW107CiAgaG91cmx5X2NvbmZpZz86IEhvdXJseUJvb2tpbmdDb25maWc7CiAgY3JlYXRlZF9hdDogc3RyaW5nOwogIHVwZGF0ZWRfYXQ6IHN0cmluZzsKICAvKiogUG9wdWxhdGVkIGJ5IGFkbWluIGVuZHBvaW50cyAqLwogIGhvc3RfbmFtZT86IHN0cmluZzsKfQoKLyoqIEEgY29uZmlybWVkIG9yIHBlbmRpbmcgYm9va2luZyBiZXR3ZWVuIGEgZ3Vlc3QgYW5kIGEgcHJvcGVydHkuICovCmV4cG9ydCBpbnRlcmZhY2UgQm9va2luZyB7CiAgaWQ6IHN0cmluZzsKICBwcm9wZXJ0eV9pZDogc3RyaW5nOwogIGd1ZXN0X2lkOiBzdHJpbmc7CiAgaG9zdF9pZDogc3RyaW5nOwogIGNoZWNrX2luOiBzdHJpbmc7CiAgY2hlY2tfb3V0OiBzdHJpbmc7CiAgdG90YWxfcHJpY2U6IG51bWJlcjsKICBib29raW5nX3R5cGU6ICJuaWdodGx5IiB8ICJob3VybHkiOwogIGhvdXJzPzogbnVtYmVyOwogIHN0YXR1czogInBlbmRpbmciIHwgImNvbmZpcm1lZCIgfCAiY2FuY2VsbGVkIiB8ICJjb21wbGV0ZWQiIHwgInJlamVjdGVkIjsKICBjcmVhdGVkX2F0OiBzdHJpbmc7CiAgdXBkYXRlZF9hdDogc3RyaW5nOwogIC8qKiBQb3B1bGF0ZWQgYnkgYWRtaW4gZW5kcG9pbnRzICovCiAgcHJvcGVydHlfdGl0bGU/OiBzdHJpbmc7CiAgZ3Vlc3RfbmFtZT86IHN0cmluZzsKfQoKLyoqIEEgbWVzc2FnaW5nIGNvbnZlcnNhdGlvbiBiZXR3ZWVuIGEgZ3Vlc3QgYW5kIGEgaG9zdCBhYm91dCBhIHByb3BlcnR5LiAqLwpleHBvcnQgaW50ZXJmYWNlIENvbnZlcnNhdGlvbiB7CiAgaWQ6IHN0cmluZzsKICBwcm9wZXJ0eV9pZDogc3RyaW5nOwogIGd1ZXN0X2lkOiBzdHJpbmc7CiAgaG9zdF9pZDogc3RyaW5nOwogIHByb3BlcnR5X3RpdGxlPzogc3RyaW5nOwogIG90aGVyX3BhcnR5X25hbWU/OiBzdHJpbmc7CiAgY3JlYXRlZF9hdDogc3RyaW5nOwogIHVwZGF0ZWRfYXQ6IHN0cmluZzsKICBsYXN0X21lc3NhZ2U/OiBNZXNzYWdlOwogIHVucmVhZF9jb3VudDogbnVtYmVyOwp9CgovKiogQSBzaW5nbGUgbWVzc2FnZSBpbiBhIGNvbnZlcnNhdGlvbi4gKi8KZXhwb3J0IGludGVyZmFjZSBNZXNzYWdlIHsKICBpZDogc3RyaW5nOwogIGNvbnZlcnNhdGlvbl9pZDogc3RyaW5nOwogIHNlbmRlcl9pZDogc3RyaW5nOwogIGNvbnRlbnQ6IHN0cmluZzsKICBtZXNzYWdlX3R5cGU6ICJ0ZXh0IjsKICBpc19yZWFkOiBib29sZWFuOwogIGNyZWF0ZWRfYXQ6IHN0cmluZzsKfQoKLyoqIEEgZ3Vlc3QgcmV2aWV3IGZvciBhIGNvbXBsZXRlZCBib29raW5nLiAqLwpleHBvcnQgaW50ZXJmYWNlIFJldmlldyB7CiAgaWQ6IHN0cmluZzsKICBib29raW5nX2lkOiBzdHJpbmc7CiAgcHJvcGVydHlfaWQ6IHN0cmluZzsKICByZXZpZXdlcl9pZDogc3RyaW5nOwogIHJhdGluZzogbnVtYmVyOwogIGNvbW1lbnQ/OiBzdHJpbmc7CiAgY3JlYXRlZF9hdDogc3RyaW5nOwp9CgovKiogRGVzY3JpYmVzIGEgbWVtYmVyc2hpcCBwbGFuIHRpZXIgKEJhc2ljLCBQcm8sIFByZW1pdW0pLiAqLwpleHBvcnQgaW50ZXJmYWNlIE1lbWJlcnNoaXBQbGFuIHsKICBwbGFuX3R5cGU6IHN0cmluZzsKICBsYWJlbDogc3RyaW5nOwogIHByaWNlOiBudW1iZXI7CiAgbWF4X2xpc3RpbmdzOiBudW1iZXI7Cn0KCi8qKiBBbiBhY3RpdmUgb3IgaGlzdG9yaWNhbCBob3N0IG1lbWJlcnNoaXAgc3Vic2NyaXB0aW9uLiAqLwpleHBvcnQgaW50ZXJmYWNlIE1lbWJlcnNoaXAgewogIGlkOiBzdHJpbmc7CiAgaG9zdF9pZDogc3RyaW5nOwogIHBsYW5fdHlwZTogc3RyaW5nOwogIHN0YXJ0X2RhdGU6IHN0cmluZzsKICBlbmRfZGF0ZTogc3RyaW5nOwogIHN0YXR1czogImFjdGl2ZSIgfCAiY2FuY2VsbGVkIiB8ICJleHBpcmVkIiB8ICJwYXN0X2R1ZSI7CiAgYXV0b19yZW5ldzogYm9vbGVhbjsKICBhbW91bnQ6IG51bWJlcjsKICBtYXhfbGlzdGluZ3M6IG51bWJlcjsKICBjcmVhdGVkX2F0OiBzdHJpbmc7CiAgdXBkYXRlZF9hdDogc3RyaW5nOwp9CgovKiogR2VuZXJpYyBwYWdpbmF0ZWQgQVBJIHJlc3BvbnNlIHdyYXBwZXIuICovCmV4cG9ydCBpbnRlcmZhY2UgUGFnaW5hdGVkUmVzcG9uc2U8VD4gewogIGl0ZW1zOiBUW107CiAgdG90YWw6IG51bWJlcjsKICBwYWdlOiBudW1iZXI7CiAgcGFnZV9zaXplOiBudW1iZXI7Cn0K</t>
   </si>
   <si>
     <t>frontend/tailwind.config.ts</t>
@@ -8310,6 +8262,131 @@
   </si>
   <si>
     <t>LyoqCiAqIFZpdGVzdCBjb25maWd1cmF0aW9uLgogKiBVc2VzIGpzZG9tIGVudmlyb25tZW50IGZvciBSZWFjdCBjb21wb25lbnQgdGVzdGluZyBhbmQgZW5mb3JjZXMg4omlODAlIGNvdmVyYWdlIHRocmVzaG9sZHMuCiAqLwovLy8gPHJlZmVyZW5jZSB0eXBlcz0idml0ZXN0IiAvPgppbXBvcnQgeyBkZWZpbmVDb25maWcgfSBmcm9tICJ2aXRlc3QvY29uZmlnIjsKaW1wb3J0IHJlYWN0IGZyb20gIkB2aXRlanMvcGx1Z2luLXJlYWN0IjsKaW1wb3J0IHBhdGggZnJvbSAicGF0aCI7CgpleHBvcnQgZGVmYXVsdCBkZWZpbmVDb25maWcoewogIHBsdWdpbnM6IFtyZWFjdCgpXSwKICB0ZXN0OiB7CiAgICBlbnZpcm9ubWVudDogImpzZG9tIiwKICAgIGdsb2JhbHM6IHRydWUsCiAgICBzZXR1cEZpbGVzOiBbIi4vc3JjL19fdGVzdHNfXy9zZXR1cC50c3giXSwKICAgIGluY2x1ZGU6IFsic3JjLyoqLyoue3Rlc3Qsc3BlY30ue3RzLHRzeH0iXSwKICAgIGNvdmVyYWdlOiB7CiAgICAgIHByb3ZpZGVyOiAidjgiLAogICAgICByZXBvcnRlcjogWyJ0ZXh0IiwgImxjb3YiXSwKICAgICAgaW5jbHVkZTogWyJzcmMvKiovKi57dHMsdHN4fSJdLAogICAgICBleGNsdWRlOiBbInNyYy9fX3Rlc3RzX18vKioiLCAic3JjL3R5cGVzLyoqIl0sCiAgICAgIHRocmVzaG9sZHM6IHsgbGluZXM6IDgwLCBicmFuY2hlczogNzAsIGZ1bmN0aW9uczogNzUsIHN0YXRlbWVudHM6IDgwIH0sCiAgICB9LAogIH0sCiAgcmVzb2x2ZTogewogICAgYWxpYXM6IHsKICAgICAgIkAiOiBwYXRoLnJlc29sdmUoX19kaXJuYW1lLCAiLi9zcmMiKSwKICAgIH0sCiAgfSwKfSk7Cg==</t>
+  </si>
+  <si>
+    <t>backend/.coverage</t>
+  </si>
+  <si>
+    <t>SQLite format 3@  
+ .�
+ VX^
+ -g��8 Ui, .X�Q�}tabletracertracer
+ CREATE TABLE tracer (
+  -- A row per file indicating the tracer used for that file.
+  file_id integer primary key,
+  tracer text,
+  foreign key (file_id) references file (id)
+ )�
+ �etablearcarcCREATE TABLE arc (
+  -- If recording branches, a row per context per from/to line transition executed.
+  file_id integer, -- foreign key to `file`.
+  context_id integer, -- foreign key to `context`.
+  fromno integer, -- line number jumped from.
+  tono integer, -- line number jumped to.
+  foreign key (file_id) references file (id),
+  foreign key (context_id) references context (id),
+  unique (file_id, context_id, fromno, tono)
+ )%9indexsqlite_autoindex_arc_1arc��qtableline_bitsline_bits CREATE TABLE line_bits (
+  -- If recording lines, a row per context per file executed.
+  -- All of the line numbers for that file/context are in one numbits.
+  file_id integer, -- foreign key to `file`.
+  context_id integer, -- foreign key to `context`.
+  numbits blob, -- see the numbits functions in coverage.numbits
+  foreign key (file_id) references file (id),
+  foreign key (context_id) references context (id),
+  unique (file_id, context_id)
+ )1 Eindexsqlite_autoindex_line_bits_1line_bits
+ �� tablecontextcontextCREATE TABLE context (
+  -- A row per context measured.
+  id integer primary key,
+  context text,
+  unique (context)
+ )-Aindexsqlite_autoindex_context_1context��qtablefilefileCREATE TABLE file (
+  -- A row per file measured.
+  id integer primary key,
+  path text,
+  unique (path)
+ )';indexsqlite_autoindex_file_1file��tablemetametaCREATE TABLE meta (
+  -- Key-value pairs, to record metadata about the data
+  key text,
+  value text,
+  unique (key)
+  -- Possible keys:
+  -- 'has_arcs' boolean -- Is this data recording branches?
+  -- 'sys_argv' text -- The coverage command line that recorded the data.
+  -- 'version' text -- The version of coverage.py that made the file.
+  -- 'when' text -- Datetime when the file was created.
+  -- 'hash' text -- Hash of the data.
+ )';indexsqlite_autoindex_meta_1meta�++�utablecoverage_schemacoverage_schemaCREATE TABLE coverage_schema (
+  -- One row, to record the version of the schema in this db.
+  version integer
+ )
+ ��
+ ���has_arcs0version7.13.5
+ ���has_arcs
+ version
+ 1*�y3��o'
+ �
+ �
+ L
+ �w3��j$
+ �
+ �
+ Q
+ � y +��S�l��7��R�t$��Q�y*M1�C:\Users\samarthjain\Downloads\stay\backend\app\tasks\membership_tasks.pyG0�C:\Users\samarthjain\Downloads\stay\backend\app\core\permissions.pyJ/�C:\Users\samarthjain\Downloads\stay\backend\app\core\logging_config.pyA.�C:\Users\samarthjain\Downloads\stay\backend\app\core\email.pyH-�C:\Users\samarthjain\Downloads\stay\backend\app\tasks\email_tasks.pyE,�C:\Users\samarthjain\Downloads\stay\backend\app\tasks\__init__.py@+�C:\Users\samarthjain\Downloads\stay\backend\app\core\csrf.pyN*�!C:\Users\samarthjain\Downloads\stay\backend\app\services\review_service.pyE)�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\review.pyE(�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\reviews.pyN'�!C:\Users\samarthjain\Downloads\stay\backend\app\services\upload_service.pyP&amp;�%C:\Users\samarthjain\Downloads\stay\backend\app\services\property_service.pyG%�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\property.pyH$�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\properties.pyO#�#C:\Users\samarthjain\Downloads\stay\backend\app\services\message_service.pyF"�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\message.pyF!�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\messages.pyR �)C:\Users\samarthjain\Downloads\stay\backend\app\services\membership_service.pyI�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\membership.pyI�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\memberships.pyO�#C:\Users\samarthjain\Downloads\stay\backend\app\services\booking_service.pyF�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\booking.pyF�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\bookings.pyF�C:\Users\samarthjain\Downloads\stay\backend\app\core\exceptions.pyL�C:\Users\samarthjain\Downloads\stay\backend\app\services\auth_service.pyH�C:\Users\samarthjain\Downloads\stay\backend\app\services\__init__.pyH�C:\Users\samarthjain\Downloads\stay\backend\app\core\rate_limiter.pyB� C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\auth.pyC�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\user.pyG�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\__init__.pyC�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\admin.pyD�
+ C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\router.pyF�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\__init__.pyC�C:\Users\samarthjain\Downloads\stay\backend\app\api\__init__.py:{C:\Users\samarthjain\Downloads\stay\backend\app\main.pyB� C:\Users\samarthjain\Downloads\stay\backend\app\models\user.pyD
+ �
+ C:\Users\samarthjain\Downloads\stay\backend\app\models\review.pyF�C:\Users\samarthjain\Downloads\stay\backend\app\models\property.pyE�C:\Users\samarthjain\Downloads\stay\backend\app\models\message.pyH
+ �C:\Users\samarthjain\Downloads\stay\backend\app\models\membership.pyE �C:\Users\samarthjain\Downloads\stay\backend\app\models\booking.pyH�C:\Users\samarthjain\Downloads\stay\backend\app\models\betterauth.pyF�C:\Users\samarthjain\Downloads\stay\backend\app\models\__init__.pyC�C:\Users\samarthjain\Downloads\stay\backend\app\dependencies.py?�C:\Users\samarthjain\Downloads\stay\backend\app\database.py&lt;C:\Users\samarthjain\Downloads\stay\backend\app\config.pyD�
+ C:\Users\samarthjain\Downloads\stay\backend\app\core\security.pyD�
+ C:\Users\samarthjain\Downloads\stay\backend\app\core\__init__.py?�C:\Users\samarthjain\Downloads\stay\backend\app\__init__.py
+ 1+��k
+ �
+ �����%�z���z �4�p�(
+ �
+ �
+ M
+ �x4
+ �Tm��u
+ R z ,8S%�R+N�C:\Users\samarthjain\Downloads\stay\backend\app\tasks\membership_tasks.py1H�C:\Users\samarthjain\Downloads\stay\backend\app\core\permissions.py0K�C:\Users\samarthjain\Downloads\stay\backend\app\core\logging_config.py/B�C:\Users\samarthjain\Downloads\stay\backend\app\core\email.py.I�C:\Users\samarthjain\Downloads\stay\backend\app\tasks\email_tasks.py-F�C:\Users\samarthjain\Downloads\stay\backend\app\tasks\__init__.py,A�C:\Users\samarthjain\Downloads\stay\backend\app\core\csrf.py+O�!C:\Users\samarthjain\Downloads\stay\backend\app\services\review_service.py*F�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\review.py)F�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\reviews.py(O�!C:\Users\samarthjain\Downloads\stay\backend\app\services\upload_service.py'Q�%C:\Users\samarthjain\Downloads\stay\backend\app\services\property_service.py&amp;H�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\property.py%I�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\properties.py$P�#C:\Users\samarthjain\Downloads\stay\backend\app\services\message_service.py#G�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\message.py"G�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\messages.py!S�)C:\Users\samarthjain\Downloads\stay\backend\app\services\membership_service.py J�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\membership.pyJ�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\memberships.pyP�#C:\Users\samarthjain\Downloads\stay\backend\app\services\booking_service.pyG�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\booking.pyG�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\bookings.pyG�C:\Users\samarthjain\Downloads\stay\backend\app\core\exceptions.pyM�C:\Users\samarthjain\Downloads\stay\backend\app\services\auth_service.pyI�C:\Users\samarthjain\Downloads\stay\backend\app\services\__init__.pyI�C:\Users\samarthjain\Downloads\stay\backend\app\core\rate_limiter.pyC� C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\auth.pyD�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\user.pyH�C:\Users\samarthjain\Downloads\stay\backend\app\schemas\__init__.pyD�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\admin.pyE�
+ C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\router.pyG�C:\Users\samarthjain\Downloads\stay\backend\app\api\v1\__init__.pyD�C:\Users\samarthjain\Downloads\stay\backend\app\api\__init__.py;{C:\Users\samarthjain\Downloads\stay\backend\app\main.pyC� C:\Users\samarthjain\Downloads\stay\backend\app\models\user.pyE�
+ C:\Users\samarthjain\Downloads\stay\backend\app\models\review.py
+ G�C:\Users\samarthjain\Downloads\stay\backend\app\models\property.pyF�C:\Users\samarthjain\Downloads\stay\backend\app\models\message.pyI�C:\Users\samarthjain\Downloads\stay\backend\app\models\membership.py
+ F�C:\Users\samarthjain\Downloads\stay\backend\app\models\booking.py I�C:\Users\samarthjain\Downloads\stay\backend\app\models\betterauth.pyG�C:\Users\samarthjain\Downloads\stay\backend\app\models\__init__.pyD�C:\Users\samarthjain\Downloads\stay\backend\app\dependencies.py@�C:\Users\samarthjain\Downloads\stay\backend\app\database.py=C:\Users\samarthjain\Downloads\stay\backend\app\config.pyE�
+ C:\Users\samarthjain\Downloads\stay\backend\app\core\security.pyE�
+ C:\Users\samarthjain\Downloads\stay\backend\app\core\__init__.py?� C:\Users\samarthjain\Downloads\stay\backend\app\__init__.py
+ ��
+ ��
+ .��������nRC:( ��������n\I2$ 
+ �
+ �
+ �
+ �
+ �
+ �
+ �
+ �
+ t
+ [
+ 1
+ ����. -j0�
+ - ,��, 'j @C���+ **j�������%j����%* L&amp;�}@m���N����%~:�'^���M���y ��() R#�&gt;�������_D/M�~ٗd����D�����';�( 0 j��l���wڜ�?a�' :z��{����۵��/q&lt;�9����&amp; $����Kۖ�",% $ "Z�3!c ;
+ # )��$" (%�b���d��3`2��! "Z�3D�Y Zx� Zf@� Z "�e��glk�� 
+ ������
+ ,�,k��&gt;�oc�;Y�&gt; $�˲�m���ڷ; "
+ z��=n����&gt; " z�}6k���&gt;� Z�[���۶
+ � .��2Џ�� 4�{%�� j�&lt;� �JJ�=}�
+ �2�0( �f���c .�W� "+�$���C �
+ "B�&lt;?I�T ��
+ (j_6���g 6$j���ߏ3���M�03 (!j�f~~l�g/3� ڃ�l�g&amp;� j_6��c33�Y 8�(���ɲ�X6܍�L�2�z% L���g�?����g��_�Ͼ���������w6� 
+ .�����}vhaZSLE&gt;7o����0������)��"�������
+ ����� -. ,- ', *+ &amp;* #) ( ' &amp; % $ )# %" "! 
+ . + 
+ (
+ $ !</t>
+  </si>
+  <si>
+    <t>U1FMaXRlIGZvcm1hdCAzABAAAQEAQCAgAAAACQAAAAoAAAAAAAAAAAAAAAcAAAAEAAAAAAAAAAAAAAABAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAJAC7vv70UCg9WAAwGWAAPXgoaDy0MZwzvv70L77+9DDgJVQtpBywJLgZYAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAO+/vVEMBxcZGQHvv719dGFibGV0cmFjZXJ0cmFjZXIKQ1JFQVRFIFRBQkxFIHRyYWNlciAoCiAgICAtLSBBIHJvdyBwZXIgZmlsZSBpbmRpY2F0aW5nIHRoZSB0cmFjZXIgdXNlZCBmb3IgdGhhdCBmaWxlLgogICAgZmlsZV9pZCBpbnRlZ2VyIHByaW1hcnkga2V5LAogICAgdHJhY2VyIHRleHQsCiAgICBmb3JlaWduIGtleSAoZmlsZV9pZCkgcmVmZXJlbmNlcyBmaWxlIChpZCkKKe+/vX8KBxcTEwHvv71ldGFibGVhcmNhcmMLQ1JFQVRFIFRBQkxFIGFyYyAoCiAgICAtLSBJZiByZWNvcmRpbmcgYnJhbmNoZXMsIGEgcm93IHBlciBjb250ZXh0IHBlciBmcm9tL3RvIGxpbmUgdHJhbnNpdGlvbiBleGVjdXRlZC4KICAgIGZpbGVfaWQgaW50ZWdlciwgICAgICAgICAgICAtLSBmb3JlaWduIGtleSB0byBgZmlsZWAuCiAgICBjb250ZXh0X2lkIGludGVnZXIsICAgICAgICAgLS0gZm9yZWlnbiBrZXkgdG8gYGNvbnRleHRgLgogICAgZnJvbW5vIGludGVnZXIsICAgICAgICAgICAgIC0tIGxpbmUgbnVtYmVyIGp1bXBlZCBmcm9tLgogICAgdG9ubyBpbnRlZ2VyLCAgICAgICAgICAgICAgIC0tIGxpbmUgbnVtYmVyIGp1bXBlZCB0by4KICAgIGZvcmVpZ24ga2V5IChmaWxlX2lkKSByZWZlcmVuY2VzIGZpbGUgKGlkKSwKICAgIGZvcmVpZ24ga2V5IChjb250ZXh0X2lkKSByZWZlcmVuY2VzIGNvbnRleHQgKGlkKSwKICAgIHVuaXF1ZSAoZmlsZV9pZCwgY29udGV4dF9pZCwgZnJvbW5vLCB0b25vKQopJQsGFzkTAQBpbmRleHNxbGl0ZV9hdXRvaW5kZXhfYXJjXzFhcmMM77+9EQgHFx8fAe+/vXF0YWJsZWxpbmVfYml0c2xpbmVfYml0cwlDUkVBVEUgVEFCTEUgbGluZV9iaXRzICgKICAgIC0tIElmIHJlY29yZGluZyBsaW5lcywgYSByb3cgcGVyIGNvbnRleHQgcGVyIGZpbGUgZXhlY3V0ZWQuCiAgICAtLSBBbGwgb2YgdGhlIGxpbmUgbnVtYmVycyBmb3IgdGhhdCBmaWxlL2NvbnRleHQgYXJlIGluIG9uZSBudW1iaXRzLgogICAgZmlsZV9pZCBpbnRlZ2VyLCAgICAgICAgICAgIC0tIGZvcmVpZ24ga2V5IHRvIGBmaWxlYC4KICAgIGNvbnRleHRfaWQgaW50ZWdlciwgICAgICAgICAtLSBmb3JlaWduIGtleSB0byBgY29udGV4dGAuCiAgICBudW1iaXRzIGJsb2IsICAgICAgICAgICAgICAgLS0gc2VlIHRoZSBudW1iaXRzIGZ1bmN0aW9ucyBpbiBjb3ZlcmFnZS5udW1iaXRzCiAgICBmb3JlaWduIGtleSAoZmlsZV9pZCkgcmVmZXJlbmNlcyBmaWxlIChpZCksCiAgICBmb3JlaWduIGtleSAoY29udGV4dF9pZCkgcmVmZXJlbmNlcyBjb250ZXh0IChpZCksCiAgICB1bmlxdWUgKGZpbGVfaWQsIGNvbnRleHRfaWQpCikxCQYXRR8BAGluZGV4c3FsaXRlX2F1dG9pbmRleF9saW5lX2JpdHNfMWxpbmVfYml0cwrvv70ZBgcXGxsB77+9CXRhYmxlY29udGV4dGNvbnRleHQHQ1JFQVRFIFRBQkxFIGNvbnRleHQgKAogICAgLS0gQSByb3cgcGVyIGNvbnRleHQgbWVhc3VyZWQuCiAgICBpZCBpbnRlZ2VyIHByaW1hcnkga2V5LAogICAgY29udGV4dCB0ZXh0LAogICAgdW5pcXVlIChjb250ZXh0KQopLQcGF0EbAQBpbmRleHNxbGl0ZV9hdXRvaW5kZXhfY29udGV4dF8xY29udGV4dAjvv70HBAcXFRUB77+9cXRhYmxlZmlsZWZpbGUFQ1JFQVRFIFRBQkxFIGZpbGUgKAogICAgLS0gQSByb3cgcGVyIGZpbGUgbWVhc3VyZWQuCiAgICBpZCBpbnRlZ2VyIHByaW1hcnkga2V5LAogICAgcGF0aCB0ZXh0LAogICAgdW5pcXVlIChwYXRoKQopJwUGFzsVAQBpbmRleHNxbGl0ZV9hdXRvaW5kZXhfZmlsZV8xZmlsZQbvv70QAgcXFRUB77+9A3RhYmxlbWV0YW1ldGEDQ1JFQVRFIFRBQkxFIG1ldGEgKAogICAgLS0gS2V5LXZhbHVlIHBhaXJzLCB0byByZWNvcmQgbWV0YWRhdGEgYWJvdXQgdGhlIGRhdGEKICAgIGtleSB0ZXh0LAogICAgdmFsdWUgdGV4dCwKICAgIHVuaXF1ZSAoa2V5KQogICAgLS0gUG9zc2libGUga2V5czoKICAgIC0tICAnaGFzX2FyY3MnIGJvb2xlYW4gICAgICAtLSBJcyB0aGlzIGRhdGEgcmVjb3JkaW5nIGJyYW5jaGVzPwogICAgLS0gICdzeXNfYXJndicgdGV4dCAgICAgICAgIC0tIFRoZSBjb3ZlcmFnZSBjb21tYW5kIGxpbmUgdGhhdCByZWNvcmRlZCB0aGUgZGF0YS4KICAgIC0tICAndmVyc2lvbicgdGV4dCAgICAgICAgICAtLSBUaGUgdmVyc2lvbiBvZiBjb3ZlcmFnZS5weSB0aGF0IG1hZGUgdGhlIGZpbGUuCiAgICAtLSAgJ3doZW4nIHRleHQgICAgICAgICAgICAgLS0gRGF0ZXRpbWUgd2hlbiB0aGUgZmlsZSB3YXMgY3JlYXRlZC4KICAgIC0tICAnaGFzaCcgdGV4dCAgICAgICAgICAgICAtLSBIYXNoIG9mIHRoZSBkYXRhLgopJwMGFzsVAQBpbmRleHNxbGl0ZV9hdXRvaW5kZXhfbWV0YV8xbWV0YQQAAAAIAAAAAO+/vR8BBxcrKwHvv711dGFibGVjb3ZlcmFnZV9zY2hlbWFjb3ZlcmFnZV9zY2hlbWECQ1JFQVRFIFRBQkxFIGNvdmVyYWdlX3NjaGVtYSAoCiAgICAtLSBPbmUgcm93LCB0byByZWNvcmQgdGhlIHZlcnNpb24gb2YgdGhlIHNjaGVtYSBpbiB0aGlzIGRiLgogICAgdmVyc2lvbiBpbnRlZ2VyCikKAAAAAQ/vv70AD++/vQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAADAQIBBwoAAAACD++/vQAP77+9D++/vQAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAADAIDHQ9oYXNfYXJjczAQAQMbGXZlcnNpb243LjEzLjUKAAAAAg/vv70AD++/vQ/vv70AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAADAMdAWhhc19hcmNzAgoDGwl2ZXJzaW9uCgAAADECKgAP77+9D3kPMw7vv70O77+9Dm8OJwrvv70K77+9CkwKBQzvv70MdwwzC++/vQvvv70LagskCu+/vQrvv70KUQoKCe+/vQl5CSsI77+9CO+/vQhTCAIH77+9B2wHGAbvv70G77+9BjcF77+9Be+/vQVSBQIE77+9BHQEJAPvv70D77+9A1EDDgLvv70CeQIqAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAE0xBADvv70fQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcdGFza3NcbWVtYmVyc2hpcF90YXNrcy5weUcwBADvv70TQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcY29yZVxwZXJtaXNzaW9ucy5weUovBADvv70ZQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcY29yZVxsb2dnaW5nX2NvbmZpZy5weUEuBADvv70HQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcY29yZVxlbWFpbC5weUgtBADvv70VQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcdGFza3NcZW1haWxfdGFza3MucHlFLAQA77+9D0M6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXHRhc2tzXF9faW5pdF9fLnB5QCsEAO+/vQVDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxjb3JlXGNzcmYucHlOKgQA77+9IUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXHNlcnZpY2VzXHJldmlld19zZXJ2aWNlLnB5RSkEAO+/vQ9DOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxzY2hlbWFzXHJldmlldy5weUUoBADvv70PQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcYXBpXHYxXHJldmlld3MucHlOJwQA77+9IUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXHNlcnZpY2VzXHVwbG9hZF9zZXJ2aWNlLnB5UCYEAO+/vSVDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxzZXJ2aWNlc1xwcm9wZXJ0eV9zZXJ2aWNlLnB5RyUEAO+/vRNDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxzY2hlbWFzXHByb3BlcnR5LnB5SCQEAO+/vRVDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxhcGlcdjFccHJvcGVydGllcy5weU8jBADvv70jQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcc2VydmljZXNcbWVzc2FnZV9zZXJ2aWNlLnB5RiIEAO+/vRFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxzY2hlbWFzXG1lc3NhZ2UucHlGIQQA77+9EUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGFwaVx2MVxtZXNzYWdlcy5weVIgBADvv70pQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcc2VydmljZXNcbWVtYmVyc2hpcF9zZXJ2aWNlLnB5SR8EAO+/vRdDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxzY2hlbWFzXG1lbWJlcnNoaXAucHlJHgQA77+9F0M6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGFwaVx2MVxtZW1iZXJzaGlwcy5weU8dBADvv70jQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcc2VydmljZXNcYm9va2luZ19zZXJ2aWNlLnB5RhwEAO+/vRFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxzY2hlbWFzXGJvb2tpbmcucHlGGwQA77+9EUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGFwaVx2MVxib29raW5ncy5weUYaBADvv70RQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcY29yZVxleGNlcHRpb25zLnB5TBkEAO+/vR1DOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxzZXJ2aWNlc1xhdXRoX3NlcnZpY2UucHlIGAQA77+9FUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXHNlcnZpY2VzXF9faW5pdF9fLnB5SBcEAO+/vRVDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxjb3JlXHJhdGVfbGltaXRlci5weUIWBADvv70JQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcYXBpXHYxXGF1dGgucHlDFQQA77+9C0M6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXHNjaGVtYXNcdXNlci5weUcUBADvv70TQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcc2NoZW1hc1xfX2luaXRfXy5weUMTBADvv70LQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcYXBpXHYxXGFkbWluLnB5RBIEAO+/vQpDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxhcGlcdjFccm91dGVyLnB5RhEEAO+/vRFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxhcGlcdjFcX19pbml0X18ucHlDEAQA77+9C0M6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGFwaVxfX2luaXRfXy5weToPAwB7QzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcbWFpbi5weUIOBADvv70JQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcbW9kZWxzXHVzZXIucHlECgQA77+9CkM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXG1vZGVsc1xyZXZpZXcucHlGDAQA77+9EUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXG1vZGVsc1xwcm9wZXJ0eS5weUULBADvv70PQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcbW9kZWxzXG1lc3NhZ2UucHlICgQA77+9FUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXG1vZGVsc1xtZW1iZXJzaGlwLnB5RQkEAO+/vQ9DOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxtb2RlbHNcYm9va2luZy5weUgIBADvv70VQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcbW9kZWxzXGJldHRlcmF1dGgucHlGBwQA77+9EUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXG1vZGVsc1xfX2luaXRfXy5weUMGBADvv70LQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcZGVwZW5kZW5jaWVzLnB5PwUEAO+/vQNDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxkYXRhYmFzZS5weTwEAwB/QzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcY29uZmlnLnB5RAMEAO+/vQpDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxjb3JlXHNlY3VyaXR5LnB5RAIEAO+/vQpDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxjb3JlXF9faW5pdF9fLnB5PwEEAO+/vQNDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxfX2luaXRfXy5weQoAAAAxAisAD++/vQvvv70Lawrvv70KDgjvv70H77+9Bu+/vQXvv70E77+9CyUO77+9D3oD77+9Aw8I77+9Au+/vQJ6Ce+/vQ80Du+/vQ5wC++/vQ4oCu+/vQrvv70KTQoGDO+/vQx4DDQK77+9CFQHbQbvv70F77+9BHUKUgl6CSwIAwcZBjgFUwQlBQMD77+9A1ICKwAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAATgTvv70fAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXHRhc2tzXG1lbWJlcnNoaXBfdGFza3MucHkxSATvv70TAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGNvcmVccGVybWlzc2lvbnMucHkwSwTvv70ZAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGNvcmVcbG9nZ2luZ19jb25maWcucHkvQgTvv70HAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGNvcmVcZW1haWwucHkuSQTvv70VAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXHRhc2tzXGVtYWlsX3Rhc2tzLnB5LUYE77+9DwFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFx0YXNrc1xfX2luaXRfXy5weSxBBO+/vQUBQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcY29yZVxjc3JmLnB5K08E77+9IQFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxzZXJ2aWNlc1xyZXZpZXdfc2VydmljZS5weSpGBO+/vQ8BQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcc2NoZW1hc1xyZXZpZXcucHkpRgTvv70PAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGFwaVx2MVxyZXZpZXdzLnB5KE8E77+9IQFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxzZXJ2aWNlc1x1cGxvYWRfc2VydmljZS5weSdRBO+/vSUBQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcc2VydmljZXNccHJvcGVydHlfc2VydmljZS5weSZIBO+/vRMBQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcc2NoZW1hc1xwcm9wZXJ0eS5weSVJBO+/vRUBQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcYXBpXHYxXHByb3BlcnRpZXMucHkkUATvv70jAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXHNlcnZpY2VzXG1lc3NhZ2Vfc2VydmljZS5weSNHBO+/vREBQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcc2NoZW1hc1xtZXNzYWdlLnB5IkcE77+9EQFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxhcGlcdjFcbWVzc2FnZXMucHkhUwTvv70pAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXHNlcnZpY2VzXG1lbWJlcnNoaXBfc2VydmljZS5weSBKBO+/vRcBQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcc2NoZW1hc1xtZW1iZXJzaGlwLnB5H0oE77+9FwFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxhcGlcdjFcbWVtYmVyc2hpcHMucHkeUATvv70jAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXHNlcnZpY2VzXGJvb2tpbmdfc2VydmljZS5weR1HBO+/vREBQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcc2NoZW1hc1xib29raW5nLnB5HEcE77+9EQFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxhcGlcdjFcYm9va2luZ3MucHkbRwTvv70RAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGNvcmVcZXhjZXB0aW9ucy5weRpNBO+/vR0BQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcc2VydmljZXNcYXV0aF9zZXJ2aWNlLnB5GUkE77+9FQFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxzZXJ2aWNlc1xfX2luaXRfXy5weRhJBO+/vRUBQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcY29yZVxyYXRlX2xpbWl0ZXIucHkXQwTvv70JAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGFwaVx2MVxhdXRoLnB5FkQE77+9CwFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxzY2hlbWFzXHVzZXIucHkVSATvv70TAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXHNjaGVtYXNcX19pbml0X18ucHkURATvv70LAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGFwaVx2MVxhZG1pbi5weRNFBO+/vQoBQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcYXBpXHYxXHJvdXRlci5weRJHBO+/vREBQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcYXBpXHYxXF9faW5pdF9fLnB5EUQE77+9CwFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxhcGlcX19pbml0X18ucHkQOwN7AUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXG1haW4ucHkPQwTvv70JAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXG1vZGVsc1x1c2VyLnB5DkUE77+9CgFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxtb2RlbHNccmV2aWV3LnB5CkcE77+9EQFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxtb2RlbHNccHJvcGVydHkucHkMRgTvv70PAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXG1vZGVsc1xtZXNzYWdlLnB5C0kE77+9FQFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxtb2RlbHNcbWVtYmVyc2hpcC5weQpGBO+/vQ8BQzpcVXNlcnNcc2FtYXJ0aGphaW5cRG93bmxvYWRzXHN0YXlcYmFja2VuZFxhcHBcbW9kZWxzXGJvb2tpbmcucHkJSQTvv70VAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXG1vZGVsc1xiZXR0ZXJhdXRoLnB5CEcE77+9EQFDOlxVc2Vyc1xzYW1hcnRoamFpblxEb3dubG9hZHNcc3RheVxiYWNrZW5kXGFwcFxtb2RlbHNcX19pbml0X18ucHkHRATvv70LAUM6XFVzZXJzXHNhbWFydGhqYWluXERvd25sb2Fkc1xzdGF5XGJhY2tlbmRcYXBwXGRlcGVuZGVuY2llcy5weQZABO+/vQMBQzpcVXN</t>
   </si>
   <si>
     <t>backend/.dockerignore</t>
@@ -9190,7 +9267,6 @@
   "id": str(p.id),
   "title": p.title,
   "city": p.city,
-  "country": p.country,
   "is_active": p.is_active,
   "price_per_night": float(p.price_per_night),
   "host_name": p.host.full_name if p.host else "Unknown",
@@ -9227,7 +9303,7 @@
   "id": str(m.id),
   "user_name": m.host.user.full_name if m.host and m.host.user else "Unknown",
   "email": m.host.user.email if m.host and m.host.user else "",
-  "plan": m.plan_type,
+  "plan_type": m.plan_type,
   "status": m.status,
   "amount": float(m.amount),
   "started_at": m.start_date.isoformat(),
@@ -9272,7 +9348,7 @@
   "host_id": str(b.host_id),
   "check_in": b.check_in.isoformat(),
   "check_out": b.check_out.isoformat(),
-  "total_price": b.total_price,
+  "total_price": float(b.total_price),
   "status": b.status,
   "booking_type": b.booking_type,
   "created_at": b.created_at.isoformat(),
@@ -9336,10 +9412,25 @@
   raise NotFoundError("User not found")
   user.is_active = not user.is_active
   await db.flush()
-  return {"id": str(user.id), "is_active": user.is_active}</t>
-  </si>
-  <si>
-    <t>IiIiQWRtaW4gZW5kcG9pbnRzIOKAlCBwbGF0Zm9ybSBtYW5hZ2VtZW50LiIiIgoKaW1wb3J0IHV1aWQKCmZyb20gZmFzdGFwaSBpbXBvcnQgQVBJUm91dGVyLCBEZXBlbmRzLCBRdWVyeQpmcm9tIHNxbGFsY2hlbXkgaW1wb3J0IGZ1bmMsIHNlbGVjdApmcm9tIHNxbGFsY2hlbXkuZXh0LmFzeW5jaW8gaW1wb3J0IEFzeW5jU2Vzc2lvbgpmcm9tIHNxbGFsY2hlbXkub3JtIGltcG9ydCBzZWxlY3RpbmxvYWQKCmZyb20gYXBwLmRhdGFiYXNlIGltcG9ydCBnZXRfZGIKZnJvbSBhcHAuZGVwZW5kZW5jaWVzIGltcG9ydCByZXF1aXJlX2FkbWluCmZyb20gYXBwLm1vZGVscy5ib29raW5nIGltcG9ydCBCb29raW5nLCBCb29raW5nU3RhdHVzCmZyb20gYXBwLm1vZGVscy5tZW1iZXJzaGlwIGltcG9ydCBNZW1iZXJzaGlwLCBNZW1iZXJzaGlwU3RhdHVzCmZyb20gYXBwLm1vZGVscy5wcm9wZXJ0eSBpbXBvcnQgUHJvcGVydHkKZnJvbSBhcHAubW9kZWxzLnVzZXIgaW1wb3J0IEhvc3RQcm9maWxlLCBVc2VyCmZyb20gYXBwLnNjaGVtYXMudXNlciBpbXBvcnQgVXNlck91dAoKcm91dGVyID0gQVBJUm91dGVyKCkKCgpAcm91dGVyLmdldCgiL3VzZXJzIiwgcmVzcG9uc2VfbW9kZWw9ZGljdCkKYXN5bmMgZGVmIGxpc3RfdXNlcnMoCiAgICBwYWdlOiBpbnQgPSBRdWVyeSgxLCBnZT0xKSwKICAgIHBhZ2Vfc2l6ZTogaW50ID0gUXVlcnkoMjAsIGdlPTEsIGxlPTEwMCksCiAgICBfYWRtaW46IFVzZXIgPSBEZXBlbmRzKHJlcXVpcmVfYWRtaW4pLAogICAgZGI6IEFzeW5jU2Vzc2lvbiA9IERlcGVuZHMoZ2V0X2RiKSwKKSAtPiBkaWN0OgogICAgIiIiTGlzdCBhbGwgdXNlcnMgKGFkbWluIG9ubHkpLiIiIgogICAgY291bnRfcmVzdWx0ID0gYXdhaXQgZGIuZXhlY3V0ZShzZWxlY3QoZnVuYy5jb3VudCgpKS5zZWxlY3RfZnJvbShVc2VyKSkKICAgIHRvdGFsID0gY291bnRfcmVzdWx0LnNjYWxhcigpIG9yIDAKCiAgICBzdG10ID0gKAogICAgICAgIHNlbGVjdChVc2VyKQogICAgICAgIC5vcmRlcl9ieShVc2VyLmNyZWF0ZWRfYXQuZGVzYygpKQogICAgICAgIC5vZmZzZXQoKHBhZ2UgLSAxKSAqIHBhZ2Vfc2l6ZSkKICAgICAgICAubGltaXQocGFnZV9zaXplKQogICAgKQogICAgcmVzdWx0ID0gYXdhaXQgZGIuZXhlY3V0ZShzdG10KQogICAgdXNlcnMgPSByZXN1bHQuc2NhbGFycygpLmFsbCgpCiAgICByZXR1cm4gewogICAgICAgICJpdGVtcyI6IFtVc2VyT3V0Lm1vZGVsX3ZhbGlkYXRlKHUpIGZvciB1IGluIHVzZXJzXSwKICAgICAgICAidG90YWwiOiB0b3RhbCwKICAgICAgICAicGFnZSI6IHBhZ2UsCiAgICAgICAgInBhZ2Vfc2l6ZSI6IHBhZ2Vfc2l6ZSwKICAgIH0KCgpAcm91dGVyLmdldCgiL3Byb3BlcnRpZXMiLCByZXNwb25zZV9tb2RlbD1kaWN0KQphc3luYyBkZWYgbGlzdF9hbGxfcHJvcGVydGllcygKICAgIHBhZ2U6IGludCA9IFF1ZXJ5KDEsIGdlPTEpLAogICAgcGFnZV9zaXplOiBpbnQgPSBRdWVyeSgyMCwgZ2U9MSwgbGU9MTAwKSwKICAgIF9hZG1pbjogVXNlciA9IERlcGVuZHMocmVxdWlyZV9hZG1pbiksCiAgICBkYjogQXN5bmNTZXNzaW9uID0gRGVwZW5kcyhnZXRfZGIpLAopIC0+IGRpY3Q6CiAgICAiIiJMaXN0IGFsbCBwcm9wZXJ0aWVzIChhZG1pbiBvbmx5KS4iIiIKICAgIGNvdW50X3Jlc3VsdCA9IGF3YWl0IGRiLmV4ZWN1dGUoc2VsZWN0KGZ1bmMuY291bnQoKSkuc2VsZWN0X2Zyb20oUHJvcGVydHkpKQogICAgdG90YWwgPSBjb3VudF9yZXN1bHQuc2NhbGFyKCkgb3IgMAoKICAgIHN0bXQgPSAoCiAgICAgICAgc2VsZWN0KFByb3BlcnR5KQogICAgICAgIC5vcHRpb25zKHNlbGVjdGlubG9hZChQcm9wZXJ0eS5ob3N0KSkKICAgICAgICAub3JkZXJfYnkoUHJvcGVydHkuY3JlYXRlZF9hdC5kZXNjKCkpCiAgICAgICAgLm9mZnNldCgocGFnZSAtIDEpICogcGFnZV9zaXplKQogICAgICAgIC5saW1pdChwYWdlX3NpemUpCiAgICApCiAgICByZXN1bHQgPSBhd2FpdCBkYi5leGVjdXRlKHN0bXQpCiAgICByZXR1cm4gewogICAgICAgICJpdGVtcyI6IFsKICAgICAgICAgICAgewogICAgICAgICAgICAgICAgImlkIjogc3RyKHAuaWQpLAogICAgICAgICAgICAgICAgInRpdGxlIjogcC50aXRsZSwKICAgICAgICAgICAgICAgICJjaXR5IjogcC5jaXR5LAogICAgICAgICAgICAgICAgImNvdW50cnkiOiBwLmNvdW50cnksCiAgICAgICAgICAgICAgICAiaXNfYWN0aXZlIjogcC5pc19hY3RpdmUsCiAgICAgICAgICAgICAgICAicHJpY2VfcGVyX25pZ2h0IjogZmxvYXQocC5wcmljZV9wZXJfbmlnaHQpLAogICAgICAgICAgICAgICAgImhvc3RfbmFtZSI6IHAuaG9zdC5mdWxsX25hbWUgaWYgcC5ob3N0IGVsc2UgIlVua25vd24iLAogICAgICAgICAgICB9CiAgICAgICAgICAgIGZvciBwIGluIHJlc3VsdC5zY2FsYXJzKCkuYWxsKCkKICAgICAgICBdLAogICAgICAgICJ0b3RhbCI6IHRvdGFsLAogICAgICAgICJwYWdlIjogcGFnZSwKICAgICAgICAicGFnZV9zaXplIjogcGFnZV9zaXplLAogICAgfQoKCkByb3V0ZXIuZ2V0KCIvbWVtYmVyc2hpcHMiLCByZXNwb25zZV9tb2RlbD1kaWN0KQphc3luYyBkZWYgbGlzdF9hbGxfbWVtYmVyc2hpcHMoCiAgICBwYWdlOiBpbnQgPSBRdWVyeSgxLCBnZT0xKSwKICAgIHBhZ2Vfc2l6ZTogaW50ID0gUXVlcnkoMjAsIGdlPTEsIGxlPTEwMCksCiAgICBfYWRtaW46IFVzZXIgPSBEZXBlbmRzKHJlcXVpcmVfYWRtaW4pLAogICAgZGI6IEFzeW5jU2Vzc2lvbiA9IERlcGVuZHMoZ2V0X2RiKSwKKSAtPiBkaWN0OgogICAgIiIiTGlzdCBhbGwgbWVtYmVyc2hpcHMgKGFkbWluIG9ubHkpLiIiIgogICAgY291bnRfcmVzdWx0ID0gYXdhaXQgZGIuZXhlY3V0ZShzZWxlY3QoZnVuYy5jb3VudCgpKS5zZWxlY3RfZnJvbShNZW1iZXJzaGlwKSkKICAgIHRvdGFsID0gY291bnRfcmVzdWx0LnNjYWxhcigpIG9yIDAKCiAgICBzdG10ID0gKAogICAgICAgIHNlbGVjdChNZW1iZXJzaGlwKQogICAgICAgIC5vcHRpb25zKAogICAgICAgICAgICBzZWxlY3RpbmxvYWQoTWVtYmVyc2hpcC5ob3N0KS5zZWxlY3RpbmxvYWQoSG9zdFByb2ZpbGUudXNlcikKICAgICAgICApCiAgICAgICAgLm9yZGVyX2J5KE1lbWJlcnNoaXAuY3JlYXRlZF9hdC5kZXNjKCkpCiAgICAgICAgLm9mZnNldCgocGFnZSAtIDEpICogcGFnZV9zaXplKQogICAgICAgIC5saW1pdChwYWdlX3NpemUpCiAgICApCiAgICByZXN1bHQgPSBhd2FpdCBkYi5leGVjdXRlKHN0bXQpCiAgICByZXR1cm4gewogICAgICAgICJpdGVtcyI6IFsKICAgICAgICAgICAgewogICAgICAgICAgICAgICAgImlkIjogc3RyKG0uaWQpLAogICAgICAgICAgICAgICAgInVzZXJfbmFtZSI6IG0uaG9zdC51c2VyLmZ1bGxfbmFtZSBpZiBtLmhvc3QgYW5kIG0uaG9zdC51c2VyIGVsc2UgIlVua25vd24iLAogICAgICAgICAgICAgICAgImVtYWlsIjogbS5ob3N0LnVzZXIuZW1haWwgaWYgbS5ob3N0IGFuZCBtLmhvc3QudXNlciBlbHNlICIiLAogICAgICAgICAgICAgICAgInBsYW4iOiBtLnBsYW5fdHlwZSwKICAgICAgICAgICAgICAgICJzdGF0dXMiOiBtLnN0YXR1cywKICAgICAgICAgICAgICAgICJhbW91bnQiOiBmbG9hdChtLmFtb3VudCksCiAgICAgICAgICAgICAgICAic3RhcnRlZF9hdCI6IG0uc3RhcnRfZGF0ZS5pc29mb3JtYXQoKSwKICAgICAgICAgICAgICAgICJleHBpcmVzX2F0IjogbS5lbmRfZGF0ZS5pc29mb3JtYXQoKSwKICAgICAgICAgICAgfQogICAgICAgICAgICBmb3IgbSBpbiByZXN1bHQuc2NhbGFycygpLmFsbCgpCiAgICAgICAgXSwKICAgICAgICAidG90YWwiOiB0b3RhbCwKICAgICAgICAicGFnZSI6IHBhZ2UsCiAgICAgICAgInBhZ2Vfc2l6ZSI6IHBhZ2Vfc2l6ZSwKICAgIH0KCgpAcm91dGVyLmdldCgiL2Jvb2tpbmdzIiwgcmVzcG9uc2VfbW9kZWw9ZGljdCkKYXN5bmMgZGVmIGxpc3RfYWxsX2Jvb2tpbmdzKAogICAgcGFnZTogaW50ID0gUXVlcnkoMSwgZ2U9MSksCiAgICBwYWdlX3NpemU6IGludCA9IFF1ZXJ5KDIwLCBnZT0xLCBsZT0xMDApLAogICAgX2FkbWluOiBVc2VyID0gRGVwZW5kcyhyZXF1aXJlX2FkbWluKSwKICAgIGRiOiBBc3luY1Nlc3Npb24gPSBEZXBlbmRzKGdldF9kYiksCikgLT4gZGljdDoKICAgICIiIkxpc3QgYWxsIGJvb2tpbmdzIChhZG1pbiBvbmx5KS4iIiIKICAgIGNvdW50X3Jlc3VsdCA9IGF3YWl0IGRiLmV4ZWN1dGUoc2VsZWN0KGZ1bmMuY291bnQoKSkuc2VsZWN0X2Zyb20oQm9va2luZykpCiAgICB0b3RhbCA9IGNvdW50X3Jlc3VsdC5zY2FsYXIoKSBvciAwCgogICAgc3RtdCA9ICgKICAgICAgICBzZWxlY3QoQm9va2luZykKICAgICAgICAub3B0aW9ucygKICAgICAgICAgICAgc2VsZWN0aW5sb2FkKEJvb2tpbmcucHJvcGVydHkpLAogICAgICAgICAgICBzZWxlY3RpbmxvYWQoQm9va2luZy5ndWVzdCksCiAgICAgICAgKQogICAgICAgIC5vcmRlcl9ieShCb29raW5nLmNyZWF0ZWRfYXQuZGVzYygpKQogICAgICAgIC5vZmZzZXQoKHBhZ2UgLSAxKSAqIHBhZ2Vfc2l6ZSkKICAgICAgICAubGltaXQocGFnZV9zaXplKQogICAgKQogICAgcmVzdWx0ID0gYXdhaXQgZGIuZXhlY3V0ZShzdG10KQogICAgYm9va2luZ3MgPSByZXN1bHQuc2NhbGFycygpLmFsbCgpCiAgICByZXR1cm4gewogICAgICAgICJpdGVtcyI6IFsKICAgICAgICAgICAgewogICAgICAgICAgICAgICAgImlkIjogc3RyKGIuaWQpLAogICAgICAgICAgICAgICAgInByb3BlcnR5X2lkIjogc3RyKGIucHJvcGVydHlfaWQpLAogICAgICAgICAgICAgICAgInByb3BlcnR5X3RpdGxlIjogYi5wcm9wZXJ0eS50aXRsZSBpZiBiLnByb3BlcnR5IGVsc2UgIkRlbGV0ZWQiLAogICAgICAgICAgICAgICAgImd1ZXN0X2lkIjogc3RyKGIuZ3Vlc3RfaWQpLAogICAgICAgICAgICAgICAgImd1ZXN0X25hbWUiOiBiLmd1ZXN0LmZ1bGxfbmFtZSBpZiBiLmd1ZXN0IGVsc2UgIlVua25vd24iLAogICAgICAgICAgICAgICAgImhvc3RfaWQiOiBzdHIoYi5ob3N0X2lkKSwKICAgICAgICAgICAgICAgICJjaGVja19pbiI6IGIuY2hlY2tfaW4uaXNvZm9ybWF0KCksCiAgICAgICAgICAgICAgICAiY2hlY2tfb3V0IjogYi5jaGVja19vdXQuaXNvZm9ybWF0KCksCiAgICAgICAgICAgICAgICAidG90YWxfcHJpY2UiOiBiLnRvdGFsX3ByaWNlLAogICAgICAgICAgICAgICAgInN0YXR1cyI6IGIuc3RhdHVzLAogICAgICAgICAgICAgICAgImJvb2tpbmdfdHlwZSI6IGIuYm9va2luZ190eXBlLAogICAgICAgICAgICAgICAgImNyZWF0ZWRfYXQiOiBiLmNyZWF0ZWRfYXQuaXNvZm9ybWF0KCksCiAgICAgICAgICAgIH0KICAgICAgICAgICAgZm9yIGIgaW4gYm9va2luZ3MKICAgICAgICBdLAogICAgICAgICJ0b3RhbCI6IHRvdGFsLAogICAgICAgICJwYWdlIjogcGFnZSwKICAgICAgICAicGFnZV9zaXplIjogcGFnZV9zaXplLAogICAgfQoKCkByb3V0ZXIuZ2V0KCIvZGFzaGJvYXJkIikKYXN5bmMgZGVmIGRhc2hib2FyZCgKICAgIF9hZG1pbjogVXNlciA9IERlcGVuZHMocmVxdWlyZV9hZG1pbiksCiAgICBkYjogQXN5bmNTZXNzaW9uID0gRGVwZW5kcyhnZXRfZGIpLAopIC0+IGRpY3Q6CiAgICAiIiJQbGF0Zm9ybSBkYXNoYm9hcmQgbWV0cmljcyAoYWRtaW4gb25seSkuIiIiCiAgICB0b3RhbF91c2VycyA9IChhd2FpdCBkYi5leGVjdXRlKHNlbGVjdChmdW5jLmNvdW50KCkpLnNlbGVjdF9mcm9tKFVzZXIpKSkuc2NhbGFyKCkgb3IgMAogICAgdG90YWxfcHJvcGVydGllcyA9IChhd2FpdCBkYi5leGVjdXRlKHNlbGVjdChmdW5jLmNvdW50KCkpLnNlbGVjdF9mcm9tKFByb3BlcnR5KSkpLnNjYWxhcigpIG9yIDAKICAgIGFjdGl2ZV9tZW1iZXJzaGlwcyA9ICgKICAgICAgICBhd2FpdCBkYi5leGVjdXRlKAogICAgICAgICAgICBzZWxlY3QoZnVuYy5jb3VudCgpKS5zZWxlY3RfZnJvbShNZW1iZXJzaGlwKS53aGVyZSgKICAgICAgICAgICAgICAgIE1lbWJlcnNoaXAuc3RhdHVzID09IE1lbWJlcnNoaXBTdGF0dXMuQUNUSVZFCiAgICAgICAgICAgICkKICAgICAgICApCiAgICApLnNjYWxhcigpIG9yIDAKICAgIHRvdGFsX2Jvb2tpbmdzID0gKGF3YWl0IGRiLmV4ZWN1dGUoc2VsZWN0KGZ1bmMuY291bnQoKSkuc2VsZWN0X2Zyb20oQm9va2luZykpKS5zY2FsYXIoKSBvciAwCiAgICBjb21wbGV0ZWRfYm9va2luZ3MgPSAoCiAgICAgICAgYXdhaXQgZGIuZXhlY3V0ZSgKICAgICAgICAgICAgc2VsZWN0KGZ1bmMuY291bnQoKSkuc2VsZWN0X2Zyb20oQm9va2luZykud2hlcmUoCiAgICAgICAgICAgICAgICBCb29raW5nLnN0YXR1cyA9PSBCb29raW5nU3RhdHVzLkNPTVBMRVRFRAogICAgICAgICAgICApCiAgICAgICAgKQogICAgKS5zY2FsYXIoKSBvciAwCiAgICBtb250aGx5X3JldmVudWUgPSAoCiAgICAgICAgYXdhaXQgZGIuZXhlY3V0ZSgKICAgICAgICAgICAgc2VsZWN0KGZ1bmMuc3VtKE1lbWJlcnNoaXAuYW1vdW50KSkud2hlcmUoCiAgICAgICAgICAgICAgICBNZW1iZXJzaGlwLnN0YXR1cyA9PSBNZW1iZXJzaGlwU3RhdHVzLkFDVElWRQogICAgICAgICAgICApCiAgICAgICAgKQogICAgKS5zY2FsYXIoKSBvciAwLjAKCiAgICByZXR1cm4gewogICAgICAgICJ0b3RhbF91c2VycyI6IHRvdGFsX3VzZXJzLAogICAgICAgICJ0b3RhbF9wcm9wZXJ0aWVzIjogdG90YWxfcHJvcGVydGllcywKICAgICAgICAiYWN0aXZlX21lbWJlcnMiOiBhY3RpdmVfbWVtYmVyc2hpcHMsCiAgICAgICAgInRvdGFsX2Jvb2tpbmdzIjogdG90YWxfYm9va2luZ3MsCiAgICAgICAgImNvbXBsZXRlZF9ib29raW5ncyI6IGNvbXBsZXRlZF9ib29raW5ncywKICAgICAgICAibW9udGhseV9yZXZlbnVlIjogZmxvYXQobW9udGhseV9yZXZlbnVlKSwKICAgICAgICAicGxhdGZvcm1fZ3Jvd3RoIjogMCwKICAgIH0KCgpAcm91dGVyLnB1dCgiL3VzZXJzL3t1c2VyX2lkfS9zdGF0dXMiKQphc3luYyBkZWYgdG9nZ2xlX3VzZXJfc3RhdHVzKAogICAgdXNlcl9pZDogdXVpZC5VVUlELAogICAgX2FkbWluOiBVc2VyID0gRGVwZW5kcyhyZXF1aXJlX2FkbWluKSwKICAgIGRiOiBBc3luY1Nlc3Npb24gPSBEZXBlbmRzKGdldF9kYiksCikgLT4gZGljdDoKICAgICIiIkVuYWJsZSBvciBkaXNhYmxlIGEgdXNlciBhY2NvdW50IChhZG1pbiBvbmx5KS4iIiIKICAgIHJlc3VsdCA9IGF3YWl0IGRiLmV4ZWN1dGUoc2VsZWN0KFVzZXIpLndoZXJlKFVzZXIuaWQgPT0gdXNlcl9pZCkpCiAgICB1c2VyID0gcmVzdWx0LnNjYWxhcl9vbmVfb3Jfbm9uZSgpCiAgICBpZiB1c2VyIGlzIE5vbmU6CiAgICAgICAgZnJvbSBhcHAuY29yZS5leGNlcHRpb25zIGltcG9ydCBOb3RGb3VuZEVycm9yICAjIG5vcWE6IEU0MDIKICAgICAgICByYWlzZSBOb3RGb3VuZEVycm9yKCJVc2VyIG5vdCBmb3VuZCIpCgogICAgdXNlci5pc19hY3RpdmUgPSBub3QgdXNlci5pc19hY3RpdmUKICAgIGF3YWl0IGRiLmZsdXNoKCkKICAgIHJldHVybiB7ImlkIjogc3RyKHVzZXIuaWQpLCAiaXNfYWN0aXZlIjogdXNlci5pc19hY3RpdmV9Cg==</t>
+  return {"id": str(user.id), "is_active": user.is_active}
+ @router.put("/properties/{property_id}/status")
+ async def toggle_property_status(
+  property_id: uuid.UUID,
+  _admin: User = Depends(require_admin),
+  db: AsyncSession = Depends(get_db),
+ ) -&gt; dict:
+  """Enable or disable a property listing (admin only)."""
+  result = await db.execute(select(Property).where(Property.id == property_id))
+  prop = result.scalar_one_or_none()
+  if prop is None:
+  from app.core.exceptions import NotFoundError # noqa: E402
+  raise NotFoundError("Property not found")
+  prop.is_active = not prop.is_active
+  await db.flush()
+  return {"id": str(prop.id), "is_active": prop.is_active}</t>
+  </si>
+  <si>
+    <t>IiIiQWRtaW4gZW5kcG9pbnRzIOKAlCBwbGF0Zm9ybSBtYW5hZ2VtZW50LiIiIgoKaW1wb3J0IHV1aWQKCmZyb20gZmFzdGFwaSBpbXBvcnQgQVBJUm91dGVyLCBEZXBlbmRzLCBRdWVyeQpmcm9tIHNxbGFsY2hlbXkgaW1wb3J0IGZ1bmMsIHNlbGVjdApmcm9tIHNxbGFsY2hlbXkuZXh0LmFzeW5jaW8gaW1wb3J0IEFzeW5jU2Vzc2lvbgpmcm9tIHNxbGFsY2hlbXkub3JtIGltcG9ydCBzZWxlY3RpbmxvYWQKCmZyb20gYXBwLmRhdGFiYXNlIGltcG9ydCBnZXRfZGIKZnJvbSBhcHAuZGVwZW5kZW5jaWVzIGltcG9ydCByZXF1aXJlX2FkbWluCmZyb20gYXBwLm1vZGVscy5ib29raW5nIGltcG9ydCBCb29raW5nLCBCb29raW5nU3RhdHVzCmZyb20gYXBwLm1vZGVscy5tZW1iZXJzaGlwIGltcG9ydCBNZW1iZXJzaGlwLCBNZW1iZXJzaGlwU3RhdHVzCmZyb20gYXBwLm1vZGVscy5wcm9wZXJ0eSBpbXBvcnQgUHJvcGVydHkKZnJvbSBhcHAubW9kZWxzLnVzZXIgaW1wb3J0IEhvc3RQcm9maWxlLCBVc2VyCmZyb20gYXBwLnNjaGVtYXMudXNlciBpbXBvcnQgVXNlck91dAoKcm91dGVyID0gQVBJUm91dGVyKCkKCgpAcm91dGVyLmdldCgiL3VzZXJzIiwgcmVzcG9uc2VfbW9kZWw9ZGljdCkKYXN5bmMgZGVmIGxpc3RfdXNlcnMoCiAgICBwYWdlOiBpbnQgPSBRdWVyeSgxLCBnZT0xKSwKICAgIHBhZ2Vfc2l6ZTogaW50ID0gUXVlcnkoMjAsIGdlPTEsIGxlPTEwMCksCiAgICBfYWRtaW46IFVzZXIgPSBEZXBlbmRzKHJlcXVpcmVfYWRtaW4pLAogICAgZGI6IEFzeW5jU2Vzc2lvbiA9IERlcGVuZHMoZ2V0X2RiKSwKKSAtPiBkaWN0OgogICAgIiIiTGlzdCBhbGwgdXNlcnMgKGFkbWluIG9ubHkpLiIiIgogICAgY291bnRfcmVzdWx0ID0gYXdhaXQgZGIuZXhlY3V0ZShzZWxlY3QoZnVuYy5jb3VudCgpKS5zZWxlY3RfZnJvbShVc2VyKSkKICAgIHRvdGFsID0gY291bnRfcmVzdWx0LnNjYWxhcigpIG9yIDAKCiAgICBzdG10ID0gKAogICAgICAgIHNlbGVjdChVc2VyKQogICAgICAgIC5vcmRlcl9ieShVc2VyLmNyZWF0ZWRfYXQuZGVzYygpKQogICAgICAgIC5vZmZzZXQoKHBhZ2UgLSAxKSAqIHBhZ2Vfc2l6ZSkKICAgICAgICAubGltaXQocGFnZV9zaXplKQogICAgKQogICAgcmVzdWx0ID0gYXdhaXQgZGIuZXhlY3V0ZShzdG10KQogICAgdXNlcnMgPSByZXN1bHQuc2NhbGFycygpLmFsbCgpCiAgICByZXR1cm4gewogICAgICAgICJpdGVtcyI6IFtVc2VyT3V0Lm1vZGVsX3ZhbGlkYXRlKHUpIGZvciB1IGluIHVzZXJzXSwKICAgICAgICAidG90YWwiOiB0b3RhbCwKICAgICAgICAicGFnZSI6IHBhZ2UsCiAgICAgICAgInBhZ2Vfc2l6ZSI6IHBhZ2Vfc2l6ZSwKICAgIH0KCgpAcm91dGVyLmdldCgiL3Byb3BlcnRpZXMiLCByZXNwb25zZV9tb2RlbD1kaWN0KQphc3luYyBkZWYgbGlzdF9hbGxfcHJvcGVydGllcygKICAgIHBhZ2U6IGludCA9IFF1ZXJ5KDEsIGdlPTEpLAogICAgcGFnZV9zaXplOiBpbnQgPSBRdWVyeSgyMCwgZ2U9MSwgbGU9MTAwKSwKICAgIF9hZG1pbjogVXNlciA9IERlcGVuZHMocmVxdWlyZV9hZG1pbiksCiAgICBkYjogQXN5bmNTZXNzaW9uID0gRGVwZW5kcyhnZXRfZGIpLAopIC0+IGRpY3Q6CiAgICAiIiJMaXN0IGFsbCBwcm9wZXJ0aWVzIChhZG1pbiBvbmx5KS4iIiIKICAgIGNvdW50X3Jlc3VsdCA9IGF3YWl0IGRiLmV4ZWN1dGUoc2VsZWN0KGZ1bmMuY291bnQoKSkuc2VsZWN0X2Zyb20oUHJvcGVydHkpKQogICAgdG90YWwgPSBjb3VudF9yZXN1bHQuc2NhbGFyKCkgb3IgMAoKICAgIHN0bXQgPSAoCiAgICAgICAgc2VsZWN0KFByb3BlcnR5KQogICAgICAgIC5vcHRpb25zKHNlbGVjdGlubG9hZChQcm9wZXJ0eS5ob3N0KSkKICAgICAgICAub3JkZXJfYnkoUHJvcGVydHkuY3JlYXRlZF9hdC5kZXNjKCkpCiAgICAgICAgLm9mZnNldCgocGFnZSAtIDEpICogcGFnZV9zaXplKQogICAgICAgIC5saW1pdChwYWdlX3NpemUpCiAgICApCiAgICByZXN1bHQgPSBhd2FpdCBkYi5leGVjdXRlKHN0bXQpCiAgICByZXR1cm4gewogICAgICAgICJpdGVtcyI6IFsKICAgICAgICAgICAgewogICAgICAgICAgICAgICAgImlkIjogc3RyKHAuaWQpLAogICAgICAgICAgICAgICAgInRpdGxlIjogcC50aXRsZSwKICAgICAgICAgICAgICAgICJjaXR5IjogcC5jaXR5LAogICAgICAgICAgICAgICAgImlzX2FjdGl2ZSI6IHAuaXNfYWN0aXZlLAogICAgICAgICAgICAgICAgInByaWNlX3Blcl9uaWdodCI6IGZsb2F0KHAucHJpY2VfcGVyX25pZ2h0KSwKICAgICAgICAgICAgICAgICJob3N0X25hbWUiOiBwLmhvc3QuZnVsbF9uYW1lIGlmIHAuaG9zdCBlbHNlICJVbmtub3duIiwKICAgICAgICAgICAgfQogICAgICAgICAgICBmb3IgcCBpbiByZXN1bHQuc2NhbGFycygpLmFsbCgpCiAgICAgICAgXSwKICAgICAgICAidG90YWwiOiB0b3RhbCwKICAgICAgICAicGFnZSI6IHBhZ2UsCiAgICAgICAgInBhZ2Vfc2l6ZSI6IHBhZ2Vfc2l6ZSwKICAgIH0KCgpAcm91dGVyLmdldCgiL21lbWJlcnNoaXBzIiwgcmVzcG9uc2VfbW9kZWw9ZGljdCkKYXN5bmMgZGVmIGxpc3RfYWxsX21lbWJlcnNoaXBzKAogICAgcGFnZTogaW50ID0gUXVlcnkoMSwgZ2U9MSksCiAgICBwYWdlX3NpemU6IGludCA9IFF1ZXJ5KDIwLCBnZT0xLCBsZT0xMDApLAogICAgX2FkbWluOiBVc2VyID0gRGVwZW5kcyhyZXF1aXJlX2FkbWluKSwKICAgIGRiOiBBc3luY1Nlc3Npb24gPSBEZXBlbmRzKGdldF9kYiksCikgLT4gZGljdDoKICAgICIiIkxpc3QgYWxsIG1lbWJlcnNoaXBzIChhZG1pbiBvbmx5KS4iIiIKICAgIGNvdW50X3Jlc3VsdCA9IGF3YWl0IGRiLmV4ZWN1dGUoc2VsZWN0KGZ1bmMuY291bnQoKSkuc2VsZWN0X2Zyb20oTWVtYmVyc2hpcCkpCiAgICB0b3RhbCA9IGNvdW50X3Jlc3VsdC5zY2FsYXIoKSBvciAwCgogICAgc3RtdCA9ICgKICAgICAgICBzZWxlY3QoTWVtYmVyc2hpcCkKICAgICAgICAub3B0aW9ucygKICAgICAgICAgICAgc2VsZWN0aW5sb2FkKE1lbWJlcnNoaXAuaG9zdCkuc2VsZWN0aW5sb2FkKEhvc3RQcm9maWxlLnVzZXIpCiAgICAgICAgKQogICAgICAgIC5vcmRlcl9ieShNZW1iZXJzaGlwLmNyZWF0ZWRfYXQuZGVzYygpKQogICAgICAgIC5vZmZzZXQoKHBhZ2UgLSAxKSAqIHBhZ2Vfc2l6ZSkKICAgICAgICAubGltaXQocGFnZV9zaXplKQogICAgKQogICAgcmVzdWx0ID0gYXdhaXQgZGIuZXhlY3V0ZShzdG10KQogICAgcmV0dXJuIHsKICAgICAgICAiaXRlbXMiOiBbCiAgICAgICAgICAgIHsKICAgICAgICAgICAgICAgICJpZCI6IHN0cihtLmlkKSwKICAgICAgICAgICAgICAgICJ1c2VyX25hbWUiOiBtLmhvc3QudXNlci5mdWxsX25hbWUgaWYgbS5ob3N0IGFuZCBtLmhvc3QudXNlciBlbHNlICJVbmtub3duIiwKICAgICAgICAgICAgICAgICJlbWFpbCI6IG0uaG9zdC51c2VyLmVtYWlsIGlmIG0uaG9zdCBhbmQgbS5ob3N0LnVzZXIgZWxzZSAiIiwKICAgICAgICAgICAgICAgICJwbGFuX3R5cGUiOiBtLnBsYW5fdHlwZSwKICAgICAgICAgICAgICAgICJzdGF0dXMiOiBtLnN0YXR1cywKICAgICAgICAgICAgICAgICJhbW91bnQiOiBmbG9hdChtLmFtb3VudCksCiAgICAgICAgICAgICAgICAic3RhcnRlZF9hdCI6IG0uc3RhcnRfZGF0ZS5pc29mb3JtYXQoKSwKICAgICAgICAgICAgICAgICJleHBpcmVzX2F0IjogbS5lbmRfZGF0ZS5pc29mb3JtYXQoKSwKICAgICAgICAgICAgfQogICAgICAgICAgICBmb3IgbSBpbiByZXN1bHQuc2NhbGFycygpLmFsbCgpCiAgICAgICAgXSwKICAgICAgICAidG90YWwiOiB0b3RhbCwKICAgICAgICAicGFnZSI6IHBhZ2UsCiAgICAgICAgInBhZ2Vfc2l6ZSI6IHBhZ2Vfc2l6ZSwKICAgIH0KCgpAcm91dGVyLmdldCgiL2Jvb2tpbmdzIiwgcmVzcG9uc2VfbW9kZWw9ZGljdCkKYXN5bmMgZGVmIGxpc3RfYWxsX2Jvb2tpbmdzKAogICAgcGFnZTogaW50ID0gUXVlcnkoMSwgZ2U9MSksCiAgICBwYWdlX3NpemU6IGludCA9IFF1ZXJ5KDIwLCBnZT0xLCBsZT0xMDApLAogICAgX2FkbWluOiBVc2VyID0gRGVwZW5kcyhyZXF1aXJlX2FkbWluKSwKICAgIGRiOiBBc3luY1Nlc3Npb24gPSBEZXBlbmRzKGdldF9kYiksCikgLT4gZGljdDoKICAgICIiIkxpc3QgYWxsIGJvb2tpbmdzIChhZG1pbiBvbmx5KS4iIiIKICAgIGNvdW50X3Jlc3VsdCA9IGF3YWl0IGRiLmV4ZWN1dGUoc2VsZWN0KGZ1bmMuY291bnQoKSkuc2VsZWN0X2Zyb20oQm9va2luZykpCiAgICB0b3RhbCA9IGNvdW50X3Jlc3VsdC5zY2FsYXIoKSBvciAwCgogICAgc3RtdCA9ICgKICAgICAgICBzZWxlY3QoQm9va2luZykKICAgICAgICAub3B0aW9ucygKICAgICAgICAgICAgc2VsZWN0aW5sb2FkKEJvb2tpbmcucHJvcGVydHkpLAogICAgICAgICAgICBzZWxlY3RpbmxvYWQoQm9va2luZy5ndWVzdCksCiAgICAgICAgKQogICAgICAgIC5vcmRlcl9ieShCb29raW5nLmNyZWF0ZWRfYXQuZGVzYygpKQogICAgICAgIC5vZmZzZXQoKHBhZ2UgLSAxKSAqIHBhZ2Vfc2l6ZSkKICAgICAgICAubGltaXQocGFnZV9zaXplKQogICAgKQogICAgcmVzdWx0ID0gYXdhaXQgZGIuZXhlY3V0ZShzdG10KQogICAgYm9va2luZ3MgPSByZXN1bHQuc2NhbGFycygpLmFsbCgpCiAgICByZXR1cm4gewogICAgICAgICJpdGVtcyI6IFsKICAgICAgICAgICAgewogICAgICAgICAgICAgICAgImlkIjogc3RyKGIuaWQpLAogICAgICAgICAgICAgICAgInByb3BlcnR5X2lkIjogc3RyKGIucHJvcGVydHlfaWQpLAogICAgICAgICAgICAgICAgInByb3BlcnR5X3RpdGxlIjogYi5wcm9wZXJ0eS50aXRsZSBpZiBiLnByb3BlcnR5IGVsc2UgIkRlbGV0ZWQiLAogICAgICAgICAgICAgICAgImd1ZXN0X2lkIjogc3RyKGIuZ3Vlc3RfaWQpLAogICAgICAgICAgICAgICAgImd1ZXN0X25hbWUiOiBiLmd1ZXN0LmZ1bGxfbmFtZSBpZiBiLmd1ZXN0IGVsc2UgIlVua25vd24iLAogICAgICAgICAgICAgICAgImhvc3RfaWQiOiBzdHIoYi5ob3N0X2lkKSwKICAgICAgICAgICAgICAgICJjaGVja19pbiI6IGIuY2hlY2tfaW4uaXNvZm9ybWF0KCksCiAgICAgICAgICAgICAgICAiY2hlY2tfb3V0IjogYi5jaGVja19vdXQuaXNvZm9ybWF0KCksCiAgICAgICAgICAgICAgICAidG90YWxfcHJpY2UiOiBmbG9hdChiLnRvdGFsX3ByaWNlKSwKICAgICAgICAgICAgICAgICJzdGF0dXMiOiBiLnN0YXR1cywKICAgICAgICAgICAgICAgICJib29raW5nX3R5cGUiOiBiLmJvb2tpbmdfdHlwZSwKICAgICAgICAgICAgICAgICJjcmVhdGVkX2F0IjogYi5jcmVhdGVkX2F0Lmlzb2Zvcm1hdCgpLAogICAgICAgICAgICB9CiAgICAgICAgICAgIGZvciBiIGluIGJvb2tpbmdzCiAgICAgICAgXSwKICAgICAgICAidG90YWwiOiB0b3RhbCwKICAgICAgICAicGFnZSI6IHBhZ2UsCiAgICAgICAgInBhZ2Vfc2l6ZSI6IHBhZ2Vfc2l6ZSwKICAgIH0KCgpAcm91dGVyLmdldCgiL2Rhc2hib2FyZCIpCmFzeW5jIGRlZiBkYXNoYm9hcmQoCiAgICBfYWRtaW46IFVzZXIgPSBEZXBlbmRzKHJlcXVpcmVfYWRtaW4pLAogICAgZGI6IEFzeW5jU2Vzc2lvbiA9IERlcGVuZHMoZ2V0X2RiKSwKKSAtPiBkaWN0OgogICAgIiIiUGxhdGZvcm0gZGFzaGJvYXJkIG1ldHJpY3MgKGFkbWluIG9ubHkpLiIiIgogICAgdG90YWxfdXNlcnMgPSAoYXdhaXQgZGIuZXhlY3V0ZShzZWxlY3QoZnVuYy5jb3VudCgpKS5zZWxlY3RfZnJvbShVc2VyKSkpLnNjYWxhcigpIG9yIDAKICAgIHRvdGFsX3Byb3BlcnRpZXMgPSAoYXdhaXQgZGIuZXhlY3V0ZShzZWxlY3QoZnVuYy5jb3VudCgpKS5zZWxlY3RfZnJvbShQcm9wZXJ0eSkpKS5zY2FsYXIoKSBvciAwCiAgICBhY3RpdmVfbWVtYmVyc2hpcHMgPSAoCiAgICAgICAgYXdhaXQgZGIuZXhlY3V0ZSgKICAgICAgICAgICAgc2VsZWN0KGZ1bmMuY291bnQoKSkuc2VsZWN0X2Zyb20oTWVtYmVyc2hpcCkud2hlcmUoCiAgICAgICAgICAgICAgICBNZW1iZXJzaGlwLnN0YXR1cyA9PSBNZW1iZXJzaGlwU3RhdHVzLkFDVElWRQogICAgICAgICAgICApCiAgICAgICAgKQogICAgKS5zY2FsYXIoKSBvciAwCiAgICB0b3RhbF9ib29raW5ncyA9IChhd2FpdCBkYi5leGVjdXRlKHNlbGVjdChmdW5jLmNvdW50KCkpLnNlbGVjdF9mcm9tKEJvb2tpbmcpKSkuc2NhbGFyKCkgb3IgMAogICAgY29tcGxldGVkX2Jvb2tpbmdzID0gKAogICAgICAgIGF3YWl0IGRiLmV4ZWN1dGUoCiAgICAgICAgICAgIHNlbGVjdChmdW5jLmNvdW50KCkpLnNlbGVjdF9mcm9tKEJvb2tpbmcpLndoZXJlKAogICAgICAgICAgICAgICAgQm9va2luZy5zdGF0dXMgPT0gQm9va2luZ1N0YXR1cy5DT01QTEVURUQKICAgICAgICAgICAgKQogICAgICAgICkKICAgICkuc2NhbGFyKCkgb3IgMAogICAgbW9udGhseV9yZXZlbnVlID0gKAogICAgICAgIGF3YWl0IGRiLmV4ZWN1dGUoCiAgICAgICAgICAgIHNlbGVjdChmdW5jLnN1bShNZW1iZXJzaGlwLmFtb3VudCkpLndoZXJlKAogICAgICAgICAgICAgICAgTWVtYmVyc2hpcC5zdGF0dXMgPT0gTWVtYmVyc2hpcFN0YXR1cy5BQ1RJVkUKICAgICAgICAgICAgKQogICAgICAgICkKICAgICkuc2NhbGFyKCkgb3IgMC4wCgogICAgcmV0dXJuIHsKICAgICAgICAidG90YWxfdXNlcnMiOiB0b3RhbF91c2VycywKICAgICAgICAidG90YWxfcHJvcGVydGllcyI6IHRvdGFsX3Byb3BlcnRpZXMsCiAgICAgICAgImFjdGl2ZV9tZW1iZXJzIjogYWN0aXZlX21lbWJlcnNoaXBzLAogICAgICAgICJ0b3RhbF9ib29raW5ncyI6IHRvdGFsX2Jvb2tpbmdzLAogICAgICAgICJjb21wbGV0ZWRfYm9va2luZ3MiOiBjb21wbGV0ZWRfYm9va2luZ3MsCiAgICAgICAgIm1vbnRobHlfcmV2ZW51ZSI6IGZsb2F0KG1vbnRobHlfcmV2ZW51ZSksCiAgICAgICAgInBsYXRmb3JtX2dyb3d0aCI6IDAsCiAgICB9CgoKQHJvdXRlci5wdXQoIi91c2Vycy97dXNlcl9pZH0vc3RhdHVzIikKYXN5bmMgZGVmIHRvZ2dsZV91c2VyX3N0YXR1cygKICAgIHVzZXJfaWQ6IHV1aWQuVVVJRCwKICAgIF9hZG1pbjogVXNlciA9IERlcGVuZHMocmVxdWlyZV9hZG1pbiksCiAgICBkYjogQXN5bmNTZXNzaW9uID0gRGVwZW5kcyhnZXRfZGIpLAopIC0+IGRpY3Q6CiAgICAiIiJFbmFibGUgb3IgZGlzYWJsZSBhIHVzZXIgYWNjb3VudCAoYWRtaW4gb25seSkuIiIiCiAgICByZXN1bHQgPSBhd2FpdCBkYi5leGVjdXRlKHNlbGVjdChVc2VyKS53aGVyZShVc2VyLmlkID09IHVzZXJfaWQpKQogICAgdXNlciA9IHJlc3VsdC5zY2FsYXJfb25lX29yX25vbmUoKQogICAgaWYgdXNlciBpcyBOb25lOgogICAgICAgIGZyb20gYXBwLmNvcmUuZXhjZXB0aW9ucyBpbXBvcnQgTm90Rm91bmRFcnJvciAgIyBub3FhOiBFNDAyCiAgICAgICAgcmFpc2UgTm90Rm91bmRFcnJvcigiVXNlciBub3QgZm91bmQiKQoKICAgIHVzZXIuaXNfYWN0aXZlID0gbm90IHVzZXIuaXNfYWN0aXZlCiAgICBhd2FpdCBkYi5mbHVzaCgpCiAgICByZXR1cm4geyJpZCI6IHN0cih1c2VyLmlkKSwgImlzX2FjdGl2ZSI6IHVzZXIuaXNfYWN0aXZlfQoKCkByb3V0ZXIucHV0KCIvcHJvcGVydGllcy97cHJvcGVydHlfaWR9L3N0YXR1cyIpCmFzeW5jIGRlZiB0b2dnbGVfcHJvcGVydHlfc3RhdHVzKAogICAgcHJvcGVydHlfaWQ6IHV1aWQuVVVJRCwKICAgIF9hZG1pbjogVXNlciA9IERlcGVuZHMocmVxdWlyZV9hZG1pbiksCiAgICBkYjogQXN5bmNTZXNzaW9uID0gRGVwZW5kcyhnZXRfZGIpLAopIC0+IGRpY3Q6CiAgICAiIiJFbmFibGUgb3IgZGlzYWJsZSBhIHByb3BlcnR5IGxpc3RpbmcgKGFkbWluIG9ubHkpLiIiIgogICAgcmVzdWx0ID0gYXdhaXQgZGIuZXhlY3V0ZShzZWxlY3QoUHJvcGVydHkpLndoZXJlKFByb3BlcnR5LmlkID09IHByb3BlcnR5X2lkKSkKICAgIHByb3AgPSByZXN1bHQuc2NhbGFyX29uZV9vcl9ub25lKCkKICAgIGlmIHByb3AgaXMgTm9uZToKICAgICAgICBmcm9tIGFwcC5jb3JlLmV4Y2VwdGlvbnMgaW1wb3J0IE5vdEZvdW5kRXJyb3IgICMgbm9xYTogRTQwMgogICAgICAgIHJhaXNlIE5vdEZvdW5kRXJyb3IoIlByb3BlcnR5IG5vdCBmb3VuZCIpCgogICAgcHJvcC5pc19hY3RpdmUgPSBub3QgcHJvcC5pc19hY3RpdmUKICAgIGF3YWl0IGRiLmZsdXNoKCkKICAgIHJldHVybiB7ImlkIjogc3RyKHByb3AuaWQpLCAiaXNfYWN0aXZlIjogcHJvcC5pc19hY3RpdmV9Cg==</t>
   </si>
   <si>
     <t>backend/app/api/v1/auth.py</t>
@@ -11401,6 +11492,8 @@
   property_id: uuid.UUID
   guest_id: uuid.UUID
   host_id: uuid.UUID
+  property_title: str | None = None
+  other_party_name: str | None = None
   created_at: datetime
   updated_at: datetime
   last_message: MessageOut | None = None
@@ -11414,7 +11507,7 @@
   page_size: int</t>
   </si>
   <si>
-    <t>IiIiTWVzc2FnaW5nIFB5ZGFudGljIHNjaGVtYXMuIiIiCgppbXBvcnQgdXVpZApmcm9tIGRhdGV0aW1lIGltcG9ydCBkYXRldGltZQoKZnJvbSBweWRhbnRpYyBpbXBvcnQgQmFzZU1vZGVsLCBGaWVsZAoKCmNsYXNzIENvbnZlcnNhdGlvbkNyZWF0ZShCYXNlTW9kZWwpOgogICAgIiIiUmVxdWVzdCBzY2hlbWEgZm9yIHN0YXJ0aW5nIGEgbmV3IGNvbnZlcnNhdGlvbiBhYm91dCBhIHByb3BlcnR5LiIiIgogICAgcHJvcGVydHlfaWQ6IHV1aWQuVVVJRAogICAgbWVzc2FnZTogc3RyID0gRmllbGQoLi4uLCBtaW5fbGVuZ3RoPTEsIG1heF9sZW5ndGg9NTAwMCkKCgpjbGFzcyBNZXNzYWdlQ3JlYXRlKEJhc2VNb2RlbCk6CiAgICAiIiJSZXF1ZXN0IHNjaGVtYSBmb3Igc2VuZGluZyBhIG1lc3NhZ2UgaW4gYSBjb252ZXJzYXRpb24uIiIiCiAgICBjb250ZW50OiBzdHIgPSBGaWVsZCguLi4sIG1pbl9sZW5ndGg9MSwgbWF4X2xlbmd0aD01MDAwKQoKCmNsYXNzIE1lc3NhZ2VPdXQoQmFzZU1vZGVsKToKICAgICIiIlJlc3BvbnNlIHNjaGVtYSBmb3IgYSBzaW5nbGUgbWVzc2FnZS4iIiIKICAgIGlkOiB1dWlkLlVVSUQKICAgIGNvbnZlcnNhdGlvbl9pZDogdXVpZC5VVUlECiAgICBzZW5kZXJfaWQ6IHV1aWQuVVVJRAogICAgY29udGVudDogc3RyCiAgICBtZXNzYWdlX3R5cGU6IHN0ciA9ICJ0ZXh0IgogICAgaXNfcmVhZDogYm9vbAogICAgY3JlYXRlZF9hdDogZGF0ZXRpbWUKCiAgICBtb2RlbF9jb25maWcgPSB7ImZyb21fYXR0cmlidXRlcyI6IFRydWV9CgoKY2xhc3MgQ29udmVyc2F0aW9uT3V0KEJhc2VNb2RlbCk6CiAgICAiIiJSZXNwb25zZSBzY2hlbWEgZm9yIGEgY29udmVyc2F0aW9uIHdpdGggbGFzdCBtZXNzYWdlIGFuZCB1bnJlYWQgY291bnQuIiIiCiAgICBpZDogdXVpZC5VVUlECiAgICBwcm9wZXJ0eV9pZDogdXVpZC5VVUlECiAgICBndWVzdF9pZDogdXVpZC5VVUlECiAgICBob3N0X2lkOiB1dWlkLlVVSUQKICAgIGNyZWF0ZWRfYXQ6IGRhdGV0aW1lCiAgICB1cGRhdGVkX2F0OiBkYXRldGltZQogICAgbGFzdF9tZXNzYWdlOiBNZXNzYWdlT3V0IHwgTm9uZSA9IE5vbmUKICAgIHVucmVhZF9jb3VudDogaW50ID0gMAoKICAgIG1vZGVsX2NvbmZpZyA9IHsiZnJvbV9hdHRyaWJ1dGVzIjogVHJ1ZX0KCgpjbGFzcyBQYWdpbmF0ZWRNZXNzYWdlcyhCYXNlTW9kZWwpOgogICAgIiIiUGFnaW5hdGVkIHdyYXBwZXIgZm9yIG1lc3NhZ2UgbGlzdHMuIiIiCiAgICBpdGVtczogbGlzdFtNZXNzYWdlT3V0XQogICAgdG90YWw6IGludAogICAgcGFnZTogaW50CiAgICBwYWdlX3NpemU6IGludAo=</t>
+    <t>IiIiTWVzc2FnaW5nIFB5ZGFudGljIHNjaGVtYXMuIiIiCgppbXBvcnQgdXVpZApmcm9tIGRhdGV0aW1lIGltcG9ydCBkYXRldGltZQoKZnJvbSBweWRhbnRpYyBpbXBvcnQgQmFzZU1vZGVsLCBGaWVsZAoKCmNsYXNzIENvbnZlcnNhdGlvbkNyZWF0ZShCYXNlTW9kZWwpOgogICAgIiIiUmVxdWVzdCBzY2hlbWEgZm9yIHN0YXJ0aW5nIGEgbmV3IGNvbnZlcnNhdGlvbiBhYm91dCBhIHByb3BlcnR5LiIiIgogICAgcHJvcGVydHlfaWQ6IHV1aWQuVVVJRAogICAgbWVzc2FnZTogc3RyID0gRmllbGQoLi4uLCBtaW5fbGVuZ3RoPTEsIG1heF9sZW5ndGg9NTAwMCkKCgpjbGFzcyBNZXNzYWdlQ3JlYXRlKEJhc2VNb2RlbCk6CiAgICAiIiJSZXF1ZXN0IHNjaGVtYSBmb3Igc2VuZGluZyBhIG1lc3NhZ2UgaW4gYSBjb252ZXJzYXRpb24uIiIiCiAgICBjb250ZW50OiBzdHIgPSBGaWVsZCguLi4sIG1pbl9sZW5ndGg9MSwgbWF4X2xlbmd0aD01MDAwKQoKCmNsYXNzIE1lc3NhZ2VPdXQoQmFzZU1vZGVsKToKICAgICIiIlJlc3BvbnNlIHNjaGVtYSBmb3IgYSBzaW5nbGUgbWVzc2FnZS4iIiIKICAgIGlkOiB1dWlkLlVVSUQKICAgIGNvbnZlcnNhdGlvbl9pZDogdXVpZC5VVUlECiAgICBzZW5kZXJfaWQ6IHV1aWQuVVVJRAogICAgY29udGVudDogc3RyCiAgICBtZXNzYWdlX3R5cGU6IHN0ciA9ICJ0ZXh0IgogICAgaXNfcmVhZDogYm9vbAogICAgY3JlYXRlZF9hdDogZGF0ZXRpbWUKCiAgICBtb2RlbF9jb25maWcgPSB7ImZyb21fYXR0cmlidXRlcyI6IFRydWV9CgoKY2xhc3MgQ29udmVyc2F0aW9uT3V0KEJhc2VNb2RlbCk6CiAgICAiIiJSZXNwb25zZSBzY2hlbWEgZm9yIGEgY29udmVyc2F0aW9uIHdpdGggbGFzdCBtZXNzYWdlIGFuZCB1bnJlYWQgY291bnQuIiIiCiAgICBpZDogdXVpZC5VVUlECiAgICBwcm9wZXJ0eV9pZDogdXVpZC5VVUlECiAgICBndWVzdF9pZDogdXVpZC5VVUlECiAgICBob3N0X2lkOiB1dWlkLlVVSUQKICAgIHByb3BlcnR5X3RpdGxlOiBzdHIgfCBOb25lID0gTm9uZQogICAgb3RoZXJfcGFydHlfbmFtZTogc3RyIHwgTm9uZSA9IE5vbmUKICAgIGNyZWF0ZWRfYXQ6IGRhdGV0aW1lCiAgICB1cGRhdGVkX2F0OiBkYXRldGltZQogICAgbGFzdF9tZXNzYWdlOiBNZXNzYWdlT3V0IHwgTm9uZSA9IE5vbmUKICAgIHVucmVhZF9jb3VudDogaW50ID0gMAoKICAgIG1vZGVsX2NvbmZpZyA9IHsiZnJvbV9hdHRyaWJ1dGVzIjogVHJ1ZX0KCgpjbGFzcyBQYWdpbmF0ZWRNZXNzYWdlcyhCYXNlTW9kZWwpOgogICAgIiIiUGFnaW5hdGVkIHdyYXBwZXIgZm9yIG1lc3NhZ2UgbGlzdHMuIiIiCiAgICBpdGVtczogbGlzdFtNZXNzYWdlT3V0XQogICAgdG90YWw6IGludAogICAgcGFnZTogaW50CiAgICBwYWdlX3NpemU6IGludAo=</t>
   </si>
   <si>
     <t>backend/app/schemas/property.py</t>
@@ -13387,10 +13480,31 @@
   endpoint,
   headers={"Authorization": f"Bearer {host_token}"},
   )
-  assert response.status_code == 403, f"Expected 403 for {endpoint}"</t>
-  </si>
-  <si>
-    <t>IiIiSW50ZWdyYXRpb24gdGVzdHMgZm9yIGFkbWluIGVuZHBvaW50cyDigJQgZXh0ZW5kZWQgc2NlbmFyaW9zLiIiIgoKaW1wb3J0IHV1aWQKCmltcG9ydCBweXRlc3QKZnJvbSBodHRweCBpbXBvcnQgQXN5bmNDbGllbnQKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9hZG1pbl9saXN0X2Jvb2tpbmdzKGNsaWVudDogQXN5bmNDbGllbnQsIGFkbWluX3Rva2VuOiBzdHIpIC0+IE5vbmU6CiAgICAiIiJBZG1pbiBjYW4gbGlzdCBhbGwgYm9va2luZ3MuIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5nZXQoCiAgICAgICAgIi9hcGkvdjEvYWRtaW4vYm9va2luZ3MiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2FkbWluX3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMAogICAgZGF0YSA9IHJlc3BvbnNlLmpzb24oKQogICAgYXNzZXJ0ICJpdGVtcyIgaW4gZGF0YQogICAgYXNzZXJ0ICJ0b3RhbCIgaW4gZGF0YQoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X2FkbWluX3RvZ2dsZV91c2VyX3N0YXR1cygKICAgIGNsaWVudDogQXN5bmNDbGllbnQsIGFkbWluX3Rva2VuOiBzdHIsIHRlc3RfdXNlcgopIC0+IE5vbmU6CiAgICAiIiJBZG1pbiBjYW4gdG9nZ2xlIGEgdXNlcidzIGFjdGl2ZSBzdGF0dXMuIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5wdXQoCiAgICAgICAgZiIvYXBpL3YxL2FkbWluL3VzZXJzL3t0ZXN0X3VzZXIuaWR9L3N0YXR1cyIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7YWRtaW5fdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgZGF0YVsiaXNfYWN0aXZlIl0gaXMgRmFsc2UKCiAgICAjIFRvZ2dsZSBiYWNrCiAgICByZXNwb25zZTIgPSBhd2FpdCBjbGllbnQucHV0KAogICAgICAgIGYiL2FwaS92MS9hZG1pbi91c2Vycy97dGVzdF91c2VyLmlkfS9zdGF0dXMiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2FkbWluX3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlMi5zdGF0dXNfY29kZSA9PSAyMDAKICAgIGFzc2VydCByZXNwb25zZTIuanNvbigpWyJpc19hY3RpdmUiXSBpcyBUcnVlCgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3RfYWRtaW5fdG9nZ2xlX25vbmV4aXN0ZW50X3VzZXIoCiAgICBjbGllbnQ6IEFzeW5jQ2xpZW50LCBhZG1pbl90b2tlbjogc3RyCikgLT4gTm9uZToKICAgICIiIlRvZ2dsaW5nIGEgbm9uZXhpc3RlbnQgdXNlciByZXR1cm5zIDQwNC4iIiIKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LnB1dCgKICAgICAgICBmIi9hcGkvdjEvYWRtaW4vdXNlcnMve3V1aWQudXVpZDQoKX0vc3RhdHVzIiwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHthZG1pbl90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSA0MDQKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9hZG1pbl9kYXNoYm9hcmRfd2l0aF9kYXRhKAogICAgY2xpZW50OiBBc3luY0NsaWVudCwKICAgIGFkbWluX3Rva2VuOiBzdHIsCiAgICBob3N0X3dpdGhfbWVtYmVyc2hpcDogc3RyLAogICAgdXNlcl90b2tlbjogc3RyLAogICAgY3JlYXRlZF9wcm9wZXJ0eTogZGljdCwKKSAtPiBOb25lOgogICAgIiIiRGFzaGJvYXJkIHNob3dzIGNvcnJlY3Qgc3RhdGlzdGljcyB3aGVuIGRhdGEgZXhpc3RzLiIiIgogICAgcmVzcG9uc2UgPSBhd2FpdCBjbGllbnQuZ2V0KAogICAgICAgICIvYXBpL3YxL2FkbWluL2Rhc2hib2FyZCIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7YWRtaW5fdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgZGF0YVsidG90YWxfdXNlcnMiXSA+PSAyCiAgICBhc3NlcnQgZGF0YVsidG90YWxfcHJvcGVydGllcyJdID49IDEKICAgIGFzc2VydCBkYXRhWyJhY3RpdmVfbWVtYmVycyJdID49IDEKICAgIGFzc2VydCAibW9udGhseV9yZXZlbnVlIiBpbiBkYXRhCgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3RfYWRtaW5fbGlzdF9wcm9wZXJ0aWVzX3dpdGhfZGF0YSgKICAgIGNsaWVudDogQXN5bmNDbGllbnQsIGFkbWluX3Rva2VuOiBzdHIsIGNyZWF0ZWRfcHJvcGVydHk6IGRpY3QKKSAtPiBOb25lOgogICAgIiIiQWRtaW4gcHJvcGVydGllcyBsaXN0IHJldHVybnMgZGF0YS4iIiIKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LmdldCgKICAgICAgICAiL2FwaS92MS9hZG1pbi9wcm9wZXJ0aWVzIiwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHthZG1pbl90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSAyMDAKICAgIGRhdGEgPSByZXNwb25zZS5qc29uKCkKICAgIGFzc2VydCBkYXRhWyJ0b3RhbCJdID49IDEKICAgIGFzc2VydCBsZW4oZGF0YVsiaXRlbXMiXSkgPj0gMQogICAgIyBDaGVjayBpdGVtIHN0cnVjdHVyZQogICAgaXRlbSA9IGRhdGFbIml0ZW1zIl1bMF0KICAgIGFzc2VydCAiaWQiIGluIGl0ZW0KICAgIGFzc2VydCAidGl0bGUiIGluIGl0ZW0KICAgIGFzc2VydCAiY2l0eSIgaW4gaXRlbQogICAgYXNzZXJ0ICJpc19hY3RpdmUiIGluIGl0ZW0KCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9hZG1pbl9saXN0X21lbWJlcnNoaXBzX3dpdGhfZGF0YSgKICAgIGNsaWVudDogQXN5bmNDbGllbnQsIGFkbWluX3Rva2VuOiBzdHIsIGhvc3Rfd2l0aF9tZW1iZXJzaGlwOiBzdHIKKSAtPiBOb25lOgogICAgIiIiQWRtaW4gbWVtYmVyc2hpcHMgbGlzdCByZXR1cm5zIGRhdGEuIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5nZXQoCiAgICAgICAgIi9hcGkvdjEvYWRtaW4vbWVtYmVyc2hpcHMiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2FkbWluX3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMAogICAgZGF0YSA9IHJlc3BvbnNlLmpzb24oKQogICAgYXNzZXJ0IGRhdGFbInRvdGFsIl0gPj0gMQogICAgaXRlbSA9IGRhdGFbIml0ZW1zIl1bMF0KICAgIGFzc2VydCAiaWQiIGluIGl0ZW0KICAgIGFzc2VydCAicGxhbl90eXBlIiBpbiBpdGVtCiAgICBhc3NlcnQgInN0YXR1cyIgaW4gaXRlbQogICAgYXNzZXJ0ICJhbW91bnQiIGluIGl0ZW0KCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9hZG1pbl9saXN0X2Jvb2tpbmdzX3dpdGhfZGF0YSgKICAgIGNsaWVudDogQXN5bmNDbGllbnQsCiAgICBhZG1pbl90b2tlbjogc3RyLAogICAgdXNlcl90b2tlbjogc3RyLAogICAgY3JlYXRlZF9wcm9wZXJ0eTogZGljdCwKKSAtPiBOb25lOgogICAgIiIiQWRtaW4gYm9va2luZ3MgbGlzdCByZXR1cm5zIGRhdGEgd2hlbiBib29raW5ncyBleGlzdC4iIiIKICAgIGZyb20gZGF0ZXRpbWUgaW1wb3J0IFVUQywgZGF0ZXRpbWUsIHRpbWVkZWx0YQoKICAgIGNpID0gKGRhdGV0aW1lLm5vdyhVVEMpICsgdGltZWRlbHRhKGRheXM9MzAwKSkuaXNvZm9ybWF0KCkKICAgIGNvID0gKGRhdGV0aW1lLm5vdyhVVEMpICsgdGltZWRlbHRhKGRheXM9MzA1KSkuaXNvZm9ybWF0KCkKICAgIGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL2Jvb2tpbmdzIiwKICAgICAgICBqc29uPXsicHJvcGVydHlfaWQiOiBjcmVhdGVkX3Byb3BlcnR5WyJpZCJdLCAiY2hlY2tfaW4iOiBjaSwgImNoZWNrX291dCI6IGNvfSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHt1c2VyX3Rva2VufSJ9LAogICAgKQoKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LmdldCgKICAgICAgICAiL2FwaS92MS9hZG1pbi9ib29raW5ncyIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7YWRtaW5fdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgZGF0YVsidG90YWwiXSA+PSAxCiAgICBpdGVtID0gZGF0YVsiaXRlbXMiXVswXQogICAgYXNzZXJ0ICJpZCIgaW4gaXRlbQogICAgYXNzZXJ0ICJzdGF0dXMiIGluIGl0ZW0KICAgIGFzc2VydCAidG90YWxfcHJpY2UiIGluIGl0ZW0KCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9hZG1pbl9saXN0X3VzZXJzX3BhZ2luYXRpb24oCiAgICBjbGllbnQ6IEFzeW5jQ2xpZW50LCBhZG1pbl90b2tlbjogc3RyLCB0ZXN0X3VzZXIsIHRlc3RfaG9zdAopIC0+IE5vbmU6CiAgICAiIiJBZG1pbiB1c2VyIGxpc3Qgc3VwcG9ydHMgcGFnaW5hdGlvbi4iIiIKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LmdldCgKICAgICAgICAiL2FwaS92MS9hZG1pbi91c2VycyIsCiAgICAgICAgcGFyYW1zPXsicGFnZSI6IDEsICJwYWdlX3NpemUiOiAxfSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHthZG1pbl90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSAyMDAKICAgIGRhdGEgPSByZXNwb25zZS5qc29uKCkKICAgIGFzc2VydCBsZW4oZGF0YVsiaXRlbXMiXSkgPT0gMQogICAgYXNzZXJ0IGRhdGFbInRvdGFsIl0gPj0gMgoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X2FkbWluX2VuZHBvaW50c19mb3JiaWRkZW5fZm9yX2hvc3QoCiAgICBjbGllbnQ6IEFzeW5jQ2xpZW50LCBob3N0X3Rva2VuOiBzdHIKKSAtPiBOb25lOgogICAgIiIiSG9zdCBjYW5ub3QgYWNjZXNzIGFkbWluIGVuZHBvaW50cy4iIiIKICAgIGZvciBlbmRwb2ludCBpbiBbIi9hcGkvdjEvYWRtaW4vdXNlcnMiLCAiL2FwaS92MS9hZG1pbi9wcm9wZXJ0aWVzIiwKICAgICAgICAgICAgICAgICAgICAgIi9hcGkvdjEvYWRtaW4vbWVtYmVyc2hpcHMiLCAiL2FwaS92MS9hZG1pbi9ib29raW5ncyIsCiAgICAgICAgICAgICAgICAgICAgICIvYXBpL3YxL2FkbWluL2Rhc2hib2FyZCJdOgogICAgICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LmdldCgKICAgICAgICAgICAgZW5kcG9pbnQsCiAgICAgICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICAgICAgKQogICAgICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSA0MDMsIGYiRXhwZWN0ZWQgNDAzIGZvciB7ZW5kcG9pbnR9Igo=</t>
+  assert response.status_code == 403, f"Expected 403 for {endpoint}"
+ @pytest.mark.asyncio
+ async def test_admin_toggle_property_status(
+  client: AsyncClient, admin_token: str, created_property: dict
+ ) -&gt; None:
+  """Admin can toggle a property's active status."""
+  prop_id = created_property["id"]
+  response = await client.put(
+  f"/api/v1/admin/properties/{prop_id}/status",
+  headers={"Authorization": f"Bearer {admin_token}"},
+  )
+  assert response.status_code == 200
+  data = response.json()
+  assert data["id"] == prop_id
+  assert data["is_active"] is False
+  # Toggle back
+  response = await client.put(
+  f"/api/v1/admin/properties/{prop_id}/status",
+  headers={"Authorization": f"Bearer {admin_token}"},
+  )
+  assert response.status_code == 200
+  assert response.json()["is_active"] is True</t>
+  </si>
+  <si>
+    <t>IiIiSW50ZWdyYXRpb24gdGVzdHMgZm9yIGFkbWluIGVuZHBvaW50cyDigJQgZXh0ZW5kZWQgc2NlbmFyaW9zLiIiIgoKaW1wb3J0IHV1aWQKCmltcG9ydCBweXRlc3QKZnJvbSBodHRweCBpbXBvcnQgQXN5bmNDbGllbnQKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9hZG1pbl9saXN0X2Jvb2tpbmdzKGNsaWVudDogQXN5bmNDbGllbnQsIGFkbWluX3Rva2VuOiBzdHIpIC0+IE5vbmU6CiAgICAiIiJBZG1pbiBjYW4gbGlzdCBhbGwgYm9va2luZ3MuIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5nZXQoCiAgICAgICAgIi9hcGkvdjEvYWRtaW4vYm9va2luZ3MiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2FkbWluX3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMAogICAgZGF0YSA9IHJlc3BvbnNlLmpzb24oKQogICAgYXNzZXJ0ICJpdGVtcyIgaW4gZGF0YQogICAgYXNzZXJ0ICJ0b3RhbCIgaW4gZGF0YQoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X2FkbWluX3RvZ2dsZV91c2VyX3N0YXR1cygKICAgIGNsaWVudDogQXN5bmNDbGllbnQsIGFkbWluX3Rva2VuOiBzdHIsIHRlc3RfdXNlcgopIC0+IE5vbmU6CiAgICAiIiJBZG1pbiBjYW4gdG9nZ2xlIGEgdXNlcidzIGFjdGl2ZSBzdGF0dXMuIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5wdXQoCiAgICAgICAgZiIvYXBpL3YxL2FkbWluL3VzZXJzL3t0ZXN0X3VzZXIuaWR9L3N0YXR1cyIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7YWRtaW5fdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgZGF0YVsiaXNfYWN0aXZlIl0gaXMgRmFsc2UKCiAgICAjIFRvZ2dsZSBiYWNrCiAgICByZXNwb25zZTIgPSBhd2FpdCBjbGllbnQucHV0KAogICAgICAgIGYiL2FwaS92MS9hZG1pbi91c2Vycy97dGVzdF91c2VyLmlkfS9zdGF0dXMiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2FkbWluX3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlMi5zdGF0dXNfY29kZSA9PSAyMDAKICAgIGFzc2VydCByZXNwb25zZTIuanNvbigpWyJpc19hY3RpdmUiXSBpcyBUcnVlCgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3RfYWRtaW5fdG9nZ2xlX25vbmV4aXN0ZW50X3VzZXIoCiAgICBjbGllbnQ6IEFzeW5jQ2xpZW50LCBhZG1pbl90b2tlbjogc3RyCikgLT4gTm9uZToKICAgICIiIlRvZ2dsaW5nIGEgbm9uZXhpc3RlbnQgdXNlciByZXR1cm5zIDQwNC4iIiIKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LnB1dCgKICAgICAgICBmIi9hcGkvdjEvYWRtaW4vdXNlcnMve3V1aWQudXVpZDQoKX0vc3RhdHVzIiwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHthZG1pbl90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSA0MDQKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9hZG1pbl9kYXNoYm9hcmRfd2l0aF9kYXRhKAogICAgY2xpZW50OiBBc3luY0NsaWVudCwKICAgIGFkbWluX3Rva2VuOiBzdHIsCiAgICBob3N0X3dpdGhfbWVtYmVyc2hpcDogc3RyLAogICAgdXNlcl90b2tlbjogc3RyLAogICAgY3JlYXRlZF9wcm9wZXJ0eTogZGljdCwKKSAtPiBOb25lOgogICAgIiIiRGFzaGJvYXJkIHNob3dzIGNvcnJlY3Qgc3RhdGlzdGljcyB3aGVuIGRhdGEgZXhpc3RzLiIiIgogICAgcmVzcG9uc2UgPSBhd2FpdCBjbGllbnQuZ2V0KAogICAgICAgICIvYXBpL3YxL2FkbWluL2Rhc2hib2FyZCIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7YWRtaW5fdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgZGF0YVsidG90YWxfdXNlcnMiXSA+PSAyCiAgICBhc3NlcnQgZGF0YVsidG90YWxfcHJvcGVydGllcyJdID49IDEKICAgIGFzc2VydCBkYXRhWyJhY3RpdmVfbWVtYmVycyJdID49IDEKICAgIGFzc2VydCAibW9udGhseV9yZXZlbnVlIiBpbiBkYXRhCgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3RfYWRtaW5fbGlzdF9wcm9wZXJ0aWVzX3dpdGhfZGF0YSgKICAgIGNsaWVudDogQXN5bmNDbGllbnQsIGFkbWluX3Rva2VuOiBzdHIsIGNyZWF0ZWRfcHJvcGVydHk6IGRpY3QKKSAtPiBOb25lOgogICAgIiIiQWRtaW4gcHJvcGVydGllcyBsaXN0IHJldHVybnMgZGF0YS4iIiIKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LmdldCgKICAgICAgICAiL2FwaS92MS9hZG1pbi9wcm9wZXJ0aWVzIiwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHthZG1pbl90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSAyMDAKICAgIGRhdGEgPSByZXNwb25zZS5qc29uKCkKICAgIGFzc2VydCBkYXRhWyJ0b3RhbCJdID49IDEKICAgIGFzc2VydCBsZW4oZGF0YVsiaXRlbXMiXSkgPj0gMQogICAgIyBDaGVjayBpdGVtIHN0cnVjdHVyZQogICAgaXRlbSA9IGRhdGFbIml0ZW1zIl1bMF0KICAgIGFzc2VydCAiaWQiIGluIGl0ZW0KICAgIGFzc2VydCAidGl0bGUiIGluIGl0ZW0KICAgIGFzc2VydCAiY2l0eSIgaW4gaXRlbQogICAgYXNzZXJ0ICJpc19hY3RpdmUiIGluIGl0ZW0KCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9hZG1pbl9saXN0X21lbWJlcnNoaXBzX3dpdGhfZGF0YSgKICAgIGNsaWVudDogQXN5bmNDbGllbnQsIGFkbWluX3Rva2VuOiBzdHIsIGhvc3Rfd2l0aF9tZW1iZXJzaGlwOiBzdHIKKSAtPiBOb25lOgogICAgIiIiQWRtaW4gbWVtYmVyc2hpcHMgbGlzdCByZXR1cm5zIGRhdGEuIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5nZXQoCiAgICAgICAgIi9hcGkvdjEvYWRtaW4vbWVtYmVyc2hpcHMiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2FkbWluX3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMAogICAgZGF0YSA9IHJlc3BvbnNlLmpzb24oKQogICAgYXNzZXJ0IGRhdGFbInRvdGFsIl0gPj0gMQogICAgaXRlbSA9IGRhdGFbIml0ZW1zIl1bMF0KICAgIGFzc2VydCAiaWQiIGluIGl0ZW0KICAgIGFzc2VydCAicGxhbl90eXBlIiBpbiBpdGVtCiAgICBhc3NlcnQgInN0YXR1cyIgaW4gaXRlbQogICAgYXNzZXJ0ICJhbW91bnQiIGluIGl0ZW0KCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9hZG1pbl9saXN0X2Jvb2tpbmdzX3dpdGhfZGF0YSgKICAgIGNsaWVudDogQXN5bmNDbGllbnQsCiAgICBhZG1pbl90b2tlbjogc3RyLAogICAgdXNlcl90b2tlbjogc3RyLAogICAgY3JlYXRlZF9wcm9wZXJ0eTogZGljdCwKKSAtPiBOb25lOgogICAgIiIiQWRtaW4gYm9va2luZ3MgbGlzdCByZXR1cm5zIGRhdGEgd2hlbiBib29raW5ncyBleGlzdC4iIiIKICAgIGZyb20gZGF0ZXRpbWUgaW1wb3J0IFVUQywgZGF0ZXRpbWUsIHRpbWVkZWx0YQoKICAgIGNpID0gKGRhdGV0aW1lLm5vdyhVVEMpICsgdGltZWRlbHRhKGRheXM9MzAwKSkuaXNvZm9ybWF0KCkKICAgIGNvID0gKGRhdGV0aW1lLm5vdyhVVEMpICsgdGltZWRlbHRhKGRheXM9MzA1KSkuaXNvZm9ybWF0KCkKICAgIGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL2Jvb2tpbmdzIiwKICAgICAgICBqc29uPXsicHJvcGVydHlfaWQiOiBjcmVhdGVkX3Byb3BlcnR5WyJpZCJdLCAiY2hlY2tfaW4iOiBjaSwgImNoZWNrX291dCI6IGNvfSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHt1c2VyX3Rva2VufSJ9LAogICAgKQoKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LmdldCgKICAgICAgICAiL2FwaS92MS9hZG1pbi9ib29raW5ncyIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7YWRtaW5fdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgZGF0YVsidG90YWwiXSA+PSAxCiAgICBpdGVtID0gZGF0YVsiaXRlbXMiXVswXQogICAgYXNzZXJ0ICJpZCIgaW4gaXRlbQogICAgYXNzZXJ0ICJzdGF0dXMiIGluIGl0ZW0KICAgIGFzc2VydCAidG90YWxfcHJpY2UiIGluIGl0ZW0KCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9hZG1pbl9saXN0X3VzZXJzX3BhZ2luYXRpb24oCiAgICBjbGllbnQ6IEFzeW5jQ2xpZW50LCBhZG1pbl90b2tlbjogc3RyLCB0ZXN0X3VzZXIsIHRlc3RfaG9zdAopIC0+IE5vbmU6CiAgICAiIiJBZG1pbiB1c2VyIGxpc3Qgc3VwcG9ydHMgcGFnaW5hdGlvbi4iIiIKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LmdldCgKICAgICAgICAiL2FwaS92MS9hZG1pbi91c2VycyIsCiAgICAgICAgcGFyYW1zPXsicGFnZSI6IDEsICJwYWdlX3NpemUiOiAxfSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHthZG1pbl90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSAyMDAKICAgIGRhdGEgPSByZXNwb25zZS5qc29uKCkKICAgIGFzc2VydCBsZW4oZGF0YVsiaXRlbXMiXSkgPT0gMQogICAgYXNzZXJ0IGRhdGFbInRvdGFsIl0gPj0gMgoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X2FkbWluX2VuZHBvaW50c19mb3JiaWRkZW5fZm9yX2hvc3QoCiAgICBjbGllbnQ6IEFzeW5jQ2xpZW50LCBob3N0X3Rva2VuOiBzdHIKKSAtPiBOb25lOgogICAgIiIiSG9zdCBjYW5ub3QgYWNjZXNzIGFkbWluIGVuZHBvaW50cy4iIiIKICAgIGZvciBlbmRwb2ludCBpbiBbIi9hcGkvdjEvYWRtaW4vdXNlcnMiLCAiL2FwaS92MS9hZG1pbi9wcm9wZXJ0aWVzIiwKICAgICAgICAgICAgICAgICAgICAgIi9hcGkvdjEvYWRtaW4vbWVtYmVyc2hpcHMiLCAiL2FwaS92MS9hZG1pbi9ib29raW5ncyIsCiAgICAgICAgICAgICAgICAgICAgICIvYXBpL3YxL2FkbWluL2Rhc2hib2FyZCJdOgogICAgICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LmdldCgKICAgICAgICAgICAgZW5kcG9pbnQsCiAgICAgICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICAgICAgKQogICAgICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSA0MDMsIGYiRXhwZWN0ZWQgNDAzIGZvciB7ZW5kcG9pbnR9IgoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X2FkbWluX3RvZ2dsZV9wcm9wZXJ0eV9zdGF0dXMoCiAgICBjbGllbnQ6IEFzeW5jQ2xpZW50LCBhZG1pbl90b2tlbjogc3RyLCBjcmVhdGVkX3Byb3BlcnR5OiBkaWN0CikgLT4gTm9uZToKICAgICIiIkFkbWluIGNhbiB0b2dnbGUgYSBwcm9wZXJ0eSdzIGFjdGl2ZSBzdGF0dXMuIiIiCiAgICBwcm9wX2lkID0gY3JlYXRlZF9wcm9wZXJ0eVsiaWQiXQogICAgcmVzcG9uc2UgPSBhd2FpdCBjbGllbnQucHV0KAogICAgICAgIGYiL2FwaS92MS9hZG1pbi9wcm9wZXJ0aWVzL3twcm9wX2lkfS9zdGF0dXMiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2FkbWluX3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMAogICAgZGF0YSA9IHJlc3BvbnNlLmpzb24oKQogICAgYXNzZXJ0IGRhdGFbImlkIl0gPT0gcHJvcF9pZAogICAgYXNzZXJ0IGRhdGFbImlzX2FjdGl2ZSJdIGlzIEZhbHNlCgogICAgIyBUb2dnbGUgYmFjawogICAgcmVzcG9uc2UgPSBhd2FpdCBjbGllbnQucHV0KAogICAgICAgIGYiL2FwaS92MS9hZG1pbi9wcm9wZXJ0aWVzL3twcm9wX2lkfS9zdGF0dXMiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2FkbWluX3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMAogICAgYXNzZXJ0IHJlc3BvbnNlLmpzb24oKVsiaXNfYWN0aXZlIl0gaXMgVHJ1ZQo=</t>
   </si>
   <si>
     <t>backend/tests/test_auth.py</t>
@@ -14201,7 +14315,7 @@
   data = response.json()
   assert data["plan_type"] == "basic"
   assert data["status"] == "active"
-  assert data["amount"] == 29.0
+  assert data["amount"] == 2499.0
  @pytest.mark.asyncio
  async def test_get_current_membership(client: AsyncClient, host_token: str) -&gt; None:
   """Test getting current membership after subscribing."""
@@ -14253,7 +14367,7 @@
   assert response.json()["status"] == "processed"</t>
   </si>
   <si>
-    <t>IiIiTWVtYmVyc2hpcCBlbmRwb2ludCB0ZXN0cy4iIiIKCmltcG9ydCBweXRlc3QKZnJvbSBodHRweCBpbXBvcnQgQXN5bmNDbGllbnQKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9saXN0X3BsYW5zX3B1YmxpYyhjbGllbnQ6IEFzeW5jQ2xpZW50KSAtPiBOb25lOgogICAgIiIiVGVzdCBsaXN0aW5nIG1lbWJlcnNoaXAgcGxhbnMgaXMgcHVibGljIGFuZCByZXR1cm5zIGFsbCBwbGFucy4iIiIKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LmdldCgiL2FwaS92MS9tZW1iZXJzaGlwcy9wbGFucyIpCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgbGVuKGRhdGEpID09IDMKICAgIHBsYW5fdHlwZXMgPSB7cFsicGxhbl90eXBlIl0gZm9yIHAgaW4gZGF0YX0KICAgIGFzc2VydCBwbGFuX3R5cGVzID09IHsiYmFzaWMiLCAicHJvIiwgInByZW1pdW0ifQoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X3N1YnNjcmliZV9yZXF1aXJlc19ob3N0KGNsaWVudDogQXN5bmNDbGllbnQsIHVzZXJfdG9rZW46IHN0cikgLT4gTm9uZToKICAgICIiIlRlc3QgdGhhdCBzdWJzY3JpYmluZyByZXF1aXJlcyBob3N0IHJvbGUuIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsCiAgICAgICAganNvbj17InBsYW5fdHlwZSI6ICJiYXNpYyIsICJwYXltZW50X3Rva2VuIjogInRva190ZXN0In0sCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7dXNlcl90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSA0MDMKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9zdWJzY3JpYmVfYXNfaG9zdChjbGllbnQ6IEFzeW5jQ2xpZW50LCBob3N0X3Rva2VuOiBzdHIpIC0+IE5vbmU6CiAgICAiIiJUZXN0IGhvc3QgY2FuIHN1YnNjcmliZSB0byBhIHBsYW4uIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsCiAgICAgICAganNvbj17InBsYW5fdHlwZSI6ICJiYXNpYyIsICJwYXltZW50X3Rva2VuIjogInRva190ZXN0XzEyMyJ9LAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAxCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgZGF0YVsicGxhbl90eXBlIl0gPT0gImJhc2ljIgogICAgYXNzZXJ0IGRhdGFbInN0YXR1cyJdID09ICJhY3RpdmUiCiAgICBhc3NlcnQgZGF0YVsiYW1vdW50Il0gPT0gMjkuMAoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X2dldF9jdXJyZW50X21lbWJlcnNoaXAoY2xpZW50OiBBc3luY0NsaWVudCwgaG9zdF90b2tlbjogc3RyKSAtPiBOb25lOgogICAgIiIiVGVzdCBnZXR0aW5nIGN1cnJlbnQgbWVtYmVyc2hpcCBhZnRlciBzdWJzY3JpYmluZy4iIiIKICAgICMgRmlyc3Qgc3Vic2NyaWJlCiAgICBhd2FpdCBjbGllbnQucG9zdCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy9zdWJzY3JpYmUiLAogICAgICAgIGpzb249eyJwbGFuX3R5cGUiOiAicHJvIiwgInBheW1lbnRfdG9rZW4iOiAidG9rX3Rlc3RfNDU2In0sCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgICMgVGhlbiBnZXQgY3VycmVudAogICAgcmVzcG9uc2UgPSBhd2FpdCBjbGllbnQuZ2V0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL2N1cnJlbnQiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgZGF0YVsicGxhbl90eXBlIl0gPT0gInBybyIKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9jYW5jZWxfbWVtYmVyc2hpcChjbGllbnQ6IEFzeW5jQ2xpZW50LCBob3N0X3Rva2VuOiBzdHIpIC0+IE5vbmU6CiAgICAiIiJUZXN0IGNhbmNlbGxpbmcgYW4gYWN0aXZlIG1lbWJlcnNoaXAuIiIiCiAgICAjIFN1YnNjcmliZSBmaXJzdAogICAgYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogImJhc2ljIiwgInBheW1lbnRfdG9rZW4iOiAidG9rX2NhbmNlbF90ZXN0In0sCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgICMgQ2FuY2VsCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5wdXQoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvY2FuY2VsIiwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMAogICAgZGF0YSA9IHJlc3BvbnNlLmpzb24oKQogICAgYXNzZXJ0IGRhdGFbInN0YXR1cyJdID09ICJjYW5jZWxsZWQiCiAgICBhc3NlcnQgZGF0YVsiYXV0b19yZW5ldyJdIGlzIEZhbHNlCgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3Rfd2ViaG9va19wcm9jZXNzaW5nKGNsaWVudDogQXN5bmNDbGllbnQpIC0+IE5vbmU6CiAgICAiIiJUZXN0IHRoZSBwYXltZW50IHdlYmhvb2sgZW5kcG9pbnQgYWNjZXB0cyB2YWxpZCBwYXlsb2FkLiIiIgogICAgcmVzcG9uc2UgPSBhd2FpdCBjbGllbnQucG9zdCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy93ZWJob29rIiwKICAgICAgICBqc29uPXsKICAgICAgICAgICAgImV2ZW50X3R5cGUiOiAicGF5bWVudC5zdWNjZWVkZWQiLAogICAgICAgICAgICAicGF5bWVudF9yZWYiOiAic2ltX3Rva19ub25leGlzdGVudCIsCiAgICAgICAgICAgICJzdGF0dXMiOiAic3VjY2VlZGVkIiwKICAgICAgICB9LAogICAgICAgIGhlYWRlcnM9eyJ4LXdlYmhvb2stc2VjcmV0IjogIkNIQU5HRS1NRS13ZWJob29rLXNlY3JldCJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMAogICAgYXNzZXJ0IHJlc3BvbnNlLmpzb24oKVsic3RhdHVzIl0gPT0gInByb2Nlc3NlZCIK</t>
+    <t>IiIiTWVtYmVyc2hpcCBlbmRwb2ludCB0ZXN0cy4iIiIKCmltcG9ydCBweXRlc3QKZnJvbSBodHRweCBpbXBvcnQgQXN5bmNDbGllbnQKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9saXN0X3BsYW5zX3B1YmxpYyhjbGllbnQ6IEFzeW5jQ2xpZW50KSAtPiBOb25lOgogICAgIiIiVGVzdCBsaXN0aW5nIG1lbWJlcnNoaXAgcGxhbnMgaXMgcHVibGljIGFuZCByZXR1cm5zIGFsbCBwbGFucy4iIiIKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LmdldCgiL2FwaS92MS9tZW1iZXJzaGlwcy9wbGFucyIpCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgbGVuKGRhdGEpID09IDMKICAgIHBsYW5fdHlwZXMgPSB7cFsicGxhbl90eXBlIl0gZm9yIHAgaW4gZGF0YX0KICAgIGFzc2VydCBwbGFuX3R5cGVzID09IHsiYmFzaWMiLCAicHJvIiwgInByZW1pdW0ifQoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X3N1YnNjcmliZV9yZXF1aXJlc19ob3N0KGNsaWVudDogQXN5bmNDbGllbnQsIHVzZXJfdG9rZW46IHN0cikgLT4gTm9uZToKICAgICIiIlRlc3QgdGhhdCBzdWJzY3JpYmluZyByZXF1aXJlcyBob3N0IHJvbGUuIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsCiAgICAgICAganNvbj17InBsYW5fdHlwZSI6ICJiYXNpYyIsICJwYXltZW50X3Rva2VuIjogInRva190ZXN0In0sCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7dXNlcl90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSA0MDMKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9zdWJzY3JpYmVfYXNfaG9zdChjbGllbnQ6IEFzeW5jQ2xpZW50LCBob3N0X3Rva2VuOiBzdHIpIC0+IE5vbmU6CiAgICAiIiJUZXN0IGhvc3QgY2FuIHN1YnNjcmliZSB0byBhIHBsYW4uIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsCiAgICAgICAganNvbj17InBsYW5fdHlwZSI6ICJiYXNpYyIsICJwYXltZW50X3Rva2VuIjogInRva190ZXN0XzEyMyJ9LAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAxCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgZGF0YVsicGxhbl90eXBlIl0gPT0gImJhc2ljIgogICAgYXNzZXJ0IGRhdGFbInN0YXR1cyJdID09ICJhY3RpdmUiCiAgICBhc3NlcnQgZGF0YVsiYW1vdW50Il0gPT0gMjQ5OS4wCgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3RfZ2V0X2N1cnJlbnRfbWVtYmVyc2hpcChjbGllbnQ6IEFzeW5jQ2xpZW50LCBob3N0X3Rva2VuOiBzdHIpIC0+IE5vbmU6CiAgICAiIiJUZXN0IGdldHRpbmcgY3VycmVudCBtZW1iZXJzaGlwIGFmdGVyIHN1YnNjcmliaW5nLiIiIgogICAgIyBGaXJzdCBzdWJzY3JpYmUKICAgIGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsCiAgICAgICAganNvbj17InBsYW5fdHlwZSI6ICJwcm8iLCAicGF5bWVudF90b2tlbiI6ICJ0b2tfdGVzdF80NTYifSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQogICAgIyBUaGVuIGdldCBjdXJyZW50CiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5nZXQoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvY3VycmVudCIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSAyMDAKICAgIGRhdGEgPSByZXNwb25zZS5qc29uKCkKICAgIGFzc2VydCBkYXRhWyJwbGFuX3R5cGUiXSA9PSAicHJvIgoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X2NhbmNlbF9tZW1iZXJzaGlwKGNsaWVudDogQXN5bmNDbGllbnQsIGhvc3RfdG9rZW46IHN0cikgLT4gTm9uZToKICAgICIiIlRlc3QgY2FuY2VsbGluZyBhbiBhY3RpdmUgbWVtYmVyc2hpcC4iIiIKICAgICMgU3Vic2NyaWJlIGZpcnN0CiAgICBhd2FpdCBjbGllbnQucG9zdCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy9zdWJzY3JpYmUiLAogICAgICAgIGpzb249eyJwbGFuX3R5cGUiOiAiYmFzaWMiLCAicGF5bWVudF90b2tlbiI6ICJ0b2tfY2FuY2VsX3Rlc3QifSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQogICAgIyBDYW5jZWwKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LnB1dCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy9jYW5jZWwiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgZGF0YVsic3RhdHVzIl0gPT0gImNhbmNlbGxlZCIKICAgIGFzc2VydCBkYXRhWyJhdXRvX3JlbmV3Il0gaXMgRmFsc2UKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF93ZWJob29rX3Byb2Nlc3NpbmcoY2xpZW50OiBBc3luY0NsaWVudCkgLT4gTm9uZToKICAgICIiIlRlc3QgdGhlIHBheW1lbnQgd2ViaG9vayBlbmRwb2ludCBhY2NlcHRzIHZhbGlkIHBheWxvYWQuIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3dlYmhvb2siLAogICAgICAgIGpzb249ewogICAgICAgICAgICAiZXZlbnRfdHlwZSI6ICJwYXltZW50LnN1Y2NlZWRlZCIsCiAgICAgICAgICAgICJwYXltZW50X3JlZiI6ICJzaW1fdG9rX25vbmV4aXN0ZW50IiwKICAgICAgICAgICAgInN0YXR1cyI6ICJzdWNjZWVkZWQiLAogICAgICAgIH0sCiAgICAgICAgaGVhZGVycz17Ingtd2ViaG9vay1zZWNyZXQiOiAiQ0hBTkdFLU1FLXdlYmhvb2stc2VjcmV0In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBhc3NlcnQgcmVzcG9uc2UuanNvbigpWyJzdGF0dXMiXSA9PSAicHJvY2Vzc2VkIgo=</t>
   </si>
   <si>
     <t>backend/tests/test_memberships_integration.py</t>
@@ -14281,7 +14395,7 @@
   data = response.json()
   assert data["plan_type"] == "pro"
   assert data["status"] == "active"
-  assert data["amount"] == 79.0
+  assert data["amount"] == 6499.0
   assert data["max_listings"] == 25
  @pytest.mark.asyncio
  async def test_subscribe_premium_plan(client: AsyncClient, host_token: str) -&gt; None:
@@ -14294,7 +14408,7 @@
   assert response.status_code == 201
   data = response.json()
   assert data["plan_type"] == "premium"
-  assert data["amount"] == 199.0
+  assert data["amount"] == 16499.0
  @pytest.mark.asyncio
  async def test_reactivate_after_cancel(client: AsyncClient, host_token: str) -&gt; None:
   """Host can reactivate after cancellation."""
@@ -14435,7 +14549,7 @@
   assert data["auto_renew"] is True</t>
   </si>
   <si>
-    <t>IiIiSW50ZWdyYXRpb24gdGVzdHMgZm9yIG1lbWJlcnNoaXAgZW5kcG9pbnRzIOKAlCBleHRlbmRlZCBzY2VuYXJpb3MuIiIiCgppbXBvcnQgcHl0ZXN0CmZyb20gaHR0cHggaW1wb3J0IEFzeW5jQ2xpZW50CgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3Rfc3Vic2NyaWJlX3VwZ3JhZGVfcGxhbihjbGllbnQ6IEFzeW5jQ2xpZW50LCBob3N0X3Rva2VuOiBzdHIpIC0+IE5vbmU6CiAgICAiIiJIb3N0IGNhbiB1cGdyYWRlIGZyb20gYmFzaWMgdG8gcHJvIHBsYW4uIiIiCiAgICAjIFN1YnNjcmliZSB0byBiYXNpYwogICAgYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogImJhc2ljIiwgInBheW1lbnRfdG9rZW4iOiAidG9rX2Jhc2ljIn0sCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKCiAgICAjIFVwZ3JhZGUgdG8gcHJvIChyZWFjdGl2YXRpb24vc3dpdGNoIG9uIGV4aXN0aW5nIHJvdykKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogInBybyIsICJwYXltZW50X3Rva2VuIjogInRva19wcm8ifSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMQogICAgZGF0YSA9IHJlc3BvbnNlLmpzb24oKQogICAgYXNzZXJ0IGRhdGFbInBsYW5fdHlwZSJdID09ICJwcm8iCiAgICBhc3NlcnQgZGF0YVsic3RhdHVzIl0gPT0gImFjdGl2ZSIKICAgIGFzc2VydCBkYXRhWyJhbW91bnQiXSA9PSA3OS4wCiAgICBhc3NlcnQgZGF0YVsibWF4X2xpc3RpbmdzIl0gPT0gMjUKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9zdWJzY3JpYmVfcHJlbWl1bV9wbGFuKGNsaWVudDogQXN5bmNDbGllbnQsIGhvc3RfdG9rZW46IHN0cikgLT4gTm9uZToKICAgICIiIkhvc3QgY2FuIHN1YnNjcmliZSB0byBwcmVtaXVtIHBsYW4uIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsCiAgICAgICAganNvbj17InBsYW5fdHlwZSI6ICJwcmVtaXVtIiwgInBheW1lbnRfdG9rZW4iOiAidG9rX3ByZW1pdW0ifSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMQogICAgZGF0YSA9IHJlc3BvbnNlLmpzb24oKQogICAgYXNzZXJ0IGRhdGFbInBsYW5fdHlwZSJdID09ICJwcmVtaXVtIgogICAgYXNzZXJ0IGRhdGFbImFtb3VudCJdID09IDE5OS4wCgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3RfcmVhY3RpdmF0ZV9hZnRlcl9jYW5jZWwoY2xpZW50OiBBc3luY0NsaWVudCwgaG9zdF90b2tlbjogc3RyKSAtPiBOb25lOgogICAgIiIiSG9zdCBjYW4gcmVhY3RpdmF0ZSBhZnRlciBjYW5jZWxsYXRpb24uIiIiCiAgICAjIFN1YnNjcmliZQogICAgYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogImJhc2ljIiwgInBheW1lbnRfdG9rZW4iOiAidG9rX3JlYWN0In0sCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgICMgQ2FuY2VsCiAgICBhd2FpdCBjbGllbnQucHV0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL2NhbmNlbCIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgICMgUmVzdWJzY3JpYmUKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogInBybyIsICJwYXltZW50X3Rva2VuIjogInRva19yZWFjdDIifSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMQogICAgYXNzZXJ0IHJlc3BvbnNlLmpzb24oKVsic3RhdHVzIl0gPT0gImFjdGl2ZSIKICAgIGFzc2VydCByZXNwb25zZS5qc29uKClbInBsYW5fdHlwZSJdID09ICJwcm8iCgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3RfY2FuY2VsX2FscmVhZHlfY2FuY2VsbGVkKGNsaWVudDogQXN5bmNDbGllbnQsIGhvc3RfdG9rZW46IHN0cikgLT4gTm9uZToKICAgICIiIkNhbmNlbGxpbmcgYW4gYWxyZWFkeS1jYW5jZWxsZWQgbWVtYmVyc2hpcCByZXR1cm5zIDQwMC4iIiIKICAgIGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsCiAgICAgICAganNvbj17InBsYW5fdHlwZSI6ICJiYXNpYyIsICJwYXltZW50X3Rva2VuIjogInRva19jYW5jZWwyIn0sCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgIGF3YWl0IGNsaWVudC5wdXQoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvY2FuY2VsIiwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQogICAgcmVzcG9uc2UgPSBhd2FpdCBjbGllbnQucHV0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL2NhbmNlbCIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSA0MDAKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9nZXRfbWVtYmVyc2hpcF9ub19zdWJzY3JpcHRpb24oY2xpZW50OiBBc3luY0NsaWVudCwgaG9zdF90b2tlbjogc3RyKSAtPiBOb25lOgogICAgIiIiR2V0dGluZyBtZW1iZXJzaGlwIHdoZW4gbm9uZSBleGlzdHMgcmV0dXJucyA0MDQuIiIiCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5nZXQoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvY3VycmVudCIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSA0MDQKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF93ZWJob29rX3BheW1lbnRfc3VjY2VlZGVkKGNsaWVudDogQXN5bmNDbGllbnQsIGhvc3RfdG9rZW46IHN0cikgLT4gTm9uZToKICAgICIiIldlYmhvb2sgZm9yIHBheW1lbnQuc3VjY2VlZGVkIHVwZGF0ZXMgbWVtYmVyc2hpcCB0byBhY3RpdmUuIiIiCiAgICBhd2FpdCBjbGllbnQucG9zdCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy9zdWJzY3JpYmUiLAogICAgICAgIGpzb249eyJwbGFuX3R5cGUiOiAiYmFzaWMiLCAicGF5bWVudF90b2tlbiI6ICJ0b2tfd2hfc3VjY2VzcyJ9LAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICBwYXltZW50X3JlZiA9ICJzaW1fdG9rX3doX3N1Y2Nlc3MiCgogICAgcmVzcG9uc2UgPSBhd2FpdCBjbGllbnQucG9zdCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy93ZWJob29rIiwKICAgICAgICBqc29uPXsKICAgICAgICAgICAgImV2ZW50X3R5cGUiOiAicGF5bWVudC5zdWNjZWVkZWQiLAogICAgICAgICAgICAicGF5bWVudF9yZWYiOiBwYXltZW50X3JlZiwKICAgICAgICAgICAgInN0YXR1cyI6ICJzdWNjZWVkZWQiLAogICAgICAgIH0sCiAgICAgICAgaGVhZGVycz17Ingtd2ViaG9vay1zZWNyZXQiOiAiQ0hBTkdFLU1FLXdlYmhvb2stc2VjcmV0In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAwCiAgICBhc3NlcnQgcmVzcG9uc2UuanNvbigpWyJzdGF0dXMiXSA9PSAicHJvY2Vzc2VkIgoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X3dlYmhvb2tfcGF5bWVudF9mYWlsZWQoY2xpZW50OiBBc3luY0NsaWVudCwgaG9zdF90b2tlbjogc3RyKSAtPiBOb25lOgogICAgIiIiV2ViaG9vayBmb3IgcGF5bWVudC5mYWlsZWQgdXBkYXRlcyBtZW1iZXJzaGlwIHRvIHBhc3RfZHVlLiIiIgogICAgYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogImJhc2ljIiwgInBheW1lbnRfdG9rZW4iOiAidG9rX3doX2ZhaWwifSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQoKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvd2ViaG9vayIsCiAgICAgICAganNvbj17CiAgICAgICAgICAgICJldmVudF90eXBlIjogInBheW1lbnQuZmFpbGVkIiwKICAgICAgICAgICAgInBheW1lbnRfcmVmIjogInNpbV90b2tfd2hfZmFpbCIsCiAgICAgICAgICAgICJzdGF0dXMiOiAiZmFpbGVkIiwKICAgICAgICB9LAogICAgICAgIGhlYWRlcnM9eyJ4LXdlYmhvb2stc2VjcmV0IjogIkNIQU5HRS1NRS13ZWJob29rLXNlY3JldCJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMAoKICAgICMgVmVyaWZ5IG1lbWJlcnNoaXAgc3RhdHVzCiAgICBtZW1fcmVzcCA9IGF3YWl0IGNsaWVudC5nZXQoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvY3VycmVudCIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCBtZW1fcmVzcC5qc29uKClbInN0YXR1cyJdID09ICJwYXN0X2R1ZSIKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF93ZWJob29rX3N1YnNjcmlwdGlvbl9jYW5jZWxsZWQoY2xpZW50OiBBc3luY0NsaWVudCwgaG9zdF90b2tlbjogc3RyKSAtPiBOb25lOgogICAgIiIiV2ViaG9vayBmb3Igc3Vic2NyaXB0aW9uLmNhbmNlbGxlZCB1cGRhdGVzIG1lbWJlcnNoaXAgc3RhdHVzLiIiIgogICAgYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogImJhc2ljIiwgInBheW1lbnRfdG9rZW4iOiAidG9rX3doX2NhbmNlbCJ9LAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCgogICAgcmVzcG9uc2UgPSBhd2FpdCBjbGllbnQucG9zdCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy93ZWJob29rIiwKICAgICAgICBqc29uPXsKICAgICAgICAgICAgImV2ZW50X3R5cGUiOiAic3Vic2NyaXB0aW9uLmNhbmNlbGxlZCIsCiAgICAgICAgICAgICJwYXltZW50X3JlZiI6ICJzaW1fdG9rX3doX2NhbmNlbCIsCiAgICAgICAgICAgICJzdGF0dXMiOiAiY2FuY2VsbGVkIiwKICAgICAgICB9LAogICAgICAgIGhlYWRlcnM9eyJ4LXdlYmhvb2stc2VjcmV0IjogIkNIQU5HRS1NRS13ZWJob29rLXNlY3JldCJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMAoKICAgIG1lbV9yZXNwID0gYXdhaXQgY2xpZW50LmdldCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy9jdXJyZW50IiwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IG1lbV9yZXNwLmpzb24oKVsic3RhdHVzIl0gPT0gImNhbmNlbGxlZCIKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF9tZW1iZXJzaGlwX2ZpZWxkc19jb21wbGV0ZShjbGllbnQ6IEFzeW5jQ2xpZW50LCBob3N0X3Rva2VuOiBzdHIpIC0+IE5vbmU6CiAgICAiIiJNZW1iZXJzaGlwIHJlc3BvbnNlIGluY2x1ZGVzIGFsbCBleHBlY3RlZCBmaWVsZHMuIiIiCiAgICBhd2FpdCBjbGllbnQucG9zdCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy9zdWJzY3JpYmUiLAogICAgICAgIGpzb249eyJwbGFuX3R5cGUiOiAiYmFzaWMiLCAicGF5bWVudF90b2tlbiI6ICJ0b2tfZmllbGRzIn0sCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LmdldCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy9jdXJyZW50IiwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQogICAgZGF0YSA9IHJlc3BvbnNlLmpzb24oKQogICAgYXNzZXJ0ICJpZCIgaW4gZGF0YQogICAgYXNzZXJ0ICJob3N0X2lkIiBpbiBkYXRhCiAgICBhc3NlcnQgInBsYW5fdHlwZSIgaW4gZGF0YQogICAgYXNzZXJ0ICJzdGFydF9kYXRlIiBpbiBkYXRhCiAgICBhc3NlcnQgImVuZF9kYXRlIiBpbiBkYXRhCiAgICBhc3NlcnQgInN0YXR1cyIgaW4gZGF0YQogICAgYXNzZXJ0ICJhdXRvX3JlbmV3IiBpbiBkYXRhCiAgICBhc3NlcnQgImFtb3VudCIgaW4gZGF0YQogICAgYXNzZXJ0ICJtYXhfbGlzdGluZ3MiIGluIGRhdGEKICAgIGFzc2VydCBkYXRhWyJhdXRvX3JlbmV3Il0gaXMgVHJ1ZQo=</t>
+    <t>IiIiSW50ZWdyYXRpb24gdGVzdHMgZm9yIG1lbWJlcnNoaXAgZW5kcG9pbnRzIOKAlCBleHRlbmRlZCBzY2VuYXJpb3MuIiIiCgppbXBvcnQgcHl0ZXN0CmZyb20gaHR0cHggaW1wb3J0IEFzeW5jQ2xpZW50CgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3Rfc3Vic2NyaWJlX3VwZ3JhZGVfcGxhbihjbGllbnQ6IEFzeW5jQ2xpZW50LCBob3N0X3Rva2VuOiBzdHIpIC0+IE5vbmU6CiAgICAiIiJIb3N0IGNhbiB1cGdyYWRlIGZyb20gYmFzaWMgdG8gcHJvIHBsYW4uIiIiCiAgICAjIFN1YnNjcmliZSB0byBiYXNpYwogICAgYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogImJhc2ljIiwgInBheW1lbnRfdG9rZW4iOiAidG9rX2Jhc2ljIn0sCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKCiAgICAjIFVwZ3JhZGUgdG8gcHJvIChyZWFjdGl2YXRpb24vc3dpdGNoIG9uIGV4aXN0aW5nIHJvdykKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogInBybyIsICJwYXltZW50X3Rva2VuIjogInRva19wcm8ifSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMQogICAgZGF0YSA9IHJlc3BvbnNlLmpzb24oKQogICAgYXNzZXJ0IGRhdGFbInBsYW5fdHlwZSJdID09ICJwcm8iCiAgICBhc3NlcnQgZGF0YVsic3RhdHVzIl0gPT0gImFjdGl2ZSIKICAgIGFzc2VydCBkYXRhWyJhbW91bnQiXSA9PSA2NDk5LjAKICAgIGFzc2VydCBkYXRhWyJtYXhfbGlzdGluZ3MiXSA9PSAyNQoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X3N1YnNjcmliZV9wcmVtaXVtX3BsYW4oY2xpZW50OiBBc3luY0NsaWVudCwgaG9zdF90b2tlbjogc3RyKSAtPiBOb25lOgogICAgIiIiSG9zdCBjYW4gc3Vic2NyaWJlIHRvIHByZW1pdW0gcGxhbi4iIiIKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogInByZW1pdW0iLCAicGF5bWVudF90b2tlbiI6ICJ0b2tfcHJlbWl1bSJ9LAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gMjAxCiAgICBkYXRhID0gcmVzcG9uc2UuanNvbigpCiAgICBhc3NlcnQgZGF0YVsicGxhbl90eXBlIl0gPT0gInByZW1pdW0iCiAgICBhc3NlcnQgZGF0YVsiYW1vdW50Il0gPT0gMTY0OTkuMAoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X3JlYWN0aXZhdGVfYWZ0ZXJfY2FuY2VsKGNsaWVudDogQXN5bmNDbGllbnQsIGhvc3RfdG9rZW46IHN0cikgLT4gTm9uZToKICAgICIiIkhvc3QgY2FuIHJlYWN0aXZhdGUgYWZ0ZXIgY2FuY2VsbGF0aW9uLiIiIgogICAgIyBTdWJzY3JpYmUKICAgIGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsCiAgICAgICAganNvbj17InBsYW5fdHlwZSI6ICJiYXNpYyIsICJwYXltZW50X3Rva2VuIjogInRva19yZWFjdCJ9LAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICAjIENhbmNlbAogICAgYXdhaXQgY2xpZW50LnB1dCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy9jYW5jZWwiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICAjIFJlc3Vic2NyaWJlCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsCiAgICAgICAganNvbj17InBsYW5fdHlwZSI6ICJwcm8iLCAicGF5bWVudF90b2tlbiI6ICJ0b2tfcmVhY3QyIn0sCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSAyMDEKICAgIGFzc2VydCByZXNwb25zZS5qc29uKClbInN0YXR1cyJdID09ICJhY3RpdmUiCiAgICBhc3NlcnQgcmVzcG9uc2UuanNvbigpWyJwbGFuX3R5cGUiXSA9PSAicHJvIgoKCkBweXRlc3QubWFyay5hc3luY2lvCmFzeW5jIGRlZiB0ZXN0X2NhbmNlbF9hbHJlYWR5X2NhbmNlbGxlZChjbGllbnQ6IEFzeW5jQ2xpZW50LCBob3N0X3Rva2VuOiBzdHIpIC0+IE5vbmU6CiAgICAiIiJDYW5jZWxsaW5nIGFuIGFscmVhZHktY2FuY2VsbGVkIG1lbWJlcnNoaXAgcmV0dXJucyA0MDAuIiIiCiAgICBhd2FpdCBjbGllbnQucG9zdCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy9zdWJzY3JpYmUiLAogICAgICAgIGpzb249eyJwbGFuX3R5cGUiOiAiYmFzaWMiLCAicGF5bWVudF90b2tlbiI6ICJ0b2tfY2FuY2VsMiJ9LAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICBhd2FpdCBjbGllbnQucHV0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL2NhbmNlbCIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LnB1dCgKICAgICAgICAiL2FwaS92MS9tZW1iZXJzaGlwcy9jYW5jZWwiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gNDAwCgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3RfZ2V0X21lbWJlcnNoaXBfbm9fc3Vic2NyaXB0aW9uKGNsaWVudDogQXN5bmNDbGllbnQsIGhvc3RfdG9rZW46IHN0cikgLT4gTm9uZToKICAgICIiIkdldHRpbmcgbWVtYmVyc2hpcCB3aGVuIG5vbmUgZXhpc3RzIHJldHVybnMgNDA0LiIiIgogICAgcmVzcG9uc2UgPSBhd2FpdCBjbGllbnQuZ2V0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL2N1cnJlbnQiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgcmVzcG9uc2Uuc3RhdHVzX2NvZGUgPT0gNDA0CgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3Rfd2ViaG9va19wYXltZW50X3N1Y2NlZWRlZChjbGllbnQ6IEFzeW5jQ2xpZW50LCBob3N0X3Rva2VuOiBzdHIpIC0+IE5vbmU6CiAgICAiIiJXZWJob29rIGZvciBwYXltZW50LnN1Y2NlZWRlZCB1cGRhdGVzIG1lbWJlcnNoaXAgdG8gYWN0aXZlLiIiIgogICAgYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogImJhc2ljIiwgInBheW1lbnRfdG9rZW4iOiAidG9rX3doX3N1Y2Nlc3MifSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQogICAgcGF5bWVudF9yZWYgPSAic2ltX3Rva193aF9zdWNjZXNzIgoKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvd2ViaG9vayIsCiAgICAgICAganNvbj17CiAgICAgICAgICAgICJldmVudF90eXBlIjogInBheW1lbnQuc3VjY2VlZGVkIiwKICAgICAgICAgICAgInBheW1lbnRfcmVmIjogcGF5bWVudF9yZWYsCiAgICAgICAgICAgICJzdGF0dXMiOiAic3VjY2VlZGVkIiwKICAgICAgICB9LAogICAgICAgIGhlYWRlcnM9eyJ4LXdlYmhvb2stc2VjcmV0IjogIkNIQU5HRS1NRS13ZWJob29rLXNlY3JldCJ9LAogICAgKQogICAgYXNzZXJ0IHJlc3BvbnNlLnN0YXR1c19jb2RlID09IDIwMAogICAgYXNzZXJ0IHJlc3BvbnNlLmpzb24oKVsic3RhdHVzIl0gPT0gInByb2Nlc3NlZCIKCgpAcHl0ZXN0Lm1hcmsuYXN5bmNpbwphc3luYyBkZWYgdGVzdF93ZWJob29rX3BheW1lbnRfZmFpbGVkKGNsaWVudDogQXN5bmNDbGllbnQsIGhvc3RfdG9rZW46IHN0cikgLT4gTm9uZToKICAgICIiIldlYmhvb2sgZm9yIHBheW1lbnQuZmFpbGVkIHVwZGF0ZXMgbWVtYmVyc2hpcCB0byBwYXN0X2R1ZS4iIiIKICAgIGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsCiAgICAgICAganNvbj17InBsYW5fdHlwZSI6ICJiYXNpYyIsICJwYXltZW50X3Rva2VuIjogInRva193aF9mYWlsIn0sCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3dlYmhvb2siLAogICAgICAgIGpzb249ewogICAgICAgICAgICAiZXZlbnRfdHlwZSI6ICJwYXltZW50LmZhaWxlZCIsCiAgICAgICAgICAgICJwYXltZW50X3JlZiI6ICJzaW1fdG9rX3doX2ZhaWwiLAogICAgICAgICAgICAic3RhdHVzIjogImZhaWxlZCIsCiAgICAgICAgfSwKICAgICAgICBoZWFkZXJzPXsieC13ZWJob29rLXNlY3JldCI6ICJDSEFOR0UtTUUtd2ViaG9vay1zZWNyZXQifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSAyMDAKCiAgICAjIFZlcmlmeSBtZW1iZXJzaGlwIHN0YXR1cwogICAgbWVtX3Jlc3AgPSBhd2FpdCBjbGllbnQuZ2V0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL2N1cnJlbnQiLAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICBhc3NlcnQgbWVtX3Jlc3AuanNvbigpWyJzdGF0dXMiXSA9PSAicGFzdF9kdWUiCgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3Rfd2ViaG9va19zdWJzY3JpcHRpb25fY2FuY2VsbGVkKGNsaWVudDogQXN5bmNDbGllbnQsIGhvc3RfdG9rZW46IHN0cikgLT4gTm9uZToKICAgICIiIldlYmhvb2sgZm9yIHN1YnNjcmlwdGlvbi5jYW5jZWxsZWQgdXBkYXRlcyBtZW1iZXJzaGlwIHN0YXR1cy4iIiIKICAgIGF3YWl0IGNsaWVudC5wb3N0KAogICAgICAgICIvYXBpL3YxL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsCiAgICAgICAganNvbj17InBsYW5fdHlwZSI6ICJiYXNpYyIsICJwYXltZW50X3Rva2VuIjogInRva193aF9jYW5jZWwifSwKICAgICAgICBoZWFkZXJzPXsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHtob3N0X3Rva2VufSJ9LAogICAgKQoKICAgIHJlc3BvbnNlID0gYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvd2ViaG9vayIsCiAgICAgICAganNvbj17CiAgICAgICAgICAgICJldmVudF90eXBlIjogInN1YnNjcmlwdGlvbi5jYW5jZWxsZWQiLAogICAgICAgICAgICAicGF5bWVudF9yZWYiOiAic2ltX3Rva193aF9jYW5jZWwiLAogICAgICAgICAgICAic3RhdHVzIjogImNhbmNlbGxlZCIsCiAgICAgICAgfSwKICAgICAgICBoZWFkZXJzPXsieC13ZWJob29rLXNlY3JldCI6ICJDSEFOR0UtTUUtd2ViaG9vay1zZWNyZXQifSwKICAgICkKICAgIGFzc2VydCByZXNwb25zZS5zdGF0dXNfY29kZSA9PSAyMDAKCiAgICBtZW1fcmVzcCA9IGF3YWl0IGNsaWVudC5nZXQoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvY3VycmVudCIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgIGFzc2VydCBtZW1fcmVzcC5qc29uKClbInN0YXR1cyJdID09ICJjYW5jZWxsZWQiCgoKQHB5dGVzdC5tYXJrLmFzeW5jaW8KYXN5bmMgZGVmIHRlc3RfbWVtYmVyc2hpcF9maWVsZHNfY29tcGxldGUoY2xpZW50OiBBc3luY0NsaWVudCwgaG9zdF90b2tlbjogc3RyKSAtPiBOb25lOgogICAgIiIiTWVtYmVyc2hpcCByZXNwb25zZSBpbmNsdWRlcyBhbGwgZXhwZWN0ZWQgZmllbGRzLiIiIgogICAgYXdhaXQgY2xpZW50LnBvc3QoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlIiwKICAgICAgICBqc29uPXsicGxhbl90eXBlIjogImJhc2ljIiwgInBheW1lbnRfdG9rZW4iOiAidG9rX2ZpZWxkcyJ9LAogICAgICAgIGhlYWRlcnM9eyJBdXRob3JpemF0aW9uIjogZiJCZWFyZXIge2hvc3RfdG9rZW59In0sCiAgICApCiAgICByZXNwb25zZSA9IGF3YWl0IGNsaWVudC5nZXQoCiAgICAgICAgIi9hcGkvdjEvbWVtYmVyc2hpcHMvY3VycmVudCIsCiAgICAgICAgaGVhZGVycz17IkF1dGhvcml6YXRpb24iOiBmIkJlYXJlciB7aG9zdF90b2tlbn0ifSwKICAgICkKICAgIGRhdGEgPSByZXNwb25zZS5qc29uKCkKICAgIGFzc2VydCAiaWQiIGluIGRhdGEKICAgIGFzc2VydCAiaG9zdF9pZCIgaW4gZGF0YQogICAgYXNzZXJ0ICJwbGFuX3R5cGUiIGluIGRhdGEKICAgIGFzc2VydCAic3RhcnRfZGF0ZSIgaW4gZGF0YQogICAgYXNzZXJ0ICJlbmRfZGF0ZSIgaW4gZGF0YQogICAgYXNzZXJ0ICJzdGF0dXMiIGluIGRhdGEKICAgIGFzc2VydCAiYXV0b19yZW5ldyIgaW4gZGF0YQogICAgYXNzZXJ0ICJhbW91bnQiIGluIGRhdGEKICAgIGFzc2VydCAibWF4X2xpc3RpbmdzIiBpbiBkYXRhCiAgICBhc3NlcnQgZGF0YVsiYXV0b19yZW5ldyJdIGlzIFRydWUK</t>
   </si>
   <si>
     <t>backend/tests/test_messages.py</t>
@@ -16457,9 +16571,9 @@
   **Response:**
   ```json
   [
-  { "plan_type": "basic", "label": "Basic", "price": 9.99, "max_listings": 3 },
-  { "plan_type": "pro", "label": "Professional", "price": 29.99, "max_listings": 15 },
-  { "plan_type": "premium", "label": "Premium", "price": 59.99, "max_listings": 999 }
+  { "plan_type": "basic", "label": "Basic", "price": 2499.00, "max_listings": 5 },
+  { "plan_type": "pro", "label": "Pro", "price": 6499.00, "max_listings": 25 },
+  { "plan_type": "premium", "label": "Premium", "price": 16499.00, "max_listings": 999999 }
   ]
   ```
   ---
@@ -16490,8 +16604,8 @@
   "end_date": "2026-04-16T10:00:00Z",
   "status": "active",
   "auto_renew": true,
-  "amount": 29.99,
-  "max_listings": 15,
+  "amount": 6499.00,
+  "max_listings": 25,
   "created_at": "2026-03-16T10:00:00Z",
   "updated_at": "2026-03-16T10:00:00Z"
   }
@@ -16552,11 +16666,12 @@
   ```json
   {
   "total_users": 150,
-  "total_hosts": 35,
   "total_properties": 80,
+  "active_members": 30,
   "total_bookings": 220,
-  "total_revenue": 45000.00,
-  "active_memberships": 30
+  "completed_bookings": 180,
+  "monthly_revenue": 45000.00,
+  "platform_growth": 0
   }
   ```
   ---
@@ -16636,7 +16751,7 @@
   | Messages List</t>
   </si>
   <si>
-    <t>IyBBUEkgUmVmZXJlbmNlIOKAlCBDb21wbGV0ZSBFbmRwb2ludCAmIEZlYXR1cmUgRG9jdW1lbnRhdGlvbgogIAogID4gKipCYXNlIFVSTDoqKiBgaHR0cDovL2xvY2FsaG9zdDo4MDAwYAogID4gKipTd2FnZ2VyIFVJOioqIGBodHRwOi8vbG9jYWxob3N0OjgwMDAvZG9jc2AKICA+ICoqUmVEb2M6KiogYGh0dHA6Ly9sb2NhbGhvc3Q6ODAwMC9yZWRvY2AKICA+ICoqQVBJIFByZWZpeDoqKiBgL2FwaS92MWAKICAKICAtLS0KICAKICAjIyBUYWJsZSBvZiBDb250ZW50cwogIAogIDEuIFtRdWljayBTdGFydCDigJQgSG93IHRvIFRlc3RdKCNxdWljay1zdGFydC0taG93LXRvLXRlc3QpCiAgMi4gW0F1dGhlbnRpY2F0aW9uIEZsb3ddKCNhdXRoZW50aWNhdGlvbi1mbG93KQogIDMuIFtFbmRwb2ludHMgT3ZlcnZpZXcgKDM2IFRvdGFsKV0oI2VuZHBvaW50cy1vdmVydmlldykKICA0LiBbSGVhbHRoXSgjMS1oZWFsdGgpCiAgNS4gW0F1dGggKDUgZW5kcG9pbnRzKV0oIzItYXV0aGVudGljYXRpb24pCiAgNi4gW1Byb3BlcnRpZXMgKDcgZW5kcG9pbnRzKV0oIzMtcHJvcGVydGllcykKICA3LiBbQm9va2luZ3MgKDUgZW5kcG9pbnRzKV0oIzQtYm9va2luZ3MpCiAgOC4gW01lc3NhZ2luZyAoNSBlbmRwb2ludHMpXSgjNS1tZXNzYWdpbmcpCiAgOS4gW1Jldmlld3MgKDMgZW5kcG9pbnRzKV0oIzYtcmV2aWV3cykKICAxMC4gW01lbWJlcnNoaXBzICg1IGVuZHBvaW50cyldKCM3LW1lbWJlcnNoaXBzKQogIDExLiBbQWRtaW4gKDUgZW5kcG9pbnRzKV0oIzgtYWRtaW4pCiAgMTIuIFtGcm9udGVuZCBQYWdlIOKGkiBFbmRwb2ludCBNYXBdKCNmcm9udGVuZC1wYWdlLS1lbmRwb2ludC1tYXApCiAgMTMuIFtGZWF0dXJlcyBXb3JraW5nIEVuZC10by1FbmRdKCNmZWF0dXJlcy13b3JraW5nLWVuZC10by1lbmQpCiAgMTQuIFtGZWF0dXJlcyBOb3QgWWV0IFdpcmVkIChQbGFjZWhvbGRlcildKCNmZWF0dXJlcy1ub3QteWV0LXdpcmVkLXBsYWNlaG9sZGVyKQogIDE1LiBbU2NoZW1hIFJlZmVyZW5jZV0oI3NjaGVtYS1yZWZlcmVuY2UpCiAgCiAgLS0tCiAgCiAgIyMgUXVpY2sgU3RhcnQg4oCUIEhvdyB0byBUZXN0CiAgCiAgIyMjIEZyb20gU3dhZ2dlciBVSSAoYC9kb2NzYCkKICAKICAxLiBPcGVuIGBodHRwOi8vbG9jYWxob3N0OjgwMDAvZG9jc2AgaW4gYSBicm93c2VyLgogIDIuICoqUmVnaXN0ZXIqKiBhIHVzZXIgdmlhIGBQT1NUIC9hcGkvdjEvYXV0aC9yZWdpc3RlcmAuCiAgMy4gKipMb2dpbioqIHZpYSBgUE9TVCAvYXBpL3YxL2F1dGgvbG9naW5gIOKGkiBjb3B5IHRoZSBgYWNjZXNzX3Rva2VuYCBmcm9tIHRoZSByZXNwb25zZS4KICA0LiBDbGljayB0aGUgKipBdXRob3JpemUg8J+UkioqIGJ1dHRvbiBhdCB0aGUgdG9wIG9mIFN3YWdnZXIgVUkg4oaSIHBhc3RlIGBCZWFyZXIgPGFjY2Vzc190b2tlbj5gIOKGkiBjbGljayAqKkF1dGhvcml6ZSoqLgogIDUuIFlvdSBhcmUgbm93IGF1dGhlbnRpY2F0ZWQgYW5kIGNhbiB0ZXN0IGFsbCBwcm90ZWN0ZWQgZW5kcG9pbnRzLgogIAogICMjIyBBdXRoZW50aWNhdGlvbiBIZWFkZXIKICAKICBBbGwgcHJvdGVjdGVkIGVuZHBvaW50cyByZXF1aXJlOgogIAogIGBgYAogIEF1dGhvcml6YXRpb246IEJlYXJlciA8YWNjZXNzX3Rva2VuPgogIGBgYAogIAogICMjIyBSb2xlcwogIAogIHwgUm9sZSB8IENhcGFiaWxpdGllcyB8CiAgfC0tLS0tLXwtLS0tLS0tLS0tLS0tfAogIHwgYHVzZXJgIHwgQnJvd3NlIHByb3BlcnRpZXMsIGNyZWF0ZSBib29raW5ncywgc2VuZCBtZXNzYWdlcywgd3JpdGUgcmV2aWV3cyB8CiAgfCBgaG9zdGAgfCBFdmVyeXRoaW5nIGEgdXNlciBjYW4gZG8gKyBjcmVhdGUvbWFuYWdlIHByb3BlcnRpZXMsIG1hbmFnZSBtZXNzYWdlcywgcmVxdWlyZXMgbWVtYmVyc2hpcCB8CiAgfCBgYWRtaW5gIHwgRnVsbCBwbGF0Zm9ybSBhZG1pbmlzdHJhdGlvbiAodXNlci9wcm9wZXJ0eS9tZW1iZXJzaGlwIG1hbmFnZW1lbnQsIGRhc2hib2FyZCBtZXRyaWNzKSB8CiAgCiAgLS0tCiAgCiAgIyMgQXV0aGVudGljYXRpb24gRmxvdwogIAogIGBgYAogIFJlZ2lzdGVyIOKGkiBMb2dpbiDihpIgR2V0IGFjY2Vzc190b2tlbiArIHJlZnJlc2hfdG9rZW4KICDihpIgVXNlIGFjY2Vzc190b2tlbiBpbiBBdXRob3JpemF0aW9uIGhlYWRlcgogIOKGkiBXaGVuIGV4cGlyZWQsIFBPU1QgL2F1dGgvcmVmcmVzaCB3aXRoIHJlZnJlc2hfdG9rZW4KICDihpIgR2V0IG5ldyBhY2Nlc3NfdG9rZW4KICBgYGAKICAKICAtLS0KICAKICAjIyBFbmRwb2ludHMgT3ZlcnZpZXcKICAKICB8IENhdGVnb3J5IHwgQ291bnQgfCBBdXRoIFJlcXVpcmVkIHwKICB8LS0tLS0tLS0tLXwtLS0tLS0tfC0tLS0tLS0tLS0tLS0tfAogIHwgSGVhbHRoIHwgMSB8IE5vIHwKICB8IEF1dGggfCA1IHwgTWl4ZWQgfAogIHwgUHJvcGVydGllcyB8IDcgfCBNaXhlZCB8CiAgfCBCb29raW5ncyB8IDUgfCBZZXMgfAogIHwgTWVzc2FnaW5nIHwgNSB8IFllcyB8CiAgfCBSZXZpZXdzIHwgMyB8IE1peGVkIHwKICB8IE1lbWJlcnNoaXBzIHwgNSB8IE1peGVkIHwKICB8IEFkbWluIHwgNSB8IFllcyAoYWRtaW4pIHwKICB8ICoqVG90YWwqKiB8ICoqMzYqKiB8IHwKICAKICAtLS0KICAKICAjIyAxLiBIZWFsdGgKICAKICAjIyMgYEdFVCAvaGVhbHRoYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8IE5vbmUgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgUmV0dXJucyBhcHAgaGVhbHRoIHN0YXR1cyBhbmQgdmVyc2lvbiB8CiAgfCAqKkZyb250ZW5kKiogfCBOb3QgdXNlZCBkaXJlY3RseSB8CiAgCiAgKipSZXNwb25zZToqKgogIGBgYGpzb24KICB7CiAgInN0YXR1cyI6ICJoZWFsdGh5IiwKICAidmVyc2lvbiI6ICIxLjAuMCIKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMgMi4gQXV0aGVudGljYXRpb24KICAKICAjIyMgMi4xIGBQT1NUIC9hcGkvdjEvYXV0aC9yZWdpc3RlcmAKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCBOb25lIHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IFJlZ2lzdGVyIGEgbmV3IHVzZXIgYWNjb3VudCB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9hdXRoL3JlZ2lzdGVyL3BhZ2UudHN4YCB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBVc2VyUmVnaXN0ZXJgKToqKgogIGBgYGpzb24KICB7CiAgImVtYWlsIjogInVzZXJAZXhhbXBsZS5jb20iLAogICJwYXNzd29yZCI6ICJzZWN1cmVwYXNzd29yZDEyMyIsCiAgImZ1bGxfbmFtZSI6ICJKb2huIERvZSIsCiAgInBob25lIjogIisxMjM0NTY3ODkwIiwKICAicm9sZSI6ICJ1c2VyIgogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgRGVmYXVsdCB8IENvbnN0cmFpbnRzIHwKICB8LS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18LS0tLS0tLS0tLS0tLXwKICB8IGBlbWFpbGAgfCBFbWFpbFN0ciB8ICoqWWVzKiogfCDigJQgfCBWYWxpZCBlbWFpbCB8CiAgfCBgcGFzc3dvcmRgIHwgc3RyaW5nIHwgKipZZXMqKiB8IOKAlCB8IG1pbiA4LCBtYXggMTI4IGNoYXJzIHwKICB8IGBmdWxsX25hbWVgIHwgc3RyaW5nIHwgKipZZXMqKiB8IOKAlCB8IG1pbiAxLCBtYXggMjU1IGNoYXJzIHwKICB8IGBwaG9uZWAgfCBzdHJpbmcgXHwgbnVsbCB8IE5vIHwgYG51bGxgIHwg4oCUIHwKICB8IGByb2xlYCB8IHN0cmluZyB8IE5vIHwgYCJ1c2VyImAgfCBgInVzZXIiYCBvciBgImhvc3QiYCB8CiAgCiAgKipSZXNwb25zZSAoYFRva2VuUmVzcG9uc2VgKToqKgogIGBgYGpzb24KICB7CiAgImFjY2Vzc190b2tlbiI6ICJleUpoYkdjaU9pSklVekkxTmlJcy4uLiIsCiAgInJlZnJlc2hfdG9rZW4iOiAiZXlKaGJHY2lPaUpJVXpJMU5pSXMuLi4iLAogICJ0b2tlbl90eXBlIjogImJlYXJlciIKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMjIDIuMiBgUE9TVCAvYXBpL3YxL2F1dGgvbG9naW5gCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgTm9uZSB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBBdXRoZW50aWNhdGUgYW5kIHJlY2VpdmUgSldUIHRva2VucyB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9hdXRoL2xvZ2luL3BhZ2UudHN4YCB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBVc2VyTG9naW5gKToqKgogIGBgYGpzb24KICB7CiAgImVtYWlsIjogInVzZXJAZXhhbXBsZS5jb20iLAogICJwYXNzd29yZCI6ICJzZWN1cmVwYXNzd29yZDEyMyIKICB9CiAgYGBgCiAgCiAgfCBGaWVsZCB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18CiAgfCBgZW1haWxgIHwgRW1haWxTdHIgfCAqKlllcyoqIHwKICB8IGBwYXNzd29yZGAgfCBzdHJpbmcgfCAqKlllcyoqIHwKICAKICAqKlJlc3BvbnNlIChgVG9rZW5SZXNwb25zZWApOioqCiAgYGBganNvbgogIHsKICAiYWNjZXNzX3Rva2VuIjogImV5SmhiR2NpT2lKSVV6STFOaUlzLi4uIiwKICAicmVmcmVzaF90b2tlbiI6ICJleUpoYkdjaU9pSklVekkxTmlJcy4uLiIsCiAgInRva2VuX3R5cGUiOiAiYmVhcmVyIgogIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgMi4zIGBQT1NUIC9hcGkvdjEvYXV0aC9yZWZyZXNoYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8IE5vbmUgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgUmVmcmVzaCBhY2Nlc3MgdG9rZW4gdXNpbmcgYSB2YWxpZCByZWZyZXNoIHRva2VuIHwKICB8ICoqRnJvbnRlbmQqKiB8IEF1dG9tYXRpYyB2aWEgQXhpb3MgaW50ZXJjZXB0b3IgaW4gYGZyb250ZW5kL3NyYy9saWIvYXBpLnRzYCB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBUb2tlblJlZnJlc2hgKToqKgogIGBgYGpzb24KICB7CiAgInJlZnJlc2hfdG9rZW4iOiAiZXlKaGJHY2lPaUpJVXpJMU5pSXMuLi4iCiAgfQogIGBgYAogIAogIHwgRmllbGQgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfAogIHwgYHJlZnJlc2hfdG9rZW5gIHwgc3RyaW5nIHwgKipZZXMqKiB8CiAgCiAgKipSZXNwb25zZSAoYFRva2VuUmVzcG9uc2VgKToqKgogIGBgYGpzb24KICB7CiAgImFjY2Vzc190b2tlbiI6ICJuZXdfYWNjZXNzX3Rva2VuLi4uIiwKICAicmVmcmVzaF90b2tlbiI6ICJuZXdfcmVmcmVzaF90b2tlbi4uLiIsCiAgInRva2VuX3R5cGUiOiAiYmVhcmVyIgogIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgMi40IGBHRVQgL2FwaS92MS9hdXRoL21lYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIEJlYXJlciB0b2tlbiB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBHZXQgdGhlIGN1cnJlbnQgdXNlcidzIHByb2ZpbGUgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvYXV0aC9sb2dpbi9wYWdlLnRzeGAsIGBmcm9udGVuZC9zcmMvYXBwL2F1dGgvcmVnaXN0ZXIvcGFnZS50c3hgIChjYWxsZWQgYWZ0ZXIgbG9naW4pIHwKICAKICAqKlBhcmFtZXRlcnM6KiogTm9uZQogIAogICoqUmVzcG9uc2UgKGBVc2VyT3V0YCk6KioKICBgYGBqc29uCiAgewogICJpZCI6ICI1NTBlODQwMC1lMjliLTQxZDQtYTcxNi00NDY2NTU0NDAwMDAiLAogICJlbWFpbCI6ICJ1c2VyQGV4YW1wbGUuY29tIiwKICAiZnVsbF9uYW1lIjogIkpvaG4gRG9lIiwKICAicGhvbmUiOiAiKzEyMzQ1Njc4OTAiLAogICJyb2xlIjogImhvc3QiLAogICJpc19hY3RpdmUiOiB0cnVlLAogICJjcmVhdGVkX2F0IjogIjIwMjYtMDMtMTZUMTA6MDA6MDBaIgogIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgMi41IGBQVVQgL2FwaS92MS9hdXRoL21lYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIEJlYXJlciB0b2tlbiB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBVcGRhdGUgdGhlIGN1cnJlbnQgdXNlcidzIHByb2ZpbGUgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvcHJvZmlsZS9wYWdlLnRzeGAgfAogIAogICoqUmVxdWVzdCBCb2R5IChgVXNlclVwZGF0ZWApOioqCiAgYGBganNvbgogIHsKICAiZnVsbF9uYW1lIjogIkpvaG4gVXBkYXRlZCIsCiAgInBob25lIjogIiswOTg3NjU0MzIxIgogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgQ29uc3RyYWludHMgfAogIHwtLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgZnVsbF9uYW1lYCB8IHN0cmluZyBcfCBudWxsIHwgTm8gfCBtaW4gMSwgbWF4IDI1NSBjaGFycyB8CiAgfCBgcGhvbmVgIHwgc3RyaW5nIFx8IG51bGwgfCBObyB8IOKAlCB8CiAgCiAgKipSZXNwb25zZSAoYFVzZXJPdXRgKToqKiBTYW1lIGFzIEdFVCAvYXV0aC9tZQogIAogIC0tLQogIAogICMjIDMuIFByb3BlcnRpZXMKICAKICAjIyMgMy4xIGBHRVQgL2FwaS92MS9wcm9wZXJ0aWVzYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8IE5vbmUgKHB1YmxpYykgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgU2VhcmNoIGFuZCBmaWx0ZXIgcHJvcGVydHkgbGlzdGluZ3MgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvcHJvcGVydGllcy9wYWdlLnRzeGAsIGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9wYWdlLnRzeGAsIGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9wcm9wZXJ0aWVzL3BhZ2UudHN4YCB8CiAgCiAgKipRdWVyeSBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfCBEZWZhdWx0IHwgQ29uc3RyYWludHMgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18LS0tLS0tLS0tLS0tLXwKICB8IGBjaXR5YCB8IHN0cmluZyB8IE5vIHwg4oCUIHwg4oCUIHwKICB8IGBtaW5fcHJpY2VgIHwgZmxvYXQgfCBObyB8IOKAlCB8ID49IDAgfAogIHwgYG1heF9wcmljZWAgfCBmbG9hdCB8IE5vIHwg4oCUIHwgPj0gMCB8CiAgfCBgbWF4X2d1ZXN0c2AgfCBpbnQgfCBObyB8IOKAlCB8ID49IDEgfAogIHwgYGhvdXJseV9hdmFpbGFibGVgIHwgYm9vbCB8IE5vIHwg4oCUIHwg4oCUIHwKICB8IGBob3N0X2lkYCB8IFVVSUQgfCBObyB8IOKAlCB8IEZpbHRlciBieSBob3N0IHwKICB8IGBwYWdlYCB8IGludCB8IE5vIHwgYDFgIHwgPj0gMSB8CiAgfCBgcGFnZV9zaXplYCB8IGludCB8IE5vIHwgYDIwYCB8IDHigJMxMDAgfAogIAogICoqRXhhbXBsZToqKiBgR0VUIC9hcGkvdjEvcHJvcGVydGllcz9jaXR5PU1pYW1pJm1pbl9wcmljZT01MCZtYXhfcHJpY2U9MjAwJnBhZ2U9MSZwYWdlX3NpemU9MTBgCiAgCiAgKipSZXNwb25zZSAoYFBhZ2luYXRlZFJlc3BvbnNlPFByb3BlcnR5T3V0PmApOioqCiAgYGBganNvbgogIHsKICAiaXRlbXMiOiBbCiAgewogICJpZCI6ICJ1dWlkIiwKICAiaG9zdF9pZCI6ICJ1dWlkIiwKICAidGl0bGUiOiAiQmVhY2ggSG91c2UgTWlhbWkiLAogICJkZXNjcmlwdGlvbiI6ICJCZWF1dGlmdWwgYmVhY2hmcm9udCBwcm9wZXJ0eS4uLiIsCiAgImNpdHkiOiAiTWlhbWkiLAogICJhZGRyZXNzIjogIjEyMyBPY2VhbiBEcml2ZSIsCiAgImxhdGl0dWRlIjogMjUuNzYxNywKICAibG9uZ2l0dWRlIjogLTgwLjE5MTgsCiAgInByaWNlX3Blcl9uaWdodCI6IDE1MC4wMCwKICAibWF4X2d1ZXN0cyI6IDQsCiAgImFtZW5pdGllcyI6IFsid2lmaSIsICJwb29sIiwgInBhcmtpbmciXSwKICAiaXNfYWN0aXZlIjogdHJ1ZSwKICAiaG91cmx5X2VuYWJsZWQiOiBmYWxzZSwKICAiaW1hZ2VzIjogWwogIHsgImlkIjogInV1aWQiLCAiaW1hZ2VfdXJsIjogIi91cGxvYWRzL2ltZy5qcGciLCAiaXNfcHJpbWFyeSI6IHRydWUsICJzb3J0X29yZGVyIjogMCB9CiAgXSwKICAiaG91cmx5X2NvbmZpZyI6IG51bGwsCiAgImNyZWF0ZWRfYXQiOiAiMjAyNi0wMy0wMVQxMDowMDowMFoiLAogICJ1cGRhdGVkX2F0IjogIjIwMjYtMDMtMTVUMTA6MDA6MDBaIgogIH0KICBdLAogICJ0b3RhbCI6IDI1LAogICJwYWdlIjogMSwKICAicGFnZV9zaXplIjogMTAKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMjIDMuMiBgR0VUIC9hcGkvdjEvcHJvcGVydGllcy97cHJvcGVydHlfaWR9YAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8IE5vbmUgKHB1YmxpYykgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgR2V0IGEgc2luZ2xlIHByb3BlcnR5IGJ5IElEIHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL3Byb3BlcnRpZXMvW2lkXS9wYWdlLnRzeGAsIGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9wcm9wZXJ0aWVzL1tpZF0vZWRpdC9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBwcm9wZXJ0eV9pZGAgfCBVVUlEIHwgKipZZXMqKiB8CiAgCiAgKipSZXNwb25zZSAoYFByb3BlcnR5T3V0YCk6KiogU2luZ2xlIHByb3BlcnR5IG9iamVjdCAoc2FtZSBzaGFwZSBhcyBpdGVtcyBpbiBzZWFyY2gpCiAgCiAgLS0tCiAgCiAgIyMjIDMuMyBgUE9TVCAvYXBpL3YxL3Byb3BlcnRpZXNgCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgKipZZXMqKiDigJQgSG9zdCBvbmx5IChyZXF1aXJlcyBhY3RpdmUgbWVtYmVyc2hpcCkgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgQ3JlYXRlIGEgbmV3IHByb3BlcnR5IGxpc3RpbmcgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvZGFzaGJvYXJkL3Byb3BlcnRpZXMvbmV3L3BhZ2UudHN4YCB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBQcm9wZXJ0eUNyZWF0ZWApOioqCiAgYGBganNvbgogIHsKICAidGl0bGUiOiAiQ296eSBBcGFydG1lbnQgRG93bnRvd24iLAogICJkZXNjcmlwdGlvbiI6ICJBIGJlYXV0aWZ1bCBhcGFydG1lbnQgaW4gdGhlIGhlYXJ0IG9mIHRoZSBjaXR5IHdpdGggYW1hemluZyB2aWV3cy4iLAogICJjaXR5IjogIk5ldyBZb3JrIiwKICAiYWRkcmVzcyI6ICI0NTYgQnJvYWR3YXksIE5ldyBZb3JrLCBOWSAxMDAxMyIsCiAgImxhdGl0dWRlIjogNDAuNzEyOCwKICAibG9uZ2l0dWRlIjogLTc0LjAwNjAsCiAgInByaWNlX3Blcl9uaWdodCI6IDEyMC4wMCwKICAibWF4X2d1ZXN0cyI6IDIsCiAgImFtZW5pdGllcyI6IFsid2lmaSIsICJraXRjaGVuIiwgImFpcl9jb25kaXRpb25pbmciXQogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgRGVmYXVsdCB8IENvbnN0cmFpbnRzIHwKICB8LS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18LS0tLS0tLS0tLS0tLXwKICB8IGB0aXRsZWAgfCBzdHJpbmcgfCAqKlllcyoqIHwg4oCUIHwgbWluIDMsIG1heCAyNTUgY2hhcnMgfAogIHwgYGRlc2NyaXB0aW9uYCB8IHN0cmluZyB8ICoqWWVzKiogfCDigJQgfCBtaW4gMTAgY2hhcnMgfAogIHwgYGNpdHlgIHwgc3RyaW5nIHwgKipZZXMqKiB8IOKAlCB8IG1pbiAxLCBtYXggMTAwIGNoYXJzIHwKICB8IGBhZGRyZXNzYCB8IHN0cmluZyB8ICoqWWVzKiogfCDigJQgfCBtaW4gNSwgbWF4IDUwMCBjaGFycyB8CiAgfCBgbGF0aXR1ZGVgIHwgZmxvYXQgXHwgbnVsbCB8IE5vIHwgYG51bGxgIHwg4oCUIHwKICB8IGBsb25naXR1ZGVgIHwgZmxvYXQgXHwgbnVsbCB8IE5vIHwgYG51bGxgIHwg4oCUIHwKICB8IGBwcmljZV9wZXJfbmlnaHRgIHwgZmxvYXQgfCAqKlllcyoqIHwg4oCUIHwgPiAwIHwKICB8IGBtYXhfZ3Vlc3RzYCB8IGludCB8IE5vIHwgYDFgIHwgMeKAkzUwIHwKICB8IGBhbWVuaXRpZXNgIHwgbGlzdFtzdHJpbmddIFx8IG51bGwgfCBObyB8IGBudWxsYCB8IOKAlCB8CiAgCiAgKipSZXNwb25zZSAoYFByb3BlcnR5T3V0YCk6KiogVGhlIGNyZWF0ZWQgcHJvcGVydHkgb2JqZWN0CiAgCiAgLS0tCiAgCiAgIyMjIDMuNCBgUFVUIC9hcGkvdjEvcHJvcGVydGllcy97cHJvcGVydHlfaWR9YAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIEhvc3Qgb25seSwgbXVzdCBiZSBwcm9wZXJ0eSBvd25lciB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBVcGRhdGUgYSBwcm9wZXJ0eSBsaXN0aW5nIHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9wcm9wZXJ0aWVzL1tpZF0vZWRpdC9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBwcm9wZXJ0eV9pZGAgfCBVVUlEIHwgKipZZXMqKiB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBQcm9wZXJ0eVVwZGF0ZWApOioqCiAgYGBganNvbgogIHsKICAidGl0bGUiOiAiVXBkYXRlZCBBcGFydG1lbnQgTmFtZSIsCiAgInByaWNlX3Blcl9uaWdodCI6IDEzNS4wMCwKICAiYW1lbml0aWVzIjogWyJ3aWZpIiwgImtpdGNoZW4iLCAiYWlyX2NvbmRpdGlvbmluZyIsICJneW0iXQogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgQ29uc3RyYWludHMgfAogIHwtLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgdGl0bGVgIHwgc3RyaW5nIFx8IG51bGwgfCBObyB8IG1pbiAzLCBtYXggMjU1IHwKICB8IGBkZXNjcmlwdGlvbmAgfCBzdHJpbmcgXHwgbnVsbCB8IE5vIHwgbWluIDEwIHwKICB8IGBjaXR5YCB8IHN0cmluZyBcfCBudWxsIHwgTm8gfCBtaW4gMSwgbWF4IDEwMCB8CiAgfCBgYWRkcmVzc2AgfCBzdHJpbmcgXHwgbnVsbCB8IE5vIHwgbWluIDUsIG1heCA1MDAgfAogIHwgYGxhdGl0dWRlYCB8IGZsb2F0IFx8IG51bGwgfCBObyB8IOKAlCB8CiAgfCBgbG9uZ2l0dWRlYCB8IGZsb2F0IFx8IG51bGwgfCBObyB8IOKAlCB8CiAgfCBgcHJpY2VfcGVyX25pZ2h0YCB8IGZsb2F0IFx8IG51bGwgfCBObyB8ID4gMCB8CiAgfCBgbWF4X2d1ZXN0c2AgfCBpbnQgXHwgbnVsbCB8IE5vIHwgMeKAkzUwIHwKICB8IGBhbWVuaXRpZXNgIHwgbGlzdFtzdHJpbmddIFx8IG51bGwgfCBObyB8IOKAlCB8CiAgfCBgaXNfYWN0aXZlYCB8IGJvb2wgXHwgbnVsbCB8IE5vIHwg4oCUIHwKICAKICAqKlJlc3BvbnNlIChgUHJvcGVydHlPdXRgKToqKiBVcGRhdGVkIHByb3BlcnR5IG9iamVjdAogIAogIC0tLQogIAogICMjIyAzLjUgYERFTEVURSAvYXBpL3YxL3Byb3BlcnRpZXMve3Byb3BlcnR5X2lkfWAKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBIb3N0IG9ubHksIG11c3QgYmUgcHJvcGVydHkgb3duZXIgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgRGVsZXRlIChkZWFjdGl2YXRlKSBhIHByb3BlcnR5IGxpc3RpbmcgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvZGFzaGJvYXJkL3Byb3BlcnRpZXMvcGFnZS50c3hgIHwKICAKICAqKlBhdGggUGFyYW1ldGVyczoqKgogIAogIHwgUGFyYW1ldGVyIHwgVHlwZSB8IFJlcXVpcmVkIHwKICB8LS0tLS0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18CiAgfCBgcHJvcGVydHlfaWRgIHwgVVVJRCB8ICoqWWVzKiogfAogIAogICoqUmVzcG9uc2U6KioKICBgYGBqc29uCiAgeyAiZGV0YWlsIjogIlByb3BlcnR5IGRlbGV0ZWQiIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgMy42IGBQT1NUIC9hcGkvdjEvcHJvcGVydGllcy97cHJvcGVydHlfaWR9L2ltYWdlc2AKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBIb3N0IG9ubHksIG11c3QgYmUgcHJvcGVydHkgb3duZXIgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgVXBsb2FkIGFuIGltYWdlIGZvciBhIHByb3BlcnR5IHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9wcm9wZXJ0aWVzL25ldy9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBwcm9wZXJ0eV9pZGAgfCBVVUlEIHwgKipZZXMqKiB8CiAgCiAgKipRdWVyeSBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfCBEZWZhdWx0IHwKICB8LS0tLS0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tfAogIHwgYGlzX3ByaW1hcnlgIHwgYm9vbCB8IE5vIHwgYGZhbHNlYCB8CiAgCiAgKipSZXF1ZXN0IEJvZHk6KiogYG11bHRpcGFydC9mb3JtLWRhdGFgCiAgCiAgfCBGaWVsZCB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18CiAgfCBgZmlsZWAgfCBVcGxvYWRGaWxlIChpbWFnZSkgfCAqKlllcyoqIHwKICAKICA+IOKaoO+4jyBJbiBTd2FnZ2VyIFVJLCB1c2UgdGhlIGZpbGUgdXBsb2FkIHdpZGdldC4gU2V0IGBDb250ZW50LVR5cGU6IG11bHRpcGFydC9mb3JtLWRhdGFgLgogIAogICoqUmVzcG9uc2UgKGBQcm9wZXJ0eUltYWdlT3V0YCk6KioKICBgYGBqc29uCiAgewogICJpZCI6ICJ1dWlkIiwKICAiaW1hZ2VfdXJsIjogIi91cGxvYWRzL3Byb3BlcnRpZXMvdXVpZC9pbWFnZS5qcGciLAogICJpc19wcmltYXJ5IjogdHJ1ZSwKICAic29ydF9vcmRlciI6IDAKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMjIDMuNyBgUFVUIC9hcGkvdjEvcHJvcGVydGllcy97cHJvcGVydHlfaWR9L2hvdXJseWAKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBIb3N0IG9ubHksIG11c3QgYmUgcHJvcGVydHkgb3duZXIgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgRW5hYmxlIGFuZCBjb25maWd1cmUgaG91cmx5IGJvb2tpbmcgZm9yIGEgcHJvcGVydHkgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvZGFzaGJvYXJkL3Byb3BlcnRpZXMvbmV3L3BhZ2UudHN4YCB8CiAgCiAgKipQYXRoIFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfAogIHwgYHByb3BlcnR5X2lkYCB8IFVVSUQgfCAqKlllcyoqIHwKICAKICAqKlJlcXVlc3QgQm9keSAoYEhvdXJseUJvb2tpbmdDb25maWdVcGRhdGVgKToqKgogIGBgYGpzb24KICB7CiAgImhvdXJseV9wcmljZSI6IDI1LjAwLAogICJtaW5faG91cnMiOiAyLAogICJtYXhfaG91cnMiOiA4LAogICJhdmFpbGFibGVfZnJvbSI6ICIwOTowMCIsCiAgImF2YWlsYWJsZV90byI6ICIyMTowMCIKICB9CiAgYGBgCiAgCiAgfCBGaWVsZCB8IFR5cGUgfCBSZXF1aXJlZCB8IERlZmF1bHQgfCBDb25zdHJhaW50cyB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgaG91cmx5X3ByaWNlYCB8IGZsb2F0IHwgKipZZXMqKiB8IOKAlCB8ID4gMCB8CiAgfCBgbWluX2hvdXJzYCB8IGludCB8IE5vIHwgYDFgIHwgPj0gMSB8CiAgfCBgbWF4X2hvdXJzYCB8IGludCB8IE5vIHwgYDEyYCB8IDHigJMyNCB8CiAgfCBgYXZhaWxhYmxlX2Zyb21gIHwgdGltZSB8IE5vIHwgYDA4OjAwYCB8IEhIOk1NIGZvcm1hdCB8CiAgfCBgYXZhaWxhYmxlX3RvYCB8IHRpbWUgfCBObyB8IGAyMjowMGAgfCBISDpNTSBmb3JtYXQgfAogIAogICoqUmVzcG9uc2UgKGBQcm9wZXJ0eU91dGApOioqIFVwZGF0ZWQgcHJvcGVydHkgb2JqZWN0IHdpdGggYGhvdXJseV9lbmFibGVkOiB0cnVlYCBhbmQgYGhvdXJseV9jb25maWdgIHBvcHVsYXRlZAogIAogIC0tLQogIAogICMjIDQuIEJvb2tpbmdzCiAgCiAgIyMjIDQuMSBgUE9TVCAvYXBpL3YxL2Jvb2tpbmdzYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIEFueSBhdXRoZW50aWNhdGVkIHVzZXIgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgQ3JlYXRlIGEgbmV3IGJvb2tpbmcgKG5pZ2h0bHkgb3IgaG91cmx5KSB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9wcm9wZXJ0aWVzL1tpZF0vcGFnZS50c3hgIHwKICAKICAqKlJlcXVlc3QgQm9keSAoYEJvb2tpbmdDcmVhdGVgKToqKgogIGBgYGpzb24KICB7CiAgInByb3BlcnR5X2lkIjogIjU1MGU4NDAwLWUyOWItNDFkNC1hNzE2LTQ0NjY1NTQ0MDAwMCIsCiAgImNoZWNrX2luIjogIjIwMjYtMDQtMDFUMTQ6MDA6MDBaIiwKICAiY2hlY2tfb3V0IjogIjIwMjYtMDQtMDVUMTE6MDA6MDBaIiwKICAiYm9va2luZ190eXBlIjogIm5pZ2h0bHkiLAogICJob3VycyI6IG51bGwKICB9CiAgYGBgCiAgCiAgfCBGaWVsZCB8IFR5cGUgfCBSZXF1aXJlZCB8IERlZmF1bHQgfCBDb25zdHJhaW50cyB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgcHJvcGVydHlfaWRgIHwgVVVJRCB8ICoqWWVzKiogfCDigJQgfCBNdXN0IGV4aXN0IHwKICB8IGBjaGVja19pbmAgfCBkYXRldGltZSB8ICoqWWVzKiogfCDigJQgfCBJU08gODYwMSBmb3JtYXQgfAogIHwgYGNoZWNrX291dGAgfCBkYXRldGltZSB8ICoqWWVzKiogfCDigJQgfCBJU08gODYwMSwgbXVzdCBiZSBhZnRlciBjaGVja19pbiB8CiAgfCBgYm9va2luZ190eXBlYCB8IHN0cmluZyB8IE5vIHwgYCJuaWdodGx5ImAgfCBgIm5pZ2h0bHkiYCBvciBgImhvdXJseSJgIHwKICB8IGBob3Vyc2AgfCBpbnQgXHwgbnVsbCB8IE5vIHwgYG51bGxgIHwgMeKAkzI0IChyZXF1aXJlZCBpZiBob3VybHkpIHwKICAKICAqKlJlc3BvbnNlIChgQm9va2luZ091dGApOioqCiAgYGBganNvbgogIHsKICAiaWQiOiAidXVpZCIsCiAgInByb3BlcnR5X2lkIjogInV1aWQiLAogICJndWVzdF9pZCI6ICJ1dWlkIiwKICAiaG9zdF9pZCI6ICJ1dWlkIiwKICAiY2hlY2tfaW4iOiAiMjAyNi0wNC0wMVQxNDowMDowMFoiLAogICJjaGVja19vdXQiOiAiMjAyNi0wNC0wNVQxMTowMDowMFoiLAogICJ0b3RhbF9wcmljZSI6IDYwMC4wMCwKICAiYm9va2luZ190eXBlIjogIm5pZ2h0bHkiLAogICJob3VycyI6IG51bGwsCiAgInN0YXR1cyI6ICJwZW5kaW5nIiwKICAiY3JlYXRlZF9hdCI6ICIyMDI2LTAzLTE2VDEwOjAwOjAwWiIsCiAgInVwZGF0ZWRfYXQiOiAiMjAyNi0wMy0xNlQxMDowMDowMFoiCiAgfQogIGBgYAogIAogIC0tLQogIAogICMjIyA0LjIgYEdFVCAvYXBpL3YxL2Jvb2tpbmdzYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIEFueSBhdXRoZW50aWNhdGVkIHVzZXIgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgTGlzdCBib29raW5ncyBmb3IgdGhlIGN1cnJlbnQgdXNlciAoYXMgZ3Vlc3Qgb3IgaG9zdCkgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvYm9va2luZ3MvcGFnZS50c3hgLCBgZnJvbnRlbmQvc3JjL2FwcC9kYXNoYm9hcmQvcGFnZS50c3hgLCBgZnJvbnRlbmQvc3JjL2FwcC9kYXNoYm9hcmQvYm9va2luZ3MvcGFnZS50c3hgIHwKICAKICAqKlF1ZXJ5IFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8IERlZmF1bHQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18CiAgfCBgcGFnZWAgfCBpbnQgfCBObyB8IGAxYCB8CiAgfCBgcGFnZV9zaXplYCB8IGludCB8IE5vIHwgYDIwYCB8CiAgCiAgKipSZXNwb25zZSAoYFBhZ2luYXRlZEJvb2tpbmdzYCk6KioKICBgYGBqc29uCiAgewogICJpdGVtcyI6IFsgLyogQm9va2luZ091dCBvYmplY3RzICovIF0sCiAgInRvdGFsIjogMTUsCiAgInBhZ2UiOiAxLAogICJwYWdlX3NpemUiOiAyMAogIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgNC4zIGBHRVQgL2FwaS92MS9ib29raW5ncy97Ym9va2luZ19pZH1gCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgKipZZXMqKiDigJQgTXVzdCBiZSBib29raW5nIGd1ZXN0IG9yIHByb3BlcnR5IGhvc3QgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgR2V0IGJvb2tpbmcgZGV0YWlscyB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9ib29raW5ncy9baWRdL3BhZ2UudHN4YCB8CiAgCiAgKipQYXRoIFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfAogIHwgYGJvb2tpbmdfaWRgIHwgVVVJRCB8ICoqWWVzKiogfAogIAogICoqUmVzcG9uc2UgKGBCb29raW5nT3V0YCk6KiogU2luZ2xlIGJvb2tpbmcgb2JqZWN0CiAgCiAgLS0tCiAgCiAgIyMjIDQuNCBgUFVUIC9hcGkvdjEvYm9va2luZ3Mve2Jvb2tpbmdfaWR9L3N0YXR1c2AKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBNdXN0IGJlIGJvb2tpbmcgcGFydGljaXBhbnQgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgVXBkYXRlIGJvb2tpbmcgc3RhdHVzIChjb25maXJtLCByZWplY3QsIGNhbmNlbCwgY29tcGxldGUpIHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9ib29raW5ncy9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBib29raW5nX2lkYCB8IFVVSUQgfCAqKlllcyoqIHwKICAKICAqKlJlcXVlc3QgQm9keSAoYEJvb2tpbmdTdGF0dXNVcGRhdGVgKToqKgogIGBgYGpzb24KICB7CiAgInN0YXR1cyI6ICJjb25maXJtZWQiCiAgfQogIGBgYAogIAogIHwgRmllbGQgfCBUeXBlIHwgUmVxdWlyZWQgfCBBbGxvd2VkIFZhbHVlcyB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tLS0tLS0tLXwKICB8IGBzdGF0dXNgIHwgc3RyaW5nIHwgKipZZXMqKiB8IGAiY29uZmlybWVkImAsIGAiY2FuY2VsbGVkImAsIGAiY29tcGxldGVkImAsIGAicmVqZWN0ZWQiYCB8CiAgCiAgKipSZXNwb25zZSAoYEJvb2tpbmdPdXRgKToqKiBVcGRhdGVkIGJvb2tpbmcgb2JqZWN0CiAgCiAgLS0tCiAgCiAgIyMjIDQuNSBgUE9TVCAvYXBpL3YxL2Jvb2tpbmdzL3tib29raW5nX2lkfS9jYW5jZWxgCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgKipZZXMqKiDigJQgTXVzdCBiZSBib29raW5nIGd1ZXN0IHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IENhbmNlbCBhIGJvb2tpbmcgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvYm9va2luZ3MvW2lkXS9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBib29raW5nX2lkYCB8IFVVSUQgfCAqKlllcyoqIHwKICAKICAqKlJlcXVlc3QgQm9keToqKiBOb25lCiAgCiAgKipSZXNwb25zZSAoYEJvb2tpbmdPdXRgKToqKiBVcGRhdGVkIGJvb2tpbmcgd2l0aCBgc3RhdHVzOiAiY2FuY2VsbGVkImAKICAKICAtLS0KICAKICAjIyA1LiBNZXNzYWdpbmcKICAKICAjIyMgNS4xIGBQT1NUIC9hcGkvdjEvY29udmVyc2F0aW9uc2AKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBBbnkgYXV0aGVudGljYXRlZCB1c2VyIHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IFN0YXJ0IGEgbmV3IGNvbnZlcnNhdGlvbiB0aHJlYWQgYWJvdXQgYSBwcm9wZXJ0eSB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9ib29raW5ncy9baWRdL3BhZ2UudHN4YCB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBDb252ZXJzYXRpb25DcmVhdGVgKToqKgogIGBgYGpzb24KICB7CiAgInByb3BlcnR5X2lkIjogIjU1MGU4NDAwLWUyOWItNDFkNC1hNzE2LTQ0NjY1NTQ0MDAwMCIsCiAgIm1lc3NhZ2UiOiAiSGksIEkgaGF2ZSBhIHF1ZXN0aW9uIGFib3V0IHlvdXIgcHJvcGVydHkuIgogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgQ29uc3RyYWludHMgfAogIHwtLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgcHJvcGVydHlfaWRgIHwgVVVJRCB8ICoqWWVzKiogfCBNdXN0IGV4aXN0IHwKICB8IGBtZXNzYWdlYCB8IHN0cmluZyB8ICoqWWVzKiogfCBtaW4gMSwgbWF4IDUwMDAgY2hhcnMgfAogIAogICoqUmVzcG9uc2UgKGBDb252ZXJzYXRpb25PdXRgKToqKgogIGBgYGpzb24KICB7CiAgImlkIjogInV1aWQiLAogICJwcm9wZXJ0eV9pZCI6ICJ1dWlkIiwKICAiZ3Vlc3RfaWQiOiAidXVpZCIsCiAgImhvc3RfaWQiOiAidXVpZCIsCiAgImNyZWF0ZWRfYXQiOiAiMjAyNi0wMy0xNlQxMDowMDowMFoiLAogICJ1cGRhdGVkX2F0IjogIjIwMjYtMDMtMTZUMTA6MDA6MDBaIiwKICAibGFzdF9tZXNzYWdlIjogewogICJpZCI6ICJ1dWlkIiwKICAiY29udmVyc2F0aW9uX2lkIjogInV1aWQiLAogICJzZW5kZXJfaWQiOiAidXVpZCIsCiAgImNvbnRlbnQiOiAiSGksIEkgaGF2ZSBhIHF1ZXN0aW9uIGFib3V0IHlvdXIgcHJvcGVydHkuIiwKICAiaXNfcmVhZCI6IGZhbHNlLAogICJjcmVhdGVkX2F0IjogIjIwMjYtMDMtMTZUMTA6MDA6MDBaIgogIH0sCiAgInVucmVhZF9jb3VudCI6IDAKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMjIDUuMiBgR0VUIC9hcGkvdjEvY29udmVyc2F0aW9uc2AKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBBbnkgYXV0aGVudGljYXRlZCB1c2VyIHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IExpc3QgYWxsIGNvbnZlcnNhdGlvbnMgZm9yIHRoZSBjdXJyZW50IHVzZXIgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvbWVzc2FnZXMvcGFnZS50c3hgIHwKICAKICAqKlF1ZXJ5IFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8IERlZmF1bHQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18CiAgfCBgcGFnZWAgfCBpbnQgfCBObyB8IGAxYCB8CiAgfCBgcGFnZV9zaXplYCB8IGludCB8IE5vIHwgYDIwYCB8CiAgCiAgKipSZXNwb25zZSAoYFBhZ2luYXRlZFJlc3BvbnNlPENvbnZlcnNhdGlvbk91dD5gKToqKgogIGBgYGpzb24KICB7CiAgIml0ZW1zIjogWyAvKiBDb252ZXJzYXRpb25PdXQgb2JqZWN0cyAqLyBdLAogICJ0b3RhbCI6IDMsCiAgInBhZ2UiOiAxLAogICJwYWdlX3NpemUiOiAyMAogIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgNS4zIGBHRVQgL2FwaS92MS9jb252ZXJzYXRpb25zL3tjb252ZXJzYXRpb25faWR9L21lc3NhZ2VzYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIE11c3QgYmUgY29udmVyc2F0aW9uIHBhcnRpY2lwYW50IHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IEdldCBtZXNzYWdlcyBpbiBhIGNvbnZlcnNhdGlvbiB0aHJlYWQgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvbWVzc2FnZXMvW2lkXS9wYWdlLnRzeGAgKHBvbGxzIGV2ZXJ5IDEwIHNlY29uZHMpIHwKICAKICAqKlBhdGggUGFyYW1ldGVyczoqKgogIAogIHwgUGFyYW1ldGVyIHwgVHlwZSB8IFJlcXVpcmVkIHwKICB8LS0tLS0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18CiAgfCBgY29udmVyc2F0aW9uX2lkYCB8IFVVSUQgfCAqKlllcyoqIHwKICAKICAqKlF1ZXJ5IFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8IERlZmF1bHQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18CiAgfCBgcGFnZWAgfCBpbnQgfCBObyB8IGAxYCB8CiAgfCBgcGFnZV9zaXplYCB8IGludCB8IE5vIHwgYDIwYCB8CiAgCiAgKipSZXNwb25zZSAoYFBhZ2luYXRlZE1lc3NhZ2VzYCk6KioKICBgYGBqc29uCiAgewogICJpdGVtcyI6IFsKICB7CiAgImlkIjogInV1aWQiLAogICJjb252ZXJzYXRpb25faWQiOiAidXVpZCIsCiAgInNlbmRlcl9pZCI6ICJ1dWlkIiwKICAiY29udGVudCI6ICJIZWxsbyEiLAogICJpc19yZWFkIjogdHJ1ZSwKICAiY3JlYXRlZF9hdCI6ICIyMDI2LTAzLTE2VDEwOjAwOjAwWiIKICB9CiAgXSwKICAidG90YWwiOiAxMCwKICAicGFnZSI6IDEsCiAgInBhZ2Vfc2l6ZSI6IDIwCiAgfQogIGBgYAogIAogIC0tLQogIAogICMjIyA1LjQgYFBPU1QgL2FwaS92MS9jb252ZXJzYXRpb25zL3tjb252ZXJzYXRpb25faWR9L21lc3NhZ2VzYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIE11c3QgYmUgY29udmVyc2F0aW9uIHBhcnRpY2lwYW50IHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IFNlbmQgYSBtZXNzYWdlIGluIGFuIGV4aXN0aW5nIGNvbnZlcnNhdGlvbiB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9tZXNzYWdlcy9baWRdL3BhZ2UudHN4YCB8CiAgCiAgKipQYXRoIFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfAogIHwgYGNvbnZlcnNhdGlvbl9pZGAgfCBVVUlEIHwgKipZZXMqKiB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBNZXNzYWdlQ3JlYXRlYCk6KioKICBgYGBqc29uCiAgewogICJjb250ZW50IjogIlRoYW5rcyBmb3IgdGhlIGluZm8hIgogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgQ29uc3RyYWludHMgfAogIHwtLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgY29udGVudGAgfCBzdHJpbmcgfCAqKlllcyoqIHwgbWluIDEsIG1heCA1MDAwIGNoYXJzIHwKICAKICAqKlJlc3BvbnNlIChgTWVzc2FnZU91dGApOioqIFRoZSBzZW50IG1lc3NhZ2Ugb2JqZWN0CiAgCiAgLS0tCiAgCiAgIyMjIDUuNSBgUFVUIC9hcGkvdjEvbWVzc2FnZXMve21lc3NhZ2VfaWR9L3JlYWRgCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgKipZZXMqKiDigJQgTXVzdCBiZSBtZXNzYWdlIHJlY2lwaWVudCB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBNYXJrIGEgbWVzc2FnZSBhcyByZWFkIHwKICB8ICoqRnJvbnRlbmQqKiB8IERlZmluZWQgaW4gYGZyb250ZW5kL3NyYy9saWIvYXBpLnRzYCBidXQgKipub3QgeWV0IHVzZWQqKiBieSBhbnkgcGFnZSB8CiAgCiAgKipQYXRoIFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfAogIHwgYG1lc3NhZ2VfaWRgIHwgVVVJRCB8ICoqWWVzKiogfAogIAogICoqUmVxdWVzdCBCb2R5OioqIE5vbmUKICAKICAqKlJlc3BvbnNlIChgTWVzc2FnZU91dGApOioqIFVwZGF0ZWQgbWVzc2FnZSB3aXRoIGBpc19yZWFkOiB0cnVlYAogIAogIC0tLQogIAogICMjIDYuIFJldmlld3MKICAKICAjIyMgNi4xIGBQT1NUIC9hcGkvdjEvcmV2aWV3c2AKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBNdXN0IGJlIGJvb2tpbmcgZ3Vlc3QsIGJvb2tpbmcgbXVzdCBiZSBjb21wbGV0ZWQgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgQ3JlYXRlIGEgcmV2aWV3IGZvciBhIGNvbXBsZXRlZCBib29raW5nIHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL2Jvb2tpbmdzL1tpZF0vcGFnZS50c3hgIHwKICAKICAqKlJlcXVlc3QgQm9keSAoYFJldmlld0NyZWF0ZWApOioqCiAgYGBganNvbgogIHsKICAiYm9va2luZ19pZCI6ICI1NTBlODQwMC1lMjliLTQxZDQtYTcxNi00NDY2NTU0NDAwMDAiLAogICJyYXRpbmciOiA0LjUsCiAgImNvbW1lbnQiOiAiR3JlYXQgcGxhY2UsIHZlcnkgY2xlYW4gYW5kIHdlbGwtbWFpbnRhaW5lZCEiCiAgfQogIGBgYAogIAogIHwgRmllbGQgfCBUeXBlIHwgUmVxdWlyZWQgfCBDb25zdHJhaW50cyB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tLS0tLXwKICB8IGBib29raW5nX2lkYCB8IFVVSUQgfCAqKlllcyoqIHwgTXVzdCBiZSBhIGNvbXBsZXRlZCBib29raW5nIHwKICB8IGByYXRpbmdgIHwgZmxvYXQgfCAqKlllcyoqIHwgMS4w4oCTNS4wIHwKICB8IGBjb21tZW50YCB8IHN0cmluZyBcfCBudWxsIHwgTm8gfCBtYXggMjAwMCBjaGFycyB8CiAgCiAgKipSZXNwb25zZSAoYFJldmlld091dGApOioqCiAgYGBganNvbgogIHsKICAiaWQiOiAidXVpZCIsCiAgImJvb2tpbmdfaWQiOiAidXVpZCIsCiAgInByb3BlcnR5X2lkIjogInV1aWQiLAogICJyZXZpZXdlcl9pZCI6ICJ1dWlkIiwKICAicmF0aW5nIjogNC41LAogICJjb21tZW50IjogIkdyZWF0IHBsYWNlLCB2ZXJ5IGNsZWFuIGFuZCB3ZWxsLW1haW50YWluZWQhIiwKICAiY3JlYXRlZF9hdCI6ICIyMDI2LTAzLTE2VDEwOjAwOjAwWiIKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMjIDYuMiBgR0VUIC9hcGkvdjEvcmV2aWV3cy9wcm9wZXJ0eS97cHJvcGVydHlfaWR9YAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8IE5vbmUgKHB1YmxpYykgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgTGlzdCByZXZpZXdzIGZvciBhIHByb3BlcnR5IHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL3Byb3BlcnRpZXMvW2lkXS9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBwcm9wZXJ0eV9pZGAgfCBVVUlEIHwgKipZZXMqKiB8CiAgCiAgKipRdWVyeSBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfCBEZWZhdWx0IHwKICB8LS0tLS0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tfAogIHwgYHBhZ2VgIHwgaW50IHwgTm8gfCBgMWAgfAogIHwgYHBhZ2Vfc2l6ZWAgfCBpbnQgfCBObyB8IGAyMGAgfAogIAogICoqUmVzcG9uc2UgKGBQYWdpbmF0ZWRSZXZpZXdzYCk6KioKICBgYGBqc29uCiAgewogICJpdGVtcyI6IFsgLyogUmV2aWV3T3V0IG9iamVjdHMgKi8gXSwKICAidG90YWwiOiAxMiwKICAicGFnZSI6IDEsCiAgInBhZ2Vfc2l6ZSI6IDIwCiAgfQogIGBgYAogIAogIC0tLQogIAogICMjIyA2LjMgYEdFVCAvYXBpL3YxL3Jldmlld3MvaG9zdGAKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBBbnkgYXV0aGVudGljYXRlZCB1c2VyIHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IExpc3QgYWxsIHJldmlld3MgZm9yIHByb3BlcnRpZXMgb3duZWQgYnkgdGhlIGN1cnJlbnQgaG9zdCB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9kYXNoYm9hcmQvcmV2aWV3cy9wYWdlLnRzeGAgfAogIAogICoqUXVlcnkgUGFyYW1ldGVyczoqKgogIAogIHwgUGFyYW1ldGVyIHwgVHlwZSB8IFJlcXVpcmVkIHwgRGVmYXVsdCB8CiAgfC0tLS0tLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfC0tLS0tLS0tLXwKICB8IGBwYWdlYCB8IGludCB8IE5vIHwgYDFgIHwKICB8IGBwYWdlX3NpemVgIHwgaW50IHwgTm8gfCBgMjBgIHwKICAKICAqKlJlc3BvbnNlIChgUGFnaW5hdGVkUmV2aWV3c2ApOioqIFNhbWUgYXMgcHJvcGVydHkgcmV2aWV3cwogIAogIC0tLQogIAogICMjIDcuIE1lbWJlcnNoaXBzCiAgCiAgIyMjIDcuMSBgR0VUIC9hcGkvdjEvbWVtYmVyc2hpcHMvcGxhbnNgCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgTm9uZSAocHVibGljKSB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBMaXN0IGFsbCBhdmFpbGFibGUgbWVtYmVyc2hpcCBwbGFucyB8CiAgfCAqKkZyb250ZW5kKiogfCBEZWZpbmVkIGluIGBmcm9udGVuZC9zcmMvbGliL2FwaS50c2AgYnV0ICoqbm90IHlldCBjYWxsZWQqKiBieSB0aGUgbWVtYmVyc2hpcCBwYWdlIChwbGFucyBhcmUgaGFyZGNvZGVkIGluIGZyb250ZW5kKSB8CiAgCiAgKipSZXNwb25zZToqKgogIGBgYGpzb24KICBbCiAgeyAicGxhbl90eXBlIjogImJhc2ljIiwgImxhYmVsIjogIkJhc2ljIiwgInByaWNlIjogOS45OSwgIm1heF9saXN0aW5ncyI6IDMgfSwKICB7ICJwbGFuX3R5cGUiOiAicHJvIiwgImxhYmVsIjogIlByb2Zlc3Npb25hbCIsICJwcmljZSI6IDI5Ljk5LCAibWF4X2xpc3RpbmdzIjogMTUgfSwKICB7ICJwbGFuX3R5cGUiOiAicHJlbWl1bSIsICJsYWJlbCI6ICJQcmVtaXVtIiwgInByaWNlIjogNTkuOTksICJtYXhfbGlzdGluZ3MiOiA5OTkgfQogIF0KICBgYGAKICAKICAtLS0KICAKICAjIyMgNy4yIGBQT1NUIC9hcGkvdjEvbWVtYmVyc2hpcHMvc3Vic2NyaWJlYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIEhvc3Qgb25seSB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBTdWJzY3JpYmUgdG8gYSBtZW1iZXJzaGlwIHBsYW4gfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvZGFzaGJvYXJkL21lbWJlcnNoaXAvcGFnZS50c3hgIHwKICAKICAqKlJlcXVlc3QgQm9keSAoYE1lbWJlcnNoaXBTdWJzY3JpYmVSZXF1ZXN0YCk6KioKICBgYGBqc29uCiAgewogICJwbGFuX3R5cGUiOiA</t>
+    <t>IyBBUEkgUmVmZXJlbmNlIOKAlCBDb21wbGV0ZSBFbmRwb2ludCAmIEZlYXR1cmUgRG9jdW1lbnRhdGlvbgogIAogID4gKipCYXNlIFVSTDoqKiBgaHR0cDovL2xvY2FsaG9zdDo4MDAwYAogID4gKipTd2FnZ2VyIFVJOioqIGBodHRwOi8vbG9jYWxob3N0OjgwMDAvZG9jc2AKICA+ICoqUmVEb2M6KiogYGh0dHA6Ly9sb2NhbGhvc3Q6ODAwMC9yZWRvY2AKICA+ICoqQVBJIFByZWZpeDoqKiBgL2FwaS92MWAKICAKICAtLS0KICAKICAjIyBUYWJsZSBvZiBDb250ZW50cwogIAogIDEuIFtRdWljayBTdGFydCDigJQgSG93IHRvIFRlc3RdKCNxdWljay1zdGFydC0taG93LXRvLXRlc3QpCiAgMi4gW0F1dGhlbnRpY2F0aW9uIEZsb3ddKCNhdXRoZW50aWNhdGlvbi1mbG93KQogIDMuIFtFbmRwb2ludHMgT3ZlcnZpZXcgKDM2IFRvdGFsKV0oI2VuZHBvaW50cy1vdmVydmlldykKICA0LiBbSGVhbHRoXSgjMS1oZWFsdGgpCiAgNS4gW0F1dGggKDUgZW5kcG9pbnRzKV0oIzItYXV0aGVudGljYXRpb24pCiAgNi4gW1Byb3BlcnRpZXMgKDcgZW5kcG9pbnRzKV0oIzMtcHJvcGVydGllcykKICA3LiBbQm9va2luZ3MgKDUgZW5kcG9pbnRzKV0oIzQtYm9va2luZ3MpCiAgOC4gW01lc3NhZ2luZyAoNSBlbmRwb2ludHMpXSgjNS1tZXNzYWdpbmcpCiAgOS4gW1Jldmlld3MgKDMgZW5kcG9pbnRzKV0oIzYtcmV2aWV3cykKICAxMC4gW01lbWJlcnNoaXBzICg1IGVuZHBvaW50cyldKCM3LW1lbWJlcnNoaXBzKQogIDExLiBbQWRtaW4gKDUgZW5kcG9pbnRzKV0oIzgtYWRtaW4pCiAgMTIuIFtGcm9udGVuZCBQYWdlIOKGkiBFbmRwb2ludCBNYXBdKCNmcm9udGVuZC1wYWdlLS1lbmRwb2ludC1tYXApCiAgMTMuIFtGZWF0dXJlcyBXb3JraW5nIEVuZC10by1FbmRdKCNmZWF0dXJlcy13b3JraW5nLWVuZC10by1lbmQpCiAgMTQuIFtGZWF0dXJlcyBOb3QgWWV0IFdpcmVkIChQbGFjZWhvbGRlcildKCNmZWF0dXJlcy1ub3QteWV0LXdpcmVkLXBsYWNlaG9sZGVyKQogIDE1LiBbU2NoZW1hIFJlZmVyZW5jZV0oI3NjaGVtYS1yZWZlcmVuY2UpCiAgCiAgLS0tCiAgCiAgIyMgUXVpY2sgU3RhcnQg4oCUIEhvdyB0byBUZXN0CiAgCiAgIyMjIEZyb20gU3dhZ2dlciBVSSAoYC9kb2NzYCkKICAKICAxLiBPcGVuIGBodHRwOi8vbG9jYWxob3N0OjgwMDAvZG9jc2AgaW4gYSBicm93c2VyLgogIDIuICoqUmVnaXN0ZXIqKiBhIHVzZXIgdmlhIGBQT1NUIC9hcGkvdjEvYXV0aC9yZWdpc3RlcmAuCiAgMy4gKipMb2dpbioqIHZpYSBgUE9TVCAvYXBpL3YxL2F1dGgvbG9naW5gIOKGkiBjb3B5IHRoZSBgYWNjZXNzX3Rva2VuYCBmcm9tIHRoZSByZXNwb25zZS4KICA0LiBDbGljayB0aGUgKipBdXRob3JpemUg8J+UkioqIGJ1dHRvbiBhdCB0aGUgdG9wIG9mIFN3YWdnZXIgVUkg4oaSIHBhc3RlIGBCZWFyZXIgPGFjY2Vzc190b2tlbj5gIOKGkiBjbGljayAqKkF1dGhvcml6ZSoqLgogIDUuIFlvdSBhcmUgbm93IGF1dGhlbnRpY2F0ZWQgYW5kIGNhbiB0ZXN0IGFsbCBwcm90ZWN0ZWQgZW5kcG9pbnRzLgogIAogICMjIyBBdXRoZW50aWNhdGlvbiBIZWFkZXIKICAKICBBbGwgcHJvdGVjdGVkIGVuZHBvaW50cyByZXF1aXJlOgogIAogIGBgYAogIEF1dGhvcml6YXRpb246IEJlYXJlciA8YWNjZXNzX3Rva2VuPgogIGBgYAogIAogICMjIyBSb2xlcwogIAogIHwgUm9sZSB8IENhcGFiaWxpdGllcyB8CiAgfC0tLS0tLXwtLS0tLS0tLS0tLS0tfAogIHwgYHVzZXJgIHwgQnJvd3NlIHByb3BlcnRpZXMsIGNyZWF0ZSBib29raW5ncywgc2VuZCBtZXNzYWdlcywgd3JpdGUgcmV2aWV3cyB8CiAgfCBgaG9zdGAgfCBFdmVyeXRoaW5nIGEgdXNlciBjYW4gZG8gKyBjcmVhdGUvbWFuYWdlIHByb3BlcnRpZXMsIG1hbmFnZSBtZXNzYWdlcywgcmVxdWlyZXMgbWVtYmVyc2hpcCB8CiAgfCBgYWRtaW5gIHwgRnVsbCBwbGF0Zm9ybSBhZG1pbmlzdHJhdGlvbiAodXNlci9wcm9wZXJ0eS9tZW1iZXJzaGlwIG1hbmFnZW1lbnQsIGRhc2hib2FyZCBtZXRyaWNzKSB8CiAgCiAgLS0tCiAgCiAgIyMgQXV0aGVudGljYXRpb24gRmxvdwogIAogIGBgYAogIFJlZ2lzdGVyIOKGkiBMb2dpbiDihpIgR2V0IGFjY2Vzc190b2tlbiArIHJlZnJlc2hfdG9rZW4KICDihpIgVXNlIGFjY2Vzc190b2tlbiBpbiBBdXRob3JpemF0aW9uIGhlYWRlcgogIOKGkiBXaGVuIGV4cGlyZWQsIFBPU1QgL2F1dGgvcmVmcmVzaCB3aXRoIHJlZnJlc2hfdG9rZW4KICDihpIgR2V0IG5ldyBhY2Nlc3NfdG9rZW4KICBgYGAKICAKICAtLS0KICAKICAjIyBFbmRwb2ludHMgT3ZlcnZpZXcKICAKICB8IENhdGVnb3J5IHwgQ291bnQgfCBBdXRoIFJlcXVpcmVkIHwKICB8LS0tLS0tLS0tLXwtLS0tLS0tfC0tLS0tLS0tLS0tLS0tfAogIHwgSGVhbHRoIHwgMSB8IE5vIHwKICB8IEF1dGggfCA1IHwgTWl4ZWQgfAogIHwgUHJvcGVydGllcyB8IDcgfCBNaXhlZCB8CiAgfCBCb29raW5ncyB8IDUgfCBZZXMgfAogIHwgTWVzc2FnaW5nIHwgNSB8IFllcyB8CiAgfCBSZXZpZXdzIHwgMyB8IE1peGVkIHwKICB8IE1lbWJlcnNoaXBzIHwgNSB8IE1peGVkIHwKICB8IEFkbWluIHwgNSB8IFllcyAoYWRtaW4pIHwKICB8ICoqVG90YWwqKiB8ICoqMzYqKiB8IHwKICAKICAtLS0KICAKICAjIyAxLiBIZWFsdGgKICAKICAjIyMgYEdFVCAvaGVhbHRoYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8IE5vbmUgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgUmV0dXJucyBhcHAgaGVhbHRoIHN0YXR1cyBhbmQgdmVyc2lvbiB8CiAgfCAqKkZyb250ZW5kKiogfCBOb3QgdXNlZCBkaXJlY3RseSB8CiAgCiAgKipSZXNwb25zZToqKgogIGBgYGpzb24KICB7CiAgInN0YXR1cyI6ICJoZWFsdGh5IiwKICAidmVyc2lvbiI6ICIxLjAuMCIKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMgMi4gQXV0aGVudGljYXRpb24KICAKICAjIyMgMi4xIGBQT1NUIC9hcGkvdjEvYXV0aC9yZWdpc3RlcmAKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCBOb25lIHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IFJlZ2lzdGVyIGEgbmV3IHVzZXIgYWNjb3VudCB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9hdXRoL3JlZ2lzdGVyL3BhZ2UudHN4YCB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBVc2VyUmVnaXN0ZXJgKToqKgogIGBgYGpzb24KICB7CiAgImVtYWlsIjogInVzZXJAZXhhbXBsZS5jb20iLAogICJwYXNzd29yZCI6ICJzZWN1cmVwYXNzd29yZDEyMyIsCiAgImZ1bGxfbmFtZSI6ICJKb2huIERvZSIsCiAgInBob25lIjogIisxMjM0NTY3ODkwIiwKICAicm9sZSI6ICJ1c2VyIgogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgRGVmYXVsdCB8IENvbnN0cmFpbnRzIHwKICB8LS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18LS0tLS0tLS0tLS0tLXwKICB8IGBlbWFpbGAgfCBFbWFpbFN0ciB8ICoqWWVzKiogfCDigJQgfCBWYWxpZCBlbWFpbCB8CiAgfCBgcGFzc3dvcmRgIHwgc3RyaW5nIHwgKipZZXMqKiB8IOKAlCB8IG1pbiA4LCBtYXggMTI4IGNoYXJzIHwKICB8IGBmdWxsX25hbWVgIHwgc3RyaW5nIHwgKipZZXMqKiB8IOKAlCB8IG1pbiAxLCBtYXggMjU1IGNoYXJzIHwKICB8IGBwaG9uZWAgfCBzdHJpbmcgXHwgbnVsbCB8IE5vIHwgYG51bGxgIHwg4oCUIHwKICB8IGByb2xlYCB8IHN0cmluZyB8IE5vIHwgYCJ1c2VyImAgfCBgInVzZXIiYCBvciBgImhvc3QiYCB8CiAgCiAgKipSZXNwb25zZSAoYFRva2VuUmVzcG9uc2VgKToqKgogIGBgYGpzb24KICB7CiAgImFjY2Vzc190b2tlbiI6ICJleUpoYkdjaU9pSklVekkxTmlJcy4uLiIsCiAgInJlZnJlc2hfdG9rZW4iOiAiZXlKaGJHY2lPaUpJVXpJMU5pSXMuLi4iLAogICJ0b2tlbl90eXBlIjogImJlYXJlciIKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMjIDIuMiBgUE9TVCAvYXBpL3YxL2F1dGgvbG9naW5gCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgTm9uZSB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBBdXRoZW50aWNhdGUgYW5kIHJlY2VpdmUgSldUIHRva2VucyB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9hdXRoL2xvZ2luL3BhZ2UudHN4YCB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBVc2VyTG9naW5gKToqKgogIGBgYGpzb24KICB7CiAgImVtYWlsIjogInVzZXJAZXhhbXBsZS5jb20iLAogICJwYXNzd29yZCI6ICJzZWN1cmVwYXNzd29yZDEyMyIKICB9CiAgYGBgCiAgCiAgfCBGaWVsZCB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18CiAgfCBgZW1haWxgIHwgRW1haWxTdHIgfCAqKlllcyoqIHwKICB8IGBwYXNzd29yZGAgfCBzdHJpbmcgfCAqKlllcyoqIHwKICAKICAqKlJlc3BvbnNlIChgVG9rZW5SZXNwb25zZWApOioqCiAgYGBganNvbgogIHsKICAiYWNjZXNzX3Rva2VuIjogImV5SmhiR2NpT2lKSVV6STFOaUlzLi4uIiwKICAicmVmcmVzaF90b2tlbiI6ICJleUpoYkdjaU9pSklVekkxTmlJcy4uLiIsCiAgInRva2VuX3R5cGUiOiAiYmVhcmVyIgogIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgMi4zIGBQT1NUIC9hcGkvdjEvYXV0aC9yZWZyZXNoYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8IE5vbmUgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgUmVmcmVzaCBhY2Nlc3MgdG9rZW4gdXNpbmcgYSB2YWxpZCByZWZyZXNoIHRva2VuIHwKICB8ICoqRnJvbnRlbmQqKiB8IEF1dG9tYXRpYyB2aWEgQXhpb3MgaW50ZXJjZXB0b3IgaW4gYGZyb250ZW5kL3NyYy9saWIvYXBpLnRzYCB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBUb2tlblJlZnJlc2hgKToqKgogIGBgYGpzb24KICB7CiAgInJlZnJlc2hfdG9rZW4iOiAiZXlKaGJHY2lPaUpJVXpJMU5pSXMuLi4iCiAgfQogIGBgYAogIAogIHwgRmllbGQgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfAogIHwgYHJlZnJlc2hfdG9rZW5gIHwgc3RyaW5nIHwgKipZZXMqKiB8CiAgCiAgKipSZXNwb25zZSAoYFRva2VuUmVzcG9uc2VgKToqKgogIGBgYGpzb24KICB7CiAgImFjY2Vzc190b2tlbiI6ICJuZXdfYWNjZXNzX3Rva2VuLi4uIiwKICAicmVmcmVzaF90b2tlbiI6ICJuZXdfcmVmcmVzaF90b2tlbi4uLiIsCiAgInRva2VuX3R5cGUiOiAiYmVhcmVyIgogIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgMi40IGBHRVQgL2FwaS92MS9hdXRoL21lYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIEJlYXJlciB0b2tlbiB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBHZXQgdGhlIGN1cnJlbnQgdXNlcidzIHByb2ZpbGUgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvYXV0aC9sb2dpbi9wYWdlLnRzeGAsIGBmcm9udGVuZC9zcmMvYXBwL2F1dGgvcmVnaXN0ZXIvcGFnZS50c3hgIChjYWxsZWQgYWZ0ZXIgbG9naW4pIHwKICAKICAqKlBhcmFtZXRlcnM6KiogTm9uZQogIAogICoqUmVzcG9uc2UgKGBVc2VyT3V0YCk6KioKICBgYGBqc29uCiAgewogICJpZCI6ICI1NTBlODQwMC1lMjliLTQxZDQtYTcxNi00NDY2NTU0NDAwMDAiLAogICJlbWFpbCI6ICJ1c2VyQGV4YW1wbGUuY29tIiwKICAiZnVsbF9uYW1lIjogIkpvaG4gRG9lIiwKICAicGhvbmUiOiAiKzEyMzQ1Njc4OTAiLAogICJyb2xlIjogImhvc3QiLAogICJpc19hY3RpdmUiOiB0cnVlLAogICJjcmVhdGVkX2F0IjogIjIwMjYtMDMtMTZUMTA6MDA6MDBaIgogIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgMi41IGBQVVQgL2FwaS92MS9hdXRoL21lYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIEJlYXJlciB0b2tlbiB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBVcGRhdGUgdGhlIGN1cnJlbnQgdXNlcidzIHByb2ZpbGUgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvcHJvZmlsZS9wYWdlLnRzeGAgfAogIAogICoqUmVxdWVzdCBCb2R5IChgVXNlclVwZGF0ZWApOioqCiAgYGBganNvbgogIHsKICAiZnVsbF9uYW1lIjogIkpvaG4gVXBkYXRlZCIsCiAgInBob25lIjogIiswOTg3NjU0MzIxIgogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgQ29uc3RyYWludHMgfAogIHwtLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgZnVsbF9uYW1lYCB8IHN0cmluZyBcfCBudWxsIHwgTm8gfCBtaW4gMSwgbWF4IDI1NSBjaGFycyB8CiAgfCBgcGhvbmVgIHwgc3RyaW5nIFx8IG51bGwgfCBObyB8IOKAlCB8CiAgCiAgKipSZXNwb25zZSAoYFVzZXJPdXRgKToqKiBTYW1lIGFzIEdFVCAvYXV0aC9tZQogIAogIC0tLQogIAogICMjIDMuIFByb3BlcnRpZXMKICAKICAjIyMgMy4xIGBHRVQgL2FwaS92MS9wcm9wZXJ0aWVzYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8IE5vbmUgKHB1YmxpYykgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgU2VhcmNoIGFuZCBmaWx0ZXIgcHJvcGVydHkgbGlzdGluZ3MgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvcHJvcGVydGllcy9wYWdlLnRzeGAsIGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9wYWdlLnRzeGAsIGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9wcm9wZXJ0aWVzL3BhZ2UudHN4YCB8CiAgCiAgKipRdWVyeSBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfCBEZWZhdWx0IHwgQ29uc3RyYWludHMgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18LS0tLS0tLS0tLS0tLXwKICB8IGBjaXR5YCB8IHN0cmluZyB8IE5vIHwg4oCUIHwg4oCUIHwKICB8IGBtaW5fcHJpY2VgIHwgZmxvYXQgfCBObyB8IOKAlCB8ID49IDAgfAogIHwgYG1heF9wcmljZWAgfCBmbG9hdCB8IE5vIHwg4oCUIHwgPj0gMCB8CiAgfCBgbWF4X2d1ZXN0c2AgfCBpbnQgfCBObyB8IOKAlCB8ID49IDEgfAogIHwgYGhvdXJseV9hdmFpbGFibGVgIHwgYm9vbCB8IE5vIHwg4oCUIHwg4oCUIHwKICB8IGBob3N0X2lkYCB8IFVVSUQgfCBObyB8IOKAlCB8IEZpbHRlciBieSBob3N0IHwKICB8IGBwYWdlYCB8IGludCB8IE5vIHwgYDFgIHwgPj0gMSB8CiAgfCBgcGFnZV9zaXplYCB8IGludCB8IE5vIHwgYDIwYCB8IDHigJMxMDAgfAogIAogICoqRXhhbXBsZToqKiBgR0VUIC9hcGkvdjEvcHJvcGVydGllcz9jaXR5PU1pYW1pJm1pbl9wcmljZT01MCZtYXhfcHJpY2U9MjAwJnBhZ2U9MSZwYWdlX3NpemU9MTBgCiAgCiAgKipSZXNwb25zZSAoYFBhZ2luYXRlZFJlc3BvbnNlPFByb3BlcnR5T3V0PmApOioqCiAgYGBganNvbgogIHsKICAiaXRlbXMiOiBbCiAgewogICJpZCI6ICJ1dWlkIiwKICAiaG9zdF9pZCI6ICJ1dWlkIiwKICAidGl0bGUiOiAiQmVhY2ggSG91c2UgTWlhbWkiLAogICJkZXNjcmlwdGlvbiI6ICJCZWF1dGlmdWwgYmVhY2hmcm9udCBwcm9wZXJ0eS4uLiIsCiAgImNpdHkiOiAiTWlhbWkiLAogICJhZGRyZXNzIjogIjEyMyBPY2VhbiBEcml2ZSIsCiAgImxhdGl0dWRlIjogMjUuNzYxNywKICAibG9uZ2l0dWRlIjogLTgwLjE5MTgsCiAgInByaWNlX3Blcl9uaWdodCI6IDE1MC4wMCwKICAibWF4X2d1ZXN0cyI6IDQsCiAgImFtZW5pdGllcyI6IFsid2lmaSIsICJwb29sIiwgInBhcmtpbmciXSwKICAiaXNfYWN0aXZlIjogdHJ1ZSwKICAiaG91cmx5X2VuYWJsZWQiOiBmYWxzZSwKICAiaW1hZ2VzIjogWwogIHsgImlkIjogInV1aWQiLCAiaW1hZ2VfdXJsIjogIi91cGxvYWRzL2ltZy5qcGciLCAiaXNfcHJpbWFyeSI6IHRydWUsICJzb3J0X29yZGVyIjogMCB9CiAgXSwKICAiaG91cmx5X2NvbmZpZyI6IG51bGwsCiAgImNyZWF0ZWRfYXQiOiAiMjAyNi0wMy0wMVQxMDowMDowMFoiLAogICJ1cGRhdGVkX2F0IjogIjIwMjYtMDMtMTVUMTA6MDA6MDBaIgogIH0KICBdLAogICJ0b3RhbCI6IDI1LAogICJwYWdlIjogMSwKICAicGFnZV9zaXplIjogMTAKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMjIDMuMiBgR0VUIC9hcGkvdjEvcHJvcGVydGllcy97cHJvcGVydHlfaWR9YAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8IE5vbmUgKHB1YmxpYykgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgR2V0IGEgc2luZ2xlIHByb3BlcnR5IGJ5IElEIHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL3Byb3BlcnRpZXMvW2lkXS9wYWdlLnRzeGAsIGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9wcm9wZXJ0aWVzL1tpZF0vZWRpdC9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBwcm9wZXJ0eV9pZGAgfCBVVUlEIHwgKipZZXMqKiB8CiAgCiAgKipSZXNwb25zZSAoYFByb3BlcnR5T3V0YCk6KiogU2luZ2xlIHByb3BlcnR5IG9iamVjdCAoc2FtZSBzaGFwZSBhcyBpdGVtcyBpbiBzZWFyY2gpCiAgCiAgLS0tCiAgCiAgIyMjIDMuMyBgUE9TVCAvYXBpL3YxL3Byb3BlcnRpZXNgCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgKipZZXMqKiDigJQgSG9zdCBvbmx5IChyZXF1aXJlcyBhY3RpdmUgbWVtYmVyc2hpcCkgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgQ3JlYXRlIGEgbmV3IHByb3BlcnR5IGxpc3RpbmcgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvZGFzaGJvYXJkL3Byb3BlcnRpZXMvbmV3L3BhZ2UudHN4YCB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBQcm9wZXJ0eUNyZWF0ZWApOioqCiAgYGBganNvbgogIHsKICAidGl0bGUiOiAiQ296eSBBcGFydG1lbnQgRG93bnRvd24iLAogICJkZXNjcmlwdGlvbiI6ICJBIGJlYXV0aWZ1bCBhcGFydG1lbnQgaW4gdGhlIGhlYXJ0IG9mIHRoZSBjaXR5IHdpdGggYW1hemluZyB2aWV3cy4iLAogICJjaXR5IjogIk5ldyBZb3JrIiwKICAiYWRkcmVzcyI6ICI0NTYgQnJvYWR3YXksIE5ldyBZb3JrLCBOWSAxMDAxMyIsCiAgImxhdGl0dWRlIjogNDAuNzEyOCwKICAibG9uZ2l0dWRlIjogLTc0LjAwNjAsCiAgInByaWNlX3Blcl9uaWdodCI6IDEyMC4wMCwKICAibWF4X2d1ZXN0cyI6IDIsCiAgImFtZW5pdGllcyI6IFsid2lmaSIsICJraXRjaGVuIiwgImFpcl9jb25kaXRpb25pbmciXQogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgRGVmYXVsdCB8IENvbnN0cmFpbnRzIHwKICB8LS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18LS0tLS0tLS0tLS0tLXwKICB8IGB0aXRsZWAgfCBzdHJpbmcgfCAqKlllcyoqIHwg4oCUIHwgbWluIDMsIG1heCAyNTUgY2hhcnMgfAogIHwgYGRlc2NyaXB0aW9uYCB8IHN0cmluZyB8ICoqWWVzKiogfCDigJQgfCBtaW4gMTAgY2hhcnMgfAogIHwgYGNpdHlgIHwgc3RyaW5nIHwgKipZZXMqKiB8IOKAlCB8IG1pbiAxLCBtYXggMTAwIGNoYXJzIHwKICB8IGBhZGRyZXNzYCB8IHN0cmluZyB8ICoqWWVzKiogfCDigJQgfCBtaW4gNSwgbWF4IDUwMCBjaGFycyB8CiAgfCBgbGF0aXR1ZGVgIHwgZmxvYXQgXHwgbnVsbCB8IE5vIHwgYG51bGxgIHwg4oCUIHwKICB8IGBsb25naXR1ZGVgIHwgZmxvYXQgXHwgbnVsbCB8IE5vIHwgYG51bGxgIHwg4oCUIHwKICB8IGBwcmljZV9wZXJfbmlnaHRgIHwgZmxvYXQgfCAqKlllcyoqIHwg4oCUIHwgPiAwIHwKICB8IGBtYXhfZ3Vlc3RzYCB8IGludCB8IE5vIHwgYDFgIHwgMeKAkzUwIHwKICB8IGBhbWVuaXRpZXNgIHwgbGlzdFtzdHJpbmddIFx8IG51bGwgfCBObyB8IGBudWxsYCB8IOKAlCB8CiAgCiAgKipSZXNwb25zZSAoYFByb3BlcnR5T3V0YCk6KiogVGhlIGNyZWF0ZWQgcHJvcGVydHkgb2JqZWN0CiAgCiAgLS0tCiAgCiAgIyMjIDMuNCBgUFVUIC9hcGkvdjEvcHJvcGVydGllcy97cHJvcGVydHlfaWR9YAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIEhvc3Qgb25seSwgbXVzdCBiZSBwcm9wZXJ0eSBvd25lciB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBVcGRhdGUgYSBwcm9wZXJ0eSBsaXN0aW5nIHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9wcm9wZXJ0aWVzL1tpZF0vZWRpdC9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBwcm9wZXJ0eV9pZGAgfCBVVUlEIHwgKipZZXMqKiB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBQcm9wZXJ0eVVwZGF0ZWApOioqCiAgYGBganNvbgogIHsKICAidGl0bGUiOiAiVXBkYXRlZCBBcGFydG1lbnQgTmFtZSIsCiAgInByaWNlX3Blcl9uaWdodCI6IDEzNS4wMCwKICAiYW1lbml0aWVzIjogWyJ3aWZpIiwgImtpdGNoZW4iLCAiYWlyX2NvbmRpdGlvbmluZyIsICJneW0iXQogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgQ29uc3RyYWludHMgfAogIHwtLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgdGl0bGVgIHwgc3RyaW5nIFx8IG51bGwgfCBObyB8IG1pbiAzLCBtYXggMjU1IHwKICB8IGBkZXNjcmlwdGlvbmAgfCBzdHJpbmcgXHwgbnVsbCB8IE5vIHwgbWluIDEwIHwKICB8IGBjaXR5YCB8IHN0cmluZyBcfCBudWxsIHwgTm8gfCBtaW4gMSwgbWF4IDEwMCB8CiAgfCBgYWRkcmVzc2AgfCBzdHJpbmcgXHwgbnVsbCB8IE5vIHwgbWluIDUsIG1heCA1MDAgfAogIHwgYGxhdGl0dWRlYCB8IGZsb2F0IFx8IG51bGwgfCBObyB8IOKAlCB8CiAgfCBgbG9uZ2l0dWRlYCB8IGZsb2F0IFx8IG51bGwgfCBObyB8IOKAlCB8CiAgfCBgcHJpY2VfcGVyX25pZ2h0YCB8IGZsb2F0IFx8IG51bGwgfCBObyB8ID4gMCB8CiAgfCBgbWF4X2d1ZXN0c2AgfCBpbnQgXHwgbnVsbCB8IE5vIHwgMeKAkzUwIHwKICB8IGBhbWVuaXRpZXNgIHwgbGlzdFtzdHJpbmddIFx8IG51bGwgfCBObyB8IOKAlCB8CiAgfCBgaXNfYWN0aXZlYCB8IGJvb2wgXHwgbnVsbCB8IE5vIHwg4oCUIHwKICAKICAqKlJlc3BvbnNlIChgUHJvcGVydHlPdXRgKToqKiBVcGRhdGVkIHByb3BlcnR5IG9iamVjdAogIAogIC0tLQogIAogICMjIyAzLjUgYERFTEVURSAvYXBpL3YxL3Byb3BlcnRpZXMve3Byb3BlcnR5X2lkfWAKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBIb3N0IG9ubHksIG11c3QgYmUgcHJvcGVydHkgb3duZXIgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgRGVsZXRlIChkZWFjdGl2YXRlKSBhIHByb3BlcnR5IGxpc3RpbmcgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvZGFzaGJvYXJkL3Byb3BlcnRpZXMvcGFnZS50c3hgIHwKICAKICAqKlBhdGggUGFyYW1ldGVyczoqKgogIAogIHwgUGFyYW1ldGVyIHwgVHlwZSB8IFJlcXVpcmVkIHwKICB8LS0tLS0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18CiAgfCBgcHJvcGVydHlfaWRgIHwgVVVJRCB8ICoqWWVzKiogfAogIAogICoqUmVzcG9uc2U6KioKICBgYGBqc29uCiAgeyAiZGV0YWlsIjogIlByb3BlcnR5IGRlbGV0ZWQiIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgMy42IGBQT1NUIC9hcGkvdjEvcHJvcGVydGllcy97cHJvcGVydHlfaWR9L2ltYWdlc2AKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBIb3N0IG9ubHksIG11c3QgYmUgcHJvcGVydHkgb3duZXIgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgVXBsb2FkIGFuIGltYWdlIGZvciBhIHByb3BlcnR5IHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9wcm9wZXJ0aWVzL25ldy9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBwcm9wZXJ0eV9pZGAgfCBVVUlEIHwgKipZZXMqKiB8CiAgCiAgKipRdWVyeSBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfCBEZWZhdWx0IHwKICB8LS0tLS0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tfAogIHwgYGlzX3ByaW1hcnlgIHwgYm9vbCB8IE5vIHwgYGZhbHNlYCB8CiAgCiAgKipSZXF1ZXN0IEJvZHk6KiogYG11bHRpcGFydC9mb3JtLWRhdGFgCiAgCiAgfCBGaWVsZCB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18CiAgfCBgZmlsZWAgfCBVcGxvYWRGaWxlIChpbWFnZSkgfCAqKlllcyoqIHwKICAKICA+IOKaoO+4jyBJbiBTd2FnZ2VyIFVJLCB1c2UgdGhlIGZpbGUgdXBsb2FkIHdpZGdldC4gU2V0IGBDb250ZW50LVR5cGU6IG11bHRpcGFydC9mb3JtLWRhdGFgLgogIAogICoqUmVzcG9uc2UgKGBQcm9wZXJ0eUltYWdlT3V0YCk6KioKICBgYGBqc29uCiAgewogICJpZCI6ICJ1dWlkIiwKICAiaW1hZ2VfdXJsIjogIi91cGxvYWRzL3Byb3BlcnRpZXMvdXVpZC9pbWFnZS5qcGciLAogICJpc19wcmltYXJ5IjogdHJ1ZSwKICAic29ydF9vcmRlciI6IDAKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMjIDMuNyBgUFVUIC9hcGkvdjEvcHJvcGVydGllcy97cHJvcGVydHlfaWR9L2hvdXJseWAKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBIb3N0IG9ubHksIG11c3QgYmUgcHJvcGVydHkgb3duZXIgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgRW5hYmxlIGFuZCBjb25maWd1cmUgaG91cmx5IGJvb2tpbmcgZm9yIGEgcHJvcGVydHkgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvZGFzaGJvYXJkL3Byb3BlcnRpZXMvbmV3L3BhZ2UudHN4YCB8CiAgCiAgKipQYXRoIFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfAogIHwgYHByb3BlcnR5X2lkYCB8IFVVSUQgfCAqKlllcyoqIHwKICAKICAqKlJlcXVlc3QgQm9keSAoYEhvdXJseUJvb2tpbmdDb25maWdVcGRhdGVgKToqKgogIGBgYGpzb24KICB7CiAgImhvdXJseV9wcmljZSI6IDI1LjAwLAogICJtaW5faG91cnMiOiAyLAogICJtYXhfaG91cnMiOiA4LAogICJhdmFpbGFibGVfZnJvbSI6ICIwOTowMCIsCiAgImF2YWlsYWJsZV90byI6ICIyMTowMCIKICB9CiAgYGBgCiAgCiAgfCBGaWVsZCB8IFR5cGUgfCBSZXF1aXJlZCB8IERlZmF1bHQgfCBDb25zdHJhaW50cyB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgaG91cmx5X3ByaWNlYCB8IGZsb2F0IHwgKipZZXMqKiB8IOKAlCB8ID4gMCB8CiAgfCBgbWluX2hvdXJzYCB8IGludCB8IE5vIHwgYDFgIHwgPj0gMSB8CiAgfCBgbWF4X2hvdXJzYCB8IGludCB8IE5vIHwgYDEyYCB8IDHigJMyNCB8CiAgfCBgYXZhaWxhYmxlX2Zyb21gIHwgdGltZSB8IE5vIHwgYDA4OjAwYCB8IEhIOk1NIGZvcm1hdCB8CiAgfCBgYXZhaWxhYmxlX3RvYCB8IHRpbWUgfCBObyB8IGAyMjowMGAgfCBISDpNTSBmb3JtYXQgfAogIAogICoqUmVzcG9uc2UgKGBQcm9wZXJ0eU91dGApOioqIFVwZGF0ZWQgcHJvcGVydHkgb2JqZWN0IHdpdGggYGhvdXJseV9lbmFibGVkOiB0cnVlYCBhbmQgYGhvdXJseV9jb25maWdgIHBvcHVsYXRlZAogIAogIC0tLQogIAogICMjIDQuIEJvb2tpbmdzCiAgCiAgIyMjIDQuMSBgUE9TVCAvYXBpL3YxL2Jvb2tpbmdzYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIEFueSBhdXRoZW50aWNhdGVkIHVzZXIgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgQ3JlYXRlIGEgbmV3IGJvb2tpbmcgKG5pZ2h0bHkgb3IgaG91cmx5KSB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9wcm9wZXJ0aWVzL1tpZF0vcGFnZS50c3hgIHwKICAKICAqKlJlcXVlc3QgQm9keSAoYEJvb2tpbmdDcmVhdGVgKToqKgogIGBgYGpzb24KICB7CiAgInByb3BlcnR5X2lkIjogIjU1MGU4NDAwLWUyOWItNDFkNC1hNzE2LTQ0NjY1NTQ0MDAwMCIsCiAgImNoZWNrX2luIjogIjIwMjYtMDQtMDFUMTQ6MDA6MDBaIiwKICAiY2hlY2tfb3V0IjogIjIwMjYtMDQtMDVUMTE6MDA6MDBaIiwKICAiYm9va2luZ190eXBlIjogIm5pZ2h0bHkiLAogICJob3VycyI6IG51bGwKICB9CiAgYGBgCiAgCiAgfCBGaWVsZCB8IFR5cGUgfCBSZXF1aXJlZCB8IERlZmF1bHQgfCBDb25zdHJhaW50cyB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgcHJvcGVydHlfaWRgIHwgVVVJRCB8ICoqWWVzKiogfCDigJQgfCBNdXN0IGV4aXN0IHwKICB8IGBjaGVja19pbmAgfCBkYXRldGltZSB8ICoqWWVzKiogfCDigJQgfCBJU08gODYwMSBmb3JtYXQgfAogIHwgYGNoZWNrX291dGAgfCBkYXRldGltZSB8ICoqWWVzKiogfCDigJQgfCBJU08gODYwMSwgbXVzdCBiZSBhZnRlciBjaGVja19pbiB8CiAgfCBgYm9va2luZ190eXBlYCB8IHN0cmluZyB8IE5vIHwgYCJuaWdodGx5ImAgfCBgIm5pZ2h0bHkiYCBvciBgImhvdXJseSJgIHwKICB8IGBob3Vyc2AgfCBpbnQgXHwgbnVsbCB8IE5vIHwgYG51bGxgIHwgMeKAkzI0IChyZXF1aXJlZCBpZiBob3VybHkpIHwKICAKICAqKlJlc3BvbnNlIChgQm9va2luZ091dGApOioqCiAgYGBganNvbgogIHsKICAiaWQiOiAidXVpZCIsCiAgInByb3BlcnR5X2lkIjogInV1aWQiLAogICJndWVzdF9pZCI6ICJ1dWlkIiwKICAiaG9zdF9pZCI6ICJ1dWlkIiwKICAiY2hlY2tfaW4iOiAiMjAyNi0wNC0wMVQxNDowMDowMFoiLAogICJjaGVja19vdXQiOiAiMjAyNi0wNC0wNVQxMTowMDowMFoiLAogICJ0b3RhbF9wcmljZSI6IDYwMC4wMCwKICAiYm9va2luZ190eXBlIjogIm5pZ2h0bHkiLAogICJob3VycyI6IG51bGwsCiAgInN0YXR1cyI6ICJwZW5kaW5nIiwKICAiY3JlYXRlZF9hdCI6ICIyMDI2LTAzLTE2VDEwOjAwOjAwWiIsCiAgInVwZGF0ZWRfYXQiOiAiMjAyNi0wMy0xNlQxMDowMDowMFoiCiAgfQogIGBgYAogIAogIC0tLQogIAogICMjIyA0LjIgYEdFVCAvYXBpL3YxL2Jvb2tpbmdzYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIEFueSBhdXRoZW50aWNhdGVkIHVzZXIgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgTGlzdCBib29raW5ncyBmb3IgdGhlIGN1cnJlbnQgdXNlciAoYXMgZ3Vlc3Qgb3IgaG9zdCkgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvYm9va2luZ3MvcGFnZS50c3hgLCBgZnJvbnRlbmQvc3JjL2FwcC9kYXNoYm9hcmQvcGFnZS50c3hgLCBgZnJvbnRlbmQvc3JjL2FwcC9kYXNoYm9hcmQvYm9va2luZ3MvcGFnZS50c3hgIHwKICAKICAqKlF1ZXJ5IFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8IERlZmF1bHQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18CiAgfCBgcGFnZWAgfCBpbnQgfCBObyB8IGAxYCB8CiAgfCBgcGFnZV9zaXplYCB8IGludCB8IE5vIHwgYDIwYCB8CiAgCiAgKipSZXNwb25zZSAoYFBhZ2luYXRlZEJvb2tpbmdzYCk6KioKICBgYGBqc29uCiAgewogICJpdGVtcyI6IFsgLyogQm9va2luZ091dCBvYmplY3RzICovIF0sCiAgInRvdGFsIjogMTUsCiAgInBhZ2UiOiAxLAogICJwYWdlX3NpemUiOiAyMAogIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgNC4zIGBHRVQgL2FwaS92MS9ib29raW5ncy97Ym9va2luZ19pZH1gCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgKipZZXMqKiDigJQgTXVzdCBiZSBib29raW5nIGd1ZXN0IG9yIHByb3BlcnR5IGhvc3QgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgR2V0IGJvb2tpbmcgZGV0YWlscyB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9ib29raW5ncy9baWRdL3BhZ2UudHN4YCB8CiAgCiAgKipQYXRoIFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfAogIHwgYGJvb2tpbmdfaWRgIHwgVVVJRCB8ICoqWWVzKiogfAogIAogICoqUmVzcG9uc2UgKGBCb29raW5nT3V0YCk6KiogU2luZ2xlIGJvb2tpbmcgb2JqZWN0CiAgCiAgLS0tCiAgCiAgIyMjIDQuNCBgUFVUIC9hcGkvdjEvYm9va2luZ3Mve2Jvb2tpbmdfaWR9L3N0YXR1c2AKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBNdXN0IGJlIGJvb2tpbmcgcGFydGljaXBhbnQgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgVXBkYXRlIGJvb2tpbmcgc3RhdHVzIChjb25maXJtLCByZWplY3QsIGNhbmNlbCwgY29tcGxldGUpIHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL2Rhc2hib2FyZC9ib29raW5ncy9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBib29raW5nX2lkYCB8IFVVSUQgfCAqKlllcyoqIHwKICAKICAqKlJlcXVlc3QgQm9keSAoYEJvb2tpbmdTdGF0dXNVcGRhdGVgKToqKgogIGBgYGpzb24KICB7CiAgInN0YXR1cyI6ICJjb25maXJtZWQiCiAgfQogIGBgYAogIAogIHwgRmllbGQgfCBUeXBlIHwgUmVxdWlyZWQgfCBBbGxvd2VkIFZhbHVlcyB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tLS0tLS0tLXwKICB8IGBzdGF0dXNgIHwgc3RyaW5nIHwgKipZZXMqKiB8IGAiY29uZmlybWVkImAsIGAiY2FuY2VsbGVkImAsIGAiY29tcGxldGVkImAsIGAicmVqZWN0ZWQiYCB8CiAgCiAgKipSZXNwb25zZSAoYEJvb2tpbmdPdXRgKToqKiBVcGRhdGVkIGJvb2tpbmcgb2JqZWN0CiAgCiAgLS0tCiAgCiAgIyMjIDQuNSBgUE9TVCAvYXBpL3YxL2Jvb2tpbmdzL3tib29raW5nX2lkfS9jYW5jZWxgCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgKipZZXMqKiDigJQgTXVzdCBiZSBib29raW5nIGd1ZXN0IHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IENhbmNlbCBhIGJvb2tpbmcgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvYm9va2luZ3MvW2lkXS9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBib29raW5nX2lkYCB8IFVVSUQgfCAqKlllcyoqIHwKICAKICAqKlJlcXVlc3QgQm9keToqKiBOb25lCiAgCiAgKipSZXNwb25zZSAoYEJvb2tpbmdPdXRgKToqKiBVcGRhdGVkIGJvb2tpbmcgd2l0aCBgc3RhdHVzOiAiY2FuY2VsbGVkImAKICAKICAtLS0KICAKICAjIyA1LiBNZXNzYWdpbmcKICAKICAjIyMgNS4xIGBQT1NUIC9hcGkvdjEvY29udmVyc2F0aW9uc2AKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBBbnkgYXV0aGVudGljYXRlZCB1c2VyIHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IFN0YXJ0IGEgbmV3IGNvbnZlcnNhdGlvbiB0aHJlYWQgYWJvdXQgYSBwcm9wZXJ0eSB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9ib29raW5ncy9baWRdL3BhZ2UudHN4YCB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBDb252ZXJzYXRpb25DcmVhdGVgKToqKgogIGBgYGpzb24KICB7CiAgInByb3BlcnR5X2lkIjogIjU1MGU4NDAwLWUyOWItNDFkNC1hNzE2LTQ0NjY1NTQ0MDAwMCIsCiAgIm1lc3NhZ2UiOiAiSGksIEkgaGF2ZSBhIHF1ZXN0aW9uIGFib3V0IHlvdXIgcHJvcGVydHkuIgogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgQ29uc3RyYWludHMgfAogIHwtLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgcHJvcGVydHlfaWRgIHwgVVVJRCB8ICoqWWVzKiogfCBNdXN0IGV4aXN0IHwKICB8IGBtZXNzYWdlYCB8IHN0cmluZyB8ICoqWWVzKiogfCBtaW4gMSwgbWF4IDUwMDAgY2hhcnMgfAogIAogICoqUmVzcG9uc2UgKGBDb252ZXJzYXRpb25PdXRgKToqKgogIGBgYGpzb24KICB7CiAgImlkIjogInV1aWQiLAogICJwcm9wZXJ0eV9pZCI6ICJ1dWlkIiwKICAiZ3Vlc3RfaWQiOiAidXVpZCIsCiAgImhvc3RfaWQiOiAidXVpZCIsCiAgImNyZWF0ZWRfYXQiOiAiMjAyNi0wMy0xNlQxMDowMDowMFoiLAogICJ1cGRhdGVkX2F0IjogIjIwMjYtMDMtMTZUMTA6MDA6MDBaIiwKICAibGFzdF9tZXNzYWdlIjogewogICJpZCI6ICJ1dWlkIiwKICAiY29udmVyc2F0aW9uX2lkIjogInV1aWQiLAogICJzZW5kZXJfaWQiOiAidXVpZCIsCiAgImNvbnRlbnQiOiAiSGksIEkgaGF2ZSBhIHF1ZXN0aW9uIGFib3V0IHlvdXIgcHJvcGVydHkuIiwKICAiaXNfcmVhZCI6IGZhbHNlLAogICJjcmVhdGVkX2F0IjogIjIwMjYtMDMtMTZUMTA6MDA6MDBaIgogIH0sCiAgInVucmVhZF9jb3VudCI6IDAKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMjIDUuMiBgR0VUIC9hcGkvdjEvY29udmVyc2F0aW9uc2AKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBBbnkgYXV0aGVudGljYXRlZCB1c2VyIHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IExpc3QgYWxsIGNvbnZlcnNhdGlvbnMgZm9yIHRoZSBjdXJyZW50IHVzZXIgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvbWVzc2FnZXMvcGFnZS50c3hgIHwKICAKICAqKlF1ZXJ5IFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8IERlZmF1bHQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18CiAgfCBgcGFnZWAgfCBpbnQgfCBObyB8IGAxYCB8CiAgfCBgcGFnZV9zaXplYCB8IGludCB8IE5vIHwgYDIwYCB8CiAgCiAgKipSZXNwb25zZSAoYFBhZ2luYXRlZFJlc3BvbnNlPENvbnZlcnNhdGlvbk91dD5gKToqKgogIGBgYGpzb24KICB7CiAgIml0ZW1zIjogWyAvKiBDb252ZXJzYXRpb25PdXQgb2JqZWN0cyAqLyBdLAogICJ0b3RhbCI6IDMsCiAgInBhZ2UiOiAxLAogICJwYWdlX3NpemUiOiAyMAogIH0KICBgYGAKICAKICAtLS0KICAKICAjIyMgNS4zIGBHRVQgL2FwaS92MS9jb252ZXJzYXRpb25zL3tjb252ZXJzYXRpb25faWR9L21lc3NhZ2VzYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIE11c3QgYmUgY29udmVyc2F0aW9uIHBhcnRpY2lwYW50IHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IEdldCBtZXNzYWdlcyBpbiBhIGNvbnZlcnNhdGlvbiB0aHJlYWQgfAogIHwgKipGcm9udGVuZCoqIHwgYGZyb250ZW5kL3NyYy9hcHAvbWVzc2FnZXMvW2lkXS9wYWdlLnRzeGAgKHBvbGxzIGV2ZXJ5IDEwIHNlY29uZHMpIHwKICAKICAqKlBhdGggUGFyYW1ldGVyczoqKgogIAogIHwgUGFyYW1ldGVyIHwgVHlwZSB8IFJlcXVpcmVkIHwKICB8LS0tLS0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18CiAgfCBgY29udmVyc2F0aW9uX2lkYCB8IFVVSUQgfCAqKlllcyoqIHwKICAKICAqKlF1ZXJ5IFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8IERlZmF1bHQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwtLS0tLS0tLS18CiAgfCBgcGFnZWAgfCBpbnQgfCBObyB8IGAxYCB8CiAgfCBgcGFnZV9zaXplYCB8IGludCB8IE5vIHwgYDIwYCB8CiAgCiAgKipSZXNwb25zZSAoYFBhZ2luYXRlZE1lc3NhZ2VzYCk6KioKICBgYGBqc29uCiAgewogICJpdGVtcyI6IFsKICB7CiAgImlkIjogInV1aWQiLAogICJjb252ZXJzYXRpb25faWQiOiAidXVpZCIsCiAgInNlbmRlcl9pZCI6ICJ1dWlkIiwKICAiY29udGVudCI6ICJIZWxsbyEiLAogICJpc19yZWFkIjogdHJ1ZSwKICAiY3JlYXRlZF9hdCI6ICIyMDI2LTAzLTE2VDEwOjAwOjAwWiIKICB9CiAgXSwKICAidG90YWwiOiAxMCwKICAicGFnZSI6IDEsCiAgInBhZ2Vfc2l6ZSI6IDIwCiAgfQogIGBgYAogIAogIC0tLQogIAogICMjIyA1LjQgYFBPU1QgL2FwaS92MS9jb252ZXJzYXRpb25zL3tjb252ZXJzYXRpb25faWR9L21lc3NhZ2VzYAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8ICoqWWVzKiog4oCUIE11c3QgYmUgY29udmVyc2F0aW9uIHBhcnRpY2lwYW50IHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IFNlbmQgYSBtZXNzYWdlIGluIGFuIGV4aXN0aW5nIGNvbnZlcnNhdGlvbiB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9tZXNzYWdlcy9baWRdL3BhZ2UudHN4YCB8CiAgCiAgKipQYXRoIFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfAogIHwgYGNvbnZlcnNhdGlvbl9pZGAgfCBVVUlEIHwgKipZZXMqKiB8CiAgCiAgKipSZXF1ZXN0IEJvZHkgKGBNZXNzYWdlQ3JlYXRlYCk6KioKICBgYGBqc29uCiAgewogICJjb250ZW50IjogIlRoYW5rcyBmb3IgdGhlIGluZm8hIgogIH0KICBgYGAKICAKICB8IEZpZWxkIHwgVHlwZSB8IFJlcXVpcmVkIHwgQ29uc3RyYWludHMgfAogIHwtLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfC0tLS0tLS0tLS0tLS18CiAgfCBgY29udGVudGAgfCBzdHJpbmcgfCAqKlllcyoqIHwgbWluIDEsIG1heCA1MDAwIGNoYXJzIHwKICAKICAqKlJlc3BvbnNlIChgTWVzc2FnZU91dGApOioqIFRoZSBzZW50IG1lc3NhZ2Ugb2JqZWN0CiAgCiAgLS0tCiAgCiAgIyMjIDUuNSBgUFVUIC9hcGkvdjEvbWVzc2FnZXMve21lc3NhZ2VfaWR9L3JlYWRgCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgKipZZXMqKiDigJQgTXVzdCBiZSBtZXNzYWdlIHJlY2lwaWVudCB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBNYXJrIGEgbWVzc2FnZSBhcyByZWFkIHwKICB8ICoqRnJvbnRlbmQqKiB8IERlZmluZWQgaW4gYGZyb250ZW5kL3NyYy9saWIvYXBpLnRzYCBidXQgKipub3QgeWV0IHVzZWQqKiBieSBhbnkgcGFnZSB8CiAgCiAgKipQYXRoIFBhcmFtZXRlcnM6KioKICAKICB8IFBhcmFtZXRlciB8IFR5cGUgfCBSZXF1aXJlZCB8CiAgfC0tLS0tLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfAogIHwgYG1lc3NhZ2VfaWRgIHwgVVVJRCB8ICoqWWVzKiogfAogIAogICoqUmVxdWVzdCBCb2R5OioqIE5vbmUKICAKICAqKlJlc3BvbnNlIChgTWVzc2FnZU91dGApOioqIFVwZGF0ZWQgbWVzc2FnZSB3aXRoIGBpc19yZWFkOiB0cnVlYAogIAogIC0tLQogIAogICMjIDYuIFJldmlld3MKICAKICAjIyMgNi4xIGBQT1NUIC9hcGkvdjEvcmV2aWV3c2AKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBNdXN0IGJlIGJvb2tpbmcgZ3Vlc3QsIGJvb2tpbmcgbXVzdCBiZSBjb21wbGV0ZWQgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgQ3JlYXRlIGEgcmV2aWV3IGZvciBhIGNvbXBsZXRlZCBib29raW5nIHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL2Jvb2tpbmdzL1tpZF0vcGFnZS50c3hgIHwKICAKICAqKlJlcXVlc3QgQm9keSAoYFJldmlld0NyZWF0ZWApOioqCiAgYGBganNvbgogIHsKICAiYm9va2luZ19pZCI6ICI1NTBlODQwMC1lMjliLTQxZDQtYTcxNi00NDY2NTU0NDAwMDAiLAogICJyYXRpbmciOiA0LjUsCiAgImNvbW1lbnQiOiAiR3JlYXQgcGxhY2UsIHZlcnkgY2xlYW4gYW5kIHdlbGwtbWFpbnRhaW5lZCEiCiAgfQogIGBgYAogIAogIHwgRmllbGQgfCBUeXBlIHwgUmVxdWlyZWQgfCBDb25zdHJhaW50cyB8CiAgfC0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tLS0tLXwKICB8IGBib29raW5nX2lkYCB8IFVVSUQgfCAqKlllcyoqIHwgTXVzdCBiZSBhIGNvbXBsZXRlZCBib29raW5nIHwKICB8IGByYXRpbmdgIHwgZmxvYXQgfCAqKlllcyoqIHwgMS4w4oCTNS4wIHwKICB8IGBjb21tZW50YCB8IHN0cmluZyBcfCBudWxsIHwgTm8gfCBtYXggMjAwMCBjaGFycyB8CiAgCiAgKipSZXNwb25zZSAoYFJldmlld091dGApOioqCiAgYGBganNvbgogIHsKICAiaWQiOiAidXVpZCIsCiAgImJvb2tpbmdfaWQiOiAidXVpZCIsCiAgInByb3BlcnR5X2lkIjogInV1aWQiLAogICJyZXZpZXdlcl9pZCI6ICJ1dWlkIiwKICAicmF0aW5nIjogNC41LAogICJjb21tZW50IjogIkdyZWF0IHBsYWNlLCB2ZXJ5IGNsZWFuIGFuZCB3ZWxsLW1haW50YWluZWQhIiwKICAiY3JlYXRlZF9hdCI6ICIyMDI2LTAzLTE2VDEwOjAwOjAwWiIKICB9CiAgYGBgCiAgCiAgLS0tCiAgCiAgIyMjIDYuMiBgR0VUIC9hcGkvdjEvcmV2aWV3cy9wcm9wZXJ0eS97cHJvcGVydHlfaWR9YAogIAogIHwgfCB8CiAgfC0tLXwtLS18CiAgfCAqKkF1dGgqKiB8IE5vbmUgKHB1YmxpYykgfAogIHwgKipEZXNjcmlwdGlvbioqIHwgTGlzdCByZXZpZXdzIGZvciBhIHByb3BlcnR5IHwKICB8ICoqRnJvbnRlbmQqKiB8IGBmcm9udGVuZC9zcmMvYXBwL3Byb3BlcnRpZXMvW2lkXS9wYWdlLnRzeGAgfAogIAogICoqUGF0aCBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfAogIHwtLS0tLS0tLS0tLXwtLS0tLS18LS0tLS0tLS0tLXwKICB8IGBwcm9wZXJ0eV9pZGAgfCBVVUlEIHwgKipZZXMqKiB8CiAgCiAgKipRdWVyeSBQYXJhbWV0ZXJzOioqCiAgCiAgfCBQYXJhbWV0ZXIgfCBUeXBlIHwgUmVxdWlyZWQgfCBEZWZhdWx0IHwKICB8LS0tLS0tLS0tLS18LS0tLS0tfC0tLS0tLS0tLS18LS0tLS0tLS0tfAogIHwgYHBhZ2VgIHwgaW50IHwgTm8gfCBgMWAgfAogIHwgYHBhZ2Vfc2l6ZWAgfCBpbnQgfCBObyB8IGAyMGAgfAogIAogICoqUmVzcG9uc2UgKGBQYWdpbmF0ZWRSZXZpZXdzYCk6KioKICBgYGBqc29uCiAgewogICJpdGVtcyI6IFsgLyogUmV2aWV3T3V0IG9iamVjdHMgKi8gXSwKICAidG90YWwiOiAxMiwKICAicGFnZSI6IDEsCiAgInBhZ2Vfc2l6ZSI6IDIwCiAgfQogIGBgYAogIAogIC0tLQogIAogICMjIyA2LjMgYEdFVCAvYXBpL3YxL3Jldmlld3MvaG9zdGAKICAKICB8IHwgfAogIHwtLS18LS0tfAogIHwgKipBdXRoKiogfCAqKlllcyoqIOKAlCBBbnkgYXV0aGVudGljYXRlZCB1c2VyIHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IExpc3QgYWxsIHJldmlld3MgZm9yIHByb3BlcnRpZXMgb3duZWQgYnkgdGhlIGN1cnJlbnQgaG9zdCB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9kYXNoYm9hcmQvcmV2aWV3cy9wYWdlLnRzeGAgfAogIAogICoqUXVlcnkgUGFyYW1ldGVyczoqKgogIAogIHwgUGFyYW1ldGVyIHwgVHlwZSB8IFJlcXVpcmVkIHwgRGVmYXVsdCB8CiAgfC0tLS0tLS0tLS0tfC0tLS0tLXwtLS0tLS0tLS0tfC0tLS0tLS0tLXwKICB8IGBwYWdlYCB8IGludCB8IE5vIHwgYDFgIHwKICB8IGBwYWdlX3NpemVgIHwgaW50IHwgTm8gfCBgMjBgIHwKICAKICAqKlJlc3BvbnNlIChgUGFnaW5hdGVkUmV2aWV3c2ApOioqIFNhbWUgYXMgcHJvcGVydHkgcmV2aWV3cwogIAogIC0tLQogIAogICMjIDcuIE1lbWJlcnNoaXBzCiAgCiAgIyMjIDcuMSBgR0VUIC9hcGkvdjEvbWVtYmVyc2hpcHMvcGxhbnNgCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgTm9uZSAocHVibGljKSB8CiAgfCAqKkRlc2NyaXB0aW9uKiogfCBMaXN0IGFsbCBhdmFpbGFibGUgbWVtYmVyc2hpcCBwbGFucyB8CiAgfCAqKkZyb250ZW5kKiogfCBEZWZpbmVkIGluIGBmcm9udGVuZC9zcmMvbGliL2FwaS50c2AgYnV0ICoqbm90IHlldCBjYWxsZWQqKiBieSB0aGUgbWVtYmVyc2hpcCBwYWdlIChwbGFucyBhcmUgaGFyZGNvZGVkIGluIGZyb250ZW5kKSB8CiAgCiAgKipSZXNwb25zZToqKgogIGBgYGpzb24KICBbCiAgeyAicGxhbl90eXBlIjogImJhc2ljIiwgImxhYmVsIjogIkJhc2ljIiwgInByaWNlIjogMjQ5OS4wMCwgIm1heF9saXN0aW5ncyI6IDUgfSwKICB7ICJwbGFuX3R5cGUiOiAicHJvIiwgImxhYmVsIjogIlBybyIsICJwcmljZSI6IDY0OTkuMDAsICJtYXhfbGlzdGluZ3MiOiAyNSB9LAogIHsgInBsYW5fdHlwZSI6ICJwcmVtaXVtIiwgImxhYmVsIjogIlByZW1pdW0iLCAicHJpY2UiOiAxNjQ5OS4wMCwgIm1heF9saXN0aW5ncyI6IDk5OTk5OSB9CiAgXQogIGBgYAogIAogIC0tLQogIAogICMjIyA3LjIgYFBPU1QgL2FwaS92MS9tZW1iZXJzaGlwcy9zdWJzY3JpYmVgCiAgCiAgfCB8IHwKICB8LS0tfC0tLXwKICB8ICoqQXV0aCoqIHwgKipZZXMqKiDigJQgSG9zdCBvbmx5IHwKICB8ICoqRGVzY3JpcHRpb24qKiB8IFN1YnNjcmliZSB0byBhIG1lbWJlcnNoaXAgcGxhbiB8CiAgfCAqKkZyb250ZW5kKiogfCBgZnJvbnRlbmQvc3JjL2FwcC9kYXNoYm9hcmQvbWVtYmVyc2hpcC9wYWdlLnRzeGAgfAogIAogICoqUmVxdWVzdCBCb2R5IChgTWVtYmVyc2hpcFN1YnNjcmliZVJlcXVlc3RgKToqKgogIGBgYGpzb24KICB7CiAgInBsYW5fdHlwZSI</t>
   </si>
   <si>
     <t>CODEBASE_REFERENCE.md</t>
@@ -20296,7 +20411,7 @@
   # ------------------------------------------------------------------
   print("\n--- Step 6: Host Confirms Booking ---")
   if booking_id:
-  r = client.patch(f"/bookings/{booking_id}/status",
+  r = client.put(f"/bookings/{booking_id}/status",
   headers=auth_header(host_access),
   json={"status": "confirmed"})
   pp("Confirm Booking", r)
@@ -20308,7 +20423,7 @@
   print("\n--- Step 7: Review Flow ---")
   if booking_id:
   # Complete the booking first
-  r = client.patch(f"/bookings/{booking_id}/status",
+  r = client.put(f"/bookings/{booking_id}/status",
   headers=auth_header(host_access),
   json={"status": "completed"})
   pp("Complete Booking", r)
@@ -20330,34 +20445,34 @@
   # ------------------------------------------------------------------
   print("\n--- Step 8: Messaging ---")
   if property_id and guest_id and host_id:
-  # Guest sends a message to host
-  r = client.post("/messages", headers=auth_header(guest_access), json={
-  "receiver_id": host_id,
+  # Guest starts a conversation about the property
+  r = client.post("/conversations", headers=auth_header(guest_access), json={
   "property_id": property_id,
-  "content": "Hi Bob! I loved the apartment. Are there any restaurants nearby?"
+  "message": "Hi Bob! I loved the apartment. Are there any restaurants nearby?"
   })
-  pp("Guest Sends Message", r)
-  # Host replies
-  r = client.post("/messages", headers=auth_header(host_access), json={
-  "receiver_id": guest_id,
-  "property_id": property_id,
+  conv_data = pp("Guest Starts Conversation", r)
+  conv_id = conv_data.get("id") if isinstance(conv_data, dict) else None
+  # Host replies in the same conversation
+  if conv_id:
+  r = client.post(f"/conversations/{conv_id}/messages", headers=auth_header(host_access), json={
   "content": "Thanks Alice! Yes, there are great restaurants within walking distance."
   })
   pp("Host Replies", r)
-  # Guest views conversation
-  r = client.get("/messages", headers=auth_header(guest_access))
-  pp("Guest's Messages", r)
+  # Guest views conversations
+  r = client.get("/conversations", headers=auth_header(guest_access))
+  pp("Guest's Conversations", r)
   else:
   print("⚠️ Skipping messaging — missing user/property IDs.")
   # ------------------------------------------------------------------
   # STEP 9 — Membership for host
   # ------------------------------------------------------------------
   print("\n--- Step 9: Host Membership ---")
-  r = client.post("/memberships", headers=auth_header(host_access), json={
-  "plan_type": "premium"
+  r = client.post("/memberships/subscribe", headers=auth_header(host_access), json={
+  "plan_type": "premium",
+  "payment_token": "tok_test_seed"
   })
   pp("Host Subscribes to Premium", r)
-  r = client.get("/memberships/me", headers=auth_header(host_access))
+  r = client.get("/memberships/current", headers=auth_header(host_access))
   pp("Host's Membership", r)
   # ------------------------------------------------------------------
   # STEP 10 — Admin operations
@@ -20425,7 +20540,7 @@
   main()</t>
   </si>
   <si>
-    <t>IiIiClN0YXlOZXN0IOKAlCBEYXRhYmFzZSBTZXR1cCAmIEVuZC10by1FbmQgQVBJIFNtb2tlIFRlc3QKPT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT0KUnVuIHRoaXMgQUZURVIgeW91ciBiYWNrZW5kICh1dmljb3JuKSBhbmQgZGF0YWJhc2UgKHBvc3RncmVzKSBhcmUgcnVubmluZy4KClVzYWdlOgogIHB5dGhvbiBzZWVkX2FuZF90ZXN0LnB5ICAgICAgICAgICAgICAjIGRlZmF1bHQ6IGh0dHA6Ly9sb2NhbGhvc3Q6ODAwMAogIHB5dGhvbiBzZWVkX2FuZF90ZXN0LnB5IGh0dHA6Ly9sb2NhbGhvc3Q6ODAwMCAgICMgY3VzdG9tIGJhc2UgVVJMCgpXaGF0IGl0IGRvZXM6CiAgMS4gUmVnaXN0ZXJzIGEgcmVndWxhciBVU0VSLCBhIEhPU1QsIGFuZCBtYW51YWxseSBwcm9tb3RlcyBhbiBBRE1JTgogIDIuIFRlc3RzIGF1dGggZmxvd3MgKGxvZ2luLCB0b2tlbiByZWZyZXNoLCBwcm9maWxlKQogIDMuIEhvc3QgY3JlYXRlcyBhIHByb3BlcnR5IGxpc3RpbmcKICA0LiBHdWVzdCBzZWFyY2hlcyAmIHZpZXdzIHByb3BlcnRpZXMKICA1LiBHdWVzdCBib29rcyBhIHByb3BlcnR5CiAgNi4gSG9zdCBjb25maXJtcyB0aGUgYm9va2luZwogIDcuIEd1ZXN0IHdyaXRlcyBhIHJldmlldyBhZnRlciBjaGVja291dAogIDguIEFkbWluIGRhc2hib2FyZCAmIHVzZXIgbWFuYWdlbWVudAogIDkuIE1lc3NhZ2luZyBiZXR3ZWVuIGd1ZXN0IGFuZCBob3N0CiAgMTAuIE1lbWJlcnNoaXAgcHVyY2hhc2UgZm9yIHRoZSBob3N0CiIiIgoKaW1wb3J0IHN5cwppbXBvcnQganNvbgppbXBvcnQgdXVpZAppbXBvcnQgaHR0cHgKZnJvbSBkYXRldGltZSBpbXBvcnQgZGF0ZXRpbWUsIHRpbWVkZWx0YQoKQkFTRSA9IHN5cy5hcmd2WzFdIGlmIGxlbihzeXMuYXJndikgPiAxIGVsc2UgImh0dHA6Ly9sb2NhbGhvc3Q6ODAwMCIKQVBJID0gZiJ7QkFTRX0vYXBpL3YxIgoKIyBQcmV0dHkgcHJpbnQgaGVscGVyCmRlZiBwcChsYWJlbDogc3RyLCByZXNwOiBodHRweC5SZXNwb25zZSkgLT4gZGljdCB8IGxpc3QgfCBzdHI6CiAgICBzdGF0dXMgPSByZXNwLnN0YXR1c19jb2RlCiAgICB0cnk6CiAgICAgICAgZGF0YSA9IHJlc3AuanNvbigpCiAgICBleGNlcHQgRXhjZXB0aW9uOgogICAgICAgIGRhdGEgPSByZXNwLnRleHQKICAgIGljb24gPSAi4pyFIiBpZiAyMDAgPD0gc3RhdHVzIDwgNDAwIGVsc2UgIuKdjCIKICAgIHByaW50KGYiXG57aWNvbn0gW3tzdGF0dXN9XSB7bGFiZWx9IikKICAgIGlmIGlzaW5zdGFuY2UoZGF0YSwgZGljdCk6CiAgICAgICAgcHJpbnQoanNvbi5kdW1wcyhkYXRhLCBpbmRlbnQ9MiwgZGVmYXVsdD1zdHIpWzo4MDBdKQogICAgZWxzZToKICAgICAgICBwcmludChzdHIoZGF0YSlbOjQwMF0pCiAgICByZXR1cm4gZGF0YQoKCmRlZiBhdXRoX2hlYWRlcih0b2tlbjogc3RyKSAtPiBkaWN0OgogICAgcmV0dXJuIHsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHt0b2tlbn0ifQoKCmRlZiBtYWluKCk6CiAgICBjbGllbnQgPSBodHRweC5DbGllbnQoYmFzZV91cmw9QVBJLCB0aW1lb3V0PTMwKQoKICAgIHByaW50KCI9IiAqIDYwKQogICAgcHJpbnQoIiAgU3RheU5lc3Qg4oCUIEZ1bGwgRW5kLXRvLUVuZCBTbW9rZSBUZXN0IikKICAgIHByaW50KCI9IiAqIDYwKQoKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICAjIFNURVAgMCDigJQgSGVhbHRoIGNoZWNrCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgMDogSGVhbHRoIENoZWNrIC0tLSIpCiAgICByID0gY2xpZW50LmdldChmIntCQVNFfS9oZWFsdGgiKQogICAgcHAoIkhlYWx0aCBDaGVjayIsIHIpCiAgICBpZiByLnN0YXR1c19jb2RlICE9IDIwMDoKICAgICAgICBwcmludCgi4pqg77iPICBCYWNrZW5kIG5vdCByZWFjaGFibGUuIE1ha2Ugc3VyZSBpdCdzIHJ1bm5pbmchIikKICAgICAgICBzeXMuZXhpdCgxKQoKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICAjIFNURVAgMSDigJQgUmVnaXN0ZXIgdXNlcnMKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICB0cyA9IGRhdGV0aW1lLm5vdygpLnN0cmZ0aW1lKCIlSCVNJVMiKSAgIyB1bmlxdWUgc3VmZml4CgogICAgZ3Vlc3RfZW1haWwgPSBmImd1ZXN0X3t0c31AZXhhbXBsZS5jb20iCiAgICBob3N0X2VtYWlsID0gZiJob3N0X3t0c31AZXhhbXBsZS5jb20iCiAgICBhZG1pbl9lbWFpbCA9IGYiYWRtaW5fe3RzfUBleGFtcGxlLmNvbSIKICAgIHBhc3N3b3JkID0gIlNlY3VyZVBhc3MxMjMhIgoKICAgIHByaW50KCJcbi0tLSBTdGVwIDE6IFJlZ2lzdGVyIFVzZXJzIC0tLSIpCgogICAgIyAxYSDigJQgR3Vlc3QgKHJvbGU9dXNlcikKICAgIHIgPSBjbGllbnQucG9zdCgiL2F1dGgvcmVnaXN0ZXIiLCBqc29uPXsKICAgICAgICAiZW1haWwiOiBndWVzdF9lbWFpbCwKICAgICAgICAicGFzc3dvcmQiOiBwYXNzd29yZCwKICAgICAgICAiZnVsbF9uYW1lIjogIkFsaWNlIEd1ZXN0IiwKICAgICAgICAicm9sZSI6ICJ1c2VyIgogICAgfSkKICAgIGd1ZXN0X2RhdGEgPSBwcCgiUmVnaXN0ZXIgR3Vlc3QiLCByKQogICAgZ3Vlc3RfaWQgPSBndWVzdF9kYXRhLmdldCgiaWQiKSBpZiBpc2luc3RhbmNlKGd1ZXN0X2RhdGEsIGRpY3QpIGVsc2UgTm9uZQoKICAgICMgMWIg4oCUIEhvc3QgKHJvbGU9aG9zdCkKICAgIHIgPSBjbGllbnQucG9zdCgiL2F1dGgvcmVnaXN0ZXIiLCBqc29uPXsKICAgICAgICAiZW1haWwiOiBob3N0X2VtYWlsLAogICAgICAgICJwYXNzd29yZCI6IHBhc3N3b3JkLAogICAgICAgICJmdWxsX25hbWUiOiAiQm9iIEhvc3QiLAogICAgICAgICJyb2xlIjogImhvc3QiCiAgICB9KQogICAgaG9zdF9kYXRhID0gcHAoIlJlZ2lzdGVyIEhvc3QiLCByKQogICAgaG9zdF9pZCA9IGhvc3RfZGF0YS5nZXQoImlkIikgaWYgaXNpbnN0YW5jZShob3N0X2RhdGEsIGRpY3QpIGVsc2UgTm9uZQoKICAgICMgMWMg4oCUIEFkbWluOiByZWdpc3RlciBhcyB1c2VyIGZpcnN0LCB0aGVuIHdlJ2xsIHByb21vdGUgdmlhIFNRTCBsYXRlcgogICAgciA9IGNsaWVudC5wb3N0KCIvYXV0aC9yZWdpc3RlciIsIGpzb249ewogICAgICAgICJlbWFpbCI6IGFkbWluX2VtYWlsLAogICAgICAgICJwYXNzd29yZCI6IHBhc3N3b3JkLAogICAgICAgICJmdWxsX25hbWUiOiAiQ2hhcmxpZSBBZG1pbiIsCiAgICAgICAgInJvbGUiOiAidXNlciIKICAgIH0pCiAgICBhZG1pbl9kYXRhID0gcHAoIlJlZ2lzdGVyIEFkbWluIChhcyB1c2VyIGZpcnN0KSIsIHIpCiAgICBhZG1pbl9pZCA9IGFkbWluX2RhdGEuZ2V0KCJpZCIpIGlmIGlzaW5zdGFuY2UoYWRtaW5fZGF0YSwgZGljdCkgZWxzZSBOb25lCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU1RFUCAyIOKAlCBMb2dpbiBhbGwgdGhyZWUgdXNlcnMKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICBwcmludCgiXG4tLS0gU3RlcCAyOiBMb2dpbiBVc2VycyAtLS0iKQoKICAgIHIgPSBjbGllbnQucG9zdCgiL2F1dGgvbG9naW4iLCBqc29uPXsiZW1haWwiOiBndWVzdF9lbWFpbCwgInBhc3N3b3JkIjogcGFzc3dvcmR9KQogICAgZ3Vlc3RfdG9rZW5zID0gcHAoIkxvZ2luIEd1ZXN0IiwgcikKICAgIGd1ZXN0X2FjY2VzcyA9IGd1ZXN0X3Rva2Vucy5nZXQoImFjY2Vzc190b2tlbiIsICIiKSBpZiBpc2luc3RhbmNlKGd1ZXN0X3Rva2VucywgZGljdCkgZWxzZSAiIgoKICAgIHIgPSBjbGllbnQucG9zdCgiL2F1dGgvbG9naW4iLCBqc29uPXsiZW1haWwiOiBob3N0X2VtYWlsLCAicGFzc3dvcmQiOiBwYXNzd29yZH0pCiAgICBob3N0X3Rva2VucyA9IHBwKCJMb2dpbiBIb3N0IiwgcikKICAgIGhvc3RfYWNjZXNzID0gaG9zdF90b2tlbnMuZ2V0KCJhY2Nlc3NfdG9rZW4iLCAiIikgaWYgaXNpbnN0YW5jZShob3N0X3Rva2VucywgZGljdCkgZWxzZSAiIgoKICAgIHIgPSBjbGllbnQucG9zdCgiL2F1dGgvbG9naW4iLCBqc29uPXsiZW1haWwiOiBhZG1pbl9lbWFpbCwgInBhc3N3b3JkIjogcGFzc3dvcmR9KQogICAgYWRtaW5fdG9rZW5zID0gcHAoIkxvZ2luIEFkbWluIChzdGlsbCB1c2VyIHJvbGUpIiwgcikKICAgIGFkbWluX2FjY2VzcyA9IGFkbWluX3Rva2Vucy5nZXQoImFjY2Vzc190b2tlbiIsICIiKSBpZiBpc2luc3RhbmNlKGFkbWluX3Rva2VucywgZGljdCkgZWxzZSAiIgoKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICAjIFNURVAgMmIg4oCUIFRva2VuIHJlZnJlc2ggdGVzdAogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgIHByaW50KCJcbi0tLSBTdGVwIDJiOiBUb2tlbiBSZWZyZXNoIC0tLSIpCiAgICBpZiBpc2luc3RhbmNlKGd1ZXN0X3Rva2VucywgZGljdCkgYW5kIGd1ZXN0X3Rva2Vucy5nZXQoInJlZnJlc2hfdG9rZW4iKToKICAgICAgICByID0gY2xpZW50LnBvc3QoIi9hdXRoL3JlZnJlc2giLCBqc29uPXsicmVmcmVzaF90b2tlbiI6IGd1ZXN0X3Rva2Vuc1sicmVmcmVzaF90b2tlbiJdfSkKICAgICAgICByZWZyZXNoZWQgPSBwcCgiUmVmcmVzaCBHdWVzdCBUb2tlbiIsIHIpCiAgICAgICAgaWYgaXNpbnN0YW5jZShyZWZyZXNoZWQsIGRpY3QpIGFuZCByZWZyZXNoZWQuZ2V0KCJhY2Nlc3NfdG9rZW4iKToKICAgICAgICAgICAgZ3Vlc3RfYWNjZXNzID0gcmVmcmVzaGVkWyJhY2Nlc3NfdG9rZW4iXQoKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICAjIFNURVAgMmMg4oCUIEdldCBwcm9maWxlCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgMmM6IEdldCBQcm9maWxlIC0tLSIpCiAgICByID0gY2xpZW50LmdldCgiL2F1dGgvbWUiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGd1ZXN0X2FjY2VzcykpCiAgICBwcCgiR3Vlc3QgUHJvZmlsZSIsIHIpCgogICAgciA9IGNsaWVudC5nZXQoIi9hdXRoL21lIiwgaGVhZGVycz1hdXRoX2hlYWRlcihob3N0X2FjY2VzcykpCiAgICBwcCgiSG9zdCBQcm9maWxlIiwgcikKCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgIyBTVEVQIDMg4oCUIEhPU1QgY3JlYXRlcyBhIHByb3BlcnR5CiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgMzogSG9zdCBDcmVhdGVzIFByb3BlcnR5IC0tLSIpCiAgICByID0gY2xpZW50LnBvc3QoIi9wcm9wZXJ0aWVzIiwgaGVhZGVycz1hdXRoX2hlYWRlcihob3N0X2FjY2VzcyksIGpzb249ewogICAgICAgICJ0aXRsZSI6ICJDb3p5IERvd250b3duIEFwYXJ0bWVudCIsCiAgICAgICAgImRlc2NyaXB0aW9uIjogIkJlYXV0aWZ1bCAyLWJlZHJvb20gYXBhcnRtZW50IGluIHRoZSBoZWFydCBvZiBkb3dudG93biB3aXRoIGdyZWF0IHZpZXdzLiIsCiAgICAgICAgImNpdHkiOiAiTmV3IFlvcmsiLAogICAgICAgICJhZGRyZXNzIjogIjEyMyBNYWluIFN0cmVldCwgQXB0IDRCLCBOZXcgWW9yaywgTlkgMTAwMDEiLAogICAgICAgICJsYXRpdHVkZSI6IDQwLjcxMjgsCiAgICAgICAgImxvbmdpdHVkZSI6IC03NC4wMDYwLAogICAgICAgICJwcmljZV9wZXJfbmlnaHQiOiAxNTAuMDAsCiAgICAgICAgIm1heF9ndWVzdHMiOiA0LAogICAgICAgICJhbWVuaXRpZXMiOiBbIndpZmkiLCAia2l0Y2hlbiIsICJhaXJfY29uZGl0aW9uaW5nIiwgIndhc2hlciJdCiAgICB9KQogICAgcHJvcGVydHlfZGF0YSA9IHBwKCJDcmVhdGUgUHJvcGVydHkiLCByKQogICAgcHJvcGVydHlfaWQgPSBwcm9wZXJ0eV9kYXRhLmdldCgiaWQiKSBpZiBpc2luc3RhbmNlKHByb3BlcnR5X2RhdGEsIGRpY3QpIGVsc2UgTm9uZQoKICAgICMgQ3JlYXRlIGEgc2Vjb25kIHByb3BlcnR5CiAgICByID0gY2xpZW50LnBvc3QoIi9wcm9wZXJ0aWVzIiwgaGVhZGVycz1hdXRoX2hlYWRlcihob3N0X2FjY2VzcyksIGpzb249ewogICAgICAgICJ0aXRsZSI6ICJCZWFjaCBIb3VzZSBQYXJhZGlzZSIsCiAgICAgICAgImRlc2NyaXB0aW9uIjogIlN0dW5uaW5nIGJlYWNoZnJvbnQgaG91c2Ugd2l0aCBwYW5vcmFtaWMgb2NlYW4gdmlld3MgYW5kIHByaXZhdGUgcG9vbC4iLAogICAgICAgICJjaXR5IjogIk1pYW1pIiwKICAgICAgICAiYWRkcmVzcyI6ICI0NTYgT2NlYW4gRHJpdmUsIE1pYW1pIEJlYWNoLCBGTCAzMzEzOSIsCiAgICAgICAgImxhdGl0dWRlIjogMjUuNzYxNywKICAgICAgICAibG9uZ2l0dWRlIjogLTgwLjE5MTgsCiAgICAgICAgInByaWNlX3Blcl9uaWdodCI6IDMwMC4wMCwKICAgICAgICAibWF4X2d1ZXN0cyI6IDgsCiAgICAgICAgImFtZW5pdGllcyI6IFsid2lmaSIsICJwb29sIiwgImJlYWNoX2FjY2VzcyIsICJwYXJraW5nIiwgImFpcl9jb25kaXRpb25pbmciXQogICAgfSkKICAgIHByb3BlcnR5Ml9kYXRhID0gcHAoIkNyZWF0ZSBTZWNvbmQgUHJvcGVydHkiLCByKQoKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICAjIFNURVAgNCDigJQgR1VFU1QgYnJvd3NlcyBwcm9wZXJ0aWVzCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgNDogQnJvd3NlIFByb3BlcnRpZXMgLS0tIikKCiAgICByID0gY2xpZW50LmdldCgiL3Byb3BlcnRpZXMiKQogICAgcHAoIkxpc3QgQWxsIFByb3BlcnRpZXMiLCByKQoKICAgIHIgPSBjbGllbnQuZ2V0KCIvcHJvcGVydGllcyIsIHBhcmFtcz17ImNpdHkiOiAiTmV3IFlvcmsifSkKICAgIHBwKCJTZWFyY2ggUHJvcGVydGllcyBpbiBOZXcgWW9yayIsIHIpCgogICAgaWYgcHJvcGVydHlfaWQ6CiAgICAgICAgciA9IGNsaWVudC5nZXQoZiIvcHJvcGVydGllcy97cHJvcGVydHlfaWR9IikKICAgICAgICBwcChmIkdldCBQcm9wZXJ0eSBEZXRhaWwgKHtwcm9wZXJ0eV9pZFs6OF19Li4uKSIsIHIpCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU1RFUCA1IOKAlCBHVUVTVCBib29rcyBhIHByb3BlcnR5CiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgNTogR3Vlc3QgQm9va3MgUHJvcGVydHkgLS0tIikKICAgIGNoZWNrX2luID0gKGRhdGV0aW1lLm5vdygpICsgdGltZWRlbHRhKGRheXM9NykpLmlzb2Zvcm1hdCgpCiAgICBjaGVja19vdXQgPSAoZGF0ZXRpbWUubm93KCkgKyB0aW1lZGVsdGEoZGF5cz0xMCkpLmlzb2Zvcm1hdCgpCgogICAgaWYgcHJvcGVydHlfaWQ6CiAgICAgICAgciA9IGNsaWVudC5wb3N0KCIvYm9va2luZ3MiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGd1ZXN0X2FjY2VzcyksIGpzb249ewogICAgICAgICAgICAicHJvcGVydHlfaWQiOiBwcm9wZXJ0eV9pZCwKICAgICAgICAgICAgImNoZWNrX2luIjogY2hlY2tfaW4sCiAgICAgICAgICAgICJjaGVja19vdXQiOiBjaGVja19vdXQsCiAgICAgICAgICAgICJib29raW5nX3R5cGUiOiAibmlnaHRseSIKICAgICAgICB9KQogICAgICAgIGJvb2tpbmdfZGF0YSA9IHBwKCJDcmVhdGUgQm9va2luZyAoMyBuaWdodHMpIiwgcikKICAgICAgICBib29raW5nX2lkID0gYm9va2luZ19kYXRhLmdldCgiaWQiKSBpZiBpc2luc3RhbmNlKGJvb2tpbmdfZGF0YSwgZGljdCkgZWxzZSBOb25lCiAgICBlbHNlOgogICAgICAgIGJvb2tpbmdfaWQgPSBOb25lCiAgICAgICAgcHJpbnQoIuKaoO+4jyAgU2tpcHBpbmcgYm9va2luZyDigJQgbm8gcHJvcGVydHlfaWQuIikKCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgIyBTVEVQIDViIOKAlCBMaXN0IGJvb2tpbmdzCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgNWI6IExpc3QgQm9va2luZ3MgLS0tIikKICAgIHIgPSBjbGllbnQuZ2V0KCIvYm9va2luZ3MiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGd1ZXN0X2FjY2VzcykpCiAgICBwcCgiR3Vlc3QncyBCb29raW5ncyIsIHIpCgogICAgciA9IGNsaWVudC5nZXQoIi9ib29raW5ncyIsIGhlYWRlcnM9YXV0aF9oZWFkZXIoaG9zdF9hY2Nlc3MpKQogICAgcHAoIkhvc3QncyBCb29raW5ncyIsIHIpCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU1RFUCA2IOKAlCBIT1NUIGNvbmZpcm1zIGJvb2tpbmcKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICBwcmludCgiXG4tLS0gU3RlcCA2OiBIb3N0IENvbmZpcm1zIEJvb2tpbmcgLS0tIikKICAgIGlmIGJvb2tpbmdfaWQ6CiAgICAgICAgciA9IGNsaWVudC5wYXRjaChmIi9ib29raW5ncy97Ym9va2luZ19pZH0vc3RhdHVzIiwKICAgICAgICAgICAgICAgICAgICAgICAgIGhlYWRlcnM9YXV0aF9oZWFkZXIoaG9zdF9hY2Nlc3MpLAogICAgICAgICAgICAgICAgICAgICAgICAganNvbj17InN0YXR1cyI6ICJjb25maXJtZWQifSkKICAgICAgICBwcCgiQ29uZmlybSBCb29raW5nIiwgcikKICAgIGVsc2U6CiAgICAgICAgcHJpbnQoIuKaoO+4jyAgU2tpcHBpbmcg4oCUIG5vIGJvb2tpbmdfaWQuIikKCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgIyBTVEVQIDcg4oCUIEd1ZXN0IHdyaXRlcyBhIHJldmlldyAoYWZ0ZXIgbWFya2luZyBjb21wbGV0ZWQpCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgNzogUmV2aWV3IEZsb3cgLS0tIikKICAgIGlmIGJvb2tpbmdfaWQ6CiAgICAgICAgIyBDb21wbGV0ZSB0aGUgYm9va2luZyBmaXJzdAogICAgICAgIHIgPSBjbGllbnQucGF0Y2goZiIvYm9va2luZ3Mve2Jvb2tpbmdfaWR9L3N0YXR1cyIsCiAgICAgICAgICAgICAgICAgICAgICAgICBoZWFkZXJzPWF1dGhfaGVhZGVyKGhvc3RfYWNjZXNzKSwKICAgICAgICAgICAgICAgICAgICAgICAgIGpzb249eyJzdGF0dXMiOiAiY29tcGxldGVkIn0pCiAgICAgICAgcHAoIkNvbXBsZXRlIEJvb2tpbmciLCByKQoKICAgICAgICAjIEd1ZXN0IHdyaXRlcyBhIHJldmlldwogICAgICAgIHIgPSBjbGllbnQucG9zdCgiL3Jldmlld3MiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGd1ZXN0X2FjY2VzcyksIGpzb249ewogICAgICAgICAgICAiYm9va2luZ19pZCI6IGJvb2tpbmdfaWQsCiAgICAgICAgICAgICJyYXRpbmciOiA1LAogICAgICAgICAgICAiY29tbWVudCI6ICJBbWF6aW5nIGFwYXJ0bWVudCEgVGhlIHZpZXdzIHdlcmUgaW5jcmVkaWJsZSBhbmQgQm9iIHdhcyBhIGdyZWF0IGhvc3QuIgogICAgICAgIH0pCiAgICAgICAgcHAoIlN1Ym1pdCBSZXZpZXciLCByKQoKICAgICAgICAjIExpc3QgcmV2aWV3cyBmb3IgdGhlIHByb3BlcnR5CiAgICAgICAgaWYgcHJvcGVydHlfaWQ6CiAgICAgICAgICAgIHIgPSBjbGllbnQuZ2V0KGYiL3Jldmlld3MvcHJvcGVydHkve3Byb3BlcnR5X2lkfSIpCiAgICAgICAgICAgIHBwKCJQcm9wZXJ0eSBSZXZpZXdzIiwgcikKICAgIGVsc2U6CiAgICAgICAgcHJpbnQoIuKaoO+4jyAgU2tpcHBpbmcgcmV2aWV3cyDigJQgbm8gYm9va2luZy4iKQoKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICAjIFNURVAgOCDigJQgTWVzc2FnaW5nIGJldHdlZW4gZ3Vlc3QgYW5kIGhvc3QKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICBwcmludCgiXG4tLS0gU3RlcCA4OiBNZXNzYWdpbmcgLS0tIikKICAgIGlmIHByb3BlcnR5X2lkIGFuZCBndWVzdF9pZCBhbmQgaG9zdF9pZDoKICAgICAgICAjIEd1ZXN0IHNlbmRzIGEgbWVzc2FnZSB0byBob3N0CiAgICAgICAgciA9IGNsaWVudC5wb3N0KCIvbWVzc2FnZXMiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGd1ZXN0X2FjY2VzcyksIGpzb249ewogICAgICAgICAgICAicmVjZWl2ZXJfaWQiOiBob3N0X2lkLAogICAgICAgICAgICAicHJvcGVydHlfaWQiOiBwcm9wZXJ0eV9pZCwKICAgICAgICAgICAgImNvbnRlbnQiOiAiSGkgQm9iISBJIGxvdmVkIHRoZSBhcGFydG1lbnQuIEFyZSB0aGVyZSBhbnkgcmVzdGF1cmFudHMgbmVhcmJ5PyIKICAgICAgICB9KQogICAgICAgIHBwKCJHdWVzdCBTZW5kcyBNZXNzYWdlIiwgcikKCiAgICAgICAgIyBIb3N0IHJlcGxpZXMKICAgICAgICByID0gY2xpZW50LnBvc3QoIi9tZXNzYWdlcyIsIGhlYWRlcnM9YXV0aF9oZWFkZXIoaG9zdF9hY2Nlc3MpLCBqc29uPXsKICAgICAgICAgICAgInJlY2VpdmVyX2lkIjogZ3Vlc3RfaWQsCiAgICAgICAgICAgICJwcm9wZXJ0eV9pZCI6IHByb3BlcnR5X2lkLAogICAgICAgICAgICAiY29udGVudCI6ICJUaGFua3MgQWxpY2UhIFllcywgdGhlcmUgYXJlIGdyZWF0IHJlc3RhdXJhbnRzIHdpdGhpbiB3YWxraW5nIGRpc3RhbmNlLiIKICAgICAgICB9KQogICAgICAgIHBwKCJIb3N0IFJlcGxpZXMiLCByKQoKICAgICAgICAjIEd1ZXN0IHZpZXdzIGNvbnZlcnNhdGlvbgogICAgICAgIHIgPSBjbGllbnQuZ2V0KCIvbWVzc2FnZXMiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGd1ZXN0X2FjY2VzcykpCiAgICAgICAgcHAoIkd1ZXN0J3MgTWVzc2FnZXMiLCByKQogICAgZWxzZToKICAgICAgICBwcmludCgi4pqg77iPICBTa2lwcGluZyBtZXNzYWdpbmcg4oCUIG1pc3NpbmcgdXNlci9wcm9wZXJ0eSBJRHMuIikKCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgIyBTVEVQIDkg4oCUIE1lbWJlcnNoaXAgZm9yIGhvc3QKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICBwcmludCgiXG4tLS0gU3RlcCA5OiBIb3N0IE1lbWJlcnNoaXAgLS0tIikKICAgIHIgPSBjbGllbnQucG9zdCgiL21lbWJlcnNoaXBzIiwgaGVhZGVycz1hdXRoX2hlYWRlcihob3N0X2FjY2VzcyksIGpzb249ewogICAgICAgICJwbGFuX3R5cGUiOiAicHJlbWl1bSIKICAgIH0pCiAgICBwcCgiSG9zdCBTdWJzY3JpYmVzIHRvIFByZW1pdW0iLCByKQoKICAgIHIgPSBjbGllbnQuZ2V0KCIvbWVtYmVyc2hpcHMvbWUiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGhvc3RfYWNjZXNzKSkKICAgIHBwKCJIb3N0J3MgTWVtYmVyc2hpcCIsIHIpCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU1RFUCAxMCDigJQgQWRtaW4gb3BlcmF0aW9ucwogICAgIyAgIE5PVEU6IFRoZSBhZG1pbiB1c2VyIG11c3QgYmUgcHJvbW90ZWQgaW4gdGhlIERCIGZpcnN0IQogICAgIyAgIFNlZSBpbnN0cnVjdGlvbnMgcHJpbnRlZCBiZWxvdy4KICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICBwcmludCgiXG4tLS0gU3RlcCAxMDogQWRtaW4gT3BlcmF0aW9ucyAtLS0iKQogICAgcHJpbnQoZiIiIgrilZTilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZcK4pWRICBUbyB0ZXN0IGFkbWluIGVuZHBvaW50cywgcHJvbW90ZSB0aGUgYWRtaW4gdXNlciBpbiB0aGUgREI6IOKVkQrilZEgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgIFVzaW5nIHBzcWwgKERvY2tlcik6ICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgZG9ja2VyIGV4ZWMgLWl0IDxkYl9jb250YWluZXI+IHBzcWwgLVUgc3RheW5lc3Qgc3RheW5lc3QgIOKVkQrilZEgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgIE9yIGlmIFBvc3RncmVzIGlzIGxvY2FsOiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgcHNxbCAtVSBzdGF5bmVzdCAtZCBzdGF5bmVzdCAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgIFRoZW4gcnVuOiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgVVBEQVRFIHVzZXJzIFNFVCByb2xlID0gJ2FkbWluJyAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgV0hFUkUgZW1haWwgPSAne2FkbWluX2VtYWlsfSc7ICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgIFRoZW4gcmUtbG9naW4gYmVsb3cgdG8gZ2V0IGFkbWluLXJvbGUgSldULiAgICAgICAgICAgICAgICAgIOKVkQrilZrilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZ0KIiIiKQoKICAgICMgVHJ5IGFkbWluIGVuZHBvaW50cyB3aXRoIGN1cnJlbnQgdG9rZW4gKHdpbGwgZmFpbCBpZiBub3QgcHJvbW90ZWQpCiAgICByID0gY2xpZW50LmdldCgiL2FkbWluL2Rhc2hib2FyZCIsIGhlYWRlcnM9YXV0aF9oZWFkZXIoYWRtaW5fYWNjZXNzKSkKICAgIHJlc3VsdCA9IHBwKCJBZG1pbiBEYXNoYm9hcmQgKG1heSBmYWlsIGlmIG5vdCBwcm9tb3RlZCB5ZXQpIiwgcikKCiAgICBpZiByLnN0YXR1c19jb2RlID09IDQwMzoKICAgICAgICBwcmludCgiXG7ij7MgQXR0ZW1wdGluZyB0byByZS1sb2dpbiBhZG1pbiBhZnRlciBwb3RlbnRpYWwgREIgcHJvbW90aW9uLi4uIikKICAgICAgICByID0gY2xpZW50LnBvc3QoIi9hdXRoL2xvZ2luIiwganNvbj17ImVtYWlsIjogYWRtaW5fZW1haWwsICJwYXNzd29yZCI6IHBhc3N3b3JkfSkKICAgICAgICBhZG1pbl90b2tlbnMyID0gcHAoIlJlLWxvZ2luIEFkbWluIiwgcikKICAgICAgICBpZiBpc2luc3RhbmNlKGFkbWluX3Rva2VuczIsIGRpY3QpIGFuZCBhZG1pbl90b2tlbnMyLmdldCgiYWNjZXNzX3Rva2VuIik6CiAgICAgICAgICAgIGFkbWluX2FjY2VzczIgPSBhZG1pbl90b2tlbnMyWyJhY2Nlc3NfdG9rZW4iXQoKICAgICAgICAgICAgciA9IGNsaWVudC5nZXQoIi9hZG1pbi9kYXNoYm9hcmQiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGFkbWluX2FjY2VzczIpKQogICAgICAgICAgICBwcCgiQWRtaW4gRGFzaGJvYXJkIChhZnRlciBwcm9tb3Rpb24pIiwgcikKCiAgICAgICAgICAgIHIgPSBjbGllbnQuZ2V0KCIvYWRtaW4vdXNlcnMiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGFkbWluX2FjY2VzczIpKQogICAgICAgICAgICBwcCgiQWRtaW4g4oCUIExpc3QgVXNlcnMiLCByKQoKICAgICAgICAgICAgciA9IGNsaWVudC5nZXQoIi9hZG1pbi9wcm9wZXJ0aWVzIiwgaGVhZGVycz1hdXRoX2hlYWRlcihhZG1pbl9hY2Nlc3MyKSkKICAgICAgICAgICAgcHAoIkFkbWluIOKAlCBMaXN0IFByb3BlcnRpZXMiLCByKQoKICAgICAgICAgICAgciA9IGNsaWVudC5nZXQoIi9hZG1pbi9tZW1iZXJzaGlwcyIsIGhlYWRlcnM9YXV0aF9oZWFkZXIoYWRtaW5fYWNjZXNzMikpCiAgICAgICAgICAgIHBwKCJBZG1pbiDigJQgTGlzdCBNZW1iZXJzaGlwcyIsIHIpCgogICAgICAgICAgICAjIFRvZ2dsZSBhIHVzZXIncyBzdGF0dXMKICAgICAgICAgICAgaWYgZ3Vlc3RfaWQ6CiAgICAgICAgICAgICAgICByID0gY2xpZW50LnB1dChmIi9hZG1pbi91c2Vycy97Z3Vlc3RfaWR9L3N0YXR1cyIsCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICBoZWFkZXJzPWF1dGhfaGVhZGVyKGFkbWluX2FjY2VzczIpKQogICAgICAgICAgICAgICAgcHAoIkFkbWluIOKAlCBUb2dnbGUgR3Vlc3QgQWN0aXZlIFN0YXR1cyIsIHIpCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU3VtbWFyeQogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgIHByaW50KCJcbiIgKyAiPSIgKiA2MCkKICAgIHByaW50KCIgIFRlc3QgU3VtbWFyeSIpCiAgICBwcmludCgiPSIgKiA2MCkKICAgIHByaW50KGYiIiIKICBHdWVzdCBlbWFpbCA6IHtndWVzdF9lbWFpbH0KICBIb3N0IGVtYWlsICA6IHtob3N0X2VtYWlsfQogIEFkbWluIGVtYWlsIDoge2FkbWluX2VtYWlsfQogIFBhc3N3b3JkICAgIDoge3Bhc3N3b3JkfQogIFByb3BlcnR5IElEIDoge3Byb3BlcnR5X2lkIG9yICdOL0EnfQogIEJvb2tpbmcgSUQgIDoge2Jvb2tpbmdfaWQgb3IgJ04vQSd9CgogIEZyb250ZW5kICAgIDogaHR0cDovL2xvY2FsaG9zdDozMDAwCiAgU3dhZ2dlciBVSSAgOiB7QkFTRX0vZG9jcwogIFJlRG9jICAgICAgIDoge0JBU0V9L3JlZG9jCiIiIikKCgppZiBfX25hbWVfXyA9PSAiX19tYWluX18iOgogICAgbWFpbigpCg==</t>
+    <t>IiIiClN0YXlOZXN0IOKAlCBEYXRhYmFzZSBTZXR1cCAmIEVuZC10by1FbmQgQVBJIFNtb2tlIFRlc3QKPT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT09PT0KUnVuIHRoaXMgQUZURVIgeW91ciBiYWNrZW5kICh1dmljb3JuKSBhbmQgZGF0YWJhc2UgKHBvc3RncmVzKSBhcmUgcnVubmluZy4KClVzYWdlOgogIHB5dGhvbiBzZWVkX2FuZF90ZXN0LnB5ICAgICAgICAgICAgICAjIGRlZmF1bHQ6IGh0dHA6Ly9sb2NhbGhvc3Q6ODAwMAogIHB5dGhvbiBzZWVkX2FuZF90ZXN0LnB5IGh0dHA6Ly9sb2NhbGhvc3Q6ODAwMCAgICMgY3VzdG9tIGJhc2UgVVJMCgpXaGF0IGl0IGRvZXM6CiAgMS4gUmVnaXN0ZXJzIGEgcmVndWxhciBVU0VSLCBhIEhPU1QsIGFuZCBtYW51YWxseSBwcm9tb3RlcyBhbiBBRE1JTgogIDIuIFRlc3RzIGF1dGggZmxvd3MgKGxvZ2luLCB0b2tlbiByZWZyZXNoLCBwcm9maWxlKQogIDMuIEhvc3QgY3JlYXRlcyBhIHByb3BlcnR5IGxpc3RpbmcKICA0LiBHdWVzdCBzZWFyY2hlcyAmIHZpZXdzIHByb3BlcnRpZXMKICA1LiBHdWVzdCBib29rcyBhIHByb3BlcnR5CiAgNi4gSG9zdCBjb25maXJtcyB0aGUgYm9va2luZwogIDcuIEd1ZXN0IHdyaXRlcyBhIHJldmlldyBhZnRlciBjaGVja291dAogIDguIEFkbWluIGRhc2hib2FyZCAmIHVzZXIgbWFuYWdlbWVudAogIDkuIE1lc3NhZ2luZyBiZXR3ZWVuIGd1ZXN0IGFuZCBob3N0CiAgMTAuIE1lbWJlcnNoaXAgcHVyY2hhc2UgZm9yIHRoZSBob3N0CiIiIgoKaW1wb3J0IHN5cwppbXBvcnQganNvbgppbXBvcnQgdXVpZAppbXBvcnQgaHR0cHgKZnJvbSBkYXRldGltZSBpbXBvcnQgZGF0ZXRpbWUsIHRpbWVkZWx0YQoKQkFTRSA9IHN5cy5hcmd2WzFdIGlmIGxlbihzeXMuYXJndikgPiAxIGVsc2UgImh0dHA6Ly9sb2NhbGhvc3Q6ODAwMCIKQVBJID0gZiJ7QkFTRX0vYXBpL3YxIgoKIyBQcmV0dHkgcHJpbnQgaGVscGVyCmRlZiBwcChsYWJlbDogc3RyLCByZXNwOiBodHRweC5SZXNwb25zZSkgLT4gZGljdCB8IGxpc3QgfCBzdHI6CiAgICBzdGF0dXMgPSByZXNwLnN0YXR1c19jb2RlCiAgICB0cnk6CiAgICAgICAgZGF0YSA9IHJlc3AuanNvbigpCiAgICBleGNlcHQgRXhjZXB0aW9uOgogICAgICAgIGRhdGEgPSByZXNwLnRleHQKICAgIGljb24gPSAi4pyFIiBpZiAyMDAgPD0gc3RhdHVzIDwgNDAwIGVsc2UgIuKdjCIKICAgIHByaW50KGYiXG57aWNvbn0gW3tzdGF0dXN9XSB7bGFiZWx9IikKICAgIGlmIGlzaW5zdGFuY2UoZGF0YSwgZGljdCk6CiAgICAgICAgcHJpbnQoanNvbi5kdW1wcyhkYXRhLCBpbmRlbnQ9MiwgZGVmYXVsdD1zdHIpWzo4MDBdKQogICAgZWxzZToKICAgICAgICBwcmludChzdHIoZGF0YSlbOjQwMF0pCiAgICByZXR1cm4gZGF0YQoKCmRlZiBhdXRoX2hlYWRlcih0b2tlbjogc3RyKSAtPiBkaWN0OgogICAgcmV0dXJuIHsiQXV0aG9yaXphdGlvbiI6IGYiQmVhcmVyIHt0b2tlbn0ifQoKCmRlZiBtYWluKCk6CiAgICBjbGllbnQgPSBodHRweC5DbGllbnQoYmFzZV91cmw9QVBJLCB0aW1lb3V0PTMwKQoKICAgIHByaW50KCI9IiAqIDYwKQogICAgcHJpbnQoIiAgU3RheU5lc3Qg4oCUIEZ1bGwgRW5kLXRvLUVuZCBTbW9rZSBUZXN0IikKICAgIHByaW50KCI9IiAqIDYwKQoKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICAjIFNURVAgMCDigJQgSGVhbHRoIGNoZWNrCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgMDogSGVhbHRoIENoZWNrIC0tLSIpCiAgICByID0gY2xpZW50LmdldChmIntCQVNFfS9oZWFsdGgiKQogICAgcHAoIkhlYWx0aCBDaGVjayIsIHIpCiAgICBpZiByLnN0YXR1c19jb2RlICE9IDIwMDoKICAgICAgICBwcmludCgi4pqg77iPICBCYWNrZW5kIG5vdCByZWFjaGFibGUuIE1ha2Ugc3VyZSBpdCdzIHJ1bm5pbmchIikKICAgICAgICBzeXMuZXhpdCgxKQoKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICAjIFNURVAgMSDigJQgUmVnaXN0ZXIgdXNlcnMKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICB0cyA9IGRhdGV0aW1lLm5vdygpLnN0cmZ0aW1lKCIlSCVNJVMiKSAgIyB1bmlxdWUgc3VmZml4CgogICAgZ3Vlc3RfZW1haWwgPSBmImd1ZXN0X3t0c31AZXhhbXBsZS5jb20iCiAgICBob3N0X2VtYWlsID0gZiJob3N0X3t0c31AZXhhbXBsZS5jb20iCiAgICBhZG1pbl9lbWFpbCA9IGYiYWRtaW5fe3RzfUBleGFtcGxlLmNvbSIKICAgIHBhc3N3b3JkID0gIlNlY3VyZVBhc3MxMjMhIgoKICAgIHByaW50KCJcbi0tLSBTdGVwIDE6IFJlZ2lzdGVyIFVzZXJzIC0tLSIpCgogICAgIyAxYSDigJQgR3Vlc3QgKHJvbGU9dXNlcikKICAgIHIgPSBjbGllbnQucG9zdCgiL2F1dGgvcmVnaXN0ZXIiLCBqc29uPXsKICAgICAgICAiZW1haWwiOiBndWVzdF9lbWFpbCwKICAgICAgICAicGFzc3dvcmQiOiBwYXNzd29yZCwKICAgICAgICAiZnVsbF9uYW1lIjogIkFsaWNlIEd1ZXN0IiwKICAgICAgICAicm9sZSI6ICJ1c2VyIgogICAgfSkKICAgIGd1ZXN0X2RhdGEgPSBwcCgiUmVnaXN0ZXIgR3Vlc3QiLCByKQogICAgZ3Vlc3RfaWQgPSBndWVzdF9kYXRhLmdldCgiaWQiKSBpZiBpc2luc3RhbmNlKGd1ZXN0X2RhdGEsIGRpY3QpIGVsc2UgTm9uZQoKICAgICMgMWIg4oCUIEhvc3QgKHJvbGU9aG9zdCkKICAgIHIgPSBjbGllbnQucG9zdCgiL2F1dGgvcmVnaXN0ZXIiLCBqc29uPXsKICAgICAgICAiZW1haWwiOiBob3N0X2VtYWlsLAogICAgICAgICJwYXNzd29yZCI6IHBhc3N3b3JkLAogICAgICAgICJmdWxsX25hbWUiOiAiQm9iIEhvc3QiLAogICAgICAgICJyb2xlIjogImhvc3QiCiAgICB9KQogICAgaG9zdF9kYXRhID0gcHAoIlJlZ2lzdGVyIEhvc3QiLCByKQogICAgaG9zdF9pZCA9IGhvc3RfZGF0YS5nZXQoImlkIikgaWYgaXNpbnN0YW5jZShob3N0X2RhdGEsIGRpY3QpIGVsc2UgTm9uZQoKICAgICMgMWMg4oCUIEFkbWluOiByZWdpc3RlciBhcyB1c2VyIGZpcnN0LCB0aGVuIHdlJ2xsIHByb21vdGUgdmlhIFNRTCBsYXRlcgogICAgciA9IGNsaWVudC5wb3N0KCIvYXV0aC9yZWdpc3RlciIsIGpzb249ewogICAgICAgICJlbWFpbCI6IGFkbWluX2VtYWlsLAogICAgICAgICJwYXNzd29yZCI6IHBhc3N3b3JkLAogICAgICAgICJmdWxsX25hbWUiOiAiQ2hhcmxpZSBBZG1pbiIsCiAgICAgICAgInJvbGUiOiAidXNlciIKICAgIH0pCiAgICBhZG1pbl9kYXRhID0gcHAoIlJlZ2lzdGVyIEFkbWluIChhcyB1c2VyIGZpcnN0KSIsIHIpCiAgICBhZG1pbl9pZCA9IGFkbWluX2RhdGEuZ2V0KCJpZCIpIGlmIGlzaW5zdGFuY2UoYWRtaW5fZGF0YSwgZGljdCkgZWxzZSBOb25lCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU1RFUCAyIOKAlCBMb2dpbiBhbGwgdGhyZWUgdXNlcnMKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICBwcmludCgiXG4tLS0gU3RlcCAyOiBMb2dpbiBVc2VycyAtLS0iKQoKICAgIHIgPSBjbGllbnQucG9zdCgiL2F1dGgvbG9naW4iLCBqc29uPXsiZW1haWwiOiBndWVzdF9lbWFpbCwgInBhc3N3b3JkIjogcGFzc3dvcmR9KQogICAgZ3Vlc3RfdG9rZW5zID0gcHAoIkxvZ2luIEd1ZXN0IiwgcikKICAgIGd1ZXN0X2FjY2VzcyA9IGd1ZXN0X3Rva2Vucy5nZXQoImFjY2Vzc190b2tlbiIsICIiKSBpZiBpc2luc3RhbmNlKGd1ZXN0X3Rva2VucywgZGljdCkgZWxzZSAiIgoKICAgIHIgPSBjbGllbnQucG9zdCgiL2F1dGgvbG9naW4iLCBqc29uPXsiZW1haWwiOiBob3N0X2VtYWlsLCAicGFzc3dvcmQiOiBwYXNzd29yZH0pCiAgICBob3N0X3Rva2VucyA9IHBwKCJMb2dpbiBIb3N0IiwgcikKICAgIGhvc3RfYWNjZXNzID0gaG9zdF90b2tlbnMuZ2V0KCJhY2Nlc3NfdG9rZW4iLCAiIikgaWYgaXNpbnN0YW5jZShob3N0X3Rva2VucywgZGljdCkgZWxzZSAiIgoKICAgIHIgPSBjbGllbnQucG9zdCgiL2F1dGgvbG9naW4iLCBqc29uPXsiZW1haWwiOiBhZG1pbl9lbWFpbCwgInBhc3N3b3JkIjogcGFzc3dvcmR9KQogICAgYWRtaW5fdG9rZW5zID0gcHAoIkxvZ2luIEFkbWluIChzdGlsbCB1c2VyIHJvbGUpIiwgcikKICAgIGFkbWluX2FjY2VzcyA9IGFkbWluX3Rva2Vucy5nZXQoImFjY2Vzc190b2tlbiIsICIiKSBpZiBpc2luc3RhbmNlKGFkbWluX3Rva2VucywgZGljdCkgZWxzZSAiIgoKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICAjIFNURVAgMmIg4oCUIFRva2VuIHJlZnJlc2ggdGVzdAogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgIHByaW50KCJcbi0tLSBTdGVwIDJiOiBUb2tlbiBSZWZyZXNoIC0tLSIpCiAgICBpZiBpc2luc3RhbmNlKGd1ZXN0X3Rva2VucywgZGljdCkgYW5kIGd1ZXN0X3Rva2Vucy5nZXQoInJlZnJlc2hfdG9rZW4iKToKICAgICAgICByID0gY2xpZW50LnBvc3QoIi9hdXRoL3JlZnJlc2giLCBqc29uPXsicmVmcmVzaF90b2tlbiI6IGd1ZXN0X3Rva2Vuc1sicmVmcmVzaF90b2tlbiJdfSkKICAgICAgICByZWZyZXNoZWQgPSBwcCgiUmVmcmVzaCBHdWVzdCBUb2tlbiIsIHIpCiAgICAgICAgaWYgaXNpbnN0YW5jZShyZWZyZXNoZWQsIGRpY3QpIGFuZCByZWZyZXNoZWQuZ2V0KCJhY2Nlc3NfdG9rZW4iKToKICAgICAgICAgICAgZ3Vlc3RfYWNjZXNzID0gcmVmcmVzaGVkWyJhY2Nlc3NfdG9rZW4iXQoKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICAjIFNURVAgMmMg4oCUIEdldCBwcm9maWxlCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgMmM6IEdldCBQcm9maWxlIC0tLSIpCiAgICByID0gY2xpZW50LmdldCgiL2F1dGgvbWUiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGd1ZXN0X2FjY2VzcykpCiAgICBwcCgiR3Vlc3QgUHJvZmlsZSIsIHIpCgogICAgciA9IGNsaWVudC5nZXQoIi9hdXRoL21lIiwgaGVhZGVycz1hdXRoX2hlYWRlcihob3N0X2FjY2VzcykpCiAgICBwcCgiSG9zdCBQcm9maWxlIiwgcikKCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgIyBTVEVQIDMg4oCUIEhPU1QgY3JlYXRlcyBhIHByb3BlcnR5CiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgMzogSG9zdCBDcmVhdGVzIFByb3BlcnR5IC0tLSIpCiAgICByID0gY2xpZW50LnBvc3QoIi9wcm9wZXJ0aWVzIiwgaGVhZGVycz1hdXRoX2hlYWRlcihob3N0X2FjY2VzcyksIGpzb249ewogICAgICAgICJ0aXRsZSI6ICJDb3p5IERvd250b3duIEFwYXJ0bWVudCIsCiAgICAgICAgImRlc2NyaXB0aW9uIjogIkJlYXV0aWZ1bCAyLWJlZHJvb20gYXBhcnRtZW50IGluIHRoZSBoZWFydCBvZiBkb3dudG93biB3aXRoIGdyZWF0IHZpZXdzLiIsCiAgICAgICAgImNpdHkiOiAiTmV3IFlvcmsiLAogICAgICAgICJhZGRyZXNzIjogIjEyMyBNYWluIFN0cmVldCwgQXB0IDRCLCBOZXcgWW9yaywgTlkgMTAwMDEiLAogICAgICAgICJsYXRpdHVkZSI6IDQwLjcxMjgsCiAgICAgICAgImxvbmdpdHVkZSI6IC03NC4wMDYwLAogICAgICAgICJwcmljZV9wZXJfbmlnaHQiOiAxNTAuMDAsCiAgICAgICAgIm1heF9ndWVzdHMiOiA0LAogICAgICAgICJhbWVuaXRpZXMiOiBbIndpZmkiLCAia2l0Y2hlbiIsICJhaXJfY29uZGl0aW9uaW5nIiwgIndhc2hlciJdCiAgICB9KQogICAgcHJvcGVydHlfZGF0YSA9IHBwKCJDcmVhdGUgUHJvcGVydHkiLCByKQogICAgcHJvcGVydHlfaWQgPSBwcm9wZXJ0eV9kYXRhLmdldCgiaWQiKSBpZiBpc2luc3RhbmNlKHByb3BlcnR5X2RhdGEsIGRpY3QpIGVsc2UgTm9uZQoKICAgICMgQ3JlYXRlIGEgc2Vjb25kIHByb3BlcnR5CiAgICByID0gY2xpZW50LnBvc3QoIi9wcm9wZXJ0aWVzIiwgaGVhZGVycz1hdXRoX2hlYWRlcihob3N0X2FjY2VzcyksIGpzb249ewogICAgICAgICJ0aXRsZSI6ICJCZWFjaCBIb3VzZSBQYXJhZGlzZSIsCiAgICAgICAgImRlc2NyaXB0aW9uIjogIlN0dW5uaW5nIGJlYWNoZnJvbnQgaG91c2Ugd2l0aCBwYW5vcmFtaWMgb2NlYW4gdmlld3MgYW5kIHByaXZhdGUgcG9vbC4iLAogICAgICAgICJjaXR5IjogIk1pYW1pIiwKICAgICAgICAiYWRkcmVzcyI6ICI0NTYgT2NlYW4gRHJpdmUsIE1pYW1pIEJlYWNoLCBGTCAzMzEzOSIsCiAgICAgICAgImxhdGl0dWRlIjogMjUuNzYxNywKICAgICAgICAibG9uZ2l0dWRlIjogLTgwLjE5MTgsCiAgICAgICAgInByaWNlX3Blcl9uaWdodCI6IDMwMC4wMCwKICAgICAgICAibWF4X2d1ZXN0cyI6IDgsCiAgICAgICAgImFtZW5pdGllcyI6IFsid2lmaSIsICJwb29sIiwgImJlYWNoX2FjY2VzcyIsICJwYXJraW5nIiwgImFpcl9jb25kaXRpb25pbmciXQogICAgfSkKICAgIHByb3BlcnR5Ml9kYXRhID0gcHAoIkNyZWF0ZSBTZWNvbmQgUHJvcGVydHkiLCByKQoKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICAjIFNURVAgNCDigJQgR1VFU1QgYnJvd3NlcyBwcm9wZXJ0aWVzCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgNDogQnJvd3NlIFByb3BlcnRpZXMgLS0tIikKCiAgICByID0gY2xpZW50LmdldCgiL3Byb3BlcnRpZXMiKQogICAgcHAoIkxpc3QgQWxsIFByb3BlcnRpZXMiLCByKQoKICAgIHIgPSBjbGllbnQuZ2V0KCIvcHJvcGVydGllcyIsIHBhcmFtcz17ImNpdHkiOiAiTmV3IFlvcmsifSkKICAgIHBwKCJTZWFyY2ggUHJvcGVydGllcyBpbiBOZXcgWW9yayIsIHIpCgogICAgaWYgcHJvcGVydHlfaWQ6CiAgICAgICAgciA9IGNsaWVudC5nZXQoZiIvcHJvcGVydGllcy97cHJvcGVydHlfaWR9IikKICAgICAgICBwcChmIkdldCBQcm9wZXJ0eSBEZXRhaWwgKHtwcm9wZXJ0eV9pZFs6OF19Li4uKSIsIHIpCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU1RFUCA1IOKAlCBHVUVTVCBib29rcyBhIHByb3BlcnR5CiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgNTogR3Vlc3QgQm9va3MgUHJvcGVydHkgLS0tIikKICAgIGNoZWNrX2luID0gKGRhdGV0aW1lLm5vdygpICsgdGltZWRlbHRhKGRheXM9NykpLmlzb2Zvcm1hdCgpCiAgICBjaGVja19vdXQgPSAoZGF0ZXRpbWUubm93KCkgKyB0aW1lZGVsdGEoZGF5cz0xMCkpLmlzb2Zvcm1hdCgpCgogICAgaWYgcHJvcGVydHlfaWQ6CiAgICAgICAgciA9IGNsaWVudC5wb3N0KCIvYm9va2luZ3MiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGd1ZXN0X2FjY2VzcyksIGpzb249ewogICAgICAgICAgICAicHJvcGVydHlfaWQiOiBwcm9wZXJ0eV9pZCwKICAgICAgICAgICAgImNoZWNrX2luIjogY2hlY2tfaW4sCiAgICAgICAgICAgICJjaGVja19vdXQiOiBjaGVja19vdXQsCiAgICAgICAgICAgICJib29raW5nX3R5cGUiOiAibmlnaHRseSIKICAgICAgICB9KQogICAgICAgIGJvb2tpbmdfZGF0YSA9IHBwKCJDcmVhdGUgQm9va2luZyAoMyBuaWdodHMpIiwgcikKICAgICAgICBib29raW5nX2lkID0gYm9va2luZ19kYXRhLmdldCgiaWQiKSBpZiBpc2luc3RhbmNlKGJvb2tpbmdfZGF0YSwgZGljdCkgZWxzZSBOb25lCiAgICBlbHNlOgogICAgICAgIGJvb2tpbmdfaWQgPSBOb25lCiAgICAgICAgcHJpbnQoIuKaoO+4jyAgU2tpcHBpbmcgYm9va2luZyDigJQgbm8gcHJvcGVydHlfaWQuIikKCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgIyBTVEVQIDViIOKAlCBMaXN0IGJvb2tpbmdzCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgcHJpbnQoIlxuLS0tIFN0ZXAgNWI6IExpc3QgQm9va2luZ3MgLS0tIikKICAgIHIgPSBjbGllbnQuZ2V0KCIvYm9va2luZ3MiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGd1ZXN0X2FjY2VzcykpCiAgICBwcCgiR3Vlc3QncyBCb29raW5ncyIsIHIpCgogICAgciA9IGNsaWVudC5nZXQoIi9ib29raW5ncyIsIGhlYWRlcnM9YXV0aF9oZWFkZXIoaG9zdF9hY2Nlc3MpKQogICAgcHAoIkhvc3QncyBCb29raW5ncyIsIHIpCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU1RFUCA2IOKAlCBIT1NUIGNvbmZpcm1zIGJvb2tpbmcKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICBwcmludCgiXG4tLS0gU3RlcCA2OiBIb3N0IENvbmZpcm1zIEJvb2tpbmcgLS0tIikKICAgIGlmIGJvb2tpbmdfaWQ6CiAgICAgICAgciA9IGNsaWVudC5wdXQoZiIvYm9va2luZ3Mve2Jvb2tpbmdfaWR9L3N0YXR1cyIsCiAgICAgICAgICAgICAgICAgICAgICAgICBoZWFkZXJzPWF1dGhfaGVhZGVyKGhvc3RfYWNjZXNzKSwKICAgICAgICAgICAgICAgICAgICAgICAgIGpzb249eyJzdGF0dXMiOiAiY29uZmlybWVkIn0pCiAgICAgICAgcHAoIkNvbmZpcm0gQm9va2luZyIsIHIpCiAgICBlbHNlOgogICAgICAgIHByaW50KCLimqDvuI8gIFNraXBwaW5nIOKAlCBubyBib29raW5nX2lkLiIpCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU1RFUCA3IOKAlCBHdWVzdCB3cml0ZXMgYSByZXZpZXcgKGFmdGVyIG1hcmtpbmcgY29tcGxldGVkKQogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgIHByaW50KCJcbi0tLSBTdGVwIDc6IFJldmlldyBGbG93IC0tLSIpCiAgICBpZiBib29raW5nX2lkOgogICAgICAgICMgQ29tcGxldGUgdGhlIGJvb2tpbmcgZmlyc3QKICAgICAgICByID0gY2xpZW50LnB1dChmIi9ib29raW5ncy97Ym9va2luZ19pZH0vc3RhdHVzIiwKICAgICAgICAgICAgICAgICAgICAgICAgIGhlYWRlcnM9YXV0aF9oZWFkZXIoaG9zdF9hY2Nlc3MpLAogICAgICAgICAgICAgICAgICAgICAgICAganNvbj17InN0YXR1cyI6ICJjb21wbGV0ZWQifSkKICAgICAgICBwcCgiQ29tcGxldGUgQm9va2luZyIsIHIpCgogICAgICAgICMgR3Vlc3Qgd3JpdGVzIGEgcmV2aWV3CiAgICAgICAgciA9IGNsaWVudC5wb3N0KCIvcmV2aWV3cyIsIGhlYWRlcnM9YXV0aF9oZWFkZXIoZ3Vlc3RfYWNjZXNzKSwganNvbj17CiAgICAgICAgICAgICJib29raW5nX2lkIjogYm9va2luZ19pZCwKICAgICAgICAgICAgInJhdGluZyI6IDUsCiAgICAgICAgICAgICJjb21tZW50IjogIkFtYXppbmcgYXBhcnRtZW50ISBUaGUgdmlld3Mgd2VyZSBpbmNyZWRpYmxlIGFuZCBCb2Igd2FzIGEgZ3JlYXQgaG9zdC4iCiAgICAgICAgfSkKICAgICAgICBwcCgiU3VibWl0IFJldmlldyIsIHIpCgogICAgICAgICMgTGlzdCByZXZpZXdzIGZvciB0aGUgcHJvcGVydHkKICAgICAgICBpZiBwcm9wZXJ0eV9pZDoKICAgICAgICAgICAgciA9IGNsaWVudC5nZXQoZiIvcmV2aWV3cy9wcm9wZXJ0eS97cHJvcGVydHlfaWR9IikKICAgICAgICAgICAgcHAoIlByb3BlcnR5IFJldmlld3MiLCByKQogICAgZWxzZToKICAgICAgICBwcmludCgi4pqg77iPICBTa2lwcGluZyByZXZpZXdzIOKAlCBubyBib29raW5nLiIpCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU1RFUCA4IOKAlCBNZXNzYWdpbmcgYmV0d2VlbiBndWVzdCBhbmQgaG9zdAogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgIHByaW50KCJcbi0tLSBTdGVwIDg6IE1lc3NhZ2luZyAtLS0iKQogICAgaWYgcHJvcGVydHlfaWQgYW5kIGd1ZXN0X2lkIGFuZCBob3N0X2lkOgogICAgICAgICMgR3Vlc3Qgc3RhcnRzIGEgY29udmVyc2F0aW9uIGFib3V0IHRoZSBwcm9wZXJ0eQogICAgICAgIHIgPSBjbGllbnQucG9zdCgiL2NvbnZlcnNhdGlvbnMiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGd1ZXN0X2FjY2VzcyksIGpzb249ewogICAgICAgICAgICAicHJvcGVydHlfaWQiOiBwcm9wZXJ0eV9pZCwKICAgICAgICAgICAgIm1lc3NhZ2UiOiAiSGkgQm9iISBJIGxvdmVkIHRoZSBhcGFydG1lbnQuIEFyZSB0aGVyZSBhbnkgcmVzdGF1cmFudHMgbmVhcmJ5PyIKICAgICAgICB9KQogICAgICAgIGNvbnZfZGF0YSA9IHBwKCJHdWVzdCBTdGFydHMgQ29udmVyc2F0aW9uIiwgcikKICAgICAgICBjb252X2lkID0gY29udl9kYXRhLmdldCgiaWQiKSBpZiBpc2luc3RhbmNlKGNvbnZfZGF0YSwgZGljdCkgZWxzZSBOb25lCgogICAgICAgICMgSG9zdCByZXBsaWVzIGluIHRoZSBzYW1lIGNvbnZlcnNhdGlvbgogICAgICAgIGlmIGNvbnZfaWQ6CiAgICAgICAgICAgIHIgPSBjbGllbnQucG9zdChmIi9jb252ZXJzYXRpb25zL3tjb252X2lkfS9tZXNzYWdlcyIsIGhlYWRlcnM9YXV0aF9oZWFkZXIoaG9zdF9hY2Nlc3MpLCBqc29uPXsKICAgICAgICAgICAgICAgICJjb250ZW50IjogIlRoYW5rcyBBbGljZSEgWWVzLCB0aGVyZSBhcmUgZ3JlYXQgcmVzdGF1cmFudHMgd2l0aGluIHdhbGtpbmcgZGlzdGFuY2UuIgogICAgICAgICAgICB9KQogICAgICAgICAgICBwcCgiSG9zdCBSZXBsaWVzIiwgcikKCiAgICAgICAgIyBHdWVzdCB2aWV3cyBjb252ZXJzYXRpb25zCiAgICAgICAgciA9IGNsaWVudC5nZXQoIi9jb252ZXJzYXRpb25zIiwgaGVhZGVycz1hdXRoX2hlYWRlcihndWVzdF9hY2Nlc3MpKQogICAgICAgIHBwKCJHdWVzdCdzIENvbnZlcnNhdGlvbnMiLCByKQogICAgZWxzZToKICAgICAgICBwcmludCgi4pqg77iPICBTa2lwcGluZyBtZXNzYWdpbmcg4oCUIG1pc3NpbmcgdXNlci9wcm9wZXJ0eSBJRHMuIikKCiAgICAjIC0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLQogICAgIyBTVEVQIDkg4oCUIE1lbWJlcnNoaXAgZm9yIGhvc3QKICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICBwcmludCgiXG4tLS0gU3RlcCA5OiBIb3N0IE1lbWJlcnNoaXAgLS0tIikKICAgIHIgPSBjbGllbnQucG9zdCgiL21lbWJlcnNoaXBzL3N1YnNjcmliZSIsIGhlYWRlcnM9YXV0aF9oZWFkZXIoaG9zdF9hY2Nlc3MpLCBqc29uPXsKICAgICAgICAicGxhbl90eXBlIjogInByZW1pdW0iLAogICAgICAgICJwYXltZW50X3Rva2VuIjogInRva190ZXN0X3NlZWQiCiAgICB9KQogICAgcHAoIkhvc3QgU3Vic2NyaWJlcyB0byBQcmVtaXVtIiwgcikKCiAgICByID0gY2xpZW50LmdldCgiL21lbWJlcnNoaXBzL2N1cnJlbnQiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGhvc3RfYWNjZXNzKSkKICAgIHBwKCJIb3N0J3MgTWVtYmVyc2hpcCIsIHIpCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU1RFUCAxMCDigJQgQWRtaW4gb3BlcmF0aW9ucwogICAgIyAgIE5PVEU6IFRoZSBhZG1pbiB1c2VyIG11c3QgYmUgcHJvbW90ZWQgaW4gdGhlIERCIGZpcnN0IQogICAgIyAgIFNlZSBpbnN0cnVjdGlvbnMgcHJpbnRlZCBiZWxvdy4KICAgICMgLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tCiAgICBwcmludCgiXG4tLS0gU3RlcCAxMDogQWRtaW4gT3BlcmF0aW9ucyAtLS0iKQogICAgcHJpbnQoZiIiIgrilZTilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZcK4pWRICBUbyB0ZXN0IGFkbWluIGVuZHBvaW50cywgcHJvbW90ZSB0aGUgYWRtaW4gdXNlciBpbiB0aGUgREI6IOKVkQrilZEgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgIFVzaW5nIHBzcWwgKERvY2tlcik6ICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgZG9ja2VyIGV4ZWMgLWl0IDxkYl9jb250YWluZXI+IHBzcWwgLVUgc3RheW5lc3Qgc3RheW5lc3QgIOKVkQrilZEgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgIE9yIGlmIFBvc3RncmVzIGlzIGxvY2FsOiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgcHNxbCAtVSBzdGF5bmVzdCAtZCBzdGF5bmVzdCAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgIFRoZW4gcnVuOiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgVVBEQVRFIHVzZXJzIFNFVCByb2xlID0gJ2FkbWluJyAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgV0hFUkUgZW1haWwgPSAne2FkbWluX2VtYWlsfSc7ICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICAgIOKVkQrilZEgIFRoZW4gcmUtbG9naW4gYmVsb3cgdG8gZ2V0IGFkbWluLXJvbGUgSldULiAgICAgICAgICAgICAgICAgIOKVkQrilZrilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZDilZ0KIiIiKQoKICAgICMgVHJ5IGFkbWluIGVuZHBvaW50cyB3aXRoIGN1cnJlbnQgdG9rZW4gKHdpbGwgZmFpbCBpZiBub3QgcHJvbW90ZWQpCiAgICByID0gY2xpZW50LmdldCgiL2FkbWluL2Rhc2hib2FyZCIsIGhlYWRlcnM9YXV0aF9oZWFkZXIoYWRtaW5fYWNjZXNzKSkKICAgIHJlc3VsdCA9IHBwKCJBZG1pbiBEYXNoYm9hcmQgKG1heSBmYWlsIGlmIG5vdCBwcm9tb3RlZCB5ZXQpIiwgcikKCiAgICBpZiByLnN0YXR1c19jb2RlID09IDQwMzoKICAgICAgICBwcmludCgiXG7ij7MgQXR0ZW1wdGluZyB0byByZS1sb2dpbiBhZG1pbiBhZnRlciBwb3RlbnRpYWwgREIgcHJvbW90aW9uLi4uIikKICAgICAgICByID0gY2xpZW50LnBvc3QoIi9hdXRoL2xvZ2luIiwganNvbj17ImVtYWlsIjogYWRtaW5fZW1haWwsICJwYXNzd29yZCI6IHBhc3N3b3JkfSkKICAgICAgICBhZG1pbl90b2tlbnMyID0gcHAoIlJlLWxvZ2luIEFkbWluIiwgcikKICAgICAgICBpZiBpc2luc3RhbmNlKGFkbWluX3Rva2VuczIsIGRpY3QpIGFuZCBhZG1pbl90b2tlbnMyLmdldCgiYWNjZXNzX3Rva2VuIik6CiAgICAgICAgICAgIGFkbWluX2FjY2VzczIgPSBhZG1pbl90b2tlbnMyWyJhY2Nlc3NfdG9rZW4iXQoKICAgICAgICAgICAgciA9IGNsaWVudC5nZXQoIi9hZG1pbi9kYXNoYm9hcmQiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGFkbWluX2FjY2VzczIpKQogICAgICAgICAgICBwcCgiQWRtaW4gRGFzaGJvYXJkIChhZnRlciBwcm9tb3Rpb24pIiwgcikKCiAgICAgICAgICAgIHIgPSBjbGllbnQuZ2V0KCIvYWRtaW4vdXNlcnMiLCBoZWFkZXJzPWF1dGhfaGVhZGVyKGFkbWluX2FjY2VzczIpKQogICAgICAgICAgICBwcCgiQWRtaW4g4oCUIExpc3QgVXNlcnMiLCByKQoKICAgICAgICAgICAgciA9IGNsaWVudC5nZXQoIi9hZG1pbi9wcm9wZXJ0aWVzIiwgaGVhZGVycz1hdXRoX2hlYWRlcihhZG1pbl9hY2Nlc3MyKSkKICAgICAgICAgICAgcHAoIkFkbWluIOKAlCBMaXN0IFByb3BlcnRpZXMiLCByKQoKICAgICAgICAgICAgciA9IGNsaWVudC5nZXQoIi9hZG1pbi9tZW1iZXJzaGlwcyIsIGhlYWRlcnM9YXV0aF9oZWFkZXIoYWRtaW5fYWNjZXNzMikpCiAgICAgICAgICAgIHBwKCJBZG1pbiDigJQgTGlzdCBNZW1iZXJzaGlwcyIsIHIpCgogICAgICAgICAgICAjIFRvZ2dsZSBhIHVzZXIncyBzdGF0dXMKICAgICAgICAgICAgaWYgZ3Vlc3RfaWQ6CiAgICAgICAgICAgICAgICByID0gY2xpZW50LnB1dChmIi9hZG1pbi91c2Vycy97Z3Vlc3RfaWR9L3N0YXR1cyIsCiAgICAgICAgICAgICAgICAgICAgICAgICAgICAgICBoZWFkZXJzPWF1dGhfaGVhZGVyKGFkbWluX2FjY2VzczIpKQogICAgICAgICAgICAgICAgcHAoIkFkbWluIOKAlCBUb2dnbGUgR3Vlc3QgQWN0aXZlIFN0YXR1cyIsIHIpCgogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgICMgU3VtbWFyeQogICAgIyAtLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0tLS0KICAgIHByaW50KCJcbiIgKyAiPSIgKiA2MCkKICAgIHByaW50KCIgIFRlc3QgU3VtbWFyeSIpCiAgICBwcmludCgiPSIgKiA2MCkKICAgIHByaW50KGYiIiIKICBHdWVzdCBlbWFpbCA6IHtndWVzdF9lbWFpbH0KICBIb3N0IGVtYWlsICA6IHtob3N0X2VtYWlsfQogIEFkbWluIGVtYWlsIDoge2FkbWluX2VtYWlsfQogIFBhc3N3b3JkICAgIDoge3Bhc3N3b3JkfQogIFByb3BlcnR5IElEIDoge3Byb3BlcnR5X2lkIG9yICdOL0EnfQogIEJvb2tpbmcgSUQgIDoge2Jvb2tpbmdfaWQgb3IgJ04vQSd9CgogIEZyb250ZW5kICAgIDogaHR0cDovL2xvY2FsaG9zdDozMDAwCiAgU3dhZ2dlciBVSSAgOiB7QkFTRX0vZG9jcwogIFJlRG9jICAgICAgIDoge0JBU0V9L3JlZG9jCiIiIikKCgppZiBfX25hbWVfXyA9PSAiX19tYWluX18iOgogICAgbWFpbigpCg==</t>
   </si>
   <si>
     <t>setup.ps1</t>
@@ -24182,6 +24297,20 @@
         <v>527</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2">
+        <v>85.0</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>530</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -24213,13 +24342,13 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="3">
@@ -24227,13 +24356,13 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4">
@@ -24241,13 +24370,13 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5">
@@ -24255,13 +24384,13 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6">
@@ -24269,13 +24398,13 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7">
@@ -24283,13 +24412,13 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -24297,13 +24426,13 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9">
@@ -24311,13 +24440,13 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="10">
@@ -24325,13 +24454,13 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="11">
@@ -24339,13 +24468,13 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12">
@@ -24353,13 +24482,13 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="13">
@@ -24367,13 +24496,13 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="14">
@@ -24381,13 +24510,13 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="15">
@@ -24395,13 +24524,13 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16">
@@ -24409,13 +24538,13 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17">
@@ -24423,13 +24552,13 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
